--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\98 PROFORMA INVOICE\Dashboard Proforma Invoice General Services\database_penyimpanan_aman\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8838BC60-5D89-4F74-854F-01FD701B1C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{74C0CBE3-4637-49B7-B5C1-074B3751C7D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1725,7 +1725,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AL118"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -1881,7 +1880,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="2" t="s">
         <v>38</v>
       </c>
@@ -1979,7 +1978,7 @@
       <c r="AK2" s="2"/>
       <c r="AL2" s="2"/>
     </row>
-    <row r="3" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="3" t="s">
         <v>38</v>
       </c>
@@ -2077,7 +2076,7 @@
       <c r="AK3" s="3"/>
       <c r="AL3" s="3"/>
     </row>
-    <row r="4" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>38</v>
       </c>
@@ -2175,7 +2174,7 @@
       <c r="AK4" s="2"/>
       <c r="AL4" s="2"/>
     </row>
-    <row r="5" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="3" t="s">
         <v>38</v>
       </c>
@@ -2273,7 +2272,7 @@
       <c r="AK5" s="3"/>
       <c r="AL5" s="3"/>
     </row>
-    <row r="6" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="2" t="s">
         <v>38</v>
       </c>
@@ -2371,7 +2370,7 @@
       <c r="AK6" s="2"/>
       <c r="AL6" s="2"/>
     </row>
-    <row r="7" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="3" t="s">
         <v>38</v>
       </c>
@@ -2469,7 +2468,7 @@
       <c r="AK7" s="3"/>
       <c r="AL7" s="3"/>
     </row>
-    <row r="8" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>38</v>
       </c>
@@ -2567,7 +2566,7 @@
       <c r="AK8" s="2"/>
       <c r="AL8" s="2"/>
     </row>
-    <row r="9" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="3" t="s">
         <v>38</v>
       </c>
@@ -2665,7 +2664,7 @@
       <c r="AK9" s="3"/>
       <c r="AL9" s="3"/>
     </row>
-    <row r="10" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="2" t="s">
         <v>38</v>
       </c>
@@ -2763,7 +2762,7 @@
       <c r="AK10" s="2"/>
       <c r="AL10" s="2"/>
     </row>
-    <row r="11" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="3" t="s">
         <v>38</v>
       </c>
@@ -2861,7 +2860,7 @@
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -3253,7 +3252,7 @@
       <c r="AK15" s="3"/>
       <c r="AL15" s="3"/>
     </row>
-    <row r="16" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A16" s="2" t="s">
         <v>38</v>
       </c>
@@ -3351,7 +3350,7 @@
       <c r="AK16" s="2"/>
       <c r="AL16" s="2"/>
     </row>
-    <row r="17" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
@@ -3449,7 +3448,7 @@
       <c r="AK17" s="3"/>
       <c r="AL17" s="3"/>
     </row>
-    <row r="18" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="2" t="s">
         <v>38</v>
       </c>
@@ -3547,7 +3546,7 @@
       <c r="AK18" s="2"/>
       <c r="AL18" s="2"/>
     </row>
-    <row r="19" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A19" s="3" t="s">
         <v>38</v>
       </c>
@@ -3645,7 +3644,7 @@
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="2" t="s">
         <v>38</v>
       </c>
@@ -3743,7 +3742,7 @@
       <c r="AK20" s="2"/>
       <c r="AL20" s="2"/>
     </row>
-    <row r="21" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="3" t="s">
         <v>38</v>
       </c>
@@ -3841,7 +3840,7 @@
       <c r="AK21" s="3"/>
       <c r="AL21" s="3"/>
     </row>
-    <row r="22" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A22" s="2" t="s">
         <v>38</v>
       </c>
@@ -3939,7 +3938,7 @@
       <c r="AK22" s="2"/>
       <c r="AL22" s="2"/>
     </row>
-    <row r="23" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
@@ -4037,7 +4036,7 @@
       <c r="AK23" s="3"/>
       <c r="AL23" s="3"/>
     </row>
-    <row r="24" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="2" t="s">
         <v>38</v>
       </c>
@@ -4135,7 +4134,7 @@
       <c r="AK24" s="2"/>
       <c r="AL24" s="2"/>
     </row>
-    <row r="25" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="3" t="s">
         <v>38</v>
       </c>
@@ -4235,7 +4234,7 @@
       </c>
       <c r="AL25" s="3"/>
     </row>
-    <row r="26" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="2" t="s">
         <v>38</v>
       </c>
@@ -4335,7 +4334,7 @@
       </c>
       <c r="AL26" s="2"/>
     </row>
-    <row r="27" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
@@ -4435,7 +4434,7 @@
       </c>
       <c r="AL27" s="3"/>
     </row>
-    <row r="28" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="2" t="s">
         <v>38</v>
       </c>
@@ -4535,7 +4534,7 @@
       </c>
       <c r="AL28" s="2"/>
     </row>
-    <row r="29" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="3" t="s">
         <v>38</v>
       </c>
@@ -4635,7 +4634,7 @@
       </c>
       <c r="AL29" s="3"/>
     </row>
-    <row r="30" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="2" t="s">
         <v>38</v>
       </c>
@@ -4735,7 +4734,7 @@
       </c>
       <c r="AL30" s="2"/>
     </row>
-    <row r="31" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="3" t="s">
         <v>38</v>
       </c>
@@ -4835,7 +4834,7 @@
       </c>
       <c r="AL31" s="3"/>
     </row>
-    <row r="32" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="2" t="s">
         <v>38</v>
       </c>
@@ -4935,7 +4934,7 @@
       </c>
       <c r="AL32" s="2"/>
     </row>
-    <row r="33" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
@@ -5035,7 +5034,7 @@
       </c>
       <c r="AL33" s="3"/>
     </row>
-    <row r="34" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="2" t="s">
         <v>38</v>
       </c>
@@ -5135,7 +5134,7 @@
       </c>
       <c r="AL34" s="2"/>
     </row>
-    <row r="35" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="3" t="s">
         <v>38</v>
       </c>
@@ -5235,7 +5234,7 @@
       </c>
       <c r="AL35" s="3"/>
     </row>
-    <row r="36" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
@@ -5335,7 +5334,7 @@
       </c>
       <c r="AL36" s="2"/>
     </row>
-    <row r="37" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="3" t="s">
         <v>38</v>
       </c>
@@ -5435,7 +5434,7 @@
       </c>
       <c r="AL37" s="3"/>
     </row>
-    <row r="38" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>
@@ -5535,7 +5534,7 @@
       </c>
       <c r="AL38" s="2"/>
     </row>
-    <row r="39" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A39" s="3" t="s">
         <v>38</v>
       </c>
@@ -5635,7 +5634,7 @@
       </c>
       <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A40" s="2" t="s">
         <v>38</v>
       </c>
@@ -5735,7 +5734,7 @@
       </c>
       <c r="AL40" s="2"/>
     </row>
-    <row r="41" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A41" s="3" t="s">
         <v>38</v>
       </c>
@@ -5835,7 +5834,7 @@
       </c>
       <c r="AL41" s="3"/>
     </row>
-    <row r="42" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A42" s="2" t="s">
         <v>38</v>
       </c>
@@ -5935,7 +5934,7 @@
       </c>
       <c r="AL42" s="2"/>
     </row>
-    <row r="43" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
@@ -6035,7 +6034,7 @@
       </c>
       <c r="AL43" s="3"/>
     </row>
-    <row r="44" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A44" s="2" t="s">
         <v>38</v>
       </c>
@@ -6135,7 +6134,7 @@
       </c>
       <c r="AL44" s="2"/>
     </row>
-    <row r="45" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A45" s="3" t="s">
         <v>38</v>
       </c>
@@ -6235,7 +6234,7 @@
       </c>
       <c r="AL45" s="3"/>
     </row>
-    <row r="46" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A46" s="2" t="s">
         <v>38</v>
       </c>
@@ -6335,7 +6334,7 @@
       </c>
       <c r="AL46" s="2"/>
     </row>
-    <row r="47" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A47" s="3" t="s">
         <v>38</v>
       </c>
@@ -6435,7 +6434,7 @@
       </c>
       <c r="AL47" s="3"/>
     </row>
-    <row r="48" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A48" s="2" t="s">
         <v>38</v>
       </c>
@@ -6535,7 +6534,7 @@
       </c>
       <c r="AL48" s="2"/>
     </row>
-    <row r="49" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A49" s="3" t="s">
         <v>38</v>
       </c>
@@ -6635,7 +6634,7 @@
       </c>
       <c r="AL49" s="3"/>
     </row>
-    <row r="50" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A50" s="2" t="s">
         <v>38</v>
       </c>
@@ -6735,7 +6734,7 @@
       </c>
       <c r="AL50" s="2"/>
     </row>
-    <row r="51" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="3" t="s">
         <v>38</v>
       </c>
@@ -6835,7 +6834,7 @@
       </c>
       <c r="AL51" s="3"/>
     </row>
-    <row r="52" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A52" s="2" t="s">
         <v>38</v>
       </c>
@@ -6935,7 +6934,7 @@
       </c>
       <c r="AL52" s="2"/>
     </row>
-    <row r="53" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A53" s="3" t="s">
         <v>38</v>
       </c>
@@ -7035,7 +7034,7 @@
       </c>
       <c r="AL53" s="3"/>
     </row>
-    <row r="54" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2" t="s">
         <v>38</v>
       </c>
@@ -7135,7 +7134,7 @@
       </c>
       <c r="AL54" s="2"/>
     </row>
-    <row r="55" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A55" s="3" t="s">
         <v>38</v>
       </c>
@@ -7235,7 +7234,7 @@
       </c>
       <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A56" s="2" t="s">
         <v>38</v>
       </c>
@@ -7335,7 +7334,7 @@
       </c>
       <c r="AL56" s="2"/>
     </row>
-    <row r="57" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A57" s="3" t="s">
         <v>38</v>
       </c>
@@ -7435,7 +7434,7 @@
       </c>
       <c r="AL57" s="3"/>
     </row>
-    <row r="58" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A58" s="2" t="s">
         <v>38</v>
       </c>
@@ -7535,7 +7534,7 @@
       </c>
       <c r="AL58" s="2"/>
     </row>
-    <row r="59" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A59" s="3" t="s">
         <v>38</v>
       </c>
@@ -7635,7 +7634,7 @@
       </c>
       <c r="AL59" s="3"/>
     </row>
-    <row r="60" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A60" s="2" t="s">
         <v>38</v>
       </c>
@@ -7735,7 +7734,7 @@
       </c>
       <c r="AL60" s="2"/>
     </row>
-    <row r="61" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A61" s="3" t="s">
         <v>38</v>
       </c>
@@ -7835,7 +7834,7 @@
       </c>
       <c r="AL61" s="3"/>
     </row>
-    <row r="62" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A62" s="2" t="s">
         <v>38</v>
       </c>
@@ -7935,7 +7934,7 @@
       </c>
       <c r="AL62" s="2"/>
     </row>
-    <row r="63" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A63" s="3" t="s">
         <v>38</v>
       </c>
@@ -8035,7 +8034,7 @@
       </c>
       <c r="AL63" s="3"/>
     </row>
-    <row r="64" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A64" s="2" t="s">
         <v>38</v>
       </c>
@@ -8135,7 +8134,7 @@
       </c>
       <c r="AL64" s="2"/>
     </row>
-    <row r="65" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A65" s="3" t="s">
         <v>38</v>
       </c>
@@ -8235,7 +8234,7 @@
       </c>
       <c r="AL65" s="3"/>
     </row>
-    <row r="66" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A66" s="2" t="s">
         <v>38</v>
       </c>
@@ -8335,7 +8334,7 @@
       </c>
       <c r="AL66" s="2"/>
     </row>
-    <row r="67" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A67" s="3" t="s">
         <v>38</v>
       </c>
@@ -8435,7 +8434,7 @@
       </c>
       <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A68" s="2" t="s">
         <v>38</v>
       </c>
@@ -8535,7 +8534,7 @@
       </c>
       <c r="AL68" s="2"/>
     </row>
-    <row r="69" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A69" s="3" t="s">
         <v>38</v>
       </c>
@@ -8635,7 +8634,7 @@
       </c>
       <c r="AL69" s="3"/>
     </row>
-    <row r="70" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A70" s="2" t="s">
         <v>38</v>
       </c>
@@ -8735,7 +8734,7 @@
       </c>
       <c r="AL70" s="2"/>
     </row>
-    <row r="71" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A71" s="3" t="s">
         <v>38</v>
       </c>
@@ -8835,7 +8834,7 @@
       </c>
       <c r="AL71" s="3"/>
     </row>
-    <row r="72" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A72" s="2" t="s">
         <v>38</v>
       </c>
@@ -8935,7 +8934,7 @@
       </c>
       <c r="AL72" s="2"/>
     </row>
-    <row r="73" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A73" s="3" t="s">
         <v>38</v>
       </c>
@@ -9035,7 +9034,7 @@
       </c>
       <c r="AL73" s="3"/>
     </row>
-    <row r="74" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A74" s="2" t="s">
         <v>38</v>
       </c>
@@ -9135,7 +9134,7 @@
       </c>
       <c r="AL74" s="2"/>
     </row>
-    <row r="75" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A75" s="3" t="s">
         <v>38</v>
       </c>
@@ -9235,7 +9234,7 @@
       </c>
       <c r="AL75" s="3"/>
     </row>
-    <row r="76" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A76" s="2" t="s">
         <v>38</v>
       </c>
@@ -9335,7 +9334,7 @@
       </c>
       <c r="AL76" s="2"/>
     </row>
-    <row r="77" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A77" s="3" t="s">
         <v>38</v>
       </c>
@@ -9435,7 +9434,7 @@
       </c>
       <c r="AL77" s="3"/>
     </row>
-    <row r="78" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A78" s="2" t="s">
         <v>38</v>
       </c>
@@ -9535,7 +9534,7 @@
       </c>
       <c r="AL78" s="2"/>
     </row>
-    <row r="79" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A79" s="3" t="s">
         <v>38</v>
       </c>
@@ -9635,7 +9634,7 @@
       </c>
       <c r="AL79" s="3"/>
     </row>
-    <row r="80" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A80" s="2" t="s">
         <v>38</v>
       </c>
@@ -9735,7 +9734,7 @@
       </c>
       <c r="AL80" s="2"/>
     </row>
-    <row r="81" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A81" s="3" t="s">
         <v>38</v>
       </c>
@@ -9835,7 +9834,7 @@
       </c>
       <c r="AL81" s="3"/>
     </row>
-    <row r="82" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A82" s="2" t="s">
         <v>38</v>
       </c>
@@ -9935,7 +9934,7 @@
       </c>
       <c r="AL82" s="2"/>
     </row>
-    <row r="83" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A83" s="3" t="s">
         <v>38</v>
       </c>
@@ -10035,7 +10034,7 @@
       </c>
       <c r="AL83" s="3"/>
     </row>
-    <row r="84" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A84" s="2" t="s">
         <v>38</v>
       </c>
@@ -10135,7 +10134,7 @@
       </c>
       <c r="AL84" s="2"/>
     </row>
-    <row r="85" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A85" s="3" t="s">
         <v>38</v>
       </c>
@@ -10235,7 +10234,7 @@
       </c>
       <c r="AL85" s="3"/>
     </row>
-    <row r="86" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A86" s="2" t="s">
         <v>38</v>
       </c>
@@ -10335,7 +10334,7 @@
       </c>
       <c r="AL86" s="2"/>
     </row>
-    <row r="87" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A87" s="3" t="s">
         <v>38</v>
       </c>
@@ -10435,7 +10434,7 @@
       </c>
       <c r="AL87" s="3"/>
     </row>
-    <row r="88" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A88" s="2" t="s">
         <v>38</v>
       </c>
@@ -10535,7 +10534,7 @@
       </c>
       <c r="AL88" s="2"/>
     </row>
-    <row r="89" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A89" s="3" t="s">
         <v>38</v>
       </c>
@@ -10635,7 +10634,7 @@
       </c>
       <c r="AL89" s="3"/>
     </row>
-    <row r="90" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A90" s="2" t="s">
         <v>38</v>
       </c>
@@ -10735,7 +10734,7 @@
       </c>
       <c r="AL90" s="2"/>
     </row>
-    <row r="91" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A91" s="3" t="s">
         <v>38</v>
       </c>
@@ -10835,7 +10834,7 @@
       </c>
       <c r="AL91" s="3"/>
     </row>
-    <row r="92" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A92" s="2" t="s">
         <v>38</v>
       </c>
@@ -10935,7 +10934,7 @@
       </c>
       <c r="AL92" s="2"/>
     </row>
-    <row r="93" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A93" s="3" t="s">
         <v>38</v>
       </c>
@@ -11035,7 +11034,7 @@
       </c>
       <c r="AL93" s="3"/>
     </row>
-    <row r="94" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A94" s="2" t="s">
         <v>38</v>
       </c>
@@ -11135,7 +11134,7 @@
       </c>
       <c r="AL94" s="2"/>
     </row>
-    <row r="95" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A95" s="3" t="s">
         <v>38</v>
       </c>
@@ -11235,7 +11234,7 @@
       </c>
       <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A96" s="2" t="s">
         <v>311</v>
       </c>
@@ -11337,7 +11336,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="97" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A97" s="3" t="s">
         <v>311</v>
       </c>
@@ -11439,7 +11438,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="98" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A98" s="2" t="s">
         <v>311</v>
       </c>
@@ -11541,7 +11540,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="99" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A99" s="3" t="s">
         <v>311</v>
       </c>
@@ -11643,7 +11642,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="100" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A100" s="2" t="s">
         <v>311</v>
       </c>
@@ -11745,7 +11744,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="101" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A101" s="3" t="s">
         <v>311</v>
       </c>
@@ -11847,7 +11846,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="102" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A102" s="2" t="s">
         <v>311</v>
       </c>
@@ -11949,7 +11948,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="103" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A103" s="3" t="s">
         <v>311</v>
       </c>
@@ -12051,7 +12050,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="104" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A104" s="2" t="s">
         <v>311</v>
       </c>
@@ -12153,7 +12152,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="105" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A105" s="3" t="s">
         <v>311</v>
       </c>
@@ -12255,7 +12254,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="106" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A106" s="2" t="s">
         <v>311</v>
       </c>
@@ -12357,7 +12356,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="107" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A107" s="3" t="s">
         <v>311</v>
       </c>
@@ -12459,7 +12458,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="108" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A108" s="2" t="s">
         <v>311</v>
       </c>
@@ -12561,7 +12560,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="109" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A109" s="3" t="s">
         <v>311</v>
       </c>
@@ -12663,7 +12662,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="110" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A110" s="2" t="s">
         <v>311</v>
       </c>
@@ -12765,7 +12764,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="111" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A111" s="3" t="s">
         <v>311</v>
       </c>
@@ -12867,7 +12866,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="112" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A112" s="2" t="s">
         <v>311</v>
       </c>
@@ -13275,7 +13274,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="116" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A116" s="2" t="s">
         <v>311</v>
       </c>
@@ -13377,7 +13376,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="117" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A117" s="3" t="s">
         <v>38</v>
       </c>
@@ -13479,7 +13478,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="118" spans="1:38" ht="20" hidden="1" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:38" ht="20" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A118" s="2" t="s">
         <v>38</v>
       </c>
@@ -13582,13 +13581,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AL118" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="7203250036"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:AL118" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4112,11 +4112,11 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>015/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -4130,19 +4130,21 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I27" t="n">
-        <v>0</v>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="K27" s="1" t="n">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -4171,16 +4173,16 @@
         <v>100</v>
       </c>
       <c r="R27" s="1" t="n">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="S27" s="1" t="n">
-        <v>46244</v>
+        <v>46250</v>
       </c>
       <c r="T27" t="n">
-        <v>7654600</v>
+        <v>13000000</v>
       </c>
       <c r="U27" t="n">
-        <v>8802790</v>
+        <v>14950000</v>
       </c>
       <c r="V27" t="inlineStr">
         <is>
@@ -4209,12 +4211,12 @@
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4226,7 +4228,7 @@
       <c r="AI27" t="inlineStr"/>
       <c r="AJ27" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK27" t="inlineStr">
@@ -4252,11 +4254,11 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/WS/VIII/2026</t>
+          <t>012/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46250</v>
+        <v>46239</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -4270,21 +4272,19 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>4500011586</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="K28" s="1" t="n">
-        <v>46250</v>
+        <v>46237</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -4319,10 +4319,10 @@
         <v>46250</v>
       </c>
       <c r="T28" t="n">
-        <v>13000000</v>
+        <v>21000000</v>
       </c>
       <c r="U28" t="n">
-        <v>14950000</v>
+        <v>24150000</v>
       </c>
       <c r="V28" t="inlineStr">
         <is>
@@ -4351,12 +4351,12 @@
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>Penyediaan  Paket Acara Peringatan  Hari Kemerdekaan RI Kegiatan Well Services 2026</t>
+          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4371,10 +4371,8 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK28" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK28" t="n">
+        <v>1000025786</v>
       </c>
       <c r="AL28" t="inlineStr"/>
     </row>
@@ -4394,11 +4392,11 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/WS/VIII/2026</t>
+          <t>017/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46239</v>
+        <v>46259</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -4416,15 +4414,15 @@
         </is>
       </c>
       <c r="I29" t="n">
-        <v>4500011586</v>
+        <v>4500011682</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Penyediaan electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46237</v>
+        <v>46258</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -4453,16 +4451,16 @@
         <v>100</v>
       </c>
       <c r="R29" s="1" t="n">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="S29" s="1" t="n">
-        <v>46250</v>
+        <v>46259</v>
       </c>
       <c r="T29" t="n">
-        <v>21000000</v>
+        <v>1160000</v>
       </c>
       <c r="U29" t="n">
-        <v>24150000</v>
+        <v>1334000</v>
       </c>
       <c r="V29" t="inlineStr">
         <is>
@@ -4491,12 +4489,12 @@
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>Meeting package pelatihan HSE untuk kegiatan wellservices 2026</t>
+          <t>Penyediaan electric cable pendukung wellservice camp Ukuran 3x25 mm NYM</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4508,11 +4506,13 @@
       <c r="AI29" t="inlineStr"/>
       <c r="AJ29" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK29" t="n">
-        <v>1000025786</v>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AL29" t="inlineStr"/>
     </row>
@@ -4532,7 +4532,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/WS/VIII/2026</t>
+          <t>018/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E30" s="1" t="n">
@@ -4554,11 +4554,11 @@
         </is>
       </c>
       <c r="I30" t="n">
-        <v>4500011682</v>
+        <v>4500011683</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Penyediaan electric cable pendukung wellservice camp</t>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="K30" s="1" t="n">
@@ -4571,12 +4571,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O30" t="n">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q30" t="n">
@@ -4597,10 +4597,10 @@
         <v>46259</v>
       </c>
       <c r="T30" t="n">
-        <v>1160000</v>
+        <v>1600000</v>
       </c>
       <c r="U30" t="n">
-        <v>1334000</v>
+        <v>1600000</v>
       </c>
       <c r="V30" t="inlineStr">
         <is>
@@ -4629,12 +4629,12 @@
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>Penyediaan electric cable pendukung wellservice camp Ukuran 3x25 mm NYM</t>
+          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       <c r="AI30" t="inlineStr"/>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK30" t="inlineStr">
@@ -4672,11 +4672,11 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>018/BSS-JOB/WS/VIII/2026</t>
+          <t>019/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4693,12 +4693,14 @@
           <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I31" t="n">
-        <v>4500011683</v>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
+          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
         </is>
       </c>
       <c r="K31" s="1" t="n">
@@ -4711,16 +4713,16 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Batam - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O31" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="P31" t="inlineStr">
         <is>
@@ -4731,16 +4733,16 @@
         <v>100</v>
       </c>
       <c r="R31" s="1" t="n">
-        <v>46259</v>
+        <v>46258</v>
       </c>
       <c r="S31" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="T31" t="n">
-        <v>1600000</v>
+        <v>150000</v>
       </c>
       <c r="U31" t="n">
-        <v>1600000</v>
+        <v>2250000</v>
       </c>
       <c r="V31" t="inlineStr">
         <is>
@@ -4769,12 +4771,12 @@
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>Transport pengangkut electric cable pendukung wellservice camp</t>
+          <t>Cargo Manifest Barang Seat Valve No GS08/01 Tgl 24 Agustus 2026</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4858,15 +4860,15 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>Batam - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Balikpapan - Batam atau sebaliknya</t>
         </is>
       </c>
       <c r="O32" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q32" t="n">
@@ -4876,13 +4878,13 @@
         <v>46258</v>
       </c>
       <c r="S32" s="1" t="n">
-        <v>46260</v>
+        <v>46258</v>
       </c>
       <c r="T32" t="n">
-        <v>150000</v>
+        <v>200000</v>
       </c>
       <c r="U32" t="n">
-        <v>2250000</v>
+        <v>200000</v>
       </c>
       <c r="V32" t="inlineStr">
         <is>
@@ -4911,12 +4913,12 @@
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>Cargo Manifest Barang Seat Valve No GS08/01 Tgl 24 Agustus 2026</t>
+          <t>Pembuatan Wooden Pallet Box</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -4995,12 +4997,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Balikpapan - Batam atau sebaliknya</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O33" t="n">
@@ -5008,7 +5010,7 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q33" t="n">
@@ -5021,10 +5023,10 @@
         <v>46258</v>
       </c>
       <c r="T33" t="n">
-        <v>200000</v>
+        <v>1600000</v>
       </c>
       <c r="U33" t="n">
-        <v>200000</v>
+        <v>1600000</v>
       </c>
       <c r="V33" t="inlineStr">
         <is>
@@ -5053,12 +5055,12 @@
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>Pembuatan Wooden Pallet Box</t>
+          <t>Kendaraan Untuk Pengiriman dari Luwuk ke Bandara Luwuk</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5096,11 +5098,11 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>019/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46260</v>
+        <v>46269</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -5117,18 +5119,16 @@
           <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I34" t="n">
+        <v>0</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Pengiriman 4 ea Set Valve dari Senoro 2 ke SPM Batam</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
-        <v>46258</v>
+        <v>46268</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
@@ -5137,12 +5137,12 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -5150,23 +5150,23 @@
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q34" t="n">
         <v>100</v>
       </c>
       <c r="R34" s="1" t="n">
-        <v>46258</v>
+        <v>46269</v>
       </c>
       <c r="S34" s="1" t="n">
-        <v>46258</v>
+        <v>46269</v>
       </c>
       <c r="T34" t="n">
-        <v>1600000</v>
+        <v>5054500</v>
       </c>
       <c r="U34" t="n">
-        <v>1600000</v>
+        <v>5812675</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>Kendaraan Untuk Pengiriman dari Luwuk ke Bandara Luwuk</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5212,7 +5212,7 @@
       <c r="AI34" t="inlineStr"/>
       <c r="AJ34" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK34" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E35" s="1" t="n">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen</t>
         </is>
       </c>
       <c r="K35" s="1" t="n">
@@ -5286,11 +5286,11 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q35" t="n">
@@ -5303,10 +5303,10 @@
         <v>46269</v>
       </c>
       <c r="T35" t="n">
-        <v>5054500</v>
+        <v>175000</v>
       </c>
       <c r="U35" t="n">
-        <v>5812675</v>
+        <v>517500</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5426,7 +5426,7 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P36" t="inlineStr">
         <is>
@@ -5443,10 +5443,10 @@
         <v>46269</v>
       </c>
       <c r="T36" t="n">
-        <v>175000</v>
+        <v>100000</v>
       </c>
       <c r="U36" t="n">
-        <v>517500</v>
+        <v>0</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -5475,12 +5475,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen</t>
+          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -5570,7 +5570,7 @@
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -5583,10 +5583,10 @@
         <v>46269</v>
       </c>
       <c r="T37" t="n">
-        <v>100000</v>
+        <v>750000</v>
       </c>
       <c r="U37" t="n">
-        <v>0</v>
+        <v>750000</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5615,12 +5615,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5632,7 +5632,7 @@
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK37" t="inlineStr">
@@ -5697,12 +5697,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O38" t="n">
@@ -5723,10 +5723,10 @@
         <v>46269</v>
       </c>
       <c r="T38" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="U38" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5798,11 +5798,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5824,11 +5824,11 @@
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46268</v>
+        <v>46241</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -5837,36 +5837,36 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q39" t="n">
         <v>100</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>46269</v>
+        <v>46242</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="T39" t="n">
-        <v>1600000</v>
+        <v>750000</v>
       </c>
       <c r="U39" t="n">
-        <v>1600000</v>
+        <v>16500000</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -5895,12 +5895,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -6006,7 +6006,7 @@
         <v>750000</v>
       </c>
       <c r="U40" t="n">
-        <v>16500000</v>
+        <v>18000000</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+          <t>Personel GS -HSE Officer  Lapangan atas I Gusti Ngurah Dwipayana</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6122,7 +6122,7 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O41" t="n">
@@ -6143,10 +6143,10 @@
         <v>46265</v>
       </c>
       <c r="T41" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="U41" t="n">
-        <v>18000000</v>
+        <v>12000000</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Personel GS -HSE Officer  Lapangan atas I Gusti Ngurah Dwipayana</t>
+          <t>Welder = Tenaga Paramedic atas Nama Meilita Bella di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Welder = Tenaga Paramedic atas Nama Meilita Bella di Lokasi Senoro</t>
+          <t>Welder = Tenaga Paramedic atas Nama Widiya Satuwo di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
@@ -6402,11 +6402,11 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -6420,13 +6420,13 @@
         <v>46242</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="T43" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="U43" t="n">
-        <v>12000000</v>
+        <v>9750000</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Welder = Tenaga Paramedic atas Nama Widiya Satuwo di Lokasi Senoro</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6546,7 +6546,7 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -6557,16 +6557,16 @@
         <v>100</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="T44" t="n">
         <v>750000</v>
       </c>
       <c r="U44" t="n">
-        <v>9750000</v>
+        <v>6750000</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6686,7 +6686,7 @@
         </is>
       </c>
       <c r="O45" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -6697,7 +6697,7 @@
         <v>100</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="S45" s="1" t="n">
         <v>46265</v>
@@ -6706,7 +6706,7 @@
         <v>750000</v>
       </c>
       <c r="U45" t="n">
-        <v>6750000</v>
+        <v>12750000</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6822,11 +6822,11 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -6843,10 +6843,10 @@
         <v>46265</v>
       </c>
       <c r="T46" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U46" t="n">
-        <v>12750000</v>
+        <v>14300000</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -6966,7 +6966,7 @@
         </is>
       </c>
       <c r="O47" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
@@ -6986,7 +6986,7 @@
         <v>650000</v>
       </c>
       <c r="U47" t="n">
-        <v>14300000</v>
+        <v>13650000</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -7015,12 +7015,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -7117,16 +7117,16 @@
         <v>100</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="S48" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T48" t="n">
-        <v>650000</v>
+        <v>500000</v>
       </c>
       <c r="U48" t="n">
-        <v>13650000</v>
+        <v>10500000</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -7155,12 +7155,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7242,11 +7242,11 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
@@ -7263,10 +7263,10 @@
         <v>46265</v>
       </c>
       <c r="T49" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="U49" t="n">
-        <v>10500000</v>
+        <v>13800000</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -7295,12 +7295,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7435,12 +7435,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E51" s="1" t="n">
@@ -7504,11 +7504,11 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -7517,36 +7517,36 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q51" t="n">
         <v>100</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="S51" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T51" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="U51" t="n">
-        <v>13800000</v>
+        <v>40000000</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -7575,12 +7575,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E52" s="1" t="n">
@@ -7644,11 +7644,11 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -7657,36 +7657,36 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.48</v>
+        <v>15</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q52" t="n">
         <v>100</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="T52" t="n">
-        <v>25000000</v>
+        <v>1600000</v>
       </c>
       <c r="U52" t="n">
-        <v>12000000</v>
+        <v>24000000</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -7715,12 +7715,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E53" s="1" t="n">
@@ -7784,11 +7784,11 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -7797,36 +7797,36 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>0.48</v>
+        <v>25</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q53" t="n">
         <v>100</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="S53" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T53" t="n">
-        <v>20000000</v>
+        <v>1600000</v>
       </c>
       <c r="U53" t="n">
-        <v>9600000</v>
+        <v>40000000</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E54" s="1" t="n">
@@ -7924,11 +7924,11 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -7937,36 +7937,36 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.74</v>
+        <v>4</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>100</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="T54" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="U54" t="n">
-        <v>44400000</v>
+        <v>6400000</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E55" s="1" t="n">
@@ -8064,11 +8064,11 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -8077,36 +8077,36 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>100</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T55" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="U55" t="n">
-        <v>44400000</v>
+        <v>40000000</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E56" s="1" t="n">
@@ -8204,11 +8204,11 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -8217,36 +8217,36 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q56" t="n">
         <v>100</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="S56" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T56" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="U56" t="n">
-        <v>11100000</v>
+        <v>35200000</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E57" s="1" t="n">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K57" s="1" t="n">
@@ -8362,31 +8362,31 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>0.74</v>
+        <v>7</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q57" t="n">
         <v>100</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="T57" t="n">
-        <v>15000000</v>
+        <v>8500000</v>
       </c>
       <c r="U57" t="n">
-        <v>11100000</v>
+        <v>59500000</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -8415,12 +8415,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8458,7 +8458,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E58" s="1" t="n">
@@ -8484,11 +8484,11 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -8497,16 +8497,16 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -8517,16 +8517,16 @@
         <v>100</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>46241</v>
+        <v>46257</v>
       </c>
       <c r="S58" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T58" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U58" t="n">
-        <v>40000000</v>
+        <v>76500000</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E59" s="1" t="n">
@@ -8624,11 +8624,11 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -8637,16 +8637,16 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -8657,16 +8657,16 @@
         <v>100</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>46255</v>
+        <v>46265</v>
       </c>
       <c r="T59" t="n">
-        <v>1600000</v>
+        <v>2750000</v>
       </c>
       <c r="U59" t="n">
-        <v>24000000</v>
+        <v>57750000</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8738,7 +8738,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E60" s="1" t="n">
@@ -8764,11 +8764,11 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -8777,36 +8777,36 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>25</v>
+        <v>1800</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q60" t="n">
         <v>100</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="S60" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T60" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="U60" t="n">
-        <v>40000000</v>
+        <v>12150000</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8852,7 +8852,7 @@
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK60" t="inlineStr">
@@ -8878,7 +8878,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E61" s="1" t="n">
@@ -8904,11 +8904,11 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -8917,36 +8917,36 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q61" t="n">
         <v>100</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>46248</v>
+        <v>46265</v>
       </c>
       <c r="T61" t="n">
-        <v>1600000</v>
+        <v>53300</v>
       </c>
       <c r="U61" t="n">
-        <v>6400000</v>
+        <v>863460</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -8975,12 +8975,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -8992,7 +8992,7 @@
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK61" t="inlineStr">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E62" s="1" t="n">
@@ -9044,11 +9044,11 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -9057,36 +9057,36 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>25</v>
+        <v>250</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q62" t="n">
         <v>100</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T62" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="U62" t="n">
-        <v>40000000</v>
+        <v>6250000</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -9115,12 +9115,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9132,7 +9132,7 @@
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK62" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E63" s="1" t="n">
@@ -9184,11 +9184,11 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -9197,36 +9197,36 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>22</v>
+        <v>200</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q63" t="n">
         <v>100</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>46265</v>
+        <v>46257</v>
       </c>
       <c r="T63" t="n">
-        <v>1600000</v>
+        <v>25000</v>
       </c>
       <c r="U63" t="n">
-        <v>35200000</v>
+        <v>5000000</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -9255,12 +9255,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9272,7 +9272,7 @@
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E64" s="1" t="n">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K64" s="1" t="n">
@@ -9337,20 +9337,20 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q64" t="n">
@@ -9360,13 +9360,13 @@
         <v>46242</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46248</v>
+        <v>46242</v>
       </c>
       <c r="T64" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="U64" t="n">
-        <v>59500000</v>
+        <v>1250000</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9412,7 +9412,7 @@
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK64" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E65" s="1" t="n">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
@@ -9477,36 +9477,36 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>9</v>
+        <v>50</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q65" t="n">
         <v>100</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T65" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="U65" t="n">
-        <v>76500000</v>
+        <v>1250000</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9552,7 +9552,7 @@
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK65" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E66" s="1" t="n">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
@@ -9617,36 +9617,36 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q66" t="n">
         <v>100</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>46243</v>
+        <v>46242</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T66" t="n">
-        <v>2750000</v>
+        <v>25000</v>
       </c>
       <c r="U66" t="n">
-        <v>57750000</v>
+        <v>1250000</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -9675,12 +9675,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9692,7 +9692,7 @@
       <c r="AI66" t="inlineStr"/>
       <c r="AJ66" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK66" t="inlineStr">
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E67" s="1" t="n">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
@@ -9757,20 +9757,20 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>1800</v>
+        <v>50</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q67" t="n">
@@ -9780,13 +9780,13 @@
         <v>46242</v>
       </c>
       <c r="S67" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T67" t="n">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="U67" t="n">
-        <v>12150000</v>
+        <v>1250000</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -9815,12 +9815,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9858,7 +9858,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E68" s="1" t="n">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
@@ -9897,36 +9897,36 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>18</v>
+        <v>115</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q68" t="n">
         <v>100</v>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="S68" s="1" t="n">
-        <v>46265</v>
+        <v>46257</v>
       </c>
       <c r="T68" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U68" t="n">
-        <v>863460</v>
+        <v>2875000</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -9955,12 +9955,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -9998,11 +9998,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46265</v>
+        <v>46140</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -10020,15 +10020,15 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>0</v>
+        <v>4500011236</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46241</v>
+        <v>46071</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -10037,36 +10037,36 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q69" t="n">
         <v>100</v>
       </c>
       <c r="R69" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="S69" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="T69" t="n">
-        <v>25000</v>
+        <v>773919900</v>
       </c>
       <c r="U69" t="n">
-        <v>6250000</v>
+        <v>890007885</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -10095,12 +10095,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10112,13 +10112,11 @@
       <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
-      <c r="AK69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK69" t="n">
+        <v>1000025165</v>
       </c>
       <c r="AL69" t="inlineStr"/>
     </row>
@@ -10138,11 +10136,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -10160,15 +10158,15 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K70" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -10182,31 +10180,31 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>200</v>
+        <v>0.524</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q70" t="n">
         <v>100</v>
       </c>
       <c r="R70" s="1" t="n">
-        <v>46257</v>
+        <v>46072</v>
       </c>
       <c r="S70" s="1" t="n">
-        <v>46257</v>
+        <v>46072</v>
       </c>
       <c r="T70" t="n">
-        <v>25000</v>
+        <v>3125000</v>
       </c>
       <c r="U70" t="n">
-        <v>5000000</v>
+        <v>1637500</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -10235,12 +10233,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10255,10 +10253,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK70" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK70" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL70" t="inlineStr"/>
     </row>
@@ -10278,11 +10274,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -10300,15 +10296,15 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K71" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -10322,31 +10318,31 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q71" t="n">
         <v>100</v>
       </c>
       <c r="R71" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S71" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T71" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="U71" t="n">
-        <v>1250000</v>
+        <v>200000</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -10375,12 +10371,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10395,10 +10391,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK71" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL71" t="inlineStr"/>
     </row>
@@ -10418,11 +10412,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -10440,15 +10434,15 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K72" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -10462,31 +10456,31 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q72" t="n">
         <v>100</v>
       </c>
       <c r="R72" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S72" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T72" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="U72" t="n">
-        <v>1250000</v>
+        <v>100000</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -10515,12 +10509,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10535,10 +10529,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK72" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL72" t="inlineStr"/>
     </row>
@@ -10558,11 +10550,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -10580,15 +10572,15 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K73" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -10602,31 +10594,31 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q73" t="n">
         <v>100</v>
       </c>
       <c r="R73" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S73" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T73" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="U73" t="n">
-        <v>1250000</v>
+        <v>100000</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -10655,12 +10647,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10675,10 +10667,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK73" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL73" t="inlineStr"/>
     </row>
@@ -10698,11 +10688,11 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10720,15 +10710,15 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K74" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -10742,31 +10732,31 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q74" t="n">
         <v>100</v>
       </c>
       <c r="R74" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S74" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T74" t="n">
-        <v>25000</v>
+        <v>55500</v>
       </c>
       <c r="U74" t="n">
-        <v>1250000</v>
+        <v>55500</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -10795,12 +10785,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10815,10 +10805,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK74" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL74" t="inlineStr"/>
     </row>
@@ -10838,11 +10826,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10860,15 +10848,15 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -10882,31 +10870,31 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q75" t="n">
         <v>100</v>
       </c>
       <c r="R75" s="1" t="n">
-        <v>46242</v>
+        <v>46275</v>
       </c>
       <c r="S75" s="1" t="n">
-        <v>46257</v>
+        <v>46275</v>
       </c>
       <c r="T75" t="n">
-        <v>25000</v>
+        <v>75000</v>
       </c>
       <c r="U75" t="n">
-        <v>2875000</v>
+        <v>75000</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -10935,12 +10923,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -10955,10 +10943,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK75" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL75" t="inlineStr"/>
     </row>
@@ -10978,11 +10964,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -11000,15 +10986,15 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4500011236</v>
+        <v>4500011203</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K76" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -11017,12 +11003,12 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -11030,23 +11016,23 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q76" t="n">
         <v>100</v>
       </c>
       <c r="R76" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="S76" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="T76" t="n">
-        <v>773919900</v>
+        <v>293750</v>
       </c>
       <c r="U76" t="n">
-        <v>890007885</v>
+        <v>293750</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -11075,12 +11061,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11092,11 +11078,11 @@
       <c r="AI76" t="inlineStr"/>
       <c r="AJ76" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK76" t="n">
-        <v>1000025165</v>
+        <v>1000025162</v>
       </c>
       <c r="AL76" t="inlineStr"/>
     </row>
@@ -11160,11 +11146,11 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>0.524</v>
+        <v>1</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
@@ -11181,10 +11167,10 @@
         <v>46072</v>
       </c>
       <c r="T77" t="n">
-        <v>3125000</v>
+        <v>400000</v>
       </c>
       <c r="U77" t="n">
-        <v>1637500</v>
+        <v>400000</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -11213,12 +11199,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
+          <t>Batu Pecah 1-2</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11298,15 +11284,15 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -11319,10 +11305,10 @@
         <v>46072</v>
       </c>
       <c r="T78" t="n">
-        <v>50000</v>
+        <v>120000</v>
       </c>
       <c r="U78" t="n">
-        <v>200000</v>
+        <v>1440000</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -11351,12 +11337,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11436,7 +11422,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -11444,7 +11430,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -11457,10 +11443,10 @@
         <v>46072</v>
       </c>
       <c r="T79" t="n">
-        <v>50000</v>
+        <v>93750</v>
       </c>
       <c r="U79" t="n">
-        <v>100000</v>
+        <v>187500</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -11489,12 +11475,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11574,7 +11560,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -11582,7 +11568,7 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q80" t="n">
@@ -11595,10 +11581,10 @@
         <v>46072</v>
       </c>
       <c r="T80" t="n">
-        <v>50000</v>
+        <v>37500</v>
       </c>
       <c r="U80" t="n">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -11627,12 +11613,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11712,7 +11698,7 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -11733,10 +11719,10 @@
         <v>46072</v>
       </c>
       <c r="T81" t="n">
-        <v>55500</v>
+        <v>37500</v>
       </c>
       <c r="U81" t="n">
-        <v>55500</v>
+        <v>37500</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -11765,12 +11751,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -11850,31 +11836,31 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q82" t="n">
         <v>100</v>
       </c>
       <c r="R82" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="S82" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="T82" t="n">
-        <v>75000</v>
+        <v>31250</v>
       </c>
       <c r="U82" t="n">
-        <v>75000</v>
+        <v>1500000</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -11903,12 +11889,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -11988,15 +11974,15 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q83" t="n">
@@ -12009,10 +11995,10 @@
         <v>46072</v>
       </c>
       <c r="T83" t="n">
-        <v>293750</v>
+        <v>31250</v>
       </c>
       <c r="U83" t="n">
-        <v>293750</v>
+        <v>625000</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -12041,12 +12027,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12126,15 +12112,15 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="Q84" t="n">
@@ -12147,10 +12133,10 @@
         <v>46072</v>
       </c>
       <c r="T84" t="n">
-        <v>400000</v>
+        <v>712500</v>
       </c>
       <c r="U84" t="n">
-        <v>400000</v>
+        <v>142500</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -12179,12 +12165,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Batu Pecah 1-2</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12264,15 +12250,15 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -12285,10 +12271,10 @@
         <v>46072</v>
       </c>
       <c r="T85" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="U85" t="n">
-        <v>1440000</v>
+        <v>25000</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -12317,12 +12303,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Paku 12 cm</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12402,31 +12388,31 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q86" t="n">
         <v>100</v>
       </c>
       <c r="R86" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S86" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T86" t="n">
-        <v>93750</v>
+        <v>50000</v>
       </c>
       <c r="U86" t="n">
-        <v>187500</v>
+        <v>25000</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -12455,12 +12441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Paku Beton 10 cm</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12496,11 +12482,11 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -12514,19 +12500,19 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4500011203</v>
+        <v>4500011579</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -12535,16 +12521,16 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -12555,16 +12541,16 @@
         <v>100</v>
       </c>
       <c r="R87" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="S87" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="T87" t="n">
-        <v>37500</v>
+        <v>575000</v>
       </c>
       <c r="U87" t="n">
-        <v>75000</v>
+        <v>661250</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -12593,12 +12579,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12614,7 +12600,7 @@
         </is>
       </c>
       <c r="AK87" t="n">
-        <v>1000025162</v>
+        <v>1000025742</v>
       </c>
       <c r="AL87" t="inlineStr"/>
     </row>
@@ -12634,11 +12620,11 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -12652,19 +12638,19 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4500011203</v>
+        <v>4500011580</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -12673,12 +12659,12 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O88" t="n">
@@ -12686,23 +12672,23 @@
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>100</v>
       </c>
       <c r="R88" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="S88" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="T88" t="n">
-        <v>37500</v>
+        <v>1600000</v>
       </c>
       <c r="U88" t="n">
-        <v>37500</v>
+        <v>1600000</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -12731,12 +12717,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -12748,35 +12734,35 @@
       <c r="AI88" t="inlineStr"/>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK88" t="n">
-        <v>1000025162</v>
+        <v>1000025743</v>
       </c>
       <c r="AL88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>001/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -12790,19 +12776,19 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4500011203</v>
+        <v>4599910747</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="K89" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L89" t="inlineStr">
         <is>
@@ -12811,36 +12797,36 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>JASA MOBILISASI</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q89" t="n">
         <v>100</v>
       </c>
       <c r="R89" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S89" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T89" t="n">
-        <v>31250</v>
+        <v>400000000</v>
       </c>
       <c r="U89" t="n">
-        <v>1500000</v>
+        <v>400000000</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -12869,12 +12855,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -12886,35 +12872,39 @@
       <c r="AI89" t="inlineStr"/>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK89" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL89" t="inlineStr"/>
+        <v>1000024733</v>
+      </c>
+      <c r="AL89" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-020</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -12928,19 +12918,19 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4500011203</v>
+        <v>4500010748</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K90" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L90" t="inlineStr">
         <is>
@@ -12949,36 +12939,36 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>20</v>
+        <v>0.39</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q90" t="n">
         <v>100</v>
       </c>
       <c r="R90" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S90" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T90" t="n">
-        <v>31250</v>
+        <v>75538000</v>
       </c>
       <c r="U90" t="n">
-        <v>625000</v>
+        <v>29459820</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -13007,12 +12997,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13028,31 +13018,35 @@
         </is>
       </c>
       <c r="AK90" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL90" t="inlineStr"/>
+        <v>1000024201</v>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -13066,19 +13060,19 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4500011203</v>
+        <v>4500010749</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K91" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L91" t="inlineStr">
         <is>
@@ -13087,36 +13081,36 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q91" t="n">
         <v>100</v>
       </c>
       <c r="R91" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S91" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T91" t="n">
-        <v>712500</v>
+        <v>62818000</v>
       </c>
       <c r="U91" t="n">
-        <v>142500</v>
+        <v>24499020</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -13145,12 +13139,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13162,35 +13156,39 @@
       <c r="AI91" t="inlineStr"/>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK91" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL91" t="inlineStr"/>
+        <v>1000024205</v>
+      </c>
+      <c r="AL91" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -13204,19 +13202,19 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4500011203</v>
+        <v>4500010750</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K92" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L92" t="inlineStr">
         <is>
@@ -13225,36 +13223,36 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q92" t="n">
         <v>100</v>
       </c>
       <c r="R92" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S92" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T92" t="n">
-        <v>50000</v>
+        <v>78225000</v>
       </c>
       <c r="U92" t="n">
-        <v>25000</v>
+        <v>30507750</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -13283,12 +13281,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Paku 12 cm</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13300,35 +13298,39 @@
       <c r="AI92" t="inlineStr"/>
       <c r="AJ92" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK92" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL92" t="inlineStr"/>
+        <v>1000024200</v>
+      </c>
+      <c r="AL92" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -13342,19 +13344,19 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4500011203</v>
+        <v>4500010746</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="K93" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L93" t="inlineStr">
         <is>
@@ -13363,36 +13365,36 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q93" t="n">
         <v>100</v>
       </c>
       <c r="R93" s="1" t="n">
-        <v>46275</v>
+        <v>46011</v>
       </c>
       <c r="S93" s="1" t="n">
-        <v>46275</v>
+        <v>46022</v>
       </c>
       <c r="T93" t="n">
-        <v>50000</v>
+        <v>189241000</v>
       </c>
       <c r="U93" t="n">
-        <v>25000</v>
+        <v>73803990</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -13421,12 +13423,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Paku Beton 10 cm</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13438,35 +13440,39 @@
       <c r="AI93" t="inlineStr"/>
       <c r="AJ93" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK93" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL93" t="inlineStr"/>
+        <v>1000024199</v>
+      </c>
+      <c r="AL93" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-005</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -13480,19 +13486,19 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4500011579</v>
+        <v>4500010745</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -13501,36 +13507,36 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>100</v>
       </c>
       <c r="R94" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S94" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T94" t="n">
-        <v>575000</v>
+        <v>131224000</v>
       </c>
       <c r="U94" t="n">
-        <v>661250</v>
+        <v>51177360</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -13559,12 +13565,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13576,35 +13582,39 @@
       <c r="AI94" t="inlineStr"/>
       <c r="AJ94" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK94" t="n">
-        <v>1000025742</v>
-      </c>
-      <c r="AL94" t="inlineStr"/>
+        <v>1000024198</v>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>007/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -13618,19 +13628,19 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4500011580</v>
+        <v>4500010745</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="K95" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L95" t="inlineStr">
         <is>
@@ -13639,12 +13649,12 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -13652,23 +13662,23 @@
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q95" t="n">
         <v>100</v>
       </c>
       <c r="R95" s="1" t="n">
-        <v>46179</v>
+        <v>46023</v>
       </c>
       <c r="S95" s="1" t="n">
-        <v>46179</v>
+        <v>46053</v>
       </c>
       <c r="T95" t="n">
-        <v>1600000</v>
+        <v>131224000</v>
       </c>
       <c r="U95" t="n">
-        <v>1600000</v>
+        <v>131224000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -13697,12 +13707,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -13718,9 +13728,13 @@
         </is>
       </c>
       <c r="AK95" t="n">
-        <v>1000025743</v>
-      </c>
-      <c r="AL95" t="inlineStr"/>
+        <v>1000024508</v>
+      </c>
+      <c r="AL95" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -13738,11 +13752,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/FLD/XII/2025</t>
+          <t>008/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -13760,11 +13774,11 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4599910747</v>
+        <v>4500010749</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K96" s="1" t="n">
@@ -13777,12 +13791,12 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>JASA MOBILISASI</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O96" t="n">
@@ -13790,23 +13804,23 @@
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>100</v>
       </c>
       <c r="R96" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S96" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T96" t="n">
-        <v>400000000</v>
+        <v>62818000</v>
       </c>
       <c r="U96" t="n">
-        <v>400000000</v>
+        <v>62818000</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -13835,12 +13849,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -13856,11 +13870,11 @@
         </is>
       </c>
       <c r="AK96" t="n">
-        <v>1000024733</v>
+        <v>1000024511</v>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-020</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -13880,11 +13894,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/FLD/XII/2025</t>
+          <t>009/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -13902,11 +13916,11 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4500010748</v>
+        <v>4500010746</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K97" s="1" t="n">
@@ -13924,11 +13938,11 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -13939,16 +13953,16 @@
         <v>100</v>
       </c>
       <c r="R97" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S97" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T97" t="n">
-        <v>75538000</v>
+        <v>189241000</v>
       </c>
       <c r="U97" t="n">
-        <v>29459820</v>
+        <v>189241000</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -13977,12 +13991,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -13994,15 +14008,15 @@
       <c r="AI97" t="inlineStr"/>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK97" t="n">
-        <v>1000024201</v>
+        <v>1000024510</v>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -14022,7 +14036,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/FLD/XII/2025</t>
+          <t>010/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E98" s="1" t="n">
@@ -14044,11 +14058,11 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4500010749</v>
+        <v>4500010748</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K98" s="1" t="n">
@@ -14066,11 +14080,11 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -14081,16 +14095,16 @@
         <v>100</v>
       </c>
       <c r="R98" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S98" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T98" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="U98" t="n">
-        <v>24499020</v>
+        <v>75538000</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -14119,12 +14133,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14140,11 +14154,11 @@
         </is>
       </c>
       <c r="AK98" t="n">
-        <v>1000024205</v>
+        <v>1000024516</v>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -14164,11 +14178,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/FLD/XII/2025</t>
+          <t>011/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -14190,7 +14204,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K99" s="1" t="n">
@@ -14212,7 +14226,7 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -14223,16 +14237,16 @@
         <v>100</v>
       </c>
       <c r="R99" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S99" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T99" t="n">
         <v>78225000</v>
       </c>
       <c r="U99" t="n">
-        <v>30507750</v>
+        <v>78225000</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -14261,12 +14275,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14282,7 +14296,7 @@
         </is>
       </c>
       <c r="AK99" t="n">
-        <v>1000024200</v>
+        <v>1000024509</v>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
@@ -14306,11 +14320,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/FLD/XII/2025</t>
+          <t>012/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46022</v>
+        <v>46063</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -14328,15 +14342,15 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4500010746</v>
+        <v>4500010980</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46011</v>
+        <v>46056</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -14345,36 +14359,36 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ON-CALL BASIS</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.39</v>
+        <v>7</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q100" t="n">
         <v>100</v>
       </c>
       <c r="R100" s="1" t="n">
-        <v>46011</v>
+        <v>46056</v>
       </c>
       <c r="S100" s="1" t="n">
-        <v>46022</v>
+        <v>46062</v>
       </c>
       <c r="T100" t="n">
-        <v>189241000</v>
+        <v>1936000</v>
       </c>
       <c r="U100" t="n">
-        <v>73803990</v>
+        <v>13552000</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -14403,12 +14417,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14424,11 +14438,11 @@
         </is>
       </c>
       <c r="AK100" t="n">
-        <v>1000024199</v>
+        <v>1000024507</v>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>7207250142-BSS-WO-2025-008</t>
         </is>
       </c>
     </row>
@@ -14448,11 +14462,11 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/FLD/XII/2025</t>
+          <t>014/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -14470,11 +14484,11 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4500010745</v>
+        <v>4500010749</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K101" s="1" t="n">
@@ -14492,11 +14506,11 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -14507,16 +14521,16 @@
         <v>100</v>
       </c>
       <c r="R101" s="1" t="n">
-        <v>46011</v>
+        <v>46054</v>
       </c>
       <c r="S101" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="T101" t="n">
-        <v>131224000</v>
+        <v>62818000</v>
       </c>
       <c r="U101" t="n">
-        <v>51177360</v>
+        <v>62818000</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -14545,12 +14559,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14566,11 +14580,11 @@
         </is>
       </c>
       <c r="AK101" t="n">
-        <v>1000024198</v>
+        <v>1000024711</v>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -14590,11 +14604,11 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/FLD/I/2026</t>
+          <t>013/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -14612,11 +14626,11 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>4500010745</v>
+        <v>4500010748</v>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K102" s="1" t="n">
@@ -14634,7 +14648,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -14649,16 +14663,16 @@
         <v>100</v>
       </c>
       <c r="R102" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S102" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T102" t="n">
-        <v>131224000</v>
+        <v>75538000</v>
       </c>
       <c r="U102" t="n">
-        <v>131224000</v>
+        <v>75538000</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -14687,12 +14701,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -14708,11 +14722,11 @@
         </is>
       </c>
       <c r="AK102" t="n">
-        <v>1000024508</v>
+        <v>1000024712</v>
       </c>
       <c r="AL102" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -14732,11 +14746,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/FLD/I/2026</t>
+          <t>015/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -14754,11 +14768,11 @@
         </is>
       </c>
       <c r="I103" t="n">
-        <v>4500010749</v>
+        <v>4500010750</v>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K103" s="1" t="n">
@@ -14776,7 +14790,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -14791,16 +14805,16 @@
         <v>100</v>
       </c>
       <c r="R103" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S103" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T103" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="U103" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -14829,12 +14843,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -14850,11 +14864,11 @@
         </is>
       </c>
       <c r="AK103" t="n">
-        <v>1000024511</v>
+        <v>1000024709</v>
       </c>
       <c r="AL103" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -14874,11 +14888,11 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>009/BSS-JOB/FLD/I/2026</t>
+          <t>016/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -14900,7 +14914,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K104" s="1" t="n">
@@ -14933,10 +14947,10 @@
         <v>100</v>
       </c>
       <c r="R104" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S104" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T104" t="n">
         <v>189241000</v>
@@ -14971,12 +14985,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -14992,7 +15006,7 @@
         </is>
       </c>
       <c r="AK104" t="n">
-        <v>1000024510</v>
+        <v>1000024708</v>
       </c>
       <c r="AL104" t="inlineStr">
         <is>
@@ -15016,11 +15030,11 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/FLD/I/2026</t>
+          <t>017/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -15038,11 +15052,11 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>4500010748</v>
+        <v>4500010745</v>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K105" s="1" t="n">
@@ -15060,7 +15074,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -15075,16 +15089,16 @@
         <v>100</v>
       </c>
       <c r="R105" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S105" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T105" t="n">
-        <v>75538000</v>
+        <v>131224000</v>
       </c>
       <c r="U105" t="n">
-        <v>75538000</v>
+        <v>131224000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -15113,12 +15127,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15134,35 +15148,37 @@
         </is>
       </c>
       <c r="AK105" t="n">
-        <v>1000024516</v>
+        <v>1000024727</v>
       </c>
       <c r="AL105" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/FLD/I/2026</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="n">
-        <v>46053</v>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -15176,19 +15192,23 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I106" t="n">
-        <v>4500010750</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
-        </is>
-      </c>
-      <c r="K106" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
@@ -15197,36 +15217,40 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q106" t="n">
         <v>100</v>
       </c>
-      <c r="R106" s="1" t="n">
-        <v>46023</v>
-      </c>
-      <c r="S106" s="1" t="n">
-        <v>46053</v>
+      <c r="R106" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T106" t="n">
-        <v>78225000</v>
+        <v>65000</v>
       </c>
       <c r="U106" t="n">
-        <v>78225000</v>
+        <v>167570000</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15255,12 +15279,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15275,36 +15299,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK106" t="n">
-        <v>1000024509</v>
-      </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
-        </is>
-      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/FLD/I/2026</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="n">
-        <v>46063</v>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -15318,19 +15342,23 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I107" t="n">
-        <v>4500010980</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
-        </is>
-      </c>
-      <c r="K107" s="1" t="n">
-        <v>46056</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
@@ -15339,36 +15367,40 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>ON-CALL BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>7</v>
+        <v>1157</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q107" t="n">
         <v>100</v>
       </c>
-      <c r="R107" s="1" t="n">
-        <v>46056</v>
-      </c>
-      <c r="S107" s="1" t="n">
-        <v>46062</v>
+      <c r="R107" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T107" t="n">
-        <v>1936000</v>
+        <v>33000</v>
       </c>
       <c r="U107" t="n">
-        <v>13552000</v>
+        <v>38181000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15397,12 +15429,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15417,36 +15449,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK107" t="n">
-        <v>1000024507</v>
-      </c>
-      <c r="AL107" t="inlineStr">
-        <is>
-          <t>7207250142-BSS-WO-2025-008</t>
-        </is>
-      </c>
+      <c r="AK107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="n">
-        <v>46081</v>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -15460,19 +15492,23 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I108" t="n">
-        <v>4500010749</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K108" s="1" t="n">
-        <v>46011</v>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="L108" t="inlineStr">
         <is>
@@ -15481,12 +15517,12 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -15494,23 +15530,27 @@
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q108" t="n">
         <v>100</v>
       </c>
-      <c r="R108" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S108" s="1" t="n">
-        <v>46081</v>
+      <c r="R108" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T108" t="n">
-        <v>62818000</v>
+        <v>7654600</v>
       </c>
       <c r="U108" t="n">
-        <v>62818000</v>
+        <v>8802790</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -15539,12 +15579,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -15556,39 +15596,41 @@
       <c r="AI108" t="inlineStr"/>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK108" t="n">
-        <v>1000024711</v>
-      </c>
-      <c r="AL108" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
-        </is>
-      </c>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL108" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" t="n">
-        <v>7207250142</v>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="n">
-        <v>46081</v>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -15602,19 +15644,23 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I109" t="n">
-        <v>4500010748</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K109" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L109" t="inlineStr">
         <is>
@@ -15623,16 +15669,16 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -15642,17 +15688,21 @@
       <c r="Q109" t="n">
         <v>100</v>
       </c>
-      <c r="R109" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S109" s="1" t="n">
-        <v>46081</v>
+      <c r="R109" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T109" t="n">
-        <v>75538000</v>
+        <v>25000000</v>
       </c>
       <c r="U109" t="n">
-        <v>75538000</v>
+        <v>12000000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -15681,12 +15731,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -15701,36 +15751,38 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK109" t="n">
-        <v>1000024712</v>
-      </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
-        </is>
-      </c>
+      <c r="AK109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL109" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" t="n">
-        <v>7207250142</v>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="n">
-        <v>46081</v>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -15744,19 +15796,23 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I110" t="n">
-        <v>4500010750</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K110" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
@@ -15765,16 +15821,16 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Portacamp - Living camp,  ukuran 20FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -15784,17 +15840,21 @@
       <c r="Q110" t="n">
         <v>100</v>
       </c>
-      <c r="R110" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S110" s="1" t="n">
-        <v>46081</v>
+      <c r="R110" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T110" t="n">
-        <v>78225000</v>
+        <v>20000000</v>
       </c>
       <c r="U110" t="n">
-        <v>78225000</v>
+        <v>9600000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -15823,12 +15883,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -15843,36 +15903,38 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK110" t="n">
-        <v>1000024709</v>
-      </c>
-      <c r="AL110" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
-        </is>
-      </c>
+      <c r="AK110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="n">
-        <v>7207250142</v>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="n">
-        <v>46081</v>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -15886,19 +15948,23 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I111" t="n">
-        <v>4500010746</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K111" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
@@ -15907,16 +15973,16 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -15926,17 +15992,21 @@
       <c r="Q111" t="n">
         <v>100</v>
       </c>
-      <c r="R111" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S111" s="1" t="n">
-        <v>46081</v>
+      <c r="R111" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T111" t="n">
-        <v>189241000</v>
+        <v>60000000</v>
       </c>
       <c r="U111" t="n">
-        <v>189241000</v>
+        <v>44400000</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -15965,12 +16035,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -15985,36 +16055,38 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK111" t="n">
-        <v>1000024708</v>
-      </c>
-      <c r="AL111" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
-        </is>
-      </c>
+      <c r="AK111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="n">
-        <v>7207250142</v>
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="n">
-        <v>46081</v>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -16028,19 +16100,23 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I112" t="n">
-        <v>4500010745</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K112" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
@@ -16049,16 +16125,16 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -16068,17 +16144,21 @@
       <c r="Q112" t="n">
         <v>100</v>
       </c>
-      <c r="R112" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S112" s="1" t="n">
-        <v>46081</v>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T112" t="n">
-        <v>131224000</v>
+        <v>60000000</v>
       </c>
       <c r="U112" t="n">
-        <v>131224000</v>
+        <v>44400000</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -16107,12 +16187,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16127,14 +16207,12 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK112" t="n">
-        <v>1000024727</v>
-      </c>
-      <c r="AL112" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
-        </is>
-      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -16154,7 +16232,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -16184,7 +16262,7 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -16199,20 +16277,20 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>2578</v>
+        <v>0.74</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q113" t="n">
@@ -16229,10 +16307,10 @@
         </is>
       </c>
       <c r="T113" t="n">
-        <v>65000</v>
+        <v>15000000</v>
       </c>
       <c r="U113" t="n">
-        <v>167570000</v>
+        <v>11100000</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -16261,12 +16339,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16306,7 +16384,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -16336,7 +16414,7 @@
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -16351,20 +16429,20 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>1157</v>
+        <v>0.74</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q114" t="n">
@@ -16381,10 +16459,10 @@
         </is>
       </c>
       <c r="T114" t="n">
-        <v>33000</v>
+        <v>15000000</v>
       </c>
       <c r="U114" t="n">
-        <v>38181000</v>
+        <v>11100000</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -16413,12 +16491,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-09-19 18:16:03</t>
+          <t>2026-09-19 19:58:31</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6040,7 +6040,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6180,7 +6180,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6460,7 +6460,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6880,7 +6880,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7580,7 +7580,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7720,7 +7720,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -8000,7 +8000,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8140,7 +8140,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8420,7 +8420,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8560,7 +8560,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8700,7 +8700,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8840,7 +8840,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8980,7 +8980,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9120,7 +9120,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9400,7 +9400,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9540,7 +9540,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9960,7 +9960,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10100,7 +10100,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10376,7 +10376,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10514,7 +10514,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10928,7 +10928,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11066,7 +11066,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11204,7 +11204,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11342,7 +11342,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11618,7 +11618,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11756,7 +11756,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12032,7 +12032,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12170,7 +12170,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12446,7 +12446,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12584,7 +12584,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -12860,7 +12860,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13002,7 +13002,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13144,7 +13144,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13428,7 +13428,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13570,7 +13570,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13712,7 +13712,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -13854,7 +13854,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -13996,7 +13996,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14138,7 +14138,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14280,7 +14280,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14422,7 +14422,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14564,7 +14564,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14706,7 +14706,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -14848,7 +14848,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -14990,7 +14990,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15132,7 +15132,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15284,7 +15284,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15434,7 +15434,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15584,7 +15584,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -15736,7 +15736,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -15826,7 +15826,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,  ukuran 20FT (4 sleepers)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -15851,10 +15851,10 @@
         </is>
       </c>
       <c r="T110" t="n">
-        <v>20000000</v>
+        <v>17500000</v>
       </c>
       <c r="U110" t="n">
-        <v>9600000</v>
+        <v>8400000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -15888,7 +15888,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16040,7 +16040,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16192,7 +16192,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16344,7 +16344,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16496,7 +16496,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-09-19 19:58:31</t>
+          <t>2026-09-19 21:27:27</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL114"/>
+  <dimension ref="A1:AL111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5760,7 +5760,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
@@ -5842,11 +5842,11 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -5860,13 +5860,13 @@
         <v>46242</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>46265</v>
+        <v>46254</v>
       </c>
       <c r="T39" t="n">
         <v>750000</v>
       </c>
       <c r="U39" t="n">
-        <v>16500000</v>
+        <v>9750000</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -5895,12 +5895,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -5938,7 +5938,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
@@ -5982,11 +5982,11 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -5997,7 +5997,7 @@
         <v>100</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="S40" s="1" t="n">
         <v>46265</v>
@@ -6006,7 +6006,7 @@
         <v>750000</v>
       </c>
       <c r="U40" t="n">
-        <v>18000000</v>
+        <v>6750000</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Personel GS -HSE Officer  Lapangan atas I Gusti Ngurah Dwipayana</t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6078,7 +6078,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
@@ -6122,11 +6122,11 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
         <v>46265</v>
       </c>
       <c r="T41" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="U41" t="n">
-        <v>12000000</v>
+        <v>12750000</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Welder = Tenaga Paramedic atas Nama Meilita Bella di Lokasi Senoro</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6218,7 +6218,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
@@ -6262,11 +6262,11 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -6283,10 +6283,10 @@
         <v>46265</v>
       </c>
       <c r="T42" t="n">
-        <v>500000</v>
+        <v>650000</v>
       </c>
       <c r="U42" t="n">
-        <v>12000000</v>
+        <v>14300000</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Welder = Tenaga Paramedic atas Nama Widiya Satuwo di Lokasi Senoro</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6402,11 +6402,11 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -6420,13 +6420,13 @@
         <v>46242</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="T43" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U43" t="n">
-        <v>9750000</v>
+        <v>13650000</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6542,11 +6542,11 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -6557,16 +6557,16 @@
         <v>100</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>46257</v>
+        <v>46243</v>
       </c>
       <c r="S44" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T44" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="U44" t="n">
-        <v>6750000</v>
+        <v>10500000</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6682,11 +6682,11 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -6697,16 +6697,16 @@
         <v>100</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="S45" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T45" t="n">
-        <v>750000</v>
+        <v>600000</v>
       </c>
       <c r="U45" t="n">
-        <v>12750000</v>
+        <v>13800000</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6822,11 +6822,11 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -6837,16 +6837,16 @@
         <v>100</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="S46" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T46" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="U46" t="n">
-        <v>14300000</v>
+        <v>13800000</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E47" s="1" t="n">
@@ -6944,11 +6944,11 @@
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
@@ -6957,36 +6957,36 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q47" t="n">
         <v>100</v>
       </c>
       <c r="R47" s="1" t="n">
-        <v>46242</v>
+        <v>46241</v>
       </c>
       <c r="S47" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T47" t="n">
-        <v>650000</v>
+        <v>1600000</v>
       </c>
       <c r="U47" t="n">
-        <v>13650000</v>
+        <v>40000000</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -7015,12 +7015,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E48" s="1" t="n">
@@ -7084,11 +7084,11 @@
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
@@ -7097,36 +7097,36 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q48" t="n">
         <v>100</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="T48" t="n">
-        <v>500000</v>
+        <v>1600000</v>
       </c>
       <c r="U48" t="n">
-        <v>10500000</v>
+        <v>24000000</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -7155,12 +7155,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7198,7 +7198,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E49" s="1" t="n">
@@ -7224,11 +7224,11 @@
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
@@ -7237,36 +7237,36 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q49" t="n">
         <v>100</v>
       </c>
       <c r="R49" s="1" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="S49" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T49" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="U49" t="n">
-        <v>13800000</v>
+        <v>40000000</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -7295,12 +7295,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E50" s="1" t="n">
@@ -7364,11 +7364,11 @@
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -7377,36 +7377,36 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q50" t="n">
         <v>100</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>46243</v>
+        <v>46245</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="T50" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="U50" t="n">
-        <v>13800000</v>
+        <v>6400000</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -7435,12 +7435,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7522,7 +7522,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7662,11 +7662,11 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -7677,16 +7677,16 @@
         <v>100</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>46255</v>
+        <v>46265</v>
       </c>
       <c r="T52" t="n">
         <v>1600000</v>
       </c>
       <c r="U52" t="n">
-        <v>24000000</v>
+        <v>35200000</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -7715,12 +7715,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E53" s="1" t="n">
@@ -7784,11 +7784,11 @@
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
@@ -7797,16 +7797,16 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -7817,16 +7817,16 @@
         <v>100</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="T53" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U53" t="n">
-        <v>40000000</v>
+        <v>59500000</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E54" s="1" t="n">
@@ -7924,11 +7924,11 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -7937,16 +7937,16 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
@@ -7957,16 +7957,16 @@
         <v>100</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46245</v>
+        <v>46257</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>46248</v>
+        <v>46265</v>
       </c>
       <c r="T54" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U54" t="n">
-        <v>6400000</v>
+        <v>76500000</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8038,7 +8038,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E55" s="1" t="n">
@@ -8064,11 +8064,11 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -8077,16 +8077,16 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -8097,16 +8097,16 @@
         <v>100</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>46241</v>
+        <v>46243</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T55" t="n">
-        <v>1600000</v>
+        <v>2750000</v>
       </c>
       <c r="U55" t="n">
-        <v>40000000</v>
+        <v>57750000</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E56" s="1" t="n">
@@ -8204,11 +8204,11 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -8217,20 +8217,20 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>22</v>
+        <v>1800</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -8243,10 +8243,10 @@
         <v>46265</v>
       </c>
       <c r="T56" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="U56" t="n">
-        <v>35200000</v>
+        <v>12150000</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8292,7 +8292,7 @@
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK56" t="inlineStr">
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E57" s="1" t="n">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K57" s="1" t="n">
@@ -8357,36 +8357,36 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q57" t="n">
         <v>100</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>46248</v>
+        <v>46265</v>
       </c>
       <c r="T57" t="n">
-        <v>8500000</v>
+        <v>53300</v>
       </c>
       <c r="U57" t="n">
-        <v>59500000</v>
+        <v>863460</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -8415,12 +8415,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8432,7 +8432,7 @@
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK57" t="inlineStr">
@@ -8458,7 +8458,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E58" s="1" t="n">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K58" s="1" t="n">
@@ -8497,36 +8497,36 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>9</v>
+        <v>250</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q58" t="n">
         <v>100</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T58" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="U58" t="n">
-        <v>76500000</v>
+        <v>6250000</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8572,7 +8572,7 @@
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK58" t="inlineStr">
@@ -8598,7 +8598,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E59" s="1" t="n">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K59" s="1" t="n">
@@ -8637,36 +8637,36 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q59" t="n">
         <v>100</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46243</v>
+        <v>46257</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>46265</v>
+        <v>46257</v>
       </c>
       <c r="T59" t="n">
-        <v>2750000</v>
+        <v>25000</v>
       </c>
       <c r="U59" t="n">
-        <v>57750000</v>
+        <v>5000000</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8712,7 +8712,7 @@
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -8738,7 +8738,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E60" s="1" t="n">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K60" s="1" t="n">
@@ -8777,20 +8777,20 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>1800</v>
+        <v>50</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -8800,13 +8800,13 @@
         <v>46242</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T60" t="n">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="U60" t="n">
-        <v>12150000</v>
+        <v>1250000</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -8835,12 +8835,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8878,7 +8878,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E61" s="1" t="n">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K61" s="1" t="n">
@@ -8917,36 +8917,36 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q61" t="n">
         <v>100</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46244</v>
+        <v>46242</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T61" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U61" t="n">
-        <v>863460</v>
+        <v>1250000</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -8975,12 +8975,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9066,11 +9066,11 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -9086,7 +9086,7 @@
         <v>25000</v>
       </c>
       <c r="U62" t="n">
-        <v>6250000</v>
+        <v>1250000</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -9115,12 +9115,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
@@ -9217,16 +9217,16 @@
         <v>100</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="T63" t="n">
         <v>25000</v>
       </c>
       <c r="U63" t="n">
-        <v>5000000</v>
+        <v>1250000</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -9255,12 +9255,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9346,7 +9346,7 @@
         </is>
       </c>
       <c r="O64" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
@@ -9360,13 +9360,13 @@
         <v>46242</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="T64" t="n">
         <v>25000</v>
       </c>
       <c r="U64" t="n">
-        <v>1250000</v>
+        <v>2875000</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -9395,12 +9395,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9438,11 +9438,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46265</v>
+        <v>46140</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9460,15 +9460,15 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0</v>
+        <v>4500011236</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46241</v>
+        <v>46071</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -9477,36 +9477,36 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q65" t="n">
         <v>100</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="T65" t="n">
-        <v>25000</v>
+        <v>773919900</v>
       </c>
       <c r="U65" t="n">
-        <v>1250000</v>
+        <v>890007885</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -9535,12 +9535,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9552,13 +9552,11 @@
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
-      <c r="AK65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>1000025165</v>
       </c>
       <c r="AL65" t="inlineStr"/>
     </row>
@@ -9578,11 +9576,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9600,15 +9598,15 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -9622,31 +9620,31 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>50</v>
+        <v>0.524</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q66" t="n">
         <v>100</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T66" t="n">
-        <v>25000</v>
+        <v>3125000</v>
       </c>
       <c r="U66" t="n">
-        <v>1250000</v>
+        <v>1637500</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -9675,12 +9673,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9695,10 +9693,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK66" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL66" t="inlineStr"/>
     </row>
@@ -9718,11 +9714,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9740,15 +9736,15 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -9762,31 +9758,31 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q67" t="n">
         <v>100</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S67" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T67" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="U67" t="n">
-        <v>1250000</v>
+        <v>200000</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -9815,12 +9811,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9835,10 +9831,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK67" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL67" t="inlineStr"/>
     </row>
@@ -9858,11 +9852,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9880,15 +9874,15 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -9902,31 +9896,31 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>115</v>
+        <v>2</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q68" t="n">
         <v>100</v>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S68" s="1" t="n">
-        <v>46257</v>
+        <v>46072</v>
       </c>
       <c r="T68" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="U68" t="n">
-        <v>2875000</v>
+        <v>100000</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -9955,12 +9949,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -9975,10 +9969,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK68" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL68" t="inlineStr"/>
     </row>
@@ -9998,11 +9990,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -10020,15 +10012,15 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4500011236</v>
+        <v>4500011203</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K69" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -10037,36 +10029,36 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q69" t="n">
         <v>100</v>
       </c>
       <c r="R69" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="S69" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="T69" t="n">
-        <v>773919900</v>
+        <v>50000</v>
       </c>
       <c r="U69" t="n">
-        <v>890007885</v>
+        <v>100000</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -10095,12 +10087,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10112,11 +10104,11 @@
       <c r="AI69" t="inlineStr"/>
       <c r="AJ69" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK69" t="n">
-        <v>1000025165</v>
+        <v>1000025162</v>
       </c>
       <c r="AL69" t="inlineStr"/>
     </row>
@@ -10180,15 +10172,15 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0.524</v>
+        <v>1</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -10201,10 +10193,10 @@
         <v>46072</v>
       </c>
       <c r="T70" t="n">
-        <v>3125000</v>
+        <v>55500</v>
       </c>
       <c r="U70" t="n">
-        <v>1637500</v>
+        <v>55500</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -10233,12 +10225,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10318,31 +10310,31 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q71" t="n">
         <v>100</v>
       </c>
       <c r="R71" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S71" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T71" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="U71" t="n">
-        <v>200000</v>
+        <v>75000</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -10371,12 +10363,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10456,15 +10448,15 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -10477,10 +10469,10 @@
         <v>46072</v>
       </c>
       <c r="T72" t="n">
-        <v>50000</v>
+        <v>293750</v>
       </c>
       <c r="U72" t="n">
-        <v>100000</v>
+        <v>293750</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -10509,12 +10501,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10594,15 +10586,15 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q73" t="n">
@@ -10615,10 +10607,10 @@
         <v>46072</v>
       </c>
       <c r="T73" t="n">
-        <v>50000</v>
+        <v>400000</v>
       </c>
       <c r="U73" t="n">
-        <v>100000</v>
+        <v>400000</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -10647,12 +10639,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Batu Pecah 1-2</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10732,11 +10724,11 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -10753,10 +10745,10 @@
         <v>46072</v>
       </c>
       <c r="T74" t="n">
-        <v>55500</v>
+        <v>120000</v>
       </c>
       <c r="U74" t="n">
-        <v>55500</v>
+        <v>1440000</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -10785,12 +10777,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10870,11 +10862,11 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -10885,16 +10877,16 @@
         <v>100</v>
       </c>
       <c r="R75" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="S75" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="T75" t="n">
-        <v>75000</v>
+        <v>93750</v>
       </c>
       <c r="U75" t="n">
-        <v>75000</v>
+        <v>187500</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -10923,12 +10915,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11008,15 +11000,15 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q76" t="n">
@@ -11029,10 +11021,10 @@
         <v>46072</v>
       </c>
       <c r="T76" t="n">
-        <v>293750</v>
+        <v>37500</v>
       </c>
       <c r="U76" t="n">
-        <v>293750</v>
+        <v>75000</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -11061,12 +11053,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11146,7 +11138,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="O77" t="n">
@@ -11154,7 +11146,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q77" t="n">
@@ -11167,10 +11159,10 @@
         <v>46072</v>
       </c>
       <c r="T77" t="n">
-        <v>400000</v>
+        <v>37500</v>
       </c>
       <c r="U77" t="n">
-        <v>400000</v>
+        <v>37500</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -11199,12 +11191,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Batu Pecah 1-2</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11284,15 +11276,15 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -11305,10 +11297,10 @@
         <v>46072</v>
       </c>
       <c r="T78" t="n">
-        <v>120000</v>
+        <v>31250</v>
       </c>
       <c r="U78" t="n">
-        <v>1440000</v>
+        <v>1500000</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -11337,12 +11329,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11422,15 +11414,15 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -11443,10 +11435,10 @@
         <v>46072</v>
       </c>
       <c r="T79" t="n">
-        <v>93750</v>
+        <v>31250</v>
       </c>
       <c r="U79" t="n">
-        <v>187500</v>
+        <v>625000</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -11475,12 +11467,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11560,15 +11552,15 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="Q80" t="n">
@@ -11581,10 +11573,10 @@
         <v>46072</v>
       </c>
       <c r="T80" t="n">
-        <v>37500</v>
+        <v>712500</v>
       </c>
       <c r="U80" t="n">
-        <v>75000</v>
+        <v>142500</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -11613,12 +11605,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11698,15 +11690,15 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -11719,10 +11711,10 @@
         <v>46072</v>
       </c>
       <c r="T81" t="n">
-        <v>37500</v>
+        <v>50000</v>
       </c>
       <c r="U81" t="n">
-        <v>37500</v>
+        <v>25000</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -11751,12 +11743,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Paku 12 cm</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -11836,31 +11828,31 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>48</v>
+        <v>0.5</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q82" t="n">
         <v>100</v>
       </c>
       <c r="R82" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S82" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T82" t="n">
-        <v>31250</v>
+        <v>50000</v>
       </c>
       <c r="U82" t="n">
-        <v>1500000</v>
+        <v>25000</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -11889,12 +11881,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Paku Beton 10 cm</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -11930,11 +11922,11 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11948,19 +11940,19 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4500011203</v>
+        <v>4500011579</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -11969,36 +11961,36 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q83" t="n">
         <v>100</v>
       </c>
       <c r="R83" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="S83" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="T83" t="n">
-        <v>31250</v>
+        <v>575000</v>
       </c>
       <c r="U83" t="n">
-        <v>625000</v>
+        <v>661250</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -12027,12 +12019,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12048,7 +12040,7 @@
         </is>
       </c>
       <c r="AK83" t="n">
-        <v>1000025162</v>
+        <v>1000025742</v>
       </c>
       <c r="AL83" t="inlineStr"/>
     </row>
@@ -12068,11 +12060,11 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -12086,19 +12078,19 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4500011203</v>
+        <v>4500011580</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -12107,36 +12099,36 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q84" t="n">
         <v>100</v>
       </c>
       <c r="R84" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="S84" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="T84" t="n">
-        <v>712500</v>
+        <v>1600000</v>
       </c>
       <c r="U84" t="n">
-        <v>142500</v>
+        <v>1600000</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -12165,12 +12157,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12182,35 +12174,35 @@
       <c r="AI84" t="inlineStr"/>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK84" t="n">
-        <v>1000025162</v>
+        <v>1000025743</v>
       </c>
       <c r="AL84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>001/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -12224,19 +12216,19 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4500011203</v>
+        <v>4599910747</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="K85" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
@@ -12245,36 +12237,36 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>JASA MOBILISASI</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q85" t="n">
         <v>100</v>
       </c>
       <c r="R85" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S85" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T85" t="n">
-        <v>50000</v>
+        <v>400000000</v>
       </c>
       <c r="U85" t="n">
-        <v>25000</v>
+        <v>400000000</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -12303,12 +12295,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Paku 12 cm</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12320,35 +12312,39 @@
       <c r="AI85" t="inlineStr"/>
       <c r="AJ85" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK85" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL85" t="inlineStr"/>
+        <v>1000024733</v>
+      </c>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-020</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -12362,19 +12358,19 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4500011203</v>
+        <v>4500010748</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K86" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L86" t="inlineStr">
         <is>
@@ -12383,36 +12379,36 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q86" t="n">
         <v>100</v>
       </c>
       <c r="R86" s="1" t="n">
-        <v>46275</v>
+        <v>46011</v>
       </c>
       <c r="S86" s="1" t="n">
-        <v>46275</v>
+        <v>46022</v>
       </c>
       <c r="T86" t="n">
-        <v>50000</v>
+        <v>75538000</v>
       </c>
       <c r="U86" t="n">
-        <v>25000</v>
+        <v>29459820</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -12441,12 +12437,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Paku Beton 10 cm</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12462,31 +12458,35 @@
         </is>
       </c>
       <c r="AK86" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL86" t="inlineStr"/>
+        <v>1000024201</v>
+      </c>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -12500,19 +12500,19 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4500011579</v>
+        <v>4500010749</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K87" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
@@ -12521,36 +12521,36 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q87" t="n">
         <v>100</v>
       </c>
       <c r="R87" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S87" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T87" t="n">
-        <v>575000</v>
+        <v>62818000</v>
       </c>
       <c r="U87" t="n">
-        <v>661250</v>
+        <v>24499020</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12596,35 +12596,39 @@
       <c r="AI87" t="inlineStr"/>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK87" t="n">
-        <v>1000025742</v>
-      </c>
-      <c r="AL87" t="inlineStr"/>
+        <v>1000024205</v>
+      </c>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -12638,19 +12642,19 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4500011580</v>
+        <v>4500010750</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K88" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L88" t="inlineStr">
         <is>
@@ -12659,36 +12663,36 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q88" t="n">
         <v>100</v>
       </c>
       <c r="R88" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S88" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T88" t="n">
-        <v>1600000</v>
+        <v>78225000</v>
       </c>
       <c r="U88" t="n">
-        <v>1600000</v>
+        <v>30507750</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -12717,12 +12721,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -12738,9 +12742,13 @@
         </is>
       </c>
       <c r="AK88" t="n">
-        <v>1000025743</v>
-      </c>
-      <c r="AL88" t="inlineStr"/>
+        <v>1000024200</v>
+      </c>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12758,7 +12766,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/FLD/XII/2025</t>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E89" s="1" t="n">
@@ -12780,11 +12788,11 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4599910747</v>
+        <v>4500010746</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="K89" s="1" t="n">
@@ -12797,20 +12805,20 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>JASA MOBILISASI</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q89" t="n">
@@ -12823,10 +12831,10 @@
         <v>46022</v>
       </c>
       <c r="T89" t="n">
-        <v>400000000</v>
+        <v>189241000</v>
       </c>
       <c r="U89" t="n">
-        <v>400000000</v>
+        <v>73803990</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -12855,12 +12863,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -12876,11 +12884,11 @@
         </is>
       </c>
       <c r="AK89" t="n">
-        <v>1000024733</v>
+        <v>1000024199</v>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-020</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -12900,7 +12908,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/FLD/XII/2025</t>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E90" s="1" t="n">
@@ -12922,11 +12930,11 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4500010748</v>
+        <v>4500010745</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K90" s="1" t="n">
@@ -12944,7 +12952,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O90" t="n">
@@ -12965,10 +12973,10 @@
         <v>46022</v>
       </c>
       <c r="T90" t="n">
-        <v>75538000</v>
+        <v>131224000</v>
       </c>
       <c r="U90" t="n">
-        <v>29459820</v>
+        <v>51177360</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -12997,12 +13005,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13014,15 +13022,15 @@
       <c r="AI90" t="inlineStr"/>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK90" t="n">
-        <v>1000024201</v>
+        <v>1000024198</v>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
@@ -13042,7 +13050,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/FLD/XII/2025</t>
+          <t>007/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E91" s="1" t="n">
@@ -13064,11 +13072,11 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4500010749</v>
+        <v>4500010745</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="K91" s="1" t="n">
@@ -13086,11 +13094,11 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -13101,16 +13109,16 @@
         <v>100</v>
       </c>
       <c r="R91" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S91" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T91" t="n">
-        <v>62818000</v>
+        <v>131224000</v>
       </c>
       <c r="U91" t="n">
-        <v>24499020</v>
+        <v>131224000</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -13139,12 +13147,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13160,11 +13168,11 @@
         </is>
       </c>
       <c r="AK91" t="n">
-        <v>1000024205</v>
+        <v>1000024508</v>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
@@ -13184,11 +13192,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/FLD/XII/2025</t>
+          <t>008/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -13206,11 +13214,11 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4500010750</v>
+        <v>4500010749</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K92" s="1" t="n">
@@ -13228,11 +13236,11 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -13243,16 +13251,16 @@
         <v>100</v>
       </c>
       <c r="R92" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S92" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T92" t="n">
-        <v>78225000</v>
+        <v>62818000</v>
       </c>
       <c r="U92" t="n">
-        <v>30507750</v>
+        <v>62818000</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -13281,12 +13289,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13302,11 +13310,11 @@
         </is>
       </c>
       <c r="AK92" t="n">
-        <v>1000024200</v>
+        <v>1000024511</v>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -13326,11 +13334,11 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/FLD/XII/2025</t>
+          <t>009/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -13352,7 +13360,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K93" s="1" t="n">
@@ -13374,7 +13382,7 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -13385,16 +13393,16 @@
         <v>100</v>
       </c>
       <c r="R93" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S93" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T93" t="n">
         <v>189241000</v>
       </c>
       <c r="U93" t="n">
-        <v>73803990</v>
+        <v>189241000</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -13423,12 +13431,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13444,7 +13452,7 @@
         </is>
       </c>
       <c r="AK93" t="n">
-        <v>1000024199</v>
+        <v>1000024510</v>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
@@ -13468,7 +13476,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/FLD/XII/2025</t>
+          <t>010/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E94" s="1" t="n">
@@ -13490,11 +13498,11 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4500010745</v>
+        <v>4500010748</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K94" s="1" t="n">
@@ -13512,11 +13520,11 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -13527,16 +13535,16 @@
         <v>100</v>
       </c>
       <c r="R94" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S94" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T94" t="n">
-        <v>131224000</v>
+        <v>75538000</v>
       </c>
       <c r="U94" t="n">
-        <v>51177360</v>
+        <v>75538000</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -13565,12 +13573,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13586,11 +13594,11 @@
         </is>
       </c>
       <c r="AK94" t="n">
-        <v>1000024198</v>
+        <v>1000024516</v>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -13610,11 +13618,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/FLD/I/2026</t>
+          <t>011/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -13632,11 +13640,11 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4500010745</v>
+        <v>4500010750</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K95" s="1" t="n">
@@ -13654,7 +13662,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -13675,10 +13683,10 @@
         <v>46053</v>
       </c>
       <c r="T95" t="n">
-        <v>131224000</v>
+        <v>78225000</v>
       </c>
       <c r="U95" t="n">
-        <v>131224000</v>
+        <v>78225000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -13707,12 +13715,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -13728,11 +13736,11 @@
         </is>
       </c>
       <c r="AK95" t="n">
-        <v>1000024508</v>
+        <v>1000024509</v>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -13752,11 +13760,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/FLD/I/2026</t>
+          <t>012/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46053</v>
+        <v>46063</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -13774,15 +13782,15 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4500010749</v>
+        <v>4500010980</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46011</v>
+        <v>46056</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -13791,36 +13799,36 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ON-CALL BASIS</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>100</v>
       </c>
       <c r="R96" s="1" t="n">
-        <v>46023</v>
+        <v>46056</v>
       </c>
       <c r="S96" s="1" t="n">
-        <v>46053</v>
+        <v>46062</v>
       </c>
       <c r="T96" t="n">
-        <v>62818000</v>
+        <v>1936000</v>
       </c>
       <c r="U96" t="n">
-        <v>62818000</v>
+        <v>13552000</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -13849,12 +13857,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -13870,11 +13878,11 @@
         </is>
       </c>
       <c r="AK96" t="n">
-        <v>1000024511</v>
+        <v>1000024507</v>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>7207250142-BSS-WO-2025-008</t>
         </is>
       </c>
     </row>
@@ -13894,11 +13902,11 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>009/BSS-JOB/FLD/I/2026</t>
+          <t>014/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -13916,11 +13924,11 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4500010746</v>
+        <v>4500010749</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K97" s="1" t="n">
@@ -13938,7 +13946,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -13953,16 +13961,16 @@
         <v>100</v>
       </c>
       <c r="R97" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S97" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T97" t="n">
-        <v>189241000</v>
+        <v>62818000</v>
       </c>
       <c r="U97" t="n">
-        <v>189241000</v>
+        <v>62818000</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -13991,12 +13999,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14012,11 +14020,11 @@
         </is>
       </c>
       <c r="AK97" t="n">
-        <v>1000024510</v>
+        <v>1000024711</v>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -14036,11 +14044,11 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/FLD/I/2026</t>
+          <t>013/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -14062,7 +14070,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K98" s="1" t="n">
@@ -14095,10 +14103,10 @@
         <v>100</v>
       </c>
       <c r="R98" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S98" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T98" t="n">
         <v>75538000</v>
@@ -14133,12 +14141,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14154,7 +14162,7 @@
         </is>
       </c>
       <c r="AK98" t="n">
-        <v>1000024516</v>
+        <v>1000024712</v>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
@@ -14178,11 +14186,11 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/FLD/I/2026</t>
+          <t>015/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -14204,7 +14212,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K99" s="1" t="n">
@@ -14237,10 +14245,10 @@
         <v>100</v>
       </c>
       <c r="R99" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S99" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T99" t="n">
         <v>78225000</v>
@@ -14275,12 +14283,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14296,7 +14304,7 @@
         </is>
       </c>
       <c r="AK99" t="n">
-        <v>1000024509</v>
+        <v>1000024709</v>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
@@ -14320,11 +14328,11 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/FLD/I/2026</t>
+          <t>016/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46063</v>
+        <v>46081</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -14342,15 +14350,15 @@
         </is>
       </c>
       <c r="I100" t="n">
-        <v>4500010980</v>
+        <v>4500010746</v>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K100" s="1" t="n">
-        <v>46056</v>
+        <v>46011</v>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -14359,36 +14367,36 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>ON-CALL BASIS</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q100" t="n">
         <v>100</v>
       </c>
       <c r="R100" s="1" t="n">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="S100" s="1" t="n">
-        <v>46062</v>
+        <v>46081</v>
       </c>
       <c r="T100" t="n">
-        <v>1936000</v>
+        <v>189241000</v>
       </c>
       <c r="U100" t="n">
-        <v>13552000</v>
+        <v>189241000</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -14417,12 +14425,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14438,11 +14446,11 @@
         </is>
       </c>
       <c r="AK100" t="n">
-        <v>1000024507</v>
+        <v>1000024708</v>
       </c>
       <c r="AL100" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2025-008</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -14462,7 +14470,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/FLD/II/2026</t>
+          <t>017/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E101" s="1" t="n">
@@ -14484,11 +14492,11 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>4500010749</v>
+        <v>4500010745</v>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K101" s="1" t="n">
@@ -14506,7 +14514,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -14527,10 +14535,10 @@
         <v>46081</v>
       </c>
       <c r="T101" t="n">
-        <v>62818000</v>
+        <v>131224000</v>
       </c>
       <c r="U101" t="n">
-        <v>62818000</v>
+        <v>131224000</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -14559,12 +14567,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14580,35 +14588,37 @@
         </is>
       </c>
       <c r="AK101" t="n">
-        <v>1000024711</v>
+        <v>1000024727</v>
       </c>
       <c r="AL101" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="n">
-        <v>46081</v>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -14622,19 +14632,23 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I102" t="n">
-        <v>4500010748</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K102" s="1" t="n">
-        <v>46011</v>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
@@ -14643,12 +14657,12 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -14656,23 +14670,27 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q102" t="n">
         <v>100</v>
       </c>
-      <c r="R102" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S102" s="1" t="n">
-        <v>46081</v>
+      <c r="R102" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T102" t="n">
-        <v>75538000</v>
+        <v>7654600</v>
       </c>
       <c r="U102" t="n">
-        <v>75538000</v>
+        <v>8802790</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -14701,12 +14719,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -14718,39 +14736,39 @@
       <c r="AI102" t="inlineStr"/>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK102" t="n">
-        <v>1000024712</v>
-      </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
-        </is>
-      </c>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="n">
-        <v>46081</v>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -14764,19 +14782,23 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I103" t="n">
-        <v>4500010750</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K103" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
@@ -14785,16 +14807,16 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -14804,17 +14826,21 @@
       <c r="Q103" t="n">
         <v>100</v>
       </c>
-      <c r="R103" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S103" s="1" t="n">
-        <v>46081</v>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T103" t="n">
-        <v>78225000</v>
+        <v>25000000</v>
       </c>
       <c r="U103" t="n">
-        <v>78225000</v>
+        <v>12000000</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -14843,12 +14869,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -14863,36 +14889,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK103" t="n">
-        <v>1000024709</v>
-      </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
-        </is>
-      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="n">
-        <v>46081</v>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -14906,19 +14932,23 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I104" t="n">
-        <v>4500010746</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K104" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
@@ -14927,16 +14957,16 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -14946,17 +14976,21 @@
       <c r="Q104" t="n">
         <v>100</v>
       </c>
-      <c r="R104" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S104" s="1" t="n">
-        <v>46081</v>
+      <c r="R104" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T104" t="n">
-        <v>189241000</v>
+        <v>17500000</v>
       </c>
       <c r="U104" t="n">
-        <v>189241000</v>
+        <v>8400000</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -14985,12 +15019,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15005,36 +15039,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK104" t="n">
-        <v>1000024708</v>
-      </c>
-      <c r="AL104" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
-        </is>
-      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="n">
-        <v>46081</v>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -15048,19 +15082,23 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I105" t="n">
-        <v>4500010745</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K105" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
@@ -15069,16 +15107,16 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -15088,17 +15126,21 @@
       <c r="Q105" t="n">
         <v>100</v>
       </c>
-      <c r="R105" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S105" s="1" t="n">
-        <v>46081</v>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T105" t="n">
-        <v>131224000</v>
+        <v>60000000</v>
       </c>
       <c r="U105" t="n">
-        <v>131224000</v>
+        <v>44400000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -15127,12 +15169,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15147,14 +15189,12 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK105" t="n">
-        <v>1000024727</v>
-      </c>
-      <c r="AL105" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
-        </is>
-      </c>
+      <c r="AK105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -15172,12 +15212,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -15197,17 +15237,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -15217,20 +15257,20 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q106" t="n">
@@ -15247,10 +15287,10 @@
         </is>
       </c>
       <c r="T106" t="n">
-        <v>7654600</v>
+        <v>60000000</v>
       </c>
       <c r="U106" t="n">
-        <v>8802790</v>
+        <v>44400000</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15279,12 +15319,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15296,7 +15336,7 @@
       <c r="AI106" t="inlineStr"/>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -15367,16 +15407,16 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -15397,10 +15437,10 @@
         </is>
       </c>
       <c r="T107" t="n">
-        <v>25000000</v>
+        <v>15000000</v>
       </c>
       <c r="U107" t="n">
-        <v>12000000</v>
+        <v>11100000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15429,12 +15469,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15517,16 +15557,16 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -15547,10 +15587,10 @@
         </is>
       </c>
       <c r="T108" t="n">
-        <v>17500000</v>
+        <v>15000000</v>
       </c>
       <c r="U108" t="n">
-        <v>8400000</v>
+        <v>11100000</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -15579,12 +15619,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -15622,7 +15662,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -15652,7 +15692,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -15667,20 +15707,20 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>0.74</v>
+        <v>2578</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -15688,19 +15728,19 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T109" t="n">
-        <v>60000000</v>
+        <v>65000</v>
       </c>
       <c r="U109" t="n">
-        <v>44400000</v>
+        <v>167570000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -15729,12 +15769,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -15772,7 +15812,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -15802,7 +15842,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -15817,20 +15857,20 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>0.74</v>
+        <v>1157</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -15838,19 +15878,19 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T110" t="n">
-        <v>60000000</v>
+        <v>33000</v>
       </c>
       <c r="U110" t="n">
-        <v>44400000</v>
+        <v>38181000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -15879,12 +15919,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -15907,8 +15947,10 @@
       <c r="AL110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="n">
-        <v>7201250141</v>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -15922,7 +15964,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -15952,7 +15994,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -15967,20 +16009,20 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q111" t="n">
@@ -15988,19 +16030,19 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T111" t="n">
-        <v>15000000</v>
+        <v>750000</v>
       </c>
       <c r="U111" t="n">
-        <v>11100000</v>
+        <v>16500000</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -16029,12 +16071,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-19 21:40:39</t>
+          <t>2026-09-20 06:43:21</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16056,460 +16098,6 @@
       </c>
       <c r="AL111" t="inlineStr"/>
     </row>
-    <row r="112">
-      <c r="A112" t="n">
-        <v>7201250141</v>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>S25048TPD</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>31 Aug 2026</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
-        </is>
-      </c>
-      <c r="K112" t="inlineStr">
-        <is>
-          <t>03 Aug 2026</t>
-        </is>
-      </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
-        </is>
-      </c>
-      <c r="O112" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="P112" t="inlineStr">
-        <is>
-          <t>Month</t>
-        </is>
-      </c>
-      <c r="Q112" t="n">
-        <v>100</v>
-      </c>
-      <c r="R112" t="inlineStr">
-        <is>
-          <t>19 Sep 2026</t>
-        </is>
-      </c>
-      <c r="S112" t="inlineStr">
-        <is>
-          <t>19 Sep 2026</t>
-        </is>
-      </c>
-      <c r="T112" t="n">
-        <v>15000000</v>
-      </c>
-      <c r="U112" t="n">
-        <v>11100000</v>
-      </c>
-      <c r="V112" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W112" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X112" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y112" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
-      <c r="AA112" t="inlineStr">
-        <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>2026-09-19 21:40:39</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr"/>
-      <c r="AD112" t="inlineStr"/>
-      <c r="AE112" t="inlineStr"/>
-      <c r="AF112" t="inlineStr"/>
-      <c r="AG112" t="inlineStr"/>
-      <c r="AH112" t="inlineStr"/>
-      <c r="AI112" t="inlineStr"/>
-      <c r="AJ112" t="inlineStr">
-        <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK112" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>S25048TPD</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>31 Aug 2026</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr">
-        <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
-        </is>
-      </c>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>03 Aug 2026</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr">
-        <is>
-          <t>Food &amp; beverage, main course</t>
-        </is>
-      </c>
-      <c r="O113" t="n">
-        <v>2578</v>
-      </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="Q113" t="n">
-        <v>100</v>
-      </c>
-      <c r="R113" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="S113" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="T113" t="n">
-        <v>65000</v>
-      </c>
-      <c r="U113" t="n">
-        <v>167570000</v>
-      </c>
-      <c r="V113" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W113" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X113" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y113" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>2026-09-19 21:40:39</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr"/>
-      <c r="AD113" t="inlineStr"/>
-      <c r="AE113" t="inlineStr"/>
-      <c r="AF113" t="inlineStr"/>
-      <c r="AG113" t="inlineStr"/>
-      <c r="AH113" t="inlineStr"/>
-      <c r="AI113" t="inlineStr"/>
-      <c r="AJ113" t="inlineStr">
-        <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK113" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>S25048TPD</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>31 Aug 2026</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>4500011739</t>
-        </is>
-      </c>
-      <c r="J114" t="inlineStr">
-        <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
-        </is>
-      </c>
-      <c r="K114" t="inlineStr">
-        <is>
-          <t>03 Aug 2026</t>
-        </is>
-      </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>IDR</t>
-        </is>
-      </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
-        </is>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
-        </is>
-      </c>
-      <c r="O114" t="n">
-        <v>1157</v>
-      </c>
-      <c r="P114" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="Q114" t="n">
-        <v>100</v>
-      </c>
-      <c r="R114" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="S114" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="T114" t="n">
-        <v>33000</v>
-      </c>
-      <c r="U114" t="n">
-        <v>38181000</v>
-      </c>
-      <c r="V114" t="inlineStr">
-        <is>
-          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
-        </is>
-      </c>
-      <c r="W114" t="inlineStr">
-        <is>
-          <t>Cabang Luwuk</t>
-        </is>
-      </c>
-      <c r="X114" t="inlineStr">
-        <is>
-          <t>0167 0167 8888 303</t>
-        </is>
-      </c>
-      <c r="Y114" t="inlineStr">
-        <is>
-          <t>PT. BANGGAI SENTRAL SULAWESI</t>
-        </is>
-      </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>Accounts Payable - Finance Department</t>
-        </is>
-      </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>2026-09-19 21:40:39</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr"/>
-      <c r="AD114" t="inlineStr"/>
-      <c r="AE114" t="inlineStr"/>
-      <c r="AF114" t="inlineStr"/>
-      <c r="AG114" t="inlineStr"/>
-      <c r="AH114" t="inlineStr"/>
-      <c r="AI114" t="inlineStr"/>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="AL114" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL111"/>
+  <dimension ref="A1:AL114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5518,11 +5518,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5544,11 +5544,11 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46268</v>
+        <v>46241</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -5562,31 +5562,31 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q37" t="n">
         <v>100</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>46269</v>
+        <v>46242</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>46269</v>
+        <v>46254</v>
       </c>
       <c r="T37" t="n">
         <v>750000</v>
       </c>
       <c r="U37" t="n">
-        <v>750000</v>
+        <v>9750000</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5615,12 +5615,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5658,11 +5658,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5684,11 +5684,11 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16</t>
+          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46268</v>
+        <v>46241</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5697,36 +5697,36 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q38" t="n">
         <v>100</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>46269</v>
+        <v>46257</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>46269</v>
+        <v>46265</v>
       </c>
       <c r="T38" t="n">
-        <v>1600000</v>
+        <v>750000</v>
       </c>
       <c r="U38" t="n">
-        <v>1600000</v>
+        <v>6750000</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -5860,13 +5860,13 @@
         <v>46242</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>46254</v>
+        <v>46265</v>
       </c>
       <c r="T39" t="n">
         <v>750000</v>
       </c>
       <c r="U39" t="n">
-        <v>9750000</v>
+        <v>12750000</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -5895,12 +5895,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -5982,11 +5982,11 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -5997,16 +5997,16 @@
         <v>100</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="S40" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T40" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U40" t="n">
-        <v>6750000</v>
+        <v>14300000</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6122,11 +6122,11 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
@@ -6143,10 +6143,10 @@
         <v>46265</v>
       </c>
       <c r="T41" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U41" t="n">
-        <v>12750000</v>
+        <v>13650000</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -6175,12 +6175,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6262,11 +6262,11 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
@@ -6277,16 +6277,16 @@
         <v>100</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="S42" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T42" t="n">
-        <v>650000</v>
+        <v>500000</v>
       </c>
       <c r="U42" t="n">
-        <v>14300000</v>
+        <v>10500000</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6402,11 +6402,11 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
@@ -6417,16 +6417,16 @@
         <v>100</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="S43" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T43" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="U43" t="n">
-        <v>13650000</v>
+        <v>13800000</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6542,11 +6542,11 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
@@ -6563,10 +6563,10 @@
         <v>46265</v>
       </c>
       <c r="T44" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="U44" t="n">
-        <v>10500000</v>
+        <v>13800000</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck) atas nama Wijayanto Sucipto</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E45" s="1" t="n">
@@ -6664,11 +6664,11 @@
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -6677,36 +6677,36 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q45" t="n">
         <v>100</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="S45" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T45" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="U45" t="n">
-        <v>13800000</v>
+        <v>40000000</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -6735,12 +6735,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E46" s="1" t="n">
@@ -6804,11 +6804,11 @@
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026</t>
+          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46241</v>
+        <v>46240</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -6817,36 +6817,36 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>100</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>46243</v>
+        <v>46241</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>46265</v>
+        <v>46255</v>
       </c>
       <c r="T46" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="U46" t="n">
-        <v>13800000</v>
+        <v>24000000</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -6875,12 +6875,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7015,12 +7015,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7106,7 +7106,7 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -7117,16 +7117,16 @@
         <v>100</v>
       </c>
       <c r="R48" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="S48" s="1" t="n">
-        <v>46255</v>
+        <v>46248</v>
       </c>
       <c r="T48" t="n">
         <v>1600000</v>
       </c>
       <c r="U48" t="n">
-        <v>24000000</v>
+        <v>6400000</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -7155,12 +7155,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7242,7 +7242,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7382,11 +7382,11 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -7397,16 +7397,16 @@
         <v>100</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>46245</v>
+        <v>46242</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>46248</v>
+        <v>46265</v>
       </c>
       <c r="T50" t="n">
         <v>1600000</v>
       </c>
       <c r="U50" t="n">
-        <v>6400000</v>
+        <v>35200000</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -7435,12 +7435,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E51" s="1" t="n">
@@ -7504,11 +7504,11 @@
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -7517,16 +7517,16 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
@@ -7537,16 +7537,16 @@
         <v>100</v>
       </c>
       <c r="R51" s="1" t="n">
-        <v>46241</v>
+        <v>46242</v>
       </c>
       <c r="S51" s="1" t="n">
-        <v>46265</v>
+        <v>46248</v>
       </c>
       <c r="T51" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U51" t="n">
-        <v>40000000</v>
+        <v>59500000</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -7575,12 +7575,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E52" s="1" t="n">
@@ -7644,11 +7644,11 @@
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Penyediaan Car &amp; Tansportation Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
@@ -7657,16 +7657,16 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
@@ -7677,16 +7677,16 @@
         <v>100</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="S52" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T52" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U52" t="n">
-        <v>35200000</v>
+        <v>76500000</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -7715,12 +7715,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7802,11 +7802,11 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
@@ -7817,16 +7817,16 @@
         <v>100</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46242</v>
+        <v>46243</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>46248</v>
+        <v>46265</v>
       </c>
       <c r="T53" t="n">
-        <v>8500000</v>
+        <v>2750000</v>
       </c>
       <c r="U53" t="n">
-        <v>59500000</v>
+        <v>57750000</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7898,7 +7898,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E54" s="1" t="n">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K54" s="1" t="n">
@@ -7937,36 +7937,36 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>9</v>
+        <v>1800</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>100</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="S54" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T54" t="n">
-        <v>8500000</v>
+        <v>7500</v>
       </c>
       <c r="U54" t="n">
-        <v>76500000</v>
+        <v>12150000</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7995,12 +7995,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8012,7 +8012,7 @@
       <c r="AI54" t="inlineStr"/>
       <c r="AJ54" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK54" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E55" s="1" t="n">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Penyediaan Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
@@ -8077,36 +8077,36 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q55" t="n">
         <v>100</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>46243</v>
+        <v>46244</v>
       </c>
       <c r="S55" s="1" t="n">
         <v>46265</v>
       </c>
       <c r="T55" t="n">
-        <v>2750000</v>
+        <v>53300</v>
       </c>
       <c r="U55" t="n">
-        <v>57750000</v>
+        <v>863460</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -8135,12 +8135,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8152,7 +8152,7 @@
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK55" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E56" s="1" t="n">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
@@ -8217,20 +8217,20 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>1800</v>
+        <v>250</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q56" t="n">
@@ -8240,13 +8240,13 @@
         <v>46242</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T56" t="n">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="U56" t="n">
-        <v>12150000</v>
+        <v>6250000</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -8275,12 +8275,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8318,7 +8318,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E57" s="1" t="n">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K57" s="1" t="n">
@@ -8357,36 +8357,36 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q57" t="n">
         <v>100</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>46244</v>
+        <v>46257</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>46265</v>
+        <v>46257</v>
       </c>
       <c r="T57" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U57" t="n">
-        <v>863460</v>
+        <v>5000000</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -8415,12 +8415,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8506,7 +8506,7 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
@@ -8526,7 +8526,7 @@
         <v>25000</v>
       </c>
       <c r="U58" t="n">
-        <v>6250000</v>
+        <v>1250000</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -8555,12 +8555,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8646,7 +8646,7 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
@@ -8657,16 +8657,16 @@
         <v>100</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="T59" t="n">
         <v>25000</v>
       </c>
       <c r="U59" t="n">
-        <v>5000000</v>
+        <v>1250000</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8695,12 +8695,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8790,7 +8790,7 @@
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8975,12 +8975,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9066,11 +9066,11 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q62" t="n">
@@ -9080,13 +9080,13 @@
         <v>46242</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="T62" t="n">
         <v>25000</v>
       </c>
       <c r="U62" t="n">
-        <v>1250000</v>
+        <v>2875000</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -9115,12 +9115,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9158,11 +9158,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46265</v>
+        <v>46140</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -9180,15 +9180,15 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0</v>
+        <v>4500011236</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46241</v>
+        <v>46071</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -9197,36 +9197,36 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q63" t="n">
         <v>100</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="T63" t="n">
-        <v>25000</v>
+        <v>773919900</v>
       </c>
       <c r="U63" t="n">
-        <v>1250000</v>
+        <v>890007885</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -9255,12 +9255,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9272,13 +9272,11 @@
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
-      <c r="AK63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK63" t="n">
+        <v>1000025165</v>
       </c>
       <c r="AL63" t="inlineStr"/>
     </row>
@@ -9298,11 +9296,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -9320,15 +9318,15 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -9342,31 +9340,31 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="O64" t="n">
-        <v>115</v>
+        <v>0.524</v>
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q64" t="n">
         <v>100</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46257</v>
+        <v>46072</v>
       </c>
       <c r="T64" t="n">
-        <v>25000</v>
+        <v>3125000</v>
       </c>
       <c r="U64" t="n">
-        <v>2875000</v>
+        <v>1637500</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -9395,12 +9393,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9415,10 +9413,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK64" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL64" t="inlineStr"/>
     </row>
@@ -9438,11 +9434,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9460,15 +9456,15 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4500011236</v>
+        <v>4500011203</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -9477,36 +9473,36 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q65" t="n">
         <v>100</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="T65" t="n">
-        <v>773919900</v>
+        <v>50000</v>
       </c>
       <c r="U65" t="n">
-        <v>890007885</v>
+        <v>200000</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -9535,12 +9531,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9552,11 +9548,11 @@
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK65" t="n">
-        <v>1000025165</v>
+        <v>1000025162</v>
       </c>
       <c r="AL65" t="inlineStr"/>
     </row>
@@ -9620,15 +9616,15 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0.524</v>
+        <v>2</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -9641,10 +9637,10 @@
         <v>46072</v>
       </c>
       <c r="T66" t="n">
-        <v>3125000</v>
+        <v>50000</v>
       </c>
       <c r="U66" t="n">
-        <v>1637500</v>
+        <v>100000</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -9673,12 +9669,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9762,7 +9758,7 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -9782,7 +9778,7 @@
         <v>50000</v>
       </c>
       <c r="U67" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -9811,12 +9807,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9896,15 +9892,15 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q68" t="n">
@@ -9917,10 +9913,10 @@
         <v>46072</v>
       </c>
       <c r="T68" t="n">
-        <v>50000</v>
+        <v>55500</v>
       </c>
       <c r="U68" t="n">
-        <v>100000</v>
+        <v>55500</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -9949,12 +9945,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10034,31 +10030,31 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q69" t="n">
         <v>100</v>
       </c>
       <c r="R69" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S69" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T69" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="U69" t="n">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -10087,12 +10083,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10172,7 +10168,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -10180,7 +10176,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q70" t="n">
@@ -10193,10 +10189,10 @@
         <v>46072</v>
       </c>
       <c r="T70" t="n">
-        <v>55500</v>
+        <v>293750</v>
       </c>
       <c r="U70" t="n">
-        <v>55500</v>
+        <v>293750</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -10225,12 +10221,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10310,7 +10306,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -10318,23 +10314,23 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q71" t="n">
         <v>100</v>
       </c>
       <c r="R71" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="S71" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="T71" t="n">
-        <v>75000</v>
+        <v>400000</v>
       </c>
       <c r="U71" t="n">
-        <v>75000</v>
+        <v>400000</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -10363,12 +10359,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Batu Pecah 1-2</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10448,15 +10444,15 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="O72" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q72" t="n">
@@ -10469,10 +10465,10 @@
         <v>46072</v>
       </c>
       <c r="T72" t="n">
-        <v>293750</v>
+        <v>120000</v>
       </c>
       <c r="U72" t="n">
-        <v>293750</v>
+        <v>1440000</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -10501,12 +10497,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10586,15 +10582,15 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q73" t="n">
@@ -10607,10 +10603,10 @@
         <v>46072</v>
       </c>
       <c r="T73" t="n">
-        <v>400000</v>
+        <v>93750</v>
       </c>
       <c r="U73" t="n">
-        <v>400000</v>
+        <v>187500</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -10639,12 +10635,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Batu Pecah 1-2</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10724,11 +10720,11 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -10745,10 +10741,10 @@
         <v>46072</v>
       </c>
       <c r="T74" t="n">
-        <v>120000</v>
+        <v>37500</v>
       </c>
       <c r="U74" t="n">
-        <v>1440000</v>
+        <v>75000</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -10777,12 +10773,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10862,11 +10858,11 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -10883,10 +10879,10 @@
         <v>46072</v>
       </c>
       <c r="T75" t="n">
-        <v>93750</v>
+        <v>37500</v>
       </c>
       <c r="U75" t="n">
-        <v>187500</v>
+        <v>37500</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -10915,12 +10911,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11000,15 +10996,15 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q76" t="n">
@@ -11021,10 +11017,10 @@
         <v>46072</v>
       </c>
       <c r="T76" t="n">
-        <v>37500</v>
+        <v>31250</v>
       </c>
       <c r="U76" t="n">
-        <v>75000</v>
+        <v>1500000</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -11053,12 +11049,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11138,15 +11134,15 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q77" t="n">
@@ -11159,10 +11155,10 @@
         <v>46072</v>
       </c>
       <c r="T77" t="n">
-        <v>37500</v>
+        <v>31250</v>
       </c>
       <c r="U77" t="n">
-        <v>37500</v>
+        <v>625000</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -11191,12 +11187,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11276,15 +11272,15 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>48</v>
+        <v>0.2</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -11297,10 +11293,10 @@
         <v>46072</v>
       </c>
       <c r="T78" t="n">
-        <v>31250</v>
+        <v>712500</v>
       </c>
       <c r="U78" t="n">
-        <v>1500000</v>
+        <v>142500</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -11329,12 +11325,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11414,15 +11410,15 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -11435,10 +11431,10 @@
         <v>46072</v>
       </c>
       <c r="T79" t="n">
-        <v>31250</v>
+        <v>50000</v>
       </c>
       <c r="U79" t="n">
-        <v>625000</v>
+        <v>25000</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -11467,12 +11463,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Paku 12 cm</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11552,31 +11548,31 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q80" t="n">
         <v>100</v>
       </c>
       <c r="R80" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S80" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T80" t="n">
-        <v>712500</v>
+        <v>50000</v>
       </c>
       <c r="U80" t="n">
-        <v>142500</v>
+        <v>25000</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -11605,12 +11601,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Paku Beton 10 cm</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11646,11 +11642,11 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -11664,19 +11660,19 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I81" t="n">
-        <v>4500011203</v>
+        <v>4500011579</v>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K81" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -11685,36 +11681,36 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q81" t="n">
         <v>100</v>
       </c>
       <c r="R81" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="S81" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="T81" t="n">
-        <v>50000</v>
+        <v>575000</v>
       </c>
       <c r="U81" t="n">
-        <v>25000</v>
+        <v>661250</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -11743,12 +11739,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Paku 12 cm</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -11764,7 +11760,7 @@
         </is>
       </c>
       <c r="AK81" t="n">
-        <v>1000025162</v>
+        <v>1000025742</v>
       </c>
       <c r="AL81" t="inlineStr"/>
     </row>
@@ -11784,11 +11780,11 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -11802,19 +11798,19 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I82" t="n">
-        <v>4500011203</v>
+        <v>4500011580</v>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K82" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -11823,36 +11819,36 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q82" t="n">
         <v>100</v>
       </c>
       <c r="R82" s="1" t="n">
-        <v>46275</v>
+        <v>46179</v>
       </c>
       <c r="S82" s="1" t="n">
-        <v>46275</v>
+        <v>46179</v>
       </c>
       <c r="T82" t="n">
-        <v>50000</v>
+        <v>1600000</v>
       </c>
       <c r="U82" t="n">
-        <v>25000</v>
+        <v>1600000</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -11881,12 +11877,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Paku Beton 10 cm</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -11898,35 +11894,35 @@
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK82" t="n">
-        <v>1000025162</v>
+        <v>1000025743</v>
       </c>
       <c r="AL82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>001/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -11940,19 +11936,19 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I83" t="n">
-        <v>4500011579</v>
+        <v>4599910747</v>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="K83" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
@@ -11961,12 +11957,12 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>JASA MOBILISASI</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
         </is>
       </c>
       <c r="O83" t="n">
@@ -11974,23 +11970,23 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q83" t="n">
         <v>100</v>
       </c>
       <c r="R83" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S83" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T83" t="n">
-        <v>575000</v>
+        <v>400000000</v>
       </c>
       <c r="U83" t="n">
-        <v>661250</v>
+        <v>400000000</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -12019,12 +12015,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12036,35 +12032,39 @@
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK83" t="n">
-        <v>1000025742</v>
-      </c>
-      <c r="AL83" t="inlineStr"/>
+        <v>1000024733</v>
+      </c>
+      <c r="AL83" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-020</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -12078,19 +12078,19 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I84" t="n">
-        <v>4500011580</v>
+        <v>4500010748</v>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K84" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
@@ -12099,36 +12099,36 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q84" t="n">
         <v>100</v>
       </c>
       <c r="R84" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S84" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T84" t="n">
-        <v>1600000</v>
+        <v>75538000</v>
       </c>
       <c r="U84" t="n">
-        <v>1600000</v>
+        <v>29459820</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -12157,12 +12157,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12174,13 +12174,17 @@
       <c r="AI84" t="inlineStr"/>
       <c r="AJ84" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK84" t="n">
-        <v>1000025743</v>
-      </c>
-      <c r="AL84" t="inlineStr"/>
+        <v>1000024201</v>
+      </c>
+      <c r="AL84" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -12198,7 +12202,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/FLD/XII/2025</t>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E85" s="1" t="n">
@@ -12220,11 +12224,11 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>4599910747</v>
+        <v>4500010749</v>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K85" s="1" t="n">
@@ -12237,20 +12241,20 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>JASA MOBILISASI</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -12263,10 +12267,10 @@
         <v>46022</v>
       </c>
       <c r="T85" t="n">
-        <v>400000000</v>
+        <v>62818000</v>
       </c>
       <c r="U85" t="n">
-        <v>400000000</v>
+        <v>24499020</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -12295,12 +12299,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12316,11 +12320,11 @@
         </is>
       </c>
       <c r="AK85" t="n">
-        <v>1000024733</v>
+        <v>1000024205</v>
       </c>
       <c r="AL85" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-020</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -12340,7 +12344,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/FLD/XII/2025</t>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E86" s="1" t="n">
@@ -12362,11 +12366,11 @@
         </is>
       </c>
       <c r="I86" t="n">
-        <v>4500010748</v>
+        <v>4500010750</v>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K86" s="1" t="n">
@@ -12384,7 +12388,7 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O86" t="n">
@@ -12405,10 +12409,10 @@
         <v>46022</v>
       </c>
       <c r="T86" t="n">
-        <v>75538000</v>
+        <v>78225000</v>
       </c>
       <c r="U86" t="n">
-        <v>29459820</v>
+        <v>30507750</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -12437,12 +12441,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12454,15 +12458,15 @@
       <c r="AI86" t="inlineStr"/>
       <c r="AJ86" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK86" t="n">
-        <v>1000024201</v>
+        <v>1000024200</v>
       </c>
       <c r="AL86" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12486,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/FLD/XII/2025</t>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E87" s="1" t="n">
@@ -12504,11 +12508,11 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>4500010749</v>
+        <v>4500010746</v>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="K87" s="1" t="n">
@@ -12526,7 +12530,7 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O87" t="n">
@@ -12547,10 +12551,10 @@
         <v>46022</v>
       </c>
       <c r="T87" t="n">
-        <v>62818000</v>
+        <v>189241000</v>
       </c>
       <c r="U87" t="n">
-        <v>24499020</v>
+        <v>73803990</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -12579,12 +12583,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12600,11 +12604,11 @@
         </is>
       </c>
       <c r="AK87" t="n">
-        <v>1000024205</v>
+        <v>1000024199</v>
       </c>
       <c r="AL87" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -12624,7 +12628,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/FLD/XII/2025</t>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E88" s="1" t="n">
@@ -12646,11 +12650,11 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>4500010750</v>
+        <v>4500010745</v>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K88" s="1" t="n">
@@ -12668,7 +12672,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O88" t="n">
@@ -12689,10 +12693,10 @@
         <v>46022</v>
       </c>
       <c r="T88" t="n">
-        <v>78225000</v>
+        <v>131224000</v>
       </c>
       <c r="U88" t="n">
-        <v>30507750</v>
+        <v>51177360</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -12721,12 +12725,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -12742,11 +12746,11 @@
         </is>
       </c>
       <c r="AK88" t="n">
-        <v>1000024200</v>
+        <v>1000024198</v>
       </c>
       <c r="AL88" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
@@ -12766,7 +12770,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/FLD/XII/2025</t>
+          <t>007/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E89" s="1" t="n">
@@ -12788,11 +12792,11 @@
         </is>
       </c>
       <c r="I89" t="n">
-        <v>4500010746</v>
+        <v>4500010745</v>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="K89" s="1" t="n">
@@ -12810,11 +12814,11 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -12825,16 +12829,16 @@
         <v>100</v>
       </c>
       <c r="R89" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S89" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T89" t="n">
-        <v>189241000</v>
+        <v>131224000</v>
       </c>
       <c r="U89" t="n">
-        <v>73803990</v>
+        <v>131224000</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -12863,12 +12867,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -12884,11 +12888,11 @@
         </is>
       </c>
       <c r="AK89" t="n">
-        <v>1000024199</v>
+        <v>1000024508</v>
       </c>
       <c r="AL89" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
@@ -12908,11 +12912,11 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/FLD/XII/2025</t>
+          <t>008/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -12930,11 +12934,11 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>4500010745</v>
+        <v>4500010749</v>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K90" s="1" t="n">
@@ -12952,11 +12956,11 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -12967,16 +12971,16 @@
         <v>100</v>
       </c>
       <c r="R90" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S90" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T90" t="n">
-        <v>131224000</v>
+        <v>62818000</v>
       </c>
       <c r="U90" t="n">
-        <v>51177360</v>
+        <v>62818000</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -13005,12 +13009,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13026,11 +13030,11 @@
         </is>
       </c>
       <c r="AK90" t="n">
-        <v>1000024198</v>
+        <v>1000024511</v>
       </c>
       <c r="AL90" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -13050,11 +13054,11 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/FLD/I/2026</t>
+          <t>009/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -13072,11 +13076,11 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>4500010745</v>
+        <v>4500010746</v>
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K91" s="1" t="n">
@@ -13094,7 +13098,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -13115,10 +13119,10 @@
         <v>46053</v>
       </c>
       <c r="T91" t="n">
-        <v>131224000</v>
+        <v>189241000</v>
       </c>
       <c r="U91" t="n">
-        <v>131224000</v>
+        <v>189241000</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -13147,12 +13151,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13168,11 +13172,11 @@
         </is>
       </c>
       <c r="AK91" t="n">
-        <v>1000024508</v>
+        <v>1000024510</v>
       </c>
       <c r="AL91" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -13192,11 +13196,11 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/FLD/I/2026</t>
+          <t>010/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -13214,11 +13218,11 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>4500010749</v>
+        <v>4500010748</v>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K92" s="1" t="n">
@@ -13236,7 +13240,7 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O92" t="n">
@@ -13257,10 +13261,10 @@
         <v>46053</v>
       </c>
       <c r="T92" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="U92" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -13289,12 +13293,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13310,11 +13314,11 @@
         </is>
       </c>
       <c r="AK92" t="n">
-        <v>1000024511</v>
+        <v>1000024516</v>
       </c>
       <c r="AL92" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -13334,7 +13338,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>009/BSS-JOB/FLD/I/2026</t>
+          <t>011/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E93" s="1" t="n">
@@ -13356,11 +13360,11 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>4500010746</v>
+        <v>4500010750</v>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K93" s="1" t="n">
@@ -13378,7 +13382,7 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -13399,10 +13403,10 @@
         <v>46053</v>
       </c>
       <c r="T93" t="n">
-        <v>189241000</v>
+        <v>78225000</v>
       </c>
       <c r="U93" t="n">
-        <v>189241000</v>
+        <v>78225000</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -13431,12 +13435,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13452,11 +13456,11 @@
         </is>
       </c>
       <c r="AK93" t="n">
-        <v>1000024510</v>
+        <v>1000024509</v>
       </c>
       <c r="AL93" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -13476,11 +13480,11 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/FLD/I/2026</t>
+          <t>012/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46022</v>
+        <v>46063</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -13498,15 +13502,15 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>4500010748</v>
+        <v>4500010980</v>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="K94" s="1" t="n">
-        <v>46011</v>
+        <v>46056</v>
       </c>
       <c r="L94" t="inlineStr">
         <is>
@@ -13515,36 +13519,36 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ON-CALL BASIS</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q94" t="n">
         <v>100</v>
       </c>
       <c r="R94" s="1" t="n">
-        <v>46023</v>
+        <v>46056</v>
       </c>
       <c r="S94" s="1" t="n">
-        <v>46053</v>
+        <v>46062</v>
       </c>
       <c r="T94" t="n">
-        <v>75538000</v>
+        <v>1936000</v>
       </c>
       <c r="U94" t="n">
-        <v>75538000</v>
+        <v>13552000</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -13573,12 +13577,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13594,11 +13598,11 @@
         </is>
       </c>
       <c r="AK94" t="n">
-        <v>1000024516</v>
+        <v>1000024507</v>
       </c>
       <c r="AL94" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>7207250142-BSS-WO-2025-008</t>
         </is>
       </c>
     </row>
@@ -13618,11 +13622,11 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/FLD/I/2026</t>
+          <t>014/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -13640,11 +13644,11 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>4500010750</v>
+        <v>4500010749</v>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K95" s="1" t="n">
@@ -13662,7 +13666,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -13677,16 +13681,16 @@
         <v>100</v>
       </c>
       <c r="R95" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S95" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T95" t="n">
-        <v>78225000</v>
+        <v>62818000</v>
       </c>
       <c r="U95" t="n">
-        <v>78225000</v>
+        <v>62818000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -13715,12 +13719,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -13736,11 +13740,11 @@
         </is>
       </c>
       <c r="AK95" t="n">
-        <v>1000024509</v>
+        <v>1000024711</v>
       </c>
       <c r="AL95" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -13760,11 +13764,11 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/FLD/I/2026</t>
+          <t>013/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46063</v>
+        <v>46081</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -13782,15 +13786,15 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>4500010980</v>
+        <v>4500010748</v>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K96" s="1" t="n">
-        <v>46056</v>
+        <v>46011</v>
       </c>
       <c r="L96" t="inlineStr">
         <is>
@@ -13799,36 +13803,36 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>ON-CALL BASIS</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q96" t="n">
         <v>100</v>
       </c>
       <c r="R96" s="1" t="n">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="S96" s="1" t="n">
-        <v>46062</v>
+        <v>46081</v>
       </c>
       <c r="T96" t="n">
-        <v>1936000</v>
+        <v>75538000</v>
       </c>
       <c r="U96" t="n">
-        <v>13552000</v>
+        <v>75538000</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -13857,12 +13861,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -13878,11 +13882,11 @@
         </is>
       </c>
       <c r="AK96" t="n">
-        <v>1000024507</v>
+        <v>1000024712</v>
       </c>
       <c r="AL96" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2025-008</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -13902,7 +13906,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/FLD/II/2026</t>
+          <t>015/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E97" s="1" t="n">
@@ -13924,11 +13928,11 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>4500010749</v>
+        <v>4500010750</v>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K97" s="1" t="n">
@@ -13946,7 +13950,7 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -13967,10 +13971,10 @@
         <v>46081</v>
       </c>
       <c r="T97" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="U97" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -13999,12 +14003,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14020,11 +14024,11 @@
         </is>
       </c>
       <c r="AK97" t="n">
-        <v>1000024711</v>
+        <v>1000024709</v>
       </c>
       <c r="AL97" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14048,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/FLD/II/2026</t>
+          <t>016/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E98" s="1" t="n">
@@ -14066,11 +14070,11 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>4500010748</v>
+        <v>4500010746</v>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K98" s="1" t="n">
@@ -14088,7 +14092,7 @@
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O98" t="n">
@@ -14109,10 +14113,10 @@
         <v>46081</v>
       </c>
       <c r="T98" t="n">
-        <v>75538000</v>
+        <v>189241000</v>
       </c>
       <c r="U98" t="n">
-        <v>75538000</v>
+        <v>189241000</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -14141,12 +14145,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14162,11 +14166,11 @@
         </is>
       </c>
       <c r="AK98" t="n">
-        <v>1000024712</v>
+        <v>1000024708</v>
       </c>
       <c r="AL98" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -14186,7 +14190,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/FLD/II/2026</t>
+          <t>017/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E99" s="1" t="n">
@@ -14208,11 +14212,11 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>4500010750</v>
+        <v>4500010745</v>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K99" s="1" t="n">
@@ -14230,7 +14234,7 @@
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O99" t="n">
@@ -14251,10 +14255,10 @@
         <v>46081</v>
       </c>
       <c r="T99" t="n">
-        <v>78225000</v>
+        <v>131224000</v>
       </c>
       <c r="U99" t="n">
-        <v>78225000</v>
+        <v>131224000</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -14283,12 +14287,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14304,35 +14308,37 @@
         </is>
       </c>
       <c r="AK99" t="n">
-        <v>1000024709</v>
+        <v>1000024727</v>
       </c>
       <c r="AL99" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="n">
-        <v>46081</v>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -14346,19 +14352,23 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I100" t="n">
-        <v>4500010746</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K100" s="1" t="n">
-        <v>46011</v>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
@@ -14367,12 +14377,12 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O100" t="n">
@@ -14380,23 +14390,27 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q100" t="n">
         <v>100</v>
       </c>
-      <c r="R100" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S100" s="1" t="n">
-        <v>46081</v>
+      <c r="R100" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T100" t="n">
-        <v>189241000</v>
+        <v>7654600</v>
       </c>
       <c r="U100" t="n">
-        <v>189241000</v>
+        <v>8802790</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -14425,12 +14439,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14442,39 +14456,39 @@
       <c r="AI100" t="inlineStr"/>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK100" t="n">
-        <v>1000024708</v>
-      </c>
-      <c r="AL100" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
-        </is>
-      </c>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="n">
-        <v>46081</v>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -14488,19 +14502,23 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I101" t="n">
-        <v>4500010745</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K101" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
@@ -14509,16 +14527,16 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -14528,17 +14546,21 @@
       <c r="Q101" t="n">
         <v>100</v>
       </c>
-      <c r="R101" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S101" s="1" t="n">
-        <v>46081</v>
+      <c r="R101" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T101" t="n">
-        <v>131224000</v>
+        <v>25000000</v>
       </c>
       <c r="U101" t="n">
-        <v>131224000</v>
+        <v>12000000</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -14567,12 +14589,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14587,14 +14609,12 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK101" t="n">
-        <v>1000024727</v>
-      </c>
-      <c r="AL101" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
-        </is>
-      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -14612,12 +14632,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -14637,17 +14657,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -14657,20 +14677,20 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q102" t="n">
@@ -14687,10 +14707,10 @@
         </is>
       </c>
       <c r="T102" t="n">
-        <v>7654600</v>
+        <v>17500000</v>
       </c>
       <c r="U102" t="n">
-        <v>8802790</v>
+        <v>8400000</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -14719,12 +14739,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -14736,7 +14756,7 @@
       <c r="AI102" t="inlineStr"/>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -14807,16 +14827,16 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
@@ -14837,10 +14857,10 @@
         </is>
       </c>
       <c r="T103" t="n">
-        <v>25000000</v>
+        <v>60000000</v>
       </c>
       <c r="U103" t="n">
-        <v>12000000</v>
+        <v>44400000</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -14869,12 +14889,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -14957,16 +14977,16 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -14987,10 +15007,10 @@
         </is>
       </c>
       <c r="T104" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="U104" t="n">
-        <v>8400000</v>
+        <v>44400000</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -15019,12 +15039,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15112,7 +15132,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -15137,10 +15157,10 @@
         </is>
       </c>
       <c r="T105" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="U105" t="n">
-        <v>44400000</v>
+        <v>11100000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -15169,12 +15189,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15262,7 +15282,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -15287,10 +15307,10 @@
         </is>
       </c>
       <c r="T106" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="U106" t="n">
-        <v>44400000</v>
+        <v>11100000</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15319,12 +15339,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15362,7 +15382,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -15392,7 +15412,7 @@
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -15407,20 +15427,20 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>0.74</v>
+        <v>2578</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -15428,19 +15448,19 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T107" t="n">
-        <v>15000000</v>
+        <v>65000</v>
       </c>
       <c r="U107" t="n">
-        <v>11100000</v>
+        <v>167570000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15469,12 +15489,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15512,7 +15532,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -15542,7 +15562,7 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -15557,20 +15577,20 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>0.74</v>
+        <v>1157</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -15578,19 +15598,19 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T108" t="n">
-        <v>15000000</v>
+        <v>33000</v>
       </c>
       <c r="U108" t="n">
-        <v>11100000</v>
+        <v>38181000</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -15619,12 +15639,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -15662,7 +15682,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -15692,7 +15712,7 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -15707,20 +15727,20 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>2578</v>
+        <v>22</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -15737,10 +15757,10 @@
         </is>
       </c>
       <c r="T109" t="n">
-        <v>65000</v>
+        <v>750000</v>
       </c>
       <c r="U109" t="n">
-        <v>167570000</v>
+        <v>16500000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -15769,12 +15789,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -15812,12 +15832,12 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -15842,7 +15862,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -15857,20 +15877,20 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>1157</v>
+        <v>1</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -15878,19 +15898,19 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T110" t="n">
-        <v>33000</v>
+        <v>750000</v>
       </c>
       <c r="U110" t="n">
-        <v>38181000</v>
+        <v>750000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -15919,12 +15939,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -15947,10 +15967,8 @@
       <c r="AL110" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A111" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B111" t="inlineStr">
         <is>
@@ -15964,12 +15982,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -15994,7 +16012,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -16009,20 +16027,20 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q111" t="n">
@@ -16030,19 +16048,19 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T111" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="U111" t="n">
-        <v>16500000</v>
+        <v>1600000</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -16071,12 +16089,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-20 06:43:21</t>
+          <t>2026-09-20 08:13:40</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16098,6 +16116,474 @@
       </c>
       <c r="AL111" t="inlineStr"/>
     </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="O112" t="n">
+        <v>24</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>100</v>
+      </c>
+      <c r="R112" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="T112" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U112" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X112" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:13:40</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr"/>
+      <c r="AD112" t="inlineStr"/>
+      <c r="AE112" t="inlineStr"/>
+      <c r="AF112" t="inlineStr"/>
+      <c r="AG112" t="inlineStr"/>
+      <c r="AH112" t="inlineStr"/>
+      <c r="AI112" t="inlineStr"/>
+      <c r="AJ112" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="O113" t="n">
+        <v>24</v>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>100</v>
+      </c>
+      <c r="R113" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="T113" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U113" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X113" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:13:40</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr"/>
+      <c r="AD113" t="inlineStr"/>
+      <c r="AE113" t="inlineStr"/>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="inlineStr"/>
+      <c r="AH113" t="inlineStr"/>
+      <c r="AI113" t="inlineStr"/>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="O114" t="n">
+        <v>24</v>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>100</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="T114" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U114" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X114" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>2026-09-20 08:13:40</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr"/>
+      <c r="AD114" t="inlineStr"/>
+      <c r="AE114" t="inlineStr"/>
+      <c r="AF114" t="inlineStr"/>
+      <c r="AG114" t="inlineStr"/>
+      <c r="AH114" t="inlineStr"/>
+      <c r="AI114" t="inlineStr"/>
+      <c r="AJ114" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
@@ -5557,20 +5557,20 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>1800</v>
+        <v>250</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q37" t="n">
@@ -5580,13 +5580,13 @@
         <v>46242</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>46265</v>
+        <v>46242</v>
       </c>
       <c r="T37" t="n">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="U37" t="n">
-        <v>12150000</v>
+        <v>6250000</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5615,12 +5615,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K38" s="1" t="n">
@@ -5697,36 +5697,36 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>18</v>
+        <v>200</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q38" t="n">
         <v>100</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>46244</v>
+        <v>46257</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>46265</v>
+        <v>46257</v>
       </c>
       <c r="T38" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U38" t="n">
-        <v>863460</v>
+        <v>5000000</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>25000</v>
       </c>
       <c r="U39" t="n">
-        <v>6250000</v>
+        <v>1250000</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -5895,12 +5895,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -5986,7 +5986,7 @@
         </is>
       </c>
       <c r="O40" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
@@ -5997,16 +5997,16 @@
         <v>100</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>46257</v>
+        <v>46242</v>
       </c>
       <c r="T40" t="n">
         <v>25000</v>
       </c>
       <c r="U40" t="n">
-        <v>5000000</v>
+        <v>1250000</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -6035,12 +6035,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6130,7 +6130,7 @@
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -6175,12 +6175,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6315,12 +6315,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6406,11 +6406,11 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q43" t="n">
@@ -6420,13 +6420,13 @@
         <v>46242</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="T43" t="n">
         <v>25000</v>
       </c>
       <c r="U43" t="n">
-        <v>1250000</v>
+        <v>2875000</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6455,12 +6455,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6498,11 +6498,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46265</v>
+        <v>46140</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6520,15 +6520,15 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>4500011236</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46241</v>
+        <v>46071</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -6537,36 +6537,36 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q44" t="n">
         <v>100</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="T44" t="n">
-        <v>25000</v>
+        <v>773919900</v>
       </c>
       <c r="U44" t="n">
-        <v>1250000</v>
+        <v>890007885</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6595,12 +6595,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6612,13 +6612,11 @@
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
-      <c r="AK44" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK44" t="n">
+        <v>1000025165</v>
       </c>
       <c r="AL44" t="inlineStr"/>
     </row>
@@ -6638,11 +6636,11 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -6660,15 +6658,15 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -6682,31 +6680,31 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>115</v>
+        <v>0.524</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q45" t="n">
         <v>100</v>
       </c>
       <c r="R45" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S45" s="1" t="n">
-        <v>46257</v>
+        <v>46072</v>
       </c>
       <c r="T45" t="n">
-        <v>25000</v>
+        <v>3125000</v>
       </c>
       <c r="U45" t="n">
-        <v>2875000</v>
+        <v>1637500</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -6735,12 +6733,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6755,10 +6753,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK45" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK45" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL45" t="inlineStr"/>
     </row>
@@ -6778,11 +6774,11 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -6800,15 +6796,15 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>4500011236</v>
+        <v>4500011203</v>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -6817,36 +6813,36 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q46" t="n">
         <v>100</v>
       </c>
       <c r="R46" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="S46" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="T46" t="n">
-        <v>773919900</v>
+        <v>50000</v>
       </c>
       <c r="U46" t="n">
-        <v>890007885</v>
+        <v>200000</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -6875,12 +6871,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -6892,11 +6888,11 @@
       <c r="AI46" t="inlineStr"/>
       <c r="AJ46" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK46" t="n">
-        <v>1000025165</v>
+        <v>1000025162</v>
       </c>
       <c r="AL46" t="inlineStr"/>
     </row>
@@ -6960,15 +6956,15 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O47" t="n">
-        <v>0.524</v>
+        <v>2</v>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -6981,10 +6977,10 @@
         <v>46072</v>
       </c>
       <c r="T47" t="n">
-        <v>3125000</v>
+        <v>50000</v>
       </c>
       <c r="U47" t="n">
-        <v>1637500</v>
+        <v>100000</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -7013,12 +7009,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7102,7 +7098,7 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -7122,7 +7118,7 @@
         <v>50000</v>
       </c>
       <c r="U48" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -7151,12 +7147,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7236,15 +7232,15 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -7257,10 +7253,10 @@
         <v>46072</v>
       </c>
       <c r="T49" t="n">
-        <v>50000</v>
+        <v>55500</v>
       </c>
       <c r="U49" t="n">
-        <v>100000</v>
+        <v>55500</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -7289,12 +7285,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7374,31 +7370,31 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q50" t="n">
         <v>100</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T50" t="n">
-        <v>50000</v>
+        <v>75000</v>
       </c>
       <c r="U50" t="n">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -7427,12 +7423,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7512,7 +7508,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="O51" t="n">
@@ -7520,7 +7516,7 @@
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -7533,10 +7529,10 @@
         <v>46072</v>
       </c>
       <c r="T51" t="n">
-        <v>55500</v>
+        <v>293750</v>
       </c>
       <c r="U51" t="n">
-        <v>55500</v>
+        <v>293750</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -7565,12 +7561,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7650,7 +7646,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O52" t="n">
@@ -7658,23 +7654,23 @@
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q52" t="n">
         <v>100</v>
       </c>
       <c r="R52" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="S52" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="T52" t="n">
-        <v>75000</v>
+        <v>400000</v>
       </c>
       <c r="U52" t="n">
-        <v>75000</v>
+        <v>400000</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -7703,12 +7699,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Batu Pecah 1-2</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7788,15 +7784,15 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -7809,10 +7805,10 @@
         <v>46072</v>
       </c>
       <c r="T53" t="n">
-        <v>293750</v>
+        <v>120000</v>
       </c>
       <c r="U53" t="n">
-        <v>293750</v>
+        <v>1440000</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -7841,12 +7837,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7926,15 +7922,15 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q54" t="n">
@@ -7947,10 +7943,10 @@
         <v>46072</v>
       </c>
       <c r="T54" t="n">
-        <v>400000</v>
+        <v>93750</v>
       </c>
       <c r="U54" t="n">
-        <v>400000</v>
+        <v>187500</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7979,12 +7975,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Batu Pecah 1-2</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8064,11 +8060,11 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -8085,10 +8081,10 @@
         <v>46072</v>
       </c>
       <c r="T55" t="n">
-        <v>120000</v>
+        <v>37500</v>
       </c>
       <c r="U55" t="n">
-        <v>1440000</v>
+        <v>75000</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -8117,12 +8113,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8202,11 +8198,11 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="O56" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P56" t="inlineStr">
         <is>
@@ -8223,10 +8219,10 @@
         <v>46072</v>
       </c>
       <c r="T56" t="n">
-        <v>93750</v>
+        <v>37500</v>
       </c>
       <c r="U56" t="n">
-        <v>187500</v>
+        <v>37500</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -8255,12 +8251,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8340,15 +8336,15 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q57" t="n">
@@ -8361,10 +8357,10 @@
         <v>46072</v>
       </c>
       <c r="T57" t="n">
-        <v>37500</v>
+        <v>31250</v>
       </c>
       <c r="U57" t="n">
-        <v>75000</v>
+        <v>1500000</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -8393,12 +8389,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8478,15 +8474,15 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q58" t="n">
@@ -8499,10 +8495,10 @@
         <v>46072</v>
       </c>
       <c r="T58" t="n">
-        <v>37500</v>
+        <v>31250</v>
       </c>
       <c r="U58" t="n">
-        <v>37500</v>
+        <v>625000</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -8531,12 +8527,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8616,15 +8612,15 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>48</v>
+        <v>0.2</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="Q59" t="n">
@@ -8637,10 +8633,10 @@
         <v>46072</v>
       </c>
       <c r="T59" t="n">
-        <v>31250</v>
+        <v>712500</v>
       </c>
       <c r="U59" t="n">
-        <v>1500000</v>
+        <v>142500</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8669,12 +8665,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8754,15 +8750,15 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>20</v>
+        <v>0.5</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q60" t="n">
@@ -8775,10 +8771,10 @@
         <v>46072</v>
       </c>
       <c r="T60" t="n">
-        <v>31250</v>
+        <v>50000</v>
       </c>
       <c r="U60" t="n">
-        <v>625000</v>
+        <v>25000</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -8807,12 +8803,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Paku 12 cm</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8892,31 +8888,31 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q61" t="n">
         <v>100</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T61" t="n">
-        <v>712500</v>
+        <v>50000</v>
       </c>
       <c r="U61" t="n">
-        <v>142500</v>
+        <v>25000</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -8945,12 +8941,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Paku Beton 10 cm</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -8986,11 +8982,11 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -9004,19 +9000,19 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4500011203</v>
+        <v>4500011579</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -9025,36 +9021,36 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q62" t="n">
         <v>100</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="T62" t="n">
-        <v>50000</v>
+        <v>575000</v>
       </c>
       <c r="U62" t="n">
-        <v>25000</v>
+        <v>661250</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -9083,12 +9079,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Paku 12 cm</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9104,7 +9100,7 @@
         </is>
       </c>
       <c r="AK62" t="n">
-        <v>1000025162</v>
+        <v>1000025742</v>
       </c>
       <c r="AL62" t="inlineStr"/>
     </row>
@@ -9124,11 +9120,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -9142,19 +9138,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4500011203</v>
+        <v>4500011580</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -9163,36 +9159,36 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O63" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q63" t="n">
         <v>100</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46275</v>
+        <v>46179</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>46275</v>
+        <v>46179</v>
       </c>
       <c r="T63" t="n">
-        <v>50000</v>
+        <v>1600000</v>
       </c>
       <c r="U63" t="n">
-        <v>25000</v>
+        <v>1600000</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -9221,12 +9217,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Paku Beton 10 cm</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9238,35 +9234,35 @@
       <c r="AI63" t="inlineStr"/>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK63" t="n">
-        <v>1000025162</v>
+        <v>1000025743</v>
       </c>
       <c r="AL63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>001/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -9280,19 +9276,19 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4500011579</v>
+        <v>4599910747</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="K64" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -9301,12 +9297,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>JASA MOBILISASI</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -9314,23 +9310,23 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q64" t="n">
         <v>100</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T64" t="n">
-        <v>575000</v>
+        <v>400000000</v>
       </c>
       <c r="U64" t="n">
-        <v>661250</v>
+        <v>400000000</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -9359,12 +9355,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9376,35 +9372,39 @@
       <c r="AI64" t="inlineStr"/>
       <c r="AJ64" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK64" t="n">
-        <v>1000025742</v>
-      </c>
-      <c r="AL64" t="inlineStr"/>
+        <v>1000024733</v>
+      </c>
+      <c r="AL64" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-020</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9418,19 +9418,19 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4500011580</v>
+        <v>4500010748</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -9439,36 +9439,36 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q65" t="n">
         <v>100</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T65" t="n">
-        <v>1600000</v>
+        <v>75538000</v>
       </c>
       <c r="U65" t="n">
-        <v>1600000</v>
+        <v>29459820</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -9497,12 +9497,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9514,13 +9514,17 @@
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK65" t="n">
-        <v>1000025743</v>
-      </c>
-      <c r="AL65" t="inlineStr"/>
+        <v>1000024201</v>
+      </c>
+      <c r="AL65" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9538,7 +9542,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/FLD/XII/2025</t>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E66" s="1" t="n">
@@ -9560,11 +9564,11 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4599910747</v>
+        <v>4500010749</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
@@ -9577,20 +9581,20 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>JASA MOBILISASI</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q66" t="n">
@@ -9603,10 +9607,10 @@
         <v>46022</v>
       </c>
       <c r="T66" t="n">
-        <v>400000000</v>
+        <v>62818000</v>
       </c>
       <c r="U66" t="n">
-        <v>400000000</v>
+        <v>24499020</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -9635,12 +9639,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9656,11 +9660,11 @@
         </is>
       </c>
       <c r="AK66" t="n">
-        <v>1000024733</v>
+        <v>1000024205</v>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-020</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -9680,7 +9684,7 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/FLD/XII/2025</t>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E67" s="1" t="n">
@@ -9702,11 +9706,11 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4500010748</v>
+        <v>4500010750</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
@@ -9724,7 +9728,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O67" t="n">
@@ -9745,10 +9749,10 @@
         <v>46022</v>
       </c>
       <c r="T67" t="n">
-        <v>75538000</v>
+        <v>78225000</v>
       </c>
       <c r="U67" t="n">
-        <v>29459820</v>
+        <v>30507750</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -9777,12 +9781,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9794,15 +9798,15 @@
       <c r="AI67" t="inlineStr"/>
       <c r="AJ67" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK67" t="n">
-        <v>1000024201</v>
+        <v>1000024200</v>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -9822,7 +9826,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/FLD/XII/2025</t>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E68" s="1" t="n">
@@ -9844,11 +9848,11 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4500010749</v>
+        <v>4500010746</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
@@ -9866,7 +9870,7 @@
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O68" t="n">
@@ -9887,10 +9891,10 @@
         <v>46022</v>
       </c>
       <c r="T68" t="n">
-        <v>62818000</v>
+        <v>189241000</v>
       </c>
       <c r="U68" t="n">
-        <v>24499020</v>
+        <v>73803990</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -9919,12 +9923,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -9940,11 +9944,11 @@
         </is>
       </c>
       <c r="AK68" t="n">
-        <v>1000024205</v>
+        <v>1000024199</v>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -9964,7 +9968,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/FLD/XII/2025</t>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E69" s="1" t="n">
@@ -9986,11 +9990,11 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4500010750</v>
+        <v>4500010745</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K69" s="1" t="n">
@@ -10008,7 +10012,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -10029,10 +10033,10 @@
         <v>46022</v>
       </c>
       <c r="T69" t="n">
-        <v>78225000</v>
+        <v>131224000</v>
       </c>
       <c r="U69" t="n">
-        <v>30507750</v>
+        <v>51177360</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -10061,12 +10065,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10082,11 +10086,11 @@
         </is>
       </c>
       <c r="AK69" t="n">
-        <v>1000024200</v>
+        <v>1000024198</v>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
@@ -10106,7 +10110,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/FLD/XII/2025</t>
+          <t>007/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E70" s="1" t="n">
@@ -10128,11 +10132,11 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4500010746</v>
+        <v>4500010745</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="K70" s="1" t="n">
@@ -10150,11 +10154,11 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O70" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P70" t="inlineStr">
         <is>
@@ -10165,16 +10169,16 @@
         <v>100</v>
       </c>
       <c r="R70" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S70" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T70" t="n">
-        <v>189241000</v>
+        <v>131224000</v>
       </c>
       <c r="U70" t="n">
-        <v>73803990</v>
+        <v>131224000</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -10203,12 +10207,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10224,11 +10228,11 @@
         </is>
       </c>
       <c r="AK70" t="n">
-        <v>1000024199</v>
+        <v>1000024508</v>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
@@ -10248,11 +10252,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/FLD/XII/2025</t>
+          <t>008/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -10270,11 +10274,11 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4500010745</v>
+        <v>4500010749</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K71" s="1" t="n">
@@ -10292,11 +10296,11 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P71" t="inlineStr">
         <is>
@@ -10307,16 +10311,16 @@
         <v>100</v>
       </c>
       <c r="R71" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S71" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T71" t="n">
-        <v>131224000</v>
+        <v>62818000</v>
       </c>
       <c r="U71" t="n">
-        <v>51177360</v>
+        <v>62818000</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -10345,12 +10349,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10366,11 +10370,11 @@
         </is>
       </c>
       <c r="AK71" t="n">
-        <v>1000024198</v>
+        <v>1000024511</v>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -10390,11 +10394,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/FLD/I/2026</t>
+          <t>009/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -10412,11 +10416,11 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4500010745</v>
+        <v>4500010746</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K72" s="1" t="n">
@@ -10434,7 +10438,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -10455,10 +10459,10 @@
         <v>46053</v>
       </c>
       <c r="T72" t="n">
-        <v>131224000</v>
+        <v>189241000</v>
       </c>
       <c r="U72" t="n">
-        <v>131224000</v>
+        <v>189241000</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -10487,12 +10491,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10508,11 +10512,11 @@
         </is>
       </c>
       <c r="AK72" t="n">
-        <v>1000024508</v>
+        <v>1000024510</v>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -10532,11 +10536,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/FLD/I/2026</t>
+          <t>010/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -10554,11 +10558,11 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4500010749</v>
+        <v>4500010748</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K73" s="1" t="n">
@@ -10576,7 +10580,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -10597,10 +10601,10 @@
         <v>46053</v>
       </c>
       <c r="T73" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="U73" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -10629,12 +10633,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10650,11 +10654,11 @@
         </is>
       </c>
       <c r="AK73" t="n">
-        <v>1000024511</v>
+        <v>1000024516</v>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -10674,7 +10678,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>009/BSS-JOB/FLD/I/2026</t>
+          <t>011/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E74" s="1" t="n">
@@ -10696,11 +10700,11 @@
         </is>
       </c>
       <c r="I74" t="n">
-        <v>4500010746</v>
+        <v>4500010750</v>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K74" s="1" t="n">
@@ -10718,7 +10722,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O74" t="n">
@@ -10739,10 +10743,10 @@
         <v>46053</v>
       </c>
       <c r="T74" t="n">
-        <v>189241000</v>
+        <v>78225000</v>
       </c>
       <c r="U74" t="n">
-        <v>189241000</v>
+        <v>78225000</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -10771,12 +10775,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10792,11 +10796,11 @@
         </is>
       </c>
       <c r="AK74" t="n">
-        <v>1000024510</v>
+        <v>1000024509</v>
       </c>
       <c r="AL74" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -10816,11 +10820,11 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/FLD/I/2026</t>
+          <t>012/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46022</v>
+        <v>46063</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10838,15 +10842,15 @@
         </is>
       </c>
       <c r="I75" t="n">
-        <v>4500010748</v>
+        <v>4500010980</v>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="K75" s="1" t="n">
-        <v>46011</v>
+        <v>46056</v>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -10855,36 +10859,36 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ON-CALL BASIS</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q75" t="n">
         <v>100</v>
       </c>
       <c r="R75" s="1" t="n">
-        <v>46023</v>
+        <v>46056</v>
       </c>
       <c r="S75" s="1" t="n">
-        <v>46053</v>
+        <v>46062</v>
       </c>
       <c r="T75" t="n">
-        <v>75538000</v>
+        <v>1936000</v>
       </c>
       <c r="U75" t="n">
-        <v>75538000</v>
+        <v>13552000</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -10913,12 +10917,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -10934,11 +10938,11 @@
         </is>
       </c>
       <c r="AK75" t="n">
-        <v>1000024516</v>
+        <v>1000024507</v>
       </c>
       <c r="AL75" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>7207250142-BSS-WO-2025-008</t>
         </is>
       </c>
     </row>
@@ -10958,11 +10962,11 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/FLD/I/2026</t>
+          <t>014/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10980,11 +10984,11 @@
         </is>
       </c>
       <c r="I76" t="n">
-        <v>4500010750</v>
+        <v>4500010749</v>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K76" s="1" t="n">
@@ -11002,7 +11006,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O76" t="n">
@@ -11017,16 +11021,16 @@
         <v>100</v>
       </c>
       <c r="R76" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S76" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T76" t="n">
-        <v>78225000</v>
+        <v>62818000</v>
       </c>
       <c r="U76" t="n">
-        <v>78225000</v>
+        <v>62818000</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -11055,12 +11059,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11076,11 +11080,11 @@
         </is>
       </c>
       <c r="AK76" t="n">
-        <v>1000024509</v>
+        <v>1000024711</v>
       </c>
       <c r="AL76" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -11100,11 +11104,11 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/FLD/I/2026</t>
+          <t>013/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46063</v>
+        <v>46081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -11122,15 +11126,15 @@
         </is>
       </c>
       <c r="I77" t="n">
-        <v>4500010980</v>
+        <v>4500010748</v>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K77" s="1" t="n">
-        <v>46056</v>
+        <v>46011</v>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -11139,36 +11143,36 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>ON-CALL BASIS</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q77" t="n">
         <v>100</v>
       </c>
       <c r="R77" s="1" t="n">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="S77" s="1" t="n">
-        <v>46062</v>
+        <v>46081</v>
       </c>
       <c r="T77" t="n">
-        <v>1936000</v>
+        <v>75538000</v>
       </c>
       <c r="U77" t="n">
-        <v>13552000</v>
+        <v>75538000</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -11197,12 +11201,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11218,11 +11222,11 @@
         </is>
       </c>
       <c r="AK77" t="n">
-        <v>1000024507</v>
+        <v>1000024712</v>
       </c>
       <c r="AL77" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2025-008</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -11242,7 +11246,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/FLD/II/2026</t>
+          <t>015/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E78" s="1" t="n">
@@ -11264,11 +11268,11 @@
         </is>
       </c>
       <c r="I78" t="n">
-        <v>4500010749</v>
+        <v>4500010750</v>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K78" s="1" t="n">
@@ -11286,7 +11290,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -11307,10 +11311,10 @@
         <v>46081</v>
       </c>
       <c r="T78" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="U78" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -11339,12 +11343,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11360,11 +11364,11 @@
         </is>
       </c>
       <c r="AK78" t="n">
-        <v>1000024711</v>
+        <v>1000024709</v>
       </c>
       <c r="AL78" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -11384,7 +11388,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/FLD/II/2026</t>
+          <t>016/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E79" s="1" t="n">
@@ -11406,11 +11410,11 @@
         </is>
       </c>
       <c r="I79" t="n">
-        <v>4500010748</v>
+        <v>4500010746</v>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K79" s="1" t="n">
@@ -11428,7 +11432,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -11449,10 +11453,10 @@
         <v>46081</v>
       </c>
       <c r="T79" t="n">
-        <v>75538000</v>
+        <v>189241000</v>
       </c>
       <c r="U79" t="n">
-        <v>75538000</v>
+        <v>189241000</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -11481,12 +11485,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11502,11 +11506,11 @@
         </is>
       </c>
       <c r="AK79" t="n">
-        <v>1000024712</v>
+        <v>1000024708</v>
       </c>
       <c r="AL79" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -11526,7 +11530,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/FLD/II/2026</t>
+          <t>017/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E80" s="1" t="n">
@@ -11548,11 +11552,11 @@
         </is>
       </c>
       <c r="I80" t="n">
-        <v>4500010750</v>
+        <v>4500010745</v>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K80" s="1" t="n">
@@ -11570,7 +11574,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O80" t="n">
@@ -11591,10 +11595,10 @@
         <v>46081</v>
       </c>
       <c r="T80" t="n">
-        <v>78225000</v>
+        <v>131224000</v>
       </c>
       <c r="U80" t="n">
-        <v>78225000</v>
+        <v>131224000</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -11623,12 +11627,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11644,35 +11648,37 @@
         </is>
       </c>
       <c r="AK80" t="n">
-        <v>1000024709</v>
+        <v>1000024727</v>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="n">
-        <v>46081</v>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -11686,19 +11692,23 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I81" t="n">
-        <v>4500010746</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K81" s="1" t="n">
-        <v>46011</v>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
@@ -11707,12 +11717,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O81" t="n">
@@ -11720,23 +11730,27 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q81" t="n">
         <v>100</v>
       </c>
-      <c r="R81" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S81" s="1" t="n">
-        <v>46081</v>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T81" t="n">
-        <v>189241000</v>
+        <v>7654600</v>
       </c>
       <c r="U81" t="n">
-        <v>189241000</v>
+        <v>8802790</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -11765,12 +11779,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -11782,39 +11796,39 @@
       <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK81" t="n">
-        <v>1000024708</v>
-      </c>
-      <c r="AL81" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
-        </is>
-      </c>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="n">
-        <v>46081</v>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -11828,19 +11842,23 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I82" t="n">
-        <v>4500010745</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K82" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
@@ -11849,36 +11867,40 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q82" t="n">
         <v>100</v>
       </c>
-      <c r="R82" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S82" s="1" t="n">
-        <v>46081</v>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="T82" t="n">
-        <v>131224000</v>
+        <v>65000</v>
       </c>
       <c r="U82" t="n">
-        <v>131224000</v>
+        <v>167570000</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -11907,12 +11929,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -11927,14 +11949,12 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK82" t="n">
-        <v>1000024727</v>
-      </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
-        </is>
-      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11952,12 +11972,12 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -11977,17 +11997,17 @@
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -11997,16 +12017,16 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>1</v>
+        <v>1157</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -12018,19 +12038,19 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T83" t="n">
-        <v>7654600</v>
+        <v>33000</v>
       </c>
       <c r="U83" t="n">
-        <v>8802790</v>
+        <v>38181000</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -12059,12 +12079,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12076,7 +12096,7 @@
       <c r="AI83" t="inlineStr"/>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
@@ -12102,7 +12122,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12132,7 +12152,7 @@
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
@@ -12147,20 +12167,20 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>2578</v>
+        <v>22</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q84" t="n">
@@ -12177,10 +12197,10 @@
         </is>
       </c>
       <c r="T84" t="n">
-        <v>65000</v>
+        <v>750000</v>
       </c>
       <c r="U84" t="n">
-        <v>167570000</v>
+        <v>16500000</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -12209,12 +12229,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12252,12 +12272,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -12282,7 +12302,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -12297,20 +12317,20 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>1157</v>
+        <v>1</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -12318,19 +12338,19 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T85" t="n">
-        <v>33000</v>
+        <v>750000</v>
       </c>
       <c r="U85" t="n">
-        <v>38181000</v>
+        <v>750000</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -12359,12 +12379,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12402,12 +12422,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -12432,7 +12452,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -12447,20 +12467,20 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q86" t="n">
@@ -12468,19 +12488,19 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T86" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="U86" t="n">
-        <v>16500000</v>
+        <v>1600000</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -12509,12 +12529,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12552,12 +12572,12 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -12582,7 +12602,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -12602,11 +12622,11 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -12618,19 +12638,19 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T87" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="U87" t="n">
-        <v>750000</v>
+        <v>12000000</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -12659,12 +12679,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12676,7 +12696,7 @@
       <c r="AI87" t="inlineStr"/>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -12684,7 +12704,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL87" t="inlineStr"/>
+      <c r="AL87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12702,12 +12726,12 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -12732,7 +12756,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -12747,16 +12771,16 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -12768,19 +12792,19 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T88" t="n">
-        <v>1600000</v>
+        <v>500000</v>
       </c>
       <c r="U88" t="n">
-        <v>1600000</v>
+        <v>12000000</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -12809,12 +12833,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -12826,7 +12850,7 @@
       <c r="AI88" t="inlineStr"/>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -12834,7 +12858,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL88" t="inlineStr"/>
+      <c r="AL88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12959,12 +12987,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13006,7 +13034,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -13056,15 +13084,15 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q90" t="n">
@@ -13077,14 +13105,14 @@
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="T90" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="U90" t="n">
-        <v>12000000</v>
+        <v>9750000</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -13113,12 +13141,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13130,7 +13158,7 @@
       <c r="AI90" t="inlineStr"/>
       <c r="AJ90" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK90" t="inlineStr">
@@ -13138,11 +13166,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13160,7 +13184,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -13210,15 +13234,15 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q91" t="n">
@@ -13226,7 +13250,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -13235,10 +13259,10 @@
         </is>
       </c>
       <c r="T91" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="U91" t="n">
-        <v>12000000</v>
+        <v>6750000</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -13267,12 +13291,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13284,7 +13308,7 @@
       <c r="AI91" t="inlineStr"/>
       <c r="AJ91" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK91" t="inlineStr">
@@ -13292,11 +13316,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL91" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -13368,7 +13388,7 @@
         </is>
       </c>
       <c r="O92" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -13385,14 +13405,14 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T92" t="n">
         <v>750000</v>
       </c>
       <c r="U92" t="n">
-        <v>9750000</v>
+        <v>12750000</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -13421,12 +13441,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13514,11 +13534,11 @@
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -13530,7 +13550,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -13539,10 +13559,10 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U93" t="n">
-        <v>6750000</v>
+        <v>14300000</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -13571,12 +13591,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13664,11 +13684,11 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -13689,10 +13709,10 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U94" t="n">
-        <v>12750000</v>
+        <v>13650000</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -13721,12 +13741,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13814,11 +13834,11 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -13830,7 +13850,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -13839,10 +13859,10 @@
         </is>
       </c>
       <c r="T95" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="U95" t="n">
-        <v>14300000</v>
+        <v>13800000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -13871,12 +13891,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -13964,11 +13984,11 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -13980,7 +14000,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -13989,10 +14009,10 @@
         </is>
       </c>
       <c r="T96" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="U96" t="n">
-        <v>13650000</v>
+        <v>13800000</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -14021,12 +14041,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14064,7 +14084,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -14114,15 +14134,15 @@
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q97" t="n">
@@ -14139,10 +14159,10 @@
         </is>
       </c>
       <c r="T97" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="U97" t="n">
-        <v>13800000</v>
+        <v>10500000</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -14171,12 +14191,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14196,7 +14216,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -14214,7 +14238,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -14244,7 +14268,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -14259,20 +14283,20 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>23</v>
+        <v>0.48</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -14289,10 +14313,10 @@
         </is>
       </c>
       <c r="T98" t="n">
-        <v>600000</v>
+        <v>25000000</v>
       </c>
       <c r="U98" t="n">
-        <v>13800000</v>
+        <v>12000000</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -14321,12 +14345,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14364,7 +14388,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>024A/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -14394,7 +14418,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -14409,20 +14433,20 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>21</v>
+        <v>0.48</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q99" t="n">
@@ -14439,10 +14463,10 @@
         </is>
       </c>
       <c r="T99" t="n">
-        <v>500000</v>
+        <v>17500000</v>
       </c>
       <c r="U99" t="n">
-        <v>10500000</v>
+        <v>8400000</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -14471,12 +14495,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14496,11 +14520,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL99" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -14563,16 +14583,16 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -14593,10 +14613,10 @@
         </is>
       </c>
       <c r="T100" t="n">
-        <v>25000000</v>
+        <v>60000000</v>
       </c>
       <c r="U100" t="n">
-        <v>12000000</v>
+        <v>44400000</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -14625,12 +14645,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14713,16 +14733,16 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
@@ -14743,10 +14763,10 @@
         </is>
       </c>
       <c r="T101" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="U101" t="n">
-        <v>8400000</v>
+        <v>44400000</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -14775,12 +14795,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14868,7 +14888,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -14893,10 +14913,10 @@
         </is>
       </c>
       <c r="T102" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="U102" t="n">
-        <v>44400000</v>
+        <v>11100000</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -14925,12 +14945,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15018,7 +15038,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -15043,10 +15063,10 @@
         </is>
       </c>
       <c r="T103" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="U103" t="n">
-        <v>44400000</v>
+        <v>11100000</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -15075,12 +15095,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15118,7 +15138,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -15148,7 +15168,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -15163,20 +15183,20 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -15184,7 +15204,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -15193,10 +15213,10 @@
         </is>
       </c>
       <c r="T104" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="U104" t="n">
-        <v>11100000</v>
+        <v>40000000</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -15225,12 +15245,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15268,7 +15288,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -15298,7 +15318,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -15313,20 +15333,20 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>0.74</v>
+        <v>15</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q105" t="n">
@@ -15334,19 +15354,19 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="T105" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="U105" t="n">
-        <v>11100000</v>
+        <v>24000000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -15375,12 +15395,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15525,12 +15545,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15622,7 +15642,7 @@
         </is>
       </c>
       <c r="O107" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -15634,19 +15654,19 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T107" t="n">
         <v>1600000</v>
       </c>
       <c r="U107" t="n">
-        <v>24000000</v>
+        <v>6400000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15675,12 +15695,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15768,7 +15788,7 @@
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -15825,12 +15845,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -15918,11 +15938,11 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
@@ -15934,19 +15954,19 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T109" t="n">
         <v>1600000</v>
       </c>
       <c r="U109" t="n">
-        <v>6400000</v>
+        <v>35200000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -15975,12 +15995,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16018,7 +16038,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -16048,7 +16068,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -16063,16 +16083,16 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
@@ -16084,19 +16104,19 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T110" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U110" t="n">
-        <v>40000000</v>
+        <v>59500000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -16125,12 +16145,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16168,7 +16188,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -16198,7 +16218,7 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -16213,16 +16233,16 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -16234,7 +16254,7 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
@@ -16243,10 +16263,10 @@
         </is>
       </c>
       <c r="T111" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U111" t="n">
-        <v>35200000</v>
+        <v>76500000</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -16275,12 +16295,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16303,10 +16323,8 @@
       <c r="AL111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A112" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B112" t="inlineStr">
         <is>
@@ -16370,11 +16388,11 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -16386,19 +16404,19 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T112" t="n">
-        <v>8500000</v>
+        <v>2750000</v>
       </c>
       <c r="U112" t="n">
-        <v>59500000</v>
+        <v>57750000</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -16427,12 +16445,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16472,7 +16490,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -16497,17 +16515,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -16517,20 +16535,20 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>9</v>
+        <v>1800</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q113" t="n">
@@ -16538,7 +16556,7 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
@@ -16547,10 +16565,10 @@
         </is>
       </c>
       <c r="T113" t="n">
-        <v>8500000</v>
+        <v>7500</v>
       </c>
       <c r="U113" t="n">
-        <v>76500000</v>
+        <v>12150000</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -16579,12 +16597,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16596,7 +16614,7 @@
       <c r="AI113" t="inlineStr"/>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -16624,7 +16642,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -16649,17 +16667,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -16669,20 +16687,20 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q114" t="n">
@@ -16690,7 +16708,7 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
@@ -16699,10 +16717,10 @@
         </is>
       </c>
       <c r="T114" t="n">
-        <v>2750000</v>
+        <v>53300</v>
       </c>
       <c r="U114" t="n">
-        <v>57750000</v>
+        <v>863460</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -16731,12 +16749,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-09-20 11:32:33</t>
+          <t>2026-09-20 13:11:24</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16748,7 +16766,7 @@
       <c r="AI114" t="inlineStr"/>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL114"/>
+  <dimension ref="A1:AL118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5518,11 +5518,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46265</v>
+        <v>46140</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5540,15 +5540,15 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>0</v>
+        <v>4500011236</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46241</v>
+        <v>46071</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -5557,36 +5557,36 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>250</v>
+        <v>1</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q37" t="n">
         <v>100</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>46242</v>
+        <v>46140</v>
       </c>
       <c r="T37" t="n">
-        <v>25000</v>
+        <v>773919900</v>
       </c>
       <c r="U37" t="n">
-        <v>6250000</v>
+        <v>890007885</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5615,12 +5615,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5632,13 +5632,11 @@
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
-      <c r="AK37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK37" t="n">
+        <v>1000025165</v>
       </c>
       <c r="AL37" t="inlineStr"/>
     </row>
@@ -5658,11 +5656,11 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -5680,15 +5678,15 @@
         </is>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K38" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -5702,31 +5700,31 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>200</v>
+        <v>0.524</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q38" t="n">
         <v>100</v>
       </c>
       <c r="R38" s="1" t="n">
-        <v>46257</v>
+        <v>46072</v>
       </c>
       <c r="S38" s="1" t="n">
-        <v>46257</v>
+        <v>46072</v>
       </c>
       <c r="T38" t="n">
-        <v>25000</v>
+        <v>3125000</v>
       </c>
       <c r="U38" t="n">
-        <v>5000000</v>
+        <v>1637500</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -5755,12 +5753,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5775,10 +5773,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK38" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK38" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL38" t="inlineStr"/>
     </row>
@@ -5798,11 +5794,11 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -5820,15 +5816,15 @@
         </is>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K39" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -5842,31 +5838,31 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>50</v>
+        <v>4</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q39" t="n">
         <v>100</v>
       </c>
       <c r="R39" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S39" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T39" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="U39" t="n">
-        <v>1250000</v>
+        <v>200000</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -5895,12 +5891,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -5915,10 +5911,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK39" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK39" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL39" t="inlineStr"/>
     </row>
@@ -5938,11 +5932,11 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5960,15 +5954,15 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K40" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -5982,31 +5976,31 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q40" t="n">
         <v>100</v>
       </c>
       <c r="R40" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S40" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T40" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="U40" t="n">
-        <v>1250000</v>
+        <v>100000</v>
       </c>
       <c r="V40" t="inlineStr">
         <is>
@@ -6035,12 +6029,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6055,10 +6049,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK40" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL40" t="inlineStr"/>
     </row>
@@ -6078,11 +6070,11 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -6100,15 +6092,15 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K41" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -6122,31 +6114,31 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>100</v>
       </c>
       <c r="R41" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S41" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T41" t="n">
-        <v>25000</v>
+        <v>50000</v>
       </c>
       <c r="U41" t="n">
-        <v>1250000</v>
+        <v>100000</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -6175,12 +6167,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6195,10 +6187,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK41" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK41" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL41" t="inlineStr"/>
     </row>
@@ -6218,11 +6208,11 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -6240,15 +6230,15 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K42" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -6262,31 +6252,31 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="O42" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q42" t="n">
         <v>100</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>46242</v>
+        <v>46072</v>
       </c>
       <c r="T42" t="n">
-        <v>25000</v>
+        <v>55500</v>
       </c>
       <c r="U42" t="n">
-        <v>1250000</v>
+        <v>55500</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -6315,12 +6305,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6335,10 +6325,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK42" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK42" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL42" t="inlineStr"/>
     </row>
@@ -6358,11 +6346,11 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46265</v>
+        <v>46072</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -6380,15 +6368,15 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>0</v>
+        <v>4500011203</v>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K43" s="1" t="n">
-        <v>46241</v>
+        <v>46072</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -6402,31 +6390,31 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="O43" t="n">
-        <v>115</v>
+        <v>1</v>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q43" t="n">
         <v>100</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>46242</v>
+        <v>46275</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>46257</v>
+        <v>46275</v>
       </c>
       <c r="T43" t="n">
-        <v>25000</v>
+        <v>75000</v>
       </c>
       <c r="U43" t="n">
-        <v>2875000</v>
+        <v>75000</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6455,12 +6443,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6475,10 +6463,8 @@
           <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
-      <c r="AK43" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="AK43" t="n">
+        <v>1000025162</v>
       </c>
       <c r="AL43" t="inlineStr"/>
     </row>
@@ -6498,11 +6484,11 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -6520,15 +6506,15 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>4500011236</v>
+        <v>4500011203</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -6537,12 +6523,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -6550,23 +6536,23 @@
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q44" t="n">
         <v>100</v>
       </c>
       <c r="R44" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="S44" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="T44" t="n">
-        <v>773919900</v>
+        <v>293750</v>
       </c>
       <c r="U44" t="n">
-        <v>890007885</v>
+        <v>293750</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6595,12 +6581,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6612,11 +6598,11 @@
       <c r="AI44" t="inlineStr"/>
       <c r="AJ44" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK44" t="n">
-        <v>1000025165</v>
+        <v>1000025162</v>
       </c>
       <c r="AL44" t="inlineStr"/>
     </row>
@@ -6680,11 +6666,11 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>0.524</v>
+        <v>1</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
@@ -6701,10 +6687,10 @@
         <v>46072</v>
       </c>
       <c r="T45" t="n">
-        <v>3125000</v>
+        <v>400000</v>
       </c>
       <c r="U45" t="n">
-        <v>1637500</v>
+        <v>400000</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -6733,12 +6719,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
+          <t>Batu Pecah 1-2</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6818,15 +6804,15 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q46" t="n">
@@ -6839,10 +6825,10 @@
         <v>46072</v>
       </c>
       <c r="T46" t="n">
-        <v>50000</v>
+        <v>120000</v>
       </c>
       <c r="U46" t="n">
-        <v>200000</v>
+        <v>1440000</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -6871,12 +6857,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -6956,7 +6942,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -6964,7 +6950,7 @@
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q47" t="n">
@@ -6977,10 +6963,10 @@
         <v>46072</v>
       </c>
       <c r="T47" t="n">
-        <v>50000</v>
+        <v>93750</v>
       </c>
       <c r="U47" t="n">
-        <v>100000</v>
+        <v>187500</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -7009,12 +6995,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7094,7 +7080,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="O48" t="n">
@@ -7102,7 +7088,7 @@
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q48" t="n">
@@ -7115,10 +7101,10 @@
         <v>46072</v>
       </c>
       <c r="T48" t="n">
-        <v>50000</v>
+        <v>37500</v>
       </c>
       <c r="U48" t="n">
-        <v>100000</v>
+        <v>75000</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -7147,12 +7133,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7232,7 +7218,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="O49" t="n">
@@ -7253,10 +7239,10 @@
         <v>46072</v>
       </c>
       <c r="T49" t="n">
-        <v>55500</v>
+        <v>37500</v>
       </c>
       <c r="U49" t="n">
-        <v>55500</v>
+        <v>37500</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -7285,12 +7271,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7370,31 +7356,31 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O50" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q50" t="n">
         <v>100</v>
       </c>
       <c r="R50" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="S50" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="T50" t="n">
-        <v>75000</v>
+        <v>31250</v>
       </c>
       <c r="U50" t="n">
-        <v>75000</v>
+        <v>1500000</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -7423,12 +7409,12 @@
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7508,15 +7494,15 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -7529,10 +7515,10 @@
         <v>46072</v>
       </c>
       <c r="T51" t="n">
-        <v>293750</v>
+        <v>31250</v>
       </c>
       <c r="U51" t="n">
-        <v>293750</v>
+        <v>625000</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -7561,12 +7547,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7646,15 +7632,15 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>1</v>
+        <v>0.2</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="Q52" t="n">
@@ -7667,10 +7653,10 @@
         <v>46072</v>
       </c>
       <c r="T52" t="n">
-        <v>400000</v>
+        <v>712500</v>
       </c>
       <c r="U52" t="n">
-        <v>400000</v>
+        <v>142500</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -7699,12 +7685,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Batu Pecah 1-2</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7784,15 +7770,15 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O53" t="n">
-        <v>12</v>
+        <v>0.5</v>
       </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q53" t="n">
@@ -7805,10 +7791,10 @@
         <v>46072</v>
       </c>
       <c r="T53" t="n">
-        <v>120000</v>
+        <v>50000</v>
       </c>
       <c r="U53" t="n">
-        <v>1440000</v>
+        <v>25000</v>
       </c>
       <c r="V53" t="inlineStr">
         <is>
@@ -7837,12 +7823,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Paku 12 cm</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7922,31 +7908,31 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>100</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T54" t="n">
-        <v>93750</v>
+        <v>50000</v>
       </c>
       <c r="U54" t="n">
-        <v>187500</v>
+        <v>25000</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7975,12 +7961,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Paku Beton 10 cm</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8016,11 +8002,11 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -8034,19 +8020,19 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4500011203</v>
+        <v>4500011579</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
@@ -8055,16 +8041,16 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Add Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O55" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P55" t="inlineStr">
         <is>
@@ -8075,16 +8061,16 @@
         <v>100</v>
       </c>
       <c r="R55" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="S55" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="T55" t="n">
-        <v>37500</v>
+        <v>575000</v>
       </c>
       <c r="U55" t="n">
-        <v>75000</v>
+        <v>661250</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -8113,12 +8099,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8134,7 +8120,7 @@
         </is>
       </c>
       <c r="AK55" t="n">
-        <v>1000025162</v>
+        <v>1000025742</v>
       </c>
       <c r="AL55" t="inlineStr"/>
     </row>
@@ -8154,11 +8140,11 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -8172,19 +8158,19 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4500011203</v>
+        <v>4500011580</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -8193,12 +8179,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -8206,23 +8192,23 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q56" t="n">
         <v>100</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="T56" t="n">
-        <v>37500</v>
+        <v>1600000</v>
       </c>
       <c r="U56" t="n">
-        <v>37500</v>
+        <v>1600000</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -8251,12 +8237,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8268,35 +8254,35 @@
       <c r="AI56" t="inlineStr"/>
       <c r="AJ56" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK56" t="n">
-        <v>1000025162</v>
+        <v>1000025743</v>
       </c>
       <c r="AL56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>001/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -8310,19 +8296,19 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4500011203</v>
+        <v>4599910747</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="K57" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
@@ -8331,36 +8317,36 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>JASA MOBILISASI</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q57" t="n">
         <v>100</v>
       </c>
       <c r="R57" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S57" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T57" t="n">
-        <v>31250</v>
+        <v>400000000</v>
       </c>
       <c r="U57" t="n">
-        <v>1500000</v>
+        <v>400000000</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -8389,12 +8375,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8406,35 +8392,39 @@
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK57" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL57" t="inlineStr"/>
+        <v>1000024733</v>
+      </c>
+      <c r="AL57" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-020</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -8448,19 +8438,19 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4500011203</v>
+        <v>4500010748</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K58" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
@@ -8469,36 +8459,36 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O58" t="n">
-        <v>20</v>
+        <v>0.39</v>
       </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q58" t="n">
         <v>100</v>
       </c>
       <c r="R58" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S58" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T58" t="n">
-        <v>31250</v>
+        <v>75538000</v>
       </c>
       <c r="U58" t="n">
-        <v>625000</v>
+        <v>29459820</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -8527,12 +8517,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8548,31 +8538,35 @@
         </is>
       </c>
       <c r="AK58" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL58" t="inlineStr"/>
+        <v>1000024201</v>
+      </c>
+      <c r="AL58" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-002</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -8586,19 +8580,19 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4500011203</v>
+        <v>4500010749</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K59" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
@@ -8607,36 +8601,36 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O59" t="n">
-        <v>0.2</v>
+        <v>0.39</v>
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q59" t="n">
         <v>100</v>
       </c>
       <c r="R59" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S59" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T59" t="n">
-        <v>712500</v>
+        <v>62818000</v>
       </c>
       <c r="U59" t="n">
-        <v>142500</v>
+        <v>24499020</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8665,12 +8659,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8682,35 +8676,39 @@
       <c r="AI59" t="inlineStr"/>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK59" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL59" t="inlineStr"/>
+        <v>1000024205</v>
+      </c>
+      <c r="AL59" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-003</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -8724,19 +8722,19 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4500011203</v>
+        <v>4500010750</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K60" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
@@ -8745,36 +8743,36 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O60" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q60" t="n">
         <v>100</v>
       </c>
       <c r="R60" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="S60" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="T60" t="n">
-        <v>50000</v>
+        <v>78225000</v>
       </c>
       <c r="U60" t="n">
-        <v>25000</v>
+        <v>30507750</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -8803,12 +8801,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Paku 12 cm</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8820,35 +8818,39 @@
       <c r="AI60" t="inlineStr"/>
       <c r="AJ60" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK60" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL60" t="inlineStr"/>
+        <v>1000024200</v>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-004</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46072</v>
+        <v>46022</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -8862,19 +8864,19 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4500011203</v>
+        <v>4500010746</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="K61" s="1" t="n">
-        <v>46072</v>
+        <v>46011</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
@@ -8883,36 +8885,36 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O61" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q61" t="n">
         <v>100</v>
       </c>
       <c r="R61" s="1" t="n">
-        <v>46275</v>
+        <v>46011</v>
       </c>
       <c r="S61" s="1" t="n">
-        <v>46275</v>
+        <v>46022</v>
       </c>
       <c r="T61" t="n">
-        <v>50000</v>
+        <v>189241000</v>
       </c>
       <c r="U61" t="n">
-        <v>25000</v>
+        <v>73803990</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -8941,12 +8943,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Paku Beton 10 cm</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -8958,35 +8960,39 @@
       <c r="AI61" t="inlineStr"/>
       <c r="AJ61" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK61" t="n">
-        <v>1000025162</v>
-      </c>
-      <c r="AL61" t="inlineStr"/>
+        <v>1000024199</v>
+      </c>
+      <c r="AL61" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-005</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -9000,19 +9006,19 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I62" t="n">
-        <v>4500011579</v>
+        <v>4500010745</v>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K62" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L62" t="inlineStr">
         <is>
@@ -9021,36 +9027,36 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q62" t="n">
         <v>100</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T62" t="n">
-        <v>575000</v>
+        <v>131224000</v>
       </c>
       <c r="U62" t="n">
-        <v>661250</v>
+        <v>51177360</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -9079,12 +9085,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9096,35 +9102,39 @@
       <c r="AI62" t="inlineStr"/>
       <c r="AJ62" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK62" t="n">
-        <v>1000025742</v>
-      </c>
-      <c r="AL62" t="inlineStr"/>
+        <v>1000024198</v>
+      </c>
+      <c r="AL62" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>007/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -9138,19 +9148,19 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4500011580</v>
+        <v>4500010745</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="K63" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
@@ -9159,12 +9169,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -9172,23 +9182,23 @@
       </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q63" t="n">
         <v>100</v>
       </c>
       <c r="R63" s="1" t="n">
-        <v>46179</v>
+        <v>46023</v>
       </c>
       <c r="S63" s="1" t="n">
-        <v>46179</v>
+        <v>46053</v>
       </c>
       <c r="T63" t="n">
-        <v>1600000</v>
+        <v>131224000</v>
       </c>
       <c r="U63" t="n">
-        <v>1600000</v>
+        <v>131224000</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -9217,12 +9227,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9238,9 +9248,13 @@
         </is>
       </c>
       <c r="AK63" t="n">
-        <v>1000025743</v>
-      </c>
-      <c r="AL63" t="inlineStr"/>
+        <v>1000024508</v>
+      </c>
+      <c r="AL63" t="inlineStr">
+        <is>
+          <t>S25051FLD-TOMORI-WO-006</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9258,11 +9272,11 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/FLD/XII/2025</t>
+          <t>008/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -9280,11 +9294,11 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4599910747</v>
+        <v>4500010749</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K64" s="1" t="n">
@@ -9297,12 +9311,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>JASA MOBILISASI</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -9310,23 +9324,23 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q64" t="n">
         <v>100</v>
       </c>
       <c r="R64" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S64" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T64" t="n">
-        <v>400000000</v>
+        <v>62818000</v>
       </c>
       <c r="U64" t="n">
-        <v>400000000</v>
+        <v>62818000</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -9355,12 +9369,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9376,11 +9390,11 @@
         </is>
       </c>
       <c r="AK64" t="n">
-        <v>1000024733</v>
+        <v>1000024511</v>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-020</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -9400,11 +9414,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/FLD/XII/2025</t>
+          <t>009/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9422,11 +9436,11 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4500010748</v>
+        <v>4500010746</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
@@ -9444,11 +9458,11 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P65" t="inlineStr">
         <is>
@@ -9459,16 +9473,16 @@
         <v>100</v>
       </c>
       <c r="R65" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S65" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T65" t="n">
-        <v>75538000</v>
+        <v>189241000</v>
       </c>
       <c r="U65" t="n">
-        <v>29459820</v>
+        <v>189241000</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -9497,12 +9511,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9514,15 +9528,15 @@
       <c r="AI65" t="inlineStr"/>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK65" t="n">
-        <v>1000024201</v>
+        <v>1000024510</v>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -9542,7 +9556,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/FLD/XII/2025</t>
+          <t>010/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E66" s="1" t="n">
@@ -9564,11 +9578,11 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4500010749</v>
+        <v>4500010748</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
@@ -9586,11 +9600,11 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P66" t="inlineStr">
         <is>
@@ -9601,16 +9615,16 @@
         <v>100</v>
       </c>
       <c r="R66" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S66" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T66" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="U66" t="n">
-        <v>24499020</v>
+        <v>75538000</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -9639,12 +9653,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9660,11 +9674,11 @@
         </is>
       </c>
       <c r="AK66" t="n">
-        <v>1000024205</v>
+        <v>1000024516</v>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -9684,11 +9698,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/FLD/XII/2025</t>
+          <t>011/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9710,7 +9724,7 @@
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
@@ -9732,7 +9746,7 @@
         </is>
       </c>
       <c r="O67" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
@@ -9743,16 +9757,16 @@
         <v>100</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S67" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T67" t="n">
         <v>78225000</v>
       </c>
       <c r="U67" t="n">
-        <v>30507750</v>
+        <v>78225000</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -9781,12 +9795,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9802,7 +9816,7 @@
         </is>
       </c>
       <c r="AK67" t="n">
-        <v>1000024200</v>
+        <v>1000024509</v>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
@@ -9826,11 +9840,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/FLD/XII/2025</t>
+          <t>012/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46022</v>
+        <v>46063</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9848,15 +9862,15 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4500010746</v>
+        <v>4500010980</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46011</v>
+        <v>46056</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -9865,36 +9879,36 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ON-CALL BASIS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>0.39</v>
+        <v>7</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q68" t="n">
         <v>100</v>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46011</v>
+        <v>46056</v>
       </c>
       <c r="S68" s="1" t="n">
-        <v>46022</v>
+        <v>46062</v>
       </c>
       <c r="T68" t="n">
-        <v>189241000</v>
+        <v>1936000</v>
       </c>
       <c r="U68" t="n">
-        <v>73803990</v>
+        <v>13552000</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -9923,12 +9937,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -9944,11 +9958,11 @@
         </is>
       </c>
       <c r="AK68" t="n">
-        <v>1000024199</v>
+        <v>1000024507</v>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>7207250142-BSS-WO-2025-008</t>
         </is>
       </c>
     </row>
@@ -9968,11 +9982,11 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/FLD/XII/2025</t>
+          <t>014/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -9990,11 +10004,11 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4500010745</v>
+        <v>4500010749</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K69" s="1" t="n">
@@ -10012,11 +10026,11 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O69" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P69" t="inlineStr">
         <is>
@@ -10027,16 +10041,16 @@
         <v>100</v>
       </c>
       <c r="R69" s="1" t="n">
-        <v>46011</v>
+        <v>46054</v>
       </c>
       <c r="S69" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="T69" t="n">
-        <v>131224000</v>
+        <v>62818000</v>
       </c>
       <c r="U69" t="n">
-        <v>51177360</v>
+        <v>62818000</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -10065,12 +10079,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10086,11 +10100,11 @@
         </is>
       </c>
       <c r="AK69" t="n">
-        <v>1000024198</v>
+        <v>1000024711</v>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -10110,11 +10124,11 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/FLD/I/2026</t>
+          <t>013/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -10132,11 +10146,11 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4500010745</v>
+        <v>4500010748</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K70" s="1" t="n">
@@ -10154,7 +10168,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -10169,16 +10183,16 @@
         <v>100</v>
       </c>
       <c r="R70" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S70" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T70" t="n">
-        <v>131224000</v>
+        <v>75538000</v>
       </c>
       <c r="U70" t="n">
-        <v>131224000</v>
+        <v>75538000</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -10207,12 +10221,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10228,11 +10242,11 @@
         </is>
       </c>
       <c r="AK70" t="n">
-        <v>1000024508</v>
+        <v>1000024712</v>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -10252,11 +10266,11 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/FLD/I/2026</t>
+          <t>015/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -10274,11 +10288,11 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4500010749</v>
+        <v>4500010750</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K71" s="1" t="n">
@@ -10296,7 +10310,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -10311,16 +10325,16 @@
         <v>100</v>
       </c>
       <c r="R71" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S71" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T71" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="U71" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -10349,12 +10363,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10370,11 +10384,11 @@
         </is>
       </c>
       <c r="AK71" t="n">
-        <v>1000024511</v>
+        <v>1000024709</v>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -10394,11 +10408,11 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>009/BSS-JOB/FLD/I/2026</t>
+          <t>016/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -10420,7 +10434,7 @@
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K72" s="1" t="n">
@@ -10453,10 +10467,10 @@
         <v>100</v>
       </c>
       <c r="R72" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S72" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T72" t="n">
         <v>189241000</v>
@@ -10491,12 +10505,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10512,7 +10526,7 @@
         </is>
       </c>
       <c r="AK72" t="n">
-        <v>1000024510</v>
+        <v>1000024708</v>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
@@ -10536,11 +10550,11 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/FLD/I/2026</t>
+          <t>017/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46022</v>
+        <v>46081</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -10558,11 +10572,11 @@
         </is>
       </c>
       <c r="I73" t="n">
-        <v>4500010748</v>
+        <v>4500010745</v>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K73" s="1" t="n">
@@ -10580,7 +10594,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O73" t="n">
@@ -10595,16 +10609,16 @@
         <v>100</v>
       </c>
       <c r="R73" s="1" t="n">
-        <v>46023</v>
+        <v>46054</v>
       </c>
       <c r="S73" s="1" t="n">
-        <v>46053</v>
+        <v>46081</v>
       </c>
       <c r="T73" t="n">
-        <v>75538000</v>
+        <v>131224000</v>
       </c>
       <c r="U73" t="n">
-        <v>75538000</v>
+        <v>131224000</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -10633,12 +10647,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10654,35 +10668,37 @@
         </is>
       </c>
       <c r="AK73" t="n">
-        <v>1000024516</v>
+        <v>1000024727</v>
       </c>
       <c r="AL73" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/FLD/I/2026</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="n">
-        <v>46053</v>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -10696,19 +10712,23 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I74" t="n">
-        <v>4500010750</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
-        </is>
-      </c>
-      <c r="K74" s="1" t="n">
-        <v>46011</v>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
@@ -10717,12 +10737,12 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O74" t="n">
@@ -10730,23 +10750,27 @@
       </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q74" t="n">
         <v>100</v>
       </c>
-      <c r="R74" s="1" t="n">
-        <v>46023</v>
-      </c>
-      <c r="S74" s="1" t="n">
-        <v>46053</v>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
       </c>
       <c r="T74" t="n">
-        <v>78225000</v>
+        <v>7654600</v>
       </c>
       <c r="U74" t="n">
-        <v>78225000</v>
+        <v>8802790</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -10775,12 +10799,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10792,39 +10816,39 @@
       <c r="AI74" t="inlineStr"/>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK74" t="n">
-        <v>1000024509</v>
-      </c>
-      <c r="AL74" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
-        </is>
-      </c>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/FLD/I/2026</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="n">
-        <v>46063</v>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -10838,19 +10862,23 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I75" t="n">
-        <v>4500010980</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
-        </is>
-      </c>
-      <c r="K75" s="1" t="n">
-        <v>46056</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
@@ -10859,36 +10887,40 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>ON-CALL BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>7</v>
+        <v>2578</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q75" t="n">
         <v>100</v>
       </c>
-      <c r="R75" s="1" t="n">
-        <v>46056</v>
-      </c>
-      <c r="S75" s="1" t="n">
-        <v>46062</v>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="T75" t="n">
-        <v>1936000</v>
+        <v>65000</v>
       </c>
       <c r="U75" t="n">
-        <v>13552000</v>
+        <v>167570000</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -10917,12 +10949,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -10937,36 +10969,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK75" t="n">
-        <v>1000024507</v>
-      </c>
-      <c r="AL75" t="inlineStr">
-        <is>
-          <t>7207250142-BSS-WO-2025-008</t>
-        </is>
-      </c>
+      <c r="AK75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E76" s="1" t="n">
-        <v>46081</v>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -10980,19 +11012,23 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I76" t="n">
-        <v>4500010749</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K76" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
@@ -11001,36 +11037,40 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>1</v>
+        <v>1157</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q76" t="n">
         <v>100</v>
       </c>
-      <c r="R76" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S76" s="1" t="n">
-        <v>46081</v>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="T76" t="n">
-        <v>62818000</v>
+        <v>33000</v>
       </c>
       <c r="U76" t="n">
-        <v>62818000</v>
+        <v>38181000</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -11059,12 +11099,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11079,36 +11119,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK76" t="n">
-        <v>1000024711</v>
-      </c>
-      <c r="AL76" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
-        </is>
-      </c>
+      <c r="AK76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="n">
-        <v>46081</v>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -11122,19 +11162,23 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I77" t="n">
-        <v>4500010748</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K77" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
@@ -11143,36 +11187,40 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O77" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q77" t="n">
         <v>100</v>
       </c>
-      <c r="R77" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S77" s="1" t="n">
-        <v>46081</v>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="T77" t="n">
-        <v>75538000</v>
+        <v>750000</v>
       </c>
       <c r="U77" t="n">
-        <v>75538000</v>
+        <v>16500000</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -11201,12 +11249,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11221,36 +11269,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK77" t="n">
-        <v>1000024712</v>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
-        </is>
-      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="n">
-        <v>46081</v>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -11264,19 +11312,23 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I78" t="n">
-        <v>4500010750</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K78" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L78" t="inlineStr">
         <is>
@@ -11285,12 +11337,12 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -11298,23 +11350,27 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q78" t="n">
         <v>100</v>
       </c>
-      <c r="R78" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S78" s="1" t="n">
-        <v>46081</v>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
       </c>
       <c r="T78" t="n">
-        <v>78225000</v>
+        <v>750000</v>
       </c>
       <c r="U78" t="n">
-        <v>78225000</v>
+        <v>750000</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -11343,12 +11399,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11363,36 +11419,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK78" t="n">
-        <v>1000024709</v>
-      </c>
-      <c r="AL78" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
-        </is>
-      </c>
+      <c r="AK78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="n">
-        <v>46081</v>
+          <t>022/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -11406,19 +11462,23 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>4500010746</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K79" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
@@ -11427,12 +11487,12 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O79" t="n">
@@ -11440,23 +11500,27 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q79" t="n">
         <v>100</v>
       </c>
-      <c r="R79" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S79" s="1" t="n">
-        <v>46081</v>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
       </c>
       <c r="T79" t="n">
-        <v>189241000</v>
+        <v>1600000</v>
       </c>
       <c r="U79" t="n">
-        <v>189241000</v>
+        <v>1600000</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -11485,12 +11549,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11505,36 +11569,36 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK79" t="n">
-        <v>1000024708</v>
-      </c>
-      <c r="AL79" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
-        </is>
-      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E80" s="1" t="n">
-        <v>46081</v>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -11548,19 +11612,23 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I80" t="n">
-        <v>4500010745</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
@@ -11569,36 +11637,40 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q80" t="n">
         <v>100</v>
       </c>
-      <c r="R80" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S80" s="1" t="n">
-        <v>46081</v>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="T80" t="n">
-        <v>131224000</v>
+        <v>500000</v>
       </c>
       <c r="U80" t="n">
-        <v>131224000</v>
+        <v>12000000</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -11627,12 +11699,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11644,15 +11716,17 @@
       <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK80" t="n">
-        <v>1000024727</v>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="AL80" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -11672,12 +11746,12 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -11697,17 +11771,17 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -11717,20 +11791,20 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -11738,19 +11812,19 @@
       </c>
       <c r="R81" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S81" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T81" t="n">
-        <v>7654600</v>
+        <v>500000</v>
       </c>
       <c r="U81" t="n">
-        <v>8802790</v>
+        <v>12000000</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -11779,12 +11853,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -11804,7 +11878,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL81" t="inlineStr"/>
+      <c r="AL81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11822,7 +11900,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -11852,7 +11930,7 @@
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
@@ -11867,20 +11945,20 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>2578</v>
+        <v>24</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -11897,10 +11975,10 @@
         </is>
       </c>
       <c r="T82" t="n">
-        <v>65000</v>
+        <v>500000</v>
       </c>
       <c r="U82" t="n">
-        <v>167570000</v>
+        <v>12000000</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -11929,12 +12007,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -11946,7 +12024,7 @@
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -11954,7 +12032,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL82" t="inlineStr"/>
+      <c r="AL82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11972,7 +12054,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -12002,7 +12084,7 @@
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
@@ -12017,20 +12099,20 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>1157</v>
+        <v>13</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q83" t="n">
@@ -12043,14 +12125,14 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="T83" t="n">
-        <v>33000</v>
+        <v>750000</v>
       </c>
       <c r="U83" t="n">
-        <v>38181000</v>
+        <v>9750000</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -12079,12 +12161,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12122,7 +12204,7 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -12172,11 +12254,11 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -12188,7 +12270,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -12200,7 +12282,7 @@
         <v>750000</v>
       </c>
       <c r="U84" t="n">
-        <v>16500000</v>
+        <v>6750000</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -12229,12 +12311,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12272,12 +12354,12 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -12302,7 +12384,7 @@
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -12322,15 +12404,15 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -12338,19 +12420,19 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T85" t="n">
         <v>750000</v>
       </c>
       <c r="U85" t="n">
-        <v>750000</v>
+        <v>12750000</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -12379,12 +12461,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12422,12 +12504,12 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -12452,7 +12534,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -12467,20 +12549,20 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q86" t="n">
@@ -12488,19 +12570,19 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T86" t="n">
-        <v>1600000</v>
+        <v>650000</v>
       </c>
       <c r="U86" t="n">
-        <v>1600000</v>
+        <v>14300000</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -12529,12 +12611,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12572,7 +12654,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -12622,15 +12704,15 @@
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q87" t="n">
@@ -12647,10 +12729,10 @@
         </is>
       </c>
       <c r="T87" t="n">
-        <v>500000</v>
+        <v>650000</v>
       </c>
       <c r="U87" t="n">
-        <v>12000000</v>
+        <v>13650000</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -12679,12 +12761,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12696,7 +12778,7 @@
       <c r="AI87" t="inlineStr"/>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
@@ -12704,11 +12786,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL87" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12726,7 +12804,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12776,15 +12854,15 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q88" t="n">
@@ -12792,7 +12870,7 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
@@ -12801,10 +12879,10 @@
         </is>
       </c>
       <c r="T88" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="U88" t="n">
-        <v>12000000</v>
+        <v>13800000</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -12833,12 +12911,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -12850,7 +12928,7 @@
       <c r="AI88" t="inlineStr"/>
       <c r="AJ88" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK88" t="inlineStr">
@@ -12858,11 +12936,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -12880,7 +12954,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12930,15 +13004,15 @@
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q89" t="n">
@@ -12946,7 +13020,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -12955,10 +13029,10 @@
         </is>
       </c>
       <c r="T89" t="n">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="U89" t="n">
-        <v>12000000</v>
+        <v>13800000</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -12987,12 +13061,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13004,7 +13078,7 @@
       <c r="AI89" t="inlineStr"/>
       <c r="AJ89" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK89" t="inlineStr">
@@ -13012,11 +13086,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL89" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -13034,7 +13104,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -13084,15 +13154,15 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q90" t="n">
@@ -13100,19 +13170,19 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T90" t="n">
-        <v>750000</v>
+        <v>500000</v>
       </c>
       <c r="U90" t="n">
-        <v>9750000</v>
+        <v>10500000</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -13141,12 +13211,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13166,7 +13236,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL90" t="inlineStr"/>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13184,7 +13258,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -13214,7 +13288,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -13229,20 +13303,20 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>9</v>
+        <v>0.48</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q91" t="n">
@@ -13250,7 +13324,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -13259,10 +13333,10 @@
         </is>
       </c>
       <c r="T91" t="n">
-        <v>750000</v>
+        <v>25000000</v>
       </c>
       <c r="U91" t="n">
-        <v>6750000</v>
+        <v>12000000</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -13291,12 +13365,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13334,7 +13408,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -13364,7 +13438,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -13379,20 +13453,20 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>17</v>
+        <v>0.48</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q92" t="n">
@@ -13400,7 +13474,7 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
@@ -13409,10 +13483,10 @@
         </is>
       </c>
       <c r="T92" t="n">
-        <v>750000</v>
+        <v>17500000</v>
       </c>
       <c r="U92" t="n">
-        <v>12750000</v>
+        <v>8400000</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -13441,12 +13515,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13484,7 +13558,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -13514,7 +13588,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -13529,20 +13603,20 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>22</v>
+        <v>0.74</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q93" t="n">
@@ -13550,7 +13624,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -13559,10 +13633,10 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>650000</v>
+        <v>60000000</v>
       </c>
       <c r="U93" t="n">
-        <v>14300000</v>
+        <v>44400000</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -13591,12 +13665,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13634,7 +13708,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -13664,7 +13738,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -13679,20 +13753,20 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>21</v>
+        <v>0.74</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q94" t="n">
@@ -13700,7 +13774,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -13709,10 +13783,10 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>650000</v>
+        <v>60000000</v>
       </c>
       <c r="U94" t="n">
-        <v>13650000</v>
+        <v>44400000</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -13741,12 +13815,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13784,7 +13858,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -13814,7 +13888,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -13829,20 +13903,20 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>23</v>
+        <v>0.74</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q95" t="n">
@@ -13859,10 +13933,10 @@
         </is>
       </c>
       <c r="T95" t="n">
-        <v>600000</v>
+        <v>15000000</v>
       </c>
       <c r="U95" t="n">
-        <v>13800000</v>
+        <v>11100000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -13891,12 +13965,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -13934,7 +14008,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -13964,7 +14038,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -13979,20 +14053,20 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>23</v>
+        <v>0.74</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q96" t="n">
@@ -14009,10 +14083,10 @@
         </is>
       </c>
       <c r="T96" t="n">
-        <v>600000</v>
+        <v>15000000</v>
       </c>
       <c r="U96" t="n">
-        <v>13800000</v>
+        <v>11100000</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -14041,12 +14115,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14084,7 +14158,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>024A/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -14114,7 +14188,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -14129,16 +14203,16 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -14150,7 +14224,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -14159,10 +14233,10 @@
         </is>
       </c>
       <c r="T97" t="n">
-        <v>500000</v>
+        <v>1600000</v>
       </c>
       <c r="U97" t="n">
-        <v>10500000</v>
+        <v>40000000</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -14191,12 +14265,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14216,11 +14290,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL97" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -14238,7 +14308,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -14268,7 +14338,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -14283,20 +14353,20 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>0.48</v>
+        <v>15</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -14304,19 +14374,19 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="T98" t="n">
-        <v>25000000</v>
+        <v>1600000</v>
       </c>
       <c r="U98" t="n">
-        <v>12000000</v>
+        <v>24000000</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -14345,12 +14415,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14388,7 +14458,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -14418,7 +14488,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -14433,20 +14503,20 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>0.48</v>
+        <v>25</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q99" t="n">
@@ -14454,7 +14524,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -14463,10 +14533,10 @@
         </is>
       </c>
       <c r="T99" t="n">
-        <v>17500000</v>
+        <v>1600000</v>
       </c>
       <c r="U99" t="n">
-        <v>8400000</v>
+        <v>40000000</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -14495,12 +14565,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14538,7 +14608,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -14568,7 +14638,7 @@
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -14583,20 +14653,20 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>0.74</v>
+        <v>4</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q100" t="n">
@@ -14604,19 +14674,19 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T100" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="U100" t="n">
-        <v>44400000</v>
+        <v>6400000</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -14645,12 +14715,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14688,7 +14758,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -14718,7 +14788,7 @@
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -14733,20 +14803,20 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q101" t="n">
@@ -14754,7 +14824,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -14763,10 +14833,10 @@
         </is>
       </c>
       <c r="T101" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="U101" t="n">
-        <v>44400000</v>
+        <v>40000000</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -14795,12 +14865,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14838,7 +14908,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -14868,7 +14938,7 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -14883,20 +14953,20 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q102" t="n">
@@ -14904,7 +14974,7 @@
       </c>
       <c r="R102" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S102" t="inlineStr">
@@ -14913,10 +14983,10 @@
         </is>
       </c>
       <c r="T102" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="U102" t="n">
-        <v>11100000</v>
+        <v>35200000</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -14945,12 +15015,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -14988,7 +15058,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -15018,7 +15088,7 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -15038,15 +15108,15 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>0.74</v>
+        <v>7</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q103" t="n">
@@ -15054,19 +15124,19 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T103" t="n">
-        <v>15000000</v>
+        <v>8500000</v>
       </c>
       <c r="U103" t="n">
-        <v>11100000</v>
+        <v>59500000</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -15095,12 +15165,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15138,7 +15208,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -15168,7 +15238,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -15183,16 +15253,16 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -15204,7 +15274,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -15213,10 +15283,10 @@
         </is>
       </c>
       <c r="T104" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U104" t="n">
-        <v>40000000</v>
+        <v>76500000</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -15245,12 +15315,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15288,7 +15358,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -15318,7 +15388,7 @@
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
@@ -15333,16 +15403,16 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -15354,19 +15424,19 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T105" t="n">
-        <v>1600000</v>
+        <v>2750000</v>
       </c>
       <c r="U105" t="n">
-        <v>24000000</v>
+        <v>57750000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -15395,12 +15465,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15438,7 +15508,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -15463,17 +15533,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -15483,20 +15553,20 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>25</v>
+        <v>1800</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q106" t="n">
@@ -15504,7 +15574,7 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
@@ -15513,10 +15583,10 @@
         </is>
       </c>
       <c r="T106" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="U106" t="n">
-        <v>40000000</v>
+        <v>12150000</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15545,12 +15615,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15562,7 +15632,7 @@
       <c r="AI106" t="inlineStr"/>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -15588,7 +15658,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -15613,17 +15683,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -15633,20 +15703,20 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -15654,19 +15724,19 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T107" t="n">
-        <v>1600000</v>
+        <v>53300</v>
       </c>
       <c r="U107" t="n">
-        <v>6400000</v>
+        <v>863460</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15695,12 +15765,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15712,7 +15782,7 @@
       <c r="AI107" t="inlineStr"/>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -15738,12 +15808,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -15768,7 +15838,9 @@
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
+Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -15783,20 +15855,20 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -15804,19 +15876,19 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T108" t="n">
-        <v>1600000</v>
+        <v>12500000</v>
       </c>
       <c r="U108" t="n">
-        <v>40000000</v>
+        <v>12500000</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -15845,12 +15917,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -15862,7 +15934,7 @@
       <c r="AI108" t="inlineStr"/>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -15870,7 +15942,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL108" t="inlineStr"/>
+      <c r="AL108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -15888,13 +15964,11 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>31 Aug 2026</t>
-        </is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E109" s="1" t="n">
+        <v>46264</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -15918,7 +15992,8 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
@@ -15933,20 +16008,20 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -15959,14 +16034,14 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="T109" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="U109" t="n">
-        <v>35200000</v>
+        <v>6000000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -15995,12 +16070,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t xml:space="preserve">Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026 </t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16020,7 +16095,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL109" t="inlineStr"/>
+      <c r="AL109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -16038,7 +16117,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -16068,7 +16147,7 @@
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
@@ -16083,20 +16162,20 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>7</v>
+        <v>316.8</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -16104,19 +16183,19 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T110" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="U110" t="n">
-        <v>59500000</v>
+        <v>7920000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -16145,12 +16224,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16170,7 +16249,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL110" t="inlineStr"/>
+      <c r="AL110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -16188,7 +16271,7 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -16213,17 +16296,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -16233,20 +16316,20 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>9</v>
+        <v>250</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q111" t="n">
@@ -16254,19 +16337,19 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T111" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="U111" t="n">
-        <v>76500000</v>
+        <v>6250000</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -16295,12 +16378,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16312,7 +16395,7 @@
       <c r="AI111" t="inlineStr"/>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -16338,7 +16421,7 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -16363,17 +16446,17 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -16383,20 +16466,20 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>21</v>
+        <v>200</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q112" t="n">
@@ -16404,19 +16487,19 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="T112" t="n">
-        <v>2750000</v>
+        <v>25000</v>
       </c>
       <c r="U112" t="n">
-        <v>57750000</v>
+        <v>5000000</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -16445,12 +16528,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16462,7 +16545,7 @@
       <c r="AI112" t="inlineStr"/>
       <c r="AJ112" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK112" t="inlineStr">
@@ -16473,10 +16556,8 @@
       <c r="AL112" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A113" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -16490,7 +16571,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -16515,12 +16596,12 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>45000000test</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -16535,20 +16616,20 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>1800</v>
+        <v>50</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q113" t="n">
@@ -16561,14 +16642,14 @@
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T113" t="n">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="U113" t="n">
-        <v>12150000</v>
+        <v>1250000</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -16597,12 +16678,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16625,10 +16706,8 @@
       <c r="AL113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A114" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -16642,7 +16721,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -16667,12 +16746,12 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>45000000test</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
@@ -16687,20 +16766,20 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q114" t="n">
@@ -16708,19 +16787,19 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T114" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U114" t="n">
-        <v>863460</v>
+        <v>1250000</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -16749,12 +16828,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-09-20 13:11:24</t>
+          <t>2026-09-21 12:59:45</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16776,6 +16855,612 @@
       </c>
       <c r="AL114" t="inlineStr"/>
     </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O115" t="n">
+        <v>50</v>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>100</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="T115" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U115" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X115" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:59:45</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr"/>
+      <c r="AD115" t="inlineStr"/>
+      <c r="AE115" t="inlineStr"/>
+      <c r="AF115" t="inlineStr"/>
+      <c r="AG115" t="inlineStr"/>
+      <c r="AH115" t="inlineStr"/>
+      <c r="AI115" t="inlineStr"/>
+      <c r="AJ115" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O116" t="n">
+        <v>50</v>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>100</v>
+      </c>
+      <c r="R116" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="T116" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U116" t="n">
+        <v>1250000</v>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X116" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:59:45</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr"/>
+      <c r="AD116" t="inlineStr"/>
+      <c r="AE116" t="inlineStr"/>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="inlineStr"/>
+      <c r="AH116" t="inlineStr"/>
+      <c r="AI116" t="inlineStr"/>
+      <c r="AJ116" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>07 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>PENGADAAN MATERIAL</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+        </is>
+      </c>
+      <c r="O117" t="n">
+        <v>115</v>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Ltr</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>100</v>
+      </c>
+      <c r="R117" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="T117" t="n">
+        <v>25000</v>
+      </c>
+      <c r="U117" t="n">
+        <v>2875000</v>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X117" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:59:45</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr"/>
+      <c r="AD117" t="inlineStr"/>
+      <c r="AE117" t="inlineStr"/>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="inlineStr"/>
+      <c r="AH117" t="inlineStr"/>
+      <c r="AI117" t="inlineStr"/>
+      <c r="AJ117" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O118" t="n">
+        <v>1</v>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>100</v>
+      </c>
+      <c r="R118" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="T118" t="n">
+        <v>5054500</v>
+      </c>
+      <c r="U118" t="n">
+        <v>5812675</v>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X118" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>2026-09-21 12:59:45</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr"/>
+      <c r="AD118" t="inlineStr"/>
+      <c r="AE118" t="inlineStr"/>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="inlineStr"/>
+      <c r="AH118" t="inlineStr"/>
+      <c r="AI118" t="inlineStr"/>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3876,7 +3876,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O25" t="n">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O26" t="n">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O27" t="n">
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4298,7 +4298,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O28" t="n">
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O29" t="n">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5142,7 +5142,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O34" t="n">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O35" t="n">
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5562,7 +5562,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O37" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>Add Cost + Fee 15%</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13258,7 +13258,7 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -13288,7 +13288,7 @@
       </c>
       <c r="J91" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K91" t="inlineStr">
@@ -13303,20 +13303,20 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>0.48</v>
+        <v>25</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q91" t="n">
@@ -13324,7 +13324,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -13333,10 +13333,10 @@
         </is>
       </c>
       <c r="T91" t="n">
-        <v>25000000</v>
+        <v>1600000</v>
       </c>
       <c r="U91" t="n">
-        <v>12000000</v>
+        <v>40000000</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -13365,12 +13365,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13408,7 +13408,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -13438,7 +13438,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -13453,20 +13453,20 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>0.48</v>
+        <v>15</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q92" t="n">
@@ -13474,19 +13474,19 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="T92" t="n">
-        <v>17500000</v>
+        <v>1600000</v>
       </c>
       <c r="U92" t="n">
-        <v>8400000</v>
+        <v>24000000</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -13515,12 +13515,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (8 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -13588,7 +13588,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -13603,20 +13603,20 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q93" t="n">
@@ -13624,7 +13624,7 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
@@ -13633,10 +13633,10 @@
         </is>
       </c>
       <c r="T93" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="U93" t="n">
-        <v>44400000</v>
+        <v>40000000</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -13665,12 +13665,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13708,7 +13708,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -13738,7 +13738,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -13753,20 +13753,20 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>0.74</v>
+        <v>4</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q94" t="n">
@@ -13774,19 +13774,19 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T94" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="U94" t="n">
-        <v>44400000</v>
+        <v>6400000</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -13815,12 +13815,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13858,7 +13858,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -13903,20 +13903,20 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>0.74</v>
+        <v>25</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q95" t="n">
@@ -13924,7 +13924,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -13933,10 +13933,10 @@
         </is>
       </c>
       <c r="T95" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="U95" t="n">
-        <v>11100000</v>
+        <v>40000000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -13965,12 +13965,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14008,7 +14008,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -14053,20 +14053,20 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>0.74</v>
+        <v>22</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q96" t="n">
@@ -14074,7 +14074,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -14083,10 +14083,10 @@
         </is>
       </c>
       <c r="T96" t="n">
-        <v>15000000</v>
+        <v>1600000</v>
       </c>
       <c r="U96" t="n">
-        <v>11100000</v>
+        <v>35200000</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -14115,12 +14115,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14158,7 +14158,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -14188,7 +14188,7 @@
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -14203,16 +14203,16 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
@@ -14224,19 +14224,19 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T97" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U97" t="n">
-        <v>40000000</v>
+        <v>59500000</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -14265,12 +14265,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14308,7 +14308,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -14338,7 +14338,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -14353,16 +14353,16 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
@@ -14374,19 +14374,19 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T98" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U98" t="n">
-        <v>24000000</v>
+        <v>76500000</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -14415,12 +14415,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14458,7 +14458,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -14488,7 +14488,7 @@
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -14503,16 +14503,16 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
@@ -14533,10 +14533,10 @@
         </is>
       </c>
       <c r="T99" t="n">
-        <v>1600000</v>
+        <v>2750000</v>
       </c>
       <c r="U99" t="n">
-        <v>40000000</v>
+        <v>57750000</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -14565,12 +14565,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14608,7 +14608,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -14633,17 +14633,17 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
@@ -14653,20 +14653,20 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>1800</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q100" t="n">
@@ -14674,19 +14674,19 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T100" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="U100" t="n">
-        <v>6400000</v>
+        <v>12150000</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -14715,12 +14715,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14732,7 +14732,7 @@
       <c r="AI100" t="inlineStr"/>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
@@ -14758,7 +14758,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -14783,17 +14783,17 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
@@ -14803,20 +14803,20 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q101" t="n">
@@ -14824,7 +14824,7 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
@@ -14833,10 +14833,10 @@
         </is>
       </c>
       <c r="T101" t="n">
-        <v>1600000</v>
+        <v>53300</v>
       </c>
       <c r="U101" t="n">
-        <v>40000000</v>
+        <v>863460</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -14865,12 +14865,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14882,7 +14882,7 @@
       <c r="AI101" t="inlineStr"/>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
@@ -14908,12 +14908,12 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -14938,7 +14938,9 @@
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
+Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -14953,20 +14955,20 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q102" t="n">
@@ -14979,14 +14981,14 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T102" t="n">
-        <v>1600000</v>
+        <v>12500000</v>
       </c>
       <c r="U102" t="n">
-        <v>35200000</v>
+        <v>12500000</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -15015,12 +15017,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15032,7 +15034,7 @@
       <c r="AI102" t="inlineStr"/>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -15040,7 +15042,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr"/>
+      <c r="AL102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -15058,13 +15064,11 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>31 Aug 2026</t>
-        </is>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E103" s="1" t="n">
+        <v>46264</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -15088,7 +15092,8 @@
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
@@ -15103,20 +15108,20 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q103" t="n">
@@ -15129,14 +15134,14 @@
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="T103" t="n">
-        <v>8500000</v>
+        <v>250000</v>
       </c>
       <c r="U103" t="n">
-        <v>59500000</v>
+        <v>6000000</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -15165,12 +15170,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t xml:space="preserve">Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026 </t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15190,7 +15195,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL103" t="inlineStr"/>
+      <c r="AL103" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -15208,7 +15217,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -15238,7 +15247,7 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
@@ -15253,20 +15262,20 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>9</v>
+        <v>316.8</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q104" t="n">
@@ -15274,7 +15283,7 @@
       </c>
       <c r="R104" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S104" t="inlineStr">
@@ -15283,10 +15292,10 @@
         </is>
       </c>
       <c r="T104" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="U104" t="n">
-        <v>76500000</v>
+        <v>7920000</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -15315,12 +15324,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15340,7 +15349,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL104" t="inlineStr"/>
+      <c r="AL104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -15358,7 +15371,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -15383,17 +15396,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -15403,20 +15416,20 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q105" t="n">
@@ -15424,19 +15437,19 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T105" t="n">
-        <v>2750000</v>
+        <v>25000</v>
       </c>
       <c r="U105" t="n">
-        <v>57750000</v>
+        <v>6250000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -15465,12 +15478,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15482,7 +15495,7 @@
       <c r="AI105" t="inlineStr"/>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -15508,7 +15521,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -15533,12 +15546,12 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>45000000test</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
@@ -15553,20 +15566,20 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>1800</v>
+        <v>200</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q106" t="n">
@@ -15574,19 +15587,19 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="T106" t="n">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="U106" t="n">
-        <v>12150000</v>
+        <v>5000000</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15615,12 +15628,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15658,7 +15671,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -15683,12 +15696,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>45000000test</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -15703,20 +15716,20 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -15724,19 +15737,19 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T107" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U107" t="n">
-        <v>863460</v>
+        <v>1250000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15765,12 +15778,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15808,12 +15821,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -15833,19 +15846,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
-Wellsite/ Contractor base</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -15855,20 +15866,20 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -15885,10 +15896,10 @@
         </is>
       </c>
       <c r="T108" t="n">
-        <v>12500000</v>
+        <v>25000</v>
       </c>
       <c r="U108" t="n">
-        <v>12500000</v>
+        <v>1250000</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -15917,12 +15928,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -15942,11 +15953,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL108" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -15964,11 +15971,13 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="n">
-        <v>46264</v>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -15987,18 +15996,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
-Helper Local (non Skilled)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -16008,20 +16016,20 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -16034,14 +16042,14 @@
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T109" t="n">
-        <v>250000</v>
+        <v>25000</v>
       </c>
       <c r="U109" t="n">
-        <v>6000000</v>
+        <v>1250000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -16070,12 +16078,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026 </t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16087,7 +16095,7 @@
       <c r="AI109" t="inlineStr"/>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -16095,11 +16103,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -16117,7 +16121,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -16142,17 +16146,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -16162,20 +16166,20 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>316.8</v>
+        <v>50</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -16183,19 +16187,19 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T110" t="n">
         <v>25000</v>
       </c>
       <c r="U110" t="n">
-        <v>7920000</v>
+        <v>1250000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -16224,12 +16228,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16241,7 +16245,7 @@
       <c r="AI110" t="inlineStr"/>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -16249,11 +16253,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL110" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -16325,7 +16325,7 @@
         </is>
       </c>
       <c r="O111" t="n">
-        <v>250</v>
+        <v>115</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -16342,14 +16342,14 @@
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="T111" t="n">
         <v>25000</v>
       </c>
       <c r="U111" t="n">
-        <v>6250000</v>
+        <v>2875000</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -16378,12 +16378,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16421,12 +16421,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>19 Sep 2026</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -16451,12 +16451,12 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>18 Sep 2026</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -16466,20 +16466,20 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>200</v>
+        <v>1</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q112" t="n">
@@ -16487,19 +16487,19 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="T112" t="n">
-        <v>25000</v>
+        <v>5054500</v>
       </c>
       <c r="U112" t="n">
-        <v>5000000</v>
+        <v>5812675</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -16528,12 +16528,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16553,11 +16553,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="113">
-      <c r="A113" t="n">
-        <v>7201250141</v>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
@@ -16571,7 +16577,7 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -16596,17 +16602,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -16616,20 +16622,20 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q113" t="n">
@@ -16637,19 +16643,19 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T113" t="n">
-        <v>25000</v>
+        <v>25000000</v>
       </c>
       <c r="U113" t="n">
-        <v>1250000</v>
+        <v>12000000</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -16678,12 +16684,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16695,7 +16701,7 @@
       <c r="AI113" t="inlineStr"/>
       <c r="AJ113" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK113" t="inlineStr">
@@ -16706,8 +16712,10 @@
       <c r="AL113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="n">
-        <v>7201250141</v>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
@@ -16721,7 +16729,7 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -16746,17 +16754,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -16766,20 +16774,20 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q114" t="n">
@@ -16787,19 +16795,19 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T114" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="U114" t="n">
-        <v>1250000</v>
+        <v>8400000</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -16828,12 +16836,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16845,7 +16853,7 @@
       <c r="AI114" t="inlineStr"/>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -16856,8 +16864,10 @@
       <c r="AL114" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" t="n">
-        <v>7201250141</v>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -16871,7 +16881,7 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -16896,17 +16906,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -16916,20 +16926,20 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q115" t="n">
@@ -16937,19 +16947,19 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T115" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="U115" t="n">
-        <v>1250000</v>
+        <v>44400000</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -16978,12 +16988,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -16995,7 +17005,7 @@
       <c r="AI115" t="inlineStr"/>
       <c r="AJ115" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK115" t="inlineStr">
@@ -17006,8 +17016,10 @@
       <c r="AL115" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" t="n">
-        <v>7201250141</v>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -17021,7 +17033,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -17046,17 +17058,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -17066,20 +17078,20 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q116" t="n">
@@ -17087,19 +17099,19 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T116" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="U116" t="n">
-        <v>1250000</v>
+        <v>44400000</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -17128,12 +17140,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17145,7 +17157,7 @@
       <c r="AI116" t="inlineStr"/>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -17156,8 +17168,10 @@
       <c r="AL116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="n">
-        <v>7201250141</v>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
@@ -17171,7 +17185,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -17196,17 +17210,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -17216,20 +17230,20 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>115</v>
+        <v>0.74</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q117" t="n">
@@ -17237,19 +17251,19 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T117" t="n">
-        <v>25000</v>
+        <v>15000000</v>
       </c>
       <c r="U117" t="n">
-        <v>2875000</v>
+        <v>11100000</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -17278,12 +17292,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17295,7 +17309,7 @@
       <c r="AI117" t="inlineStr"/>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -17323,12 +17337,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17348,17 +17362,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -17368,20 +17382,20 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q118" t="n">
@@ -17389,19 +17403,19 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T118" t="n">
-        <v>5054500</v>
+        <v>15000000</v>
       </c>
       <c r="U118" t="n">
-        <v>5812675</v>
+        <v>11100000</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -17430,12 +17444,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-09-21 12:59:45</t>
+          <t>2026-09-22 10:54:16</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17447,7 +17461,7 @@
       <c r="AI118" t="inlineStr"/>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -17455,11 +17469,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL118"/>
+  <dimension ref="A1:AL120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11858,7 +11858,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12012,7 +12012,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12166,7 +12166,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12316,7 +12316,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12466,7 +12466,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12616,7 +12616,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12766,7 +12766,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12916,7 +12916,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13066,7 +13066,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13216,7 +13216,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13520,7 +13520,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13820,7 +13820,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13970,7 +13970,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14120,7 +14120,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14270,7 +14270,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14570,7 +14570,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14720,7 +14720,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -15019,7 +15019,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15173,7 +15173,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15327,7 +15327,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15477,7 +15477,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15627,7 +15627,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15777,7 +15777,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15927,7 +15927,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -16077,7 +16077,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16227,7 +16227,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16377,7 +16377,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16531,7 +16531,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16681,7 +16681,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16831,7 +16831,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16981,7 +16981,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17281,7 +17281,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17304,10 +17304,8 @@
       <c r="AL117" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A118" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B118" t="inlineStr">
         <is>
@@ -17435,7 +17433,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-09-24 09:50:04</t>
+          <t>2026-09-29 20:32:07</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17461,6 +17459,314 @@
         </is>
       </c>
     </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>036/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O119" t="n">
+        <v>2</v>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>100</v>
+      </c>
+      <c r="R119" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="T119" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U119" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X119" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>test drive</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>2026-09-29 20:32:07</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr"/>
+      <c r="AD119" t="inlineStr"/>
+      <c r="AE119" t="inlineStr"/>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="inlineStr"/>
+      <c r="AH119" t="inlineStr"/>
+      <c r="AI119" t="inlineStr"/>
+      <c r="AJ119" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>036/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>19 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>18 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O120" t="n">
+        <v>2</v>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>100</v>
+      </c>
+      <c r="R120" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>2026-09-29</t>
+        </is>
+      </c>
+      <c r="T120" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U120" t="n">
+        <v>3200000</v>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X120" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr"/>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>2026-09-29 20:32:07</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr"/>
+      <c r="AD120" t="inlineStr"/>
+      <c r="AE120" t="inlineStr"/>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="inlineStr"/>
+      <c r="AH120" t="inlineStr"/>
+      <c r="AI120" t="inlineStr"/>
+      <c r="AJ120" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL120"/>
+  <dimension ref="A1:AL129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10692,12 +10692,12 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -10717,17 +10717,17 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -10737,16 +10737,16 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -10758,19 +10758,19 @@
       </c>
       <c r="R74" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S74" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T74" t="n">
-        <v>7654600</v>
+        <v>65000</v>
       </c>
       <c r="U74" t="n">
-        <v>8802790</v>
+        <v>167570000</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -10799,12 +10799,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10816,7 +10816,7 @@
       <c r="AI74" t="inlineStr"/>
       <c r="AJ74" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK74" t="inlineStr">
@@ -10892,11 +10892,11 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>2578</v>
+        <v>1157</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
@@ -10917,10 +10917,10 @@
         </is>
       </c>
       <c r="T75" t="n">
-        <v>65000</v>
+        <v>33000</v>
       </c>
       <c r="U75" t="n">
-        <v>167570000</v>
+        <v>38181000</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -10949,12 +10949,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -10992,7 +10992,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -11022,7 +11022,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -11037,20 +11037,20 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O76" t="n">
-        <v>1157</v>
+        <v>22</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q76" t="n">
@@ -11067,10 +11067,10 @@
         </is>
       </c>
       <c r="T76" t="n">
-        <v>33000</v>
+        <v>750000</v>
       </c>
       <c r="U76" t="n">
-        <v>38181000</v>
+        <v>16500000</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -11099,12 +11099,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11142,12 +11142,12 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -11172,7 +11172,7 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
@@ -11196,11 +11196,11 @@
         </is>
       </c>
       <c r="O77" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q77" t="n">
@@ -11208,19 +11208,19 @@
       </c>
       <c r="R77" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T77" t="n">
         <v>750000</v>
       </c>
       <c r="U77" t="n">
-        <v>16500000</v>
+        <v>750000</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -11249,12 +11249,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11337,12 +11337,12 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O78" t="n">
@@ -11367,10 +11367,10 @@
         </is>
       </c>
       <c r="T78" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="U78" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -11399,12 +11399,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11442,12 +11442,12 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -11472,7 +11472,7 @@
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
@@ -11487,20 +11487,20 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O79" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q79" t="n">
@@ -11508,19 +11508,19 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="T79" t="n">
-        <v>1600000</v>
+        <v>750000</v>
       </c>
       <c r="U79" t="n">
-        <v>1600000</v>
+        <v>9750000</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -11549,12 +11549,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11592,7 +11592,7 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -11642,15 +11642,15 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O80" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q80" t="n">
@@ -11658,7 +11658,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -11667,10 +11667,10 @@
         </is>
       </c>
       <c r="T80" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="U80" t="n">
-        <v>12000000</v>
+        <v>6750000</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -11699,12 +11699,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11716,7 +11716,7 @@
       <c r="AI80" t="inlineStr"/>
       <c r="AJ80" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK80" t="inlineStr">
@@ -11724,11 +11724,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL80" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11746,7 +11742,7 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -11796,15 +11792,15 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q81" t="n">
@@ -11821,10 +11817,10 @@
         </is>
       </c>
       <c r="T81" t="n">
-        <v>500000</v>
+        <v>750000</v>
       </c>
       <c r="U81" t="n">
-        <v>12000000</v>
+        <v>12750000</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -11853,12 +11849,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -11870,7 +11866,7 @@
       <c r="AI81" t="inlineStr"/>
       <c r="AJ81" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK81" t="inlineStr">
@@ -11878,11 +11874,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL81" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11900,7 +11892,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -11950,15 +11942,15 @@
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O82" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q82" t="n">
@@ -11975,10 +11967,10 @@
         </is>
       </c>
       <c r="T82" t="n">
-        <v>500000</v>
+        <v>650000</v>
       </c>
       <c r="U82" t="n">
-        <v>12000000</v>
+        <v>14300000</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -12007,12 +11999,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12024,7 +12016,7 @@
       <c r="AI82" t="inlineStr"/>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
@@ -12032,11 +12024,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL82" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -12104,11 +12092,11 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -12125,14 +12113,14 @@
       </c>
       <c r="S83" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T83" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U83" t="n">
-        <v>9750000</v>
+        <v>13650000</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -12161,12 +12149,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12254,11 +12242,11 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O84" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="P84" t="inlineStr">
         <is>
@@ -12270,7 +12258,7 @@
       </c>
       <c r="R84" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S84" t="inlineStr">
@@ -12279,10 +12267,10 @@
         </is>
       </c>
       <c r="T84" t="n">
-        <v>750000</v>
+        <v>600000</v>
       </c>
       <c r="U84" t="n">
-        <v>6750000</v>
+        <v>13800000</v>
       </c>
       <c r="V84" t="inlineStr">
         <is>
@@ -12311,12 +12299,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12404,11 +12392,11 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
@@ -12420,7 +12408,7 @@
       </c>
       <c r="R85" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S85" t="inlineStr">
@@ -12429,10 +12417,10 @@
         </is>
       </c>
       <c r="T85" t="n">
-        <v>750000</v>
+        <v>600000</v>
       </c>
       <c r="U85" t="n">
-        <v>12750000</v>
+        <v>13800000</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -12461,12 +12449,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12504,7 +12492,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -12554,15 +12542,15 @@
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q86" t="n">
@@ -12570,7 +12558,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -12579,10 +12567,10 @@
         </is>
       </c>
       <c r="T86" t="n">
-        <v>650000</v>
+        <v>500000</v>
       </c>
       <c r="U86" t="n">
-        <v>14300000</v>
+        <v>10500000</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -12611,12 +12599,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12636,7 +12624,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL86" t="inlineStr"/>
+      <c r="AL86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12654,7 +12646,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -12684,7 +12676,7 @@
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K87" t="inlineStr">
@@ -12699,20 +12691,20 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O87" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q87" t="n">
@@ -12720,7 +12712,7 @@
       </c>
       <c r="R87" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S87" t="inlineStr">
@@ -12729,10 +12721,10 @@
         </is>
       </c>
       <c r="T87" t="n">
-        <v>650000</v>
+        <v>1600000</v>
       </c>
       <c r="U87" t="n">
-        <v>13650000</v>
+        <v>40000000</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -12761,12 +12753,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12804,7 +12796,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -12834,7 +12826,7 @@
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
@@ -12849,20 +12841,20 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O88" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q88" t="n">
@@ -12870,19 +12862,19 @@
       </c>
       <c r="R88" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="T88" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="U88" t="n">
-        <v>13800000</v>
+        <v>24000000</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -12911,12 +12903,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -12954,7 +12946,7 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -12984,7 +12976,7 @@
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K89" t="inlineStr">
@@ -12999,20 +12991,20 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O89" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q89" t="n">
@@ -13020,7 +13012,7 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
@@ -13029,10 +13021,10 @@
         </is>
       </c>
       <c r="T89" t="n">
-        <v>600000</v>
+        <v>1600000</v>
       </c>
       <c r="U89" t="n">
-        <v>13800000</v>
+        <v>40000000</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -13061,12 +13053,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13104,7 +13096,7 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>024A/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -13134,7 +13126,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -13149,16 +13141,16 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -13170,19 +13162,19 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T90" t="n">
-        <v>500000</v>
+        <v>1600000</v>
       </c>
       <c r="U90" t="n">
-        <v>10500000</v>
+        <v>6400000</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -13211,12 +13203,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13236,11 +13228,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL90" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -13308,7 +13296,7 @@
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O91" t="n">
@@ -13365,12 +13353,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13458,11 +13446,11 @@
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -13474,19 +13462,19 @@
       </c>
       <c r="R92" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T92" t="n">
         <v>1600000</v>
       </c>
       <c r="U92" t="n">
-        <v>24000000</v>
+        <v>35200000</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -13515,12 +13503,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13558,7 +13546,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -13588,7 +13576,7 @@
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K93" t="inlineStr">
@@ -13603,16 +13591,16 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O93" t="n">
-        <v>25</v>
+        <v>7</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -13624,19 +13612,19 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T93" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U93" t="n">
-        <v>40000000</v>
+        <v>59500000</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -13665,12 +13653,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13708,7 +13696,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -13738,7 +13726,7 @@
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -13753,16 +13741,16 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -13774,19 +13762,19 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T94" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U94" t="n">
-        <v>6400000</v>
+        <v>76500000</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -13815,12 +13803,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13858,7 +13846,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -13888,7 +13876,7 @@
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -13903,16 +13891,16 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
@@ -13924,7 +13912,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -13933,10 +13921,10 @@
         </is>
       </c>
       <c r="T95" t="n">
-        <v>1600000</v>
+        <v>2750000</v>
       </c>
       <c r="U95" t="n">
-        <v>40000000</v>
+        <v>57750000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -13965,12 +13953,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14008,7 +13996,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -14033,17 +14021,17 @@
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
@@ -14053,20 +14041,20 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>22</v>
+        <v>1800</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q96" t="n">
@@ -14083,10 +14071,10 @@
         </is>
       </c>
       <c r="T96" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="U96" t="n">
-        <v>35200000</v>
+        <v>12150000</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -14115,12 +14103,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14132,7 +14120,7 @@
       <c r="AI96" t="inlineStr"/>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -14158,7 +14146,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -14183,17 +14171,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -14203,20 +14191,20 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q97" t="n">
@@ -14224,19 +14212,19 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T97" t="n">
-        <v>8500000</v>
+        <v>53300</v>
       </c>
       <c r="U97" t="n">
-        <v>59500000</v>
+        <v>863460</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -14265,12 +14253,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14282,7 +14270,7 @@
       <c r="AI97" t="inlineStr"/>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -14308,7 +14296,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -14338,7 +14326,7 @@
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
@@ -14353,20 +14341,20 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>9</v>
+        <v>316.8</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -14374,7 +14362,7 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
@@ -14383,10 +14371,10 @@
         </is>
       </c>
       <c r="T98" t="n">
-        <v>8500000</v>
+        <v>25000</v>
       </c>
       <c r="U98" t="n">
-        <v>76500000</v>
+        <v>7920000</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -14415,12 +14403,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14440,7 +14428,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL98" t="inlineStr"/>
+      <c r="AL98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -14458,7 +14450,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -14483,17 +14475,17 @@
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -14503,20 +14495,20 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>21</v>
+        <v>250</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q99" t="n">
@@ -14524,19 +14516,19 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T99" t="n">
-        <v>2750000</v>
+        <v>25000</v>
       </c>
       <c r="U99" t="n">
-        <v>57750000</v>
+        <v>6250000</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -14565,12 +14557,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14582,7 +14574,7 @@
       <c r="AI99" t="inlineStr"/>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
@@ -14608,7 +14600,7 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -14633,12 +14625,12 @@
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>45000000test</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K100" t="inlineStr">
@@ -14653,20 +14645,20 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O100" t="n">
-        <v>1800</v>
+        <v>200</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q100" t="n">
@@ -14674,19 +14666,19 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="T100" t="n">
-        <v>7500</v>
+        <v>25000</v>
       </c>
       <c r="U100" t="n">
-        <v>12150000</v>
+        <v>5000000</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -14715,12 +14707,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14758,7 +14750,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -14783,12 +14775,12 @@
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>45000000test</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K101" t="inlineStr">
@@ -14803,20 +14795,20 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O101" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q101" t="n">
@@ -14824,19 +14816,19 @@
       </c>
       <c r="R101" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S101" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T101" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U101" t="n">
-        <v>863460</v>
+        <v>1250000</v>
       </c>
       <c r="V101" t="inlineStr">
         <is>
@@ -14865,12 +14857,12 @@
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14908,11 +14900,13 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="n">
-        <v>46264</v>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -14931,18 +14925,17 @@
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
-Helper Local (non Skilled)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
@@ -14952,20 +14945,20 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O102" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q102" t="n">
@@ -14978,14 +14971,14 @@
       </c>
       <c r="S102" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T102" t="n">
-        <v>250000</v>
+        <v>25000</v>
       </c>
       <c r="U102" t="n">
-        <v>6000000</v>
+        <v>1250000</v>
       </c>
       <c r="V102" t="inlineStr">
         <is>
@@ -15014,12 +15007,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t xml:space="preserve">Upah harian Flagman Periode tgl 08 sd 30 Agustus 2026 </t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15031,7 +15024,7 @@
       <c r="AI102" t="inlineStr"/>
       <c r="AJ102" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK102" t="inlineStr">
@@ -15039,11 +15032,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL102" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -15061,7 +15050,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -15086,17 +15075,17 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K103" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
@@ -15106,20 +15095,20 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O103" t="n">
-        <v>316.8</v>
+        <v>50</v>
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q103" t="n">
@@ -15127,19 +15116,19 @@
       </c>
       <c r="R103" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S103" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T103" t="n">
         <v>25000</v>
       </c>
       <c r="U103" t="n">
-        <v>7920000</v>
+        <v>1250000</v>
       </c>
       <c r="V103" t="inlineStr">
         <is>
@@ -15168,12 +15157,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15185,7 +15174,7 @@
       <c r="AI103" t="inlineStr"/>
       <c r="AJ103" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK103" t="inlineStr">
@@ -15193,11 +15182,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL103" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -15269,7 +15254,7 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>250</v>
+        <v>50</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -15293,7 +15278,7 @@
         <v>25000</v>
       </c>
       <c r="U104" t="n">
-        <v>6250000</v>
+        <v>1250000</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -15322,12 +15307,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15419,7 +15404,7 @@
         </is>
       </c>
       <c r="O105" t="n">
-        <v>200</v>
+        <v>115</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
@@ -15431,7 +15416,7 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
@@ -15443,7 +15428,7 @@
         <v>25000</v>
       </c>
       <c r="U105" t="n">
-        <v>5000000</v>
+        <v>2875000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -15472,12 +15457,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15515,12 +15500,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>19 Sep 2026</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -15545,12 +15530,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>18 Sep 2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -15560,20 +15545,20 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q106" t="n">
@@ -15581,19 +15566,19 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="T106" t="n">
-        <v>25000</v>
+        <v>5054500</v>
       </c>
       <c r="U106" t="n">
-        <v>1250000</v>
+        <v>5812675</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15622,12 +15607,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15647,7 +15632,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL106" t="inlineStr"/>
+      <c r="AL106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -15665,7 +15654,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -15690,17 +15679,17 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
@@ -15710,20 +15699,20 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -15731,19 +15720,19 @@
       </c>
       <c r="R107" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S107" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T107" t="n">
-        <v>25000</v>
+        <v>25000000</v>
       </c>
       <c r="U107" t="n">
-        <v>1250000</v>
+        <v>12000000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15772,12 +15761,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15789,7 +15778,7 @@
       <c r="AI107" t="inlineStr"/>
       <c r="AJ107" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK107" t="inlineStr">
@@ -15815,7 +15804,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -15840,17 +15829,17 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -15860,20 +15849,20 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>50</v>
+        <v>0.48</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -15881,19 +15870,19 @@
       </c>
       <c r="R108" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T108" t="n">
-        <v>25000</v>
+        <v>17500000</v>
       </c>
       <c r="U108" t="n">
-        <v>1250000</v>
+        <v>8400000</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -15922,12 +15911,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -15939,7 +15928,7 @@
       <c r="AI108" t="inlineStr"/>
       <c r="AJ108" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK108" t="inlineStr">
@@ -15965,7 +15954,7 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -15990,17 +15979,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -16010,20 +15999,20 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>50</v>
+        <v>0.74</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -16031,19 +16020,19 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T109" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="U109" t="n">
-        <v>1250000</v>
+        <v>44400000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -16072,12 +16061,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16089,7 +16078,7 @@
       <c r="AI109" t="inlineStr"/>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -16115,7 +16104,7 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -16140,17 +16129,17 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
@@ -16160,20 +16149,20 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O110" t="n">
-        <v>115</v>
+        <v>0.74</v>
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q110" t="n">
@@ -16181,19 +16170,19 @@
       </c>
       <c r="R110" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S110" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T110" t="n">
-        <v>25000</v>
+        <v>60000000</v>
       </c>
       <c r="U110" t="n">
-        <v>2875000</v>
+        <v>44400000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -16222,12 +16211,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16239,7 +16228,7 @@
       <c r="AI110" t="inlineStr"/>
       <c r="AJ110" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK110" t="inlineStr">
@@ -16265,12 +16254,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -16290,17 +16279,17 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
@@ -16310,20 +16299,20 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>1</v>
+        <v>0.74</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q111" t="n">
@@ -16331,19 +16320,19 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T111" t="n">
-        <v>5054500</v>
+        <v>15000000</v>
       </c>
       <c r="U111" t="n">
-        <v>5812675</v>
+        <v>11100000</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -16372,12 +16361,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16389,7 +16378,7 @@
       <c r="AI111" t="inlineStr"/>
       <c r="AJ111" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK111" t="inlineStr">
@@ -16397,11 +16386,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL111" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -16464,16 +16449,16 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -16494,10 +16479,10 @@
         </is>
       </c>
       <c r="T112" t="n">
-        <v>25000000</v>
+        <v>15000000</v>
       </c>
       <c r="U112" t="n">
-        <v>12000000</v>
+        <v>11100000</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -16526,12 +16511,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16569,12 +16554,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -16599,7 +16584,9 @@
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
+Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
@@ -16614,20 +16601,20 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>0.48</v>
+        <v>1</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q113" t="n">
@@ -16635,19 +16622,19 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T113" t="n">
-        <v>17500000</v>
+        <v>12500000</v>
       </c>
       <c r="U113" t="n">
-        <v>8400000</v>
+        <v>12500000</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -16676,12 +16663,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16701,7 +16688,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL113" t="inlineStr"/>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -16719,12 +16710,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>19 Sep 2026</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -16744,17 +16735,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 Sep 2026</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -16764,20 +16755,20 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>0.74</v>
+        <v>2</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q114" t="n">
@@ -16785,19 +16776,19 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="T114" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="U114" t="n">
-        <v>44400000</v>
+        <v>3200000</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -16826,12 +16817,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>test drive</t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16851,7 +16842,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL114" t="inlineStr"/>
+      <c r="AL114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -16869,12 +16864,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>19 Sep 2026</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -16894,17 +16889,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 Sep 2026</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -16914,20 +16909,20 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>0.74</v>
+        <v>2</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q115" t="n">
@@ -16935,19 +16930,19 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="T115" t="n">
-        <v>60000000</v>
+        <v>1600000</v>
       </c>
       <c r="U115" t="n">
-        <v>44400000</v>
+        <v>3200000</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -16974,14 +16969,10 @@
           <t>Accounts Payable - Finance Department</t>
         </is>
       </c>
-      <c r="AA115" t="inlineStr">
-        <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
-        </is>
-      </c>
+      <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17001,7 +16992,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL115" t="inlineStr"/>
+      <c r="AL115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -17019,7 +17014,7 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -17049,7 +17044,7 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -17064,20 +17059,20 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>0.74</v>
+        <v>24</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q116" t="n">
@@ -17085,7 +17080,7 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
@@ -17094,10 +17089,10 @@
         </is>
       </c>
       <c r="T116" t="n">
-        <v>15000000</v>
+        <v>500000</v>
       </c>
       <c r="U116" t="n">
-        <v>11100000</v>
+        <v>12000000</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -17126,12 +17121,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17151,7 +17146,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL116" t="inlineStr"/>
+      <c r="AL116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -17169,7 +17168,7 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -17199,7 +17198,7 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -17214,20 +17213,20 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>0.74</v>
+        <v>24</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q117" t="n">
@@ -17235,7 +17234,7 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
@@ -17244,10 +17243,10 @@
         </is>
       </c>
       <c r="T117" t="n">
-        <v>15000000</v>
+        <v>500000</v>
       </c>
       <c r="U117" t="n">
-        <v>11100000</v>
+        <v>12000000</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -17276,12 +17275,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17301,7 +17300,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -17319,12 +17322,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17349,9 +17352,7 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
-Wellsite/ Contractor base</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -17366,20 +17367,20 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q118" t="n">
@@ -17392,14 +17393,14 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T118" t="n">
-        <v>12500000</v>
+        <v>500000</v>
       </c>
       <c r="U118" t="n">
-        <v>12500000</v>
+        <v>12000000</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -17428,12 +17429,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17460,10 +17461,8 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A119" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B119" t="inlineStr">
         <is>
@@ -17477,12 +17476,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>30 Aug 2026</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17502,17 +17501,18 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -17522,16 +17522,16 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>2</v>
+        <v>48</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -17543,19 +17543,19 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="T119" t="n">
-        <v>1600000</v>
+        <v>250000</v>
       </c>
       <c r="U119" t="n">
-        <v>3200000</v>
+        <v>12000000</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -17584,12 +17584,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>test drive</t>
+          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -17633,12 +17633,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17663,12 +17663,12 @@
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -17678,20 +17678,20 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>2</v>
+        <v>240</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q120" t="n">
@@ -17699,19 +17699,19 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T120" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="U120" t="n">
-        <v>3200000</v>
+        <v>1620000</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -17738,10 +17738,14 @@
           <t>Accounts Payable - Finance Department</t>
         </is>
       </c>
-      <c r="AA120" t="inlineStr"/>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-09-29 20:32:07</t>
+          <t>2026-09-30 13:22:47</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -17753,7 +17757,7 @@
       <c r="AI120" t="inlineStr"/>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -17761,11 +17765,1375 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL120" t="inlineStr">
+      <c r="AL120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="O121" t="n">
+        <v>24</v>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>100</v>
+      </c>
+      <c r="R121" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T121" t="n">
+        <v>19500</v>
+      </c>
+      <c r="U121" t="n">
+        <v>421200</v>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X121" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr"/>
+      <c r="AD121" t="inlineStr"/>
+      <c r="AE121" t="inlineStr"/>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="inlineStr"/>
+      <c r="AH121" t="inlineStr"/>
+      <c r="AI121" t="inlineStr"/>
+      <c r="AJ121" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK121" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="AL121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="O122" t="n">
+        <v>24</v>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>100</v>
+      </c>
+      <c r="R122" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T122" t="n">
+        <v>15600</v>
+      </c>
+      <c r="U122" t="n">
+        <v>336960</v>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X122" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr"/>
+      <c r="AD122" t="inlineStr"/>
+      <c r="AE122" t="inlineStr"/>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="inlineStr"/>
+      <c r="AH122" t="inlineStr"/>
+      <c r="AI122" t="inlineStr"/>
+      <c r="AJ122" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="O123" t="n">
+        <v>48</v>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>100</v>
+      </c>
+      <c r="R123" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T123" t="n">
+        <v>13000</v>
+      </c>
+      <c r="U123" t="n">
+        <v>561600</v>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X123" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr"/>
+      <c r="AD123" t="inlineStr"/>
+      <c r="AE123" t="inlineStr"/>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="inlineStr"/>
+      <c r="AH123" t="inlineStr"/>
+      <c r="AI123" t="inlineStr"/>
+      <c r="AJ123" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK123" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L124" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="O124" t="n">
+        <v>48</v>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>100</v>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
+        <v>84500</v>
+      </c>
+      <c r="U124" t="n">
+        <v>3650400</v>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X124" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr"/>
+      <c r="AD124" t="inlineStr"/>
+      <c r="AE124" t="inlineStr"/>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="inlineStr"/>
+      <c r="AH124" t="inlineStr"/>
+      <c r="AI124" t="inlineStr"/>
+      <c r="AJ124" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK124" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N125" t="inlineStr">
+        <is>
+          <t>Coca Cola</t>
+        </is>
+      </c>
+      <c r="O125" t="n">
+        <v>48</v>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>100</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T125" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U125" t="n">
+        <v>421200</v>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X125" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC125" t="inlineStr"/>
+      <c r="AD125" t="inlineStr"/>
+      <c r="AE125" t="inlineStr"/>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="inlineStr"/>
+      <c r="AH125" t="inlineStr"/>
+      <c r="AI125" t="inlineStr"/>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N126" t="inlineStr">
+        <is>
+          <t>Fanta</t>
+        </is>
+      </c>
+      <c r="O126" t="n">
+        <v>48</v>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>100</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U126" t="n">
+        <v>421200</v>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X126" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC126" t="inlineStr"/>
+      <c r="AD126" t="inlineStr"/>
+      <c r="AE126" t="inlineStr"/>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="inlineStr"/>
+      <c r="AH126" t="inlineStr"/>
+      <c r="AI126" t="inlineStr"/>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N127" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="O127" t="n">
+        <v>48</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>100</v>
+      </c>
+      <c r="R127" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T127" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U127" t="n">
+        <v>421200</v>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X127" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC127" t="inlineStr"/>
+      <c r="AD127" t="inlineStr"/>
+      <c r="AE127" t="inlineStr"/>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="inlineStr"/>
+      <c r="AH127" t="inlineStr"/>
+      <c r="AI127" t="inlineStr"/>
+      <c r="AJ127" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="O128" t="n">
+        <v>48</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>100</v>
+      </c>
+      <c r="R128" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T128" t="n">
+        <v>19500</v>
+      </c>
+      <c r="U128" t="n">
+        <v>842400</v>
+      </c>
+      <c r="V128" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W128" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X128" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y128" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z128" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB128" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC128" t="inlineStr"/>
+      <c r="AD128" t="inlineStr"/>
+      <c r="AE128" t="inlineStr"/>
+      <c r="AF128" t="inlineStr"/>
+      <c r="AG128" t="inlineStr"/>
+      <c r="AH128" t="inlineStr"/>
+      <c r="AI128" t="inlineStr"/>
+      <c r="AJ128" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="O129" t="n">
+        <v>48</v>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q129" t="n">
+        <v>100</v>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T129" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U129" t="n">
+        <v>421200</v>
+      </c>
+      <c r="V129" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W129" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X129" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y129" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z129" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB129" t="inlineStr">
+        <is>
+          <t>2026-09-30 13:22:47</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr"/>
+      <c r="AD129" t="inlineStr"/>
+      <c r="AE129" t="inlineStr"/>
+      <c r="AF129" t="inlineStr"/>
+      <c r="AG129" t="inlineStr"/>
+      <c r="AH129" t="inlineStr"/>
+      <c r="AI129" t="inlineStr"/>
+      <c r="AJ129" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL129" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL129"/>
+  <dimension ref="A1:AL131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15500,12 +15500,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -15525,17 +15525,17 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -15545,20 +15545,20 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>1</v>
+        <v>0.48</v>
       </c>
       <c r="P106" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q106" t="n">
@@ -15566,19 +15566,19 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T106" t="n">
-        <v>5054500</v>
+        <v>25000000</v>
       </c>
       <c r="U106" t="n">
-        <v>5812675</v>
+        <v>12000000</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15607,12 +15607,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15624,7 +15624,7 @@
       <c r="AI106" t="inlineStr"/>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -15632,11 +15632,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL106" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -15704,7 +15700,7 @@
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O107" t="n">
@@ -15729,10 +15725,10 @@
         </is>
       </c>
       <c r="T107" t="n">
-        <v>25000000</v>
+        <v>17500000</v>
       </c>
       <c r="U107" t="n">
-        <v>12000000</v>
+        <v>8400000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15761,12 +15757,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15849,16 +15845,16 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
@@ -15879,10 +15875,10 @@
         </is>
       </c>
       <c r="T108" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="U108" t="n">
-        <v>8400000</v>
+        <v>44400000</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -15911,12 +15907,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -16061,12 +16057,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16154,7 +16150,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -16179,10 +16175,10 @@
         </is>
       </c>
       <c r="T110" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="U110" t="n">
-        <v>44400000</v>
+        <v>11100000</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -16211,12 +16207,12 @@
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16366,7 +16362,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16404,12 +16400,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -16434,7 +16430,9 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
+Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -16454,15 +16452,15 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q112" t="n">
@@ -16470,19 +16468,19 @@
       </c>
       <c r="R112" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T112" t="n">
-        <v>15000000</v>
+        <v>12500000</v>
       </c>
       <c r="U112" t="n">
-        <v>11100000</v>
+        <v>12500000</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -16511,12 +16509,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16536,7 +16534,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL112" t="inlineStr"/>
+      <c r="AL112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -16554,12 +16556,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>19 Sep 2026</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -16579,19 +16581,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
-Wellsite/ Contractor base</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>18 Sep 2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -16601,20 +16601,20 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q113" t="n">
@@ -16622,19 +16622,19 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="T113" t="n">
-        <v>12500000</v>
+        <v>1600000</v>
       </c>
       <c r="U113" t="n">
-        <v>12500000</v>
+        <v>3200000</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -16663,12 +16663,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t>test drive</t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16760,7 +16760,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O114" t="n">
@@ -16815,14 +16815,10 @@
           <t>Accounts Payable - Finance Department</t>
         </is>
       </c>
-      <c r="AA114" t="inlineStr">
-        <is>
-          <t>test drive</t>
-        </is>
-      </c>
+      <c r="AA114" t="inlineStr"/>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16864,12 +16860,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -16889,17 +16885,17 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
@@ -16909,16 +16905,16 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -16930,19 +16926,19 @@
       </c>
       <c r="R115" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T115" t="n">
-        <v>1600000</v>
+        <v>500000</v>
       </c>
       <c r="U115" t="n">
-        <v>3200000</v>
+        <v>12000000</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -16969,10 +16965,14 @@
           <t>Accounts Payable - Finance Department</t>
         </is>
       </c>
-      <c r="AA115" t="inlineStr"/>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+        </is>
+      </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17121,12 +17121,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17275,12 +17275,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17322,12 +17322,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>30 Aug 2026</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17352,7 +17352,8 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
@@ -17372,11 +17373,11 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
@@ -17393,11 +17394,11 @@
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="T118" t="n">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="U118" t="n">
         <v>12000000</v>
@@ -17429,12 +17430,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
+          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17476,12 +17477,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>30 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17501,18 +17502,17 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
-Helper Local (non Skilled)</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -17522,20 +17522,20 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>48</v>
+        <v>240</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q119" t="n">
@@ -17543,19 +17543,19 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T119" t="n">
-        <v>250000</v>
+        <v>7500</v>
       </c>
       <c r="U119" t="n">
-        <v>12000000</v>
+        <v>1620000</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -17584,12 +17584,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -17601,7 +17601,7 @@
       <c r="AI119" t="inlineStr"/>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -17609,17 +17609,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL119" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL119" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A120" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B120" t="inlineStr">
         <is>
@@ -17683,11 +17677,11 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -17699,19 +17693,19 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="T120" t="n">
-        <v>7500</v>
+        <v>19500</v>
       </c>
       <c r="U120" t="n">
-        <v>1620000</v>
+        <v>421200</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -17745,7 +17739,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -17768,10 +17762,8 @@
       <c r="AL120" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A121" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B121" t="inlineStr">
         <is>
@@ -17835,7 +17827,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="O121" t="n">
@@ -17851,19 +17843,19 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T121" t="n">
-        <v>19500</v>
+        <v>15600</v>
       </c>
       <c r="U121" t="n">
-        <v>421200</v>
+        <v>336960</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -17897,7 +17889,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
@@ -17920,10 +17912,8 @@
       <c r="AL121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A122" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -17987,11 +17977,11 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -18012,10 +18002,10 @@
         </is>
       </c>
       <c r="T122" t="n">
-        <v>15600</v>
+        <v>13000</v>
       </c>
       <c r="U122" t="n">
-        <v>336960</v>
+        <v>561600</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -18049,7 +18039,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
@@ -18072,10 +18062,8 @@
       <c r="AL122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A123" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -18139,7 +18127,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -18164,10 +18152,10 @@
         </is>
       </c>
       <c r="T123" t="n">
-        <v>13000</v>
+        <v>84500</v>
       </c>
       <c r="U123" t="n">
-        <v>561600</v>
+        <v>3650400</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -18201,7 +18189,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
@@ -18224,10 +18212,8 @@
       <c r="AL123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A124" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -18291,7 +18277,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Coca Cola</t>
         </is>
       </c>
       <c r="O124" t="n">
@@ -18316,10 +18302,10 @@
         </is>
       </c>
       <c r="T124" t="n">
-        <v>84500</v>
+        <v>9750</v>
       </c>
       <c r="U124" t="n">
-        <v>3650400</v>
+        <v>421200</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -18353,7 +18339,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
@@ -18376,10 +18362,8 @@
       <c r="AL124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A125" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -18443,7 +18427,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Coca Cola</t>
+          <t>Fanta</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -18451,7 +18435,7 @@
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q125" t="n">
@@ -18505,7 +18489,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
@@ -18528,10 +18512,8 @@
       <c r="AL125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A126" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -18595,7 +18577,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Fanta</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -18657,7 +18639,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
@@ -18680,10 +18662,8 @@
       <c r="AL126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A127" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -18747,7 +18727,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -18763,19 +18743,19 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="T127" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="U127" t="n">
-        <v>421200</v>
+        <v>842400</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -18809,7 +18789,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
@@ -18832,10 +18812,8 @@
       <c r="AL127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A128" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -18899,7 +18877,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -18924,10 +18902,10 @@
         </is>
       </c>
       <c r="T128" t="n">
-        <v>19500</v>
+        <v>9750</v>
       </c>
       <c r="U128" t="n">
-        <v>842400</v>
+        <v>421200</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -18961,7 +18939,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
@@ -18984,10 +18962,8 @@
       <c r="AL128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A129" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -19001,12 +18977,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -19031,12 +19007,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -19046,16 +19022,16 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -19067,19 +19043,19 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="T129" t="n">
-        <v>9750</v>
+        <v>5054500</v>
       </c>
       <c r="U129" t="n">
-        <v>421200</v>
+        <v>5812675</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -19108,12 +19084,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-09-30 13:22:47</t>
+          <t>2026-10-01 13:42:08</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
@@ -19133,7 +19109,321 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL129" t="inlineStr"/>
+      <c r="AL129" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O130" t="n">
+        <v>1</v>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q130" t="n">
+        <v>100</v>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T130" t="n">
+        <v>5054500</v>
+      </c>
+      <c r="U130" t="n">
+        <v>5812675</v>
+      </c>
+      <c r="V130" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W130" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X130" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y130" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z130" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB130" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:42:08</t>
+        </is>
+      </c>
+      <c r="AC130" t="inlineStr"/>
+      <c r="AD130" t="inlineStr"/>
+      <c r="AE130" t="inlineStr"/>
+      <c r="AF130" t="inlineStr"/>
+      <c r="AG130" t="inlineStr"/>
+      <c r="AH130" t="inlineStr"/>
+      <c r="AI130" t="inlineStr"/>
+      <c r="AJ130" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL130" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>035/BSS-JOB/WS/X/2026</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>02 Oct 2026</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>PROVISIONAL SUM</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>At Cost + Fee 15%</t>
+        </is>
+      </c>
+      <c r="O131" t="n">
+        <v>1</v>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q131" t="n">
+        <v>100</v>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
+        <v>131650000</v>
+      </c>
+      <c r="U131" t="n">
+        <v>151397500</v>
+      </c>
+      <c r="V131" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W131" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X131" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y131" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z131" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+        </is>
+      </c>
+      <c r="AB131" t="inlineStr">
+        <is>
+          <t>2026-10-01 13:42:08</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr"/>
+      <c r="AD131" t="inlineStr"/>
+      <c r="AE131" t="inlineStr"/>
+      <c r="AF131" t="inlineStr"/>
+      <c r="AG131" t="inlineStr"/>
+      <c r="AH131" t="inlineStr"/>
+      <c r="AI131" t="inlineStr"/>
+      <c r="AJ131" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL131" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16556,12 +16556,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -16581,17 +16581,17 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
@@ -16601,16 +16601,16 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -16622,19 +16622,19 @@
       </c>
       <c r="R113" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S113" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T113" t="n">
-        <v>1600000</v>
+        <v>500000</v>
       </c>
       <c r="U113" t="n">
-        <v>3200000</v>
+        <v>12000000</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -16663,12 +16663,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>test drive</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16710,12 +16710,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>19 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -16735,17 +16735,17 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>18 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -16755,16 +16755,16 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -16776,19 +16776,19 @@
       </c>
       <c r="R114" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S114" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T114" t="n">
-        <v>1600000</v>
+        <v>500000</v>
       </c>
       <c r="U114" t="n">
-        <v>3200000</v>
+        <v>12000000</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -16815,10 +16815,14 @@
           <t>Accounts Payable - Finance Department</t>
         </is>
       </c>
-      <c r="AA114" t="inlineStr"/>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+        </is>
+      </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16967,12 +16971,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17014,12 +17018,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>30 Aug 2026</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17044,7 +17048,8 @@
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
@@ -17064,11 +17069,11 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
@@ -17085,11 +17090,11 @@
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="T116" t="n">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="U116" t="n">
         <v>12000000</v>
@@ -17121,12 +17126,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17168,12 +17173,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17193,17 +17198,17 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -17213,20 +17218,20 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>24</v>
+        <v>240</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q117" t="n">
@@ -17234,19 +17239,19 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T117" t="n">
-        <v>500000</v>
+        <v>7500</v>
       </c>
       <c r="U117" t="n">
-        <v>12000000</v>
+        <v>1620000</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -17275,12 +17280,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17292,7 +17297,7 @@
       <c r="AI117" t="inlineStr"/>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -17300,11 +17305,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL117" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -17322,12 +17323,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>30 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17347,18 +17348,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
-Helper Local (non Skilled)</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -17368,20 +17368,20 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>48</v>
+        <v>24</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q118" t="n">
@@ -17389,19 +17389,19 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="T118" t="n">
-        <v>250000</v>
+        <v>19500</v>
       </c>
       <c r="U118" t="n">
-        <v>12000000</v>
+        <v>421200</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -17430,12 +17430,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17447,7 +17447,7 @@
       <c r="AI118" t="inlineStr"/>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -17455,11 +17455,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL118" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -17527,11 +17523,11 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>240</v>
+        <v>24</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
@@ -17552,10 +17548,10 @@
         </is>
       </c>
       <c r="T119" t="n">
-        <v>7500</v>
+        <v>15600</v>
       </c>
       <c r="U119" t="n">
-        <v>1620000</v>
+        <v>336960</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -17589,7 +17585,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -17677,11 +17673,11 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -17693,19 +17689,19 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T120" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="U120" t="n">
-        <v>421200</v>
+        <v>561600</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -17739,7 +17735,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -17827,11 +17823,11 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
@@ -17852,10 +17848,10 @@
         </is>
       </c>
       <c r="T121" t="n">
-        <v>15600</v>
+        <v>84500</v>
       </c>
       <c r="U121" t="n">
-        <v>336960</v>
+        <v>3650400</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -17889,7 +17885,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
@@ -17977,7 +17973,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Coca Cola</t>
         </is>
       </c>
       <c r="O122" t="n">
@@ -18002,10 +17998,10 @@
         </is>
       </c>
       <c r="T122" t="n">
-        <v>13000</v>
+        <v>9750</v>
       </c>
       <c r="U122" t="n">
-        <v>561600</v>
+        <v>421200</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -18039,7 +18035,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
@@ -18127,7 +18123,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Fanta</t>
         </is>
       </c>
       <c r="O123" t="n">
@@ -18135,7 +18131,7 @@
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q123" t="n">
@@ -18152,10 +18148,10 @@
         </is>
       </c>
       <c r="T123" t="n">
-        <v>84500</v>
+        <v>9750</v>
       </c>
       <c r="U123" t="n">
-        <v>3650400</v>
+        <v>421200</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -18189,7 +18185,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
@@ -18277,7 +18273,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Coca Cola</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="O124" t="n">
@@ -18285,7 +18281,7 @@
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q124" t="n">
@@ -18339,7 +18335,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
@@ -18427,7 +18423,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Fanta</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -18443,19 +18439,19 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="T125" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="U125" t="n">
-        <v>421200</v>
+        <v>842400</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -18489,7 +18485,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
@@ -18577,7 +18573,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="O126" t="n">
@@ -18593,12 +18589,12 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="T126" t="n">
@@ -18639,7 +18635,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
@@ -18677,12 +18673,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18707,12 +18703,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -18722,16 +18718,16 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
@@ -18743,19 +18739,19 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="T127" t="n">
-        <v>19500</v>
+        <v>5054500</v>
       </c>
       <c r="U127" t="n">
-        <v>842400</v>
+        <v>5812675</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -18784,12 +18780,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
@@ -18809,7 +18805,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL127" t="inlineStr"/>
+      <c r="AL127" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -18827,12 +18827,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18857,12 +18857,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -18872,16 +18872,16 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -18893,19 +18893,19 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="T128" t="n">
-        <v>9750</v>
+        <v>5054500</v>
       </c>
       <c r="U128" t="n">
-        <v>421200</v>
+        <v>5812675</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -18934,12 +18934,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
@@ -18959,7 +18959,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL128" t="inlineStr"/>
+      <c r="AL128" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -18977,12 +18981,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -19007,12 +19011,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -19043,19 +19047,19 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="T129" t="n">
-        <v>5054500</v>
+        <v>131650000</v>
       </c>
       <c r="U129" t="n">
-        <v>5812675</v>
+        <v>151397500</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -19084,12 +19088,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
@@ -19101,7 +19105,7 @@
       <c r="AI129" t="inlineStr"/>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -19131,12 +19135,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -19156,17 +19160,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -19176,20 +19180,20 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>1</v>
+        <v>489.8</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q130" t="n">
@@ -19197,19 +19201,19 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="T130" t="n">
-        <v>5054500</v>
+        <v>25000</v>
       </c>
       <c r="U130" t="n">
-        <v>5812675</v>
+        <v>12245000</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -19238,12 +19242,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr"/>
@@ -19255,7 +19259,7 @@
       <c r="AI130" t="inlineStr"/>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -19287,12 +19291,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>02 Oct 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -19312,12 +19316,12 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
@@ -19358,14 +19362,14 @@
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T131" t="n">
-        <v>131650000</v>
+        <v>46750000</v>
       </c>
       <c r="U131" t="n">
-        <v>151397500</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -19394,12 +19398,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-01 13:42:08</t>
+          <t>2026-10-02 09:38:18</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL131"/>
+  <dimension ref="A1:AL133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17173,12 +17173,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>034/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17203,12 +17203,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>14 Sep 2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -17218,20 +17218,20 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>240</v>
+        <v>1</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q117" t="n">
@@ -17239,19 +17239,19 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="T117" t="n">
-        <v>7500</v>
+        <v>5054500</v>
       </c>
       <c r="U117" t="n">
-        <v>1620000</v>
+        <v>5812675</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -17280,12 +17280,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17305,7 +17305,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL117" t="inlineStr"/>
+      <c r="AL117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -17323,12 +17327,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17353,12 +17357,12 @@
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -17368,20 +17372,20 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q118" t="n">
@@ -17389,19 +17393,19 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="T118" t="n">
-        <v>19500</v>
+        <v>5054500</v>
       </c>
       <c r="U118" t="n">
-        <v>421200</v>
+        <v>5812675</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -17430,12 +17434,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17455,7 +17459,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL118" t="inlineStr"/>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -17473,12 +17481,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17503,12 +17511,12 @@
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -17518,20 +17526,20 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O119" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="P119" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q119" t="n">
@@ -17539,19 +17547,19 @@
       </c>
       <c r="R119" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="T119" t="n">
-        <v>15600</v>
+        <v>131650000</v>
       </c>
       <c r="U119" t="n">
-        <v>336960</v>
+        <v>151397500</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -17580,12 +17588,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -17597,7 +17605,7 @@
       <c r="AI119" t="inlineStr"/>
       <c r="AJ119" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK119" t="inlineStr">
@@ -17605,7 +17613,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL119" t="inlineStr"/>
+      <c r="AL119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -17623,12 +17635,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17648,17 +17660,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -17668,20 +17680,20 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>48</v>
+        <v>489.8</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q120" t="n">
@@ -17689,19 +17701,19 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="T120" t="n">
-        <v>13000</v>
+        <v>25000</v>
       </c>
       <c r="U120" t="n">
-        <v>561600</v>
+        <v>12245000</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -17730,12 +17742,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -17747,7 +17759,7 @@
       <c r="AI120" t="inlineStr"/>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -17755,7 +17767,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL120" t="inlineStr"/>
+      <c r="AL120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -17773,12 +17789,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17798,17 +17814,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -17818,20 +17834,20 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q121" t="n">
@@ -17839,19 +17855,19 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T121" t="n">
-        <v>84500</v>
+        <v>46750000</v>
       </c>
       <c r="U121" t="n">
-        <v>3650400</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -17880,12 +17896,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
@@ -17897,7 +17913,7 @@
       <c r="AI121" t="inlineStr"/>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -17905,11 +17921,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL121" t="inlineStr"/>
+      <c r="AL121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="122">
-      <c r="A122" t="n">
-        <v>7201250141</v>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -17973,11 +17995,11 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Coca Cola</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -17998,10 +18020,10 @@
         </is>
       </c>
       <c r="T122" t="n">
-        <v>9750</v>
+        <v>32500</v>
       </c>
       <c r="U122" t="n">
-        <v>421200</v>
+        <v>234000</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -18035,7 +18057,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
@@ -18058,8 +18080,10 @@
       <c r="AL122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="n">
-        <v>7201250141</v>
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -18123,15 +18147,15 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Fanta</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q123" t="n">
@@ -18148,10 +18172,10 @@
         </is>
       </c>
       <c r="T123" t="n">
-        <v>9750</v>
+        <v>84500</v>
       </c>
       <c r="U123" t="n">
-        <v>421200</v>
+        <v>608400</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -18185,7 +18209,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
@@ -18208,8 +18232,10 @@
       <c r="AL123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="n">
-        <v>7201250141</v>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -18273,15 +18299,15 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>48</v>
+        <v>9</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q124" t="n">
@@ -18298,10 +18324,10 @@
         </is>
       </c>
       <c r="T124" t="n">
-        <v>9750</v>
+        <v>26000</v>
       </c>
       <c r="U124" t="n">
-        <v>421200</v>
+        <v>210600</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -18335,7 +18361,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
@@ -18358,8 +18384,10 @@
       <c r="AL124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="n">
-        <v>7201250141</v>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -18423,15 +18451,15 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q125" t="n">
@@ -18439,19 +18467,19 @@
       </c>
       <c r="R125" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S125" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T125" t="n">
-        <v>19500</v>
+        <v>9750</v>
       </c>
       <c r="U125" t="n">
-        <v>842400</v>
+        <v>631800</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -18485,7 +18513,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
@@ -18508,8 +18536,10 @@
       <c r="AL125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="n">
-        <v>7201250141</v>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -18573,15 +18603,15 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q126" t="n">
@@ -18589,19 +18619,19 @@
       </c>
       <c r="R126" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S126" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T126" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="U126" t="n">
-        <v>421200</v>
+        <v>210600</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -18635,7 +18665,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
@@ -18658,8 +18688,10 @@
       <c r="AL126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="n">
-        <v>7201250141</v>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -18673,12 +18705,12 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -18703,12 +18735,12 @@
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -18718,20 +18750,20 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="O127" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q127" t="n">
@@ -18739,19 +18771,19 @@
       </c>
       <c r="R127" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S127" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T127" t="n">
-        <v>5054500</v>
+        <v>13000</v>
       </c>
       <c r="U127" t="n">
-        <v>5812675</v>
+        <v>842400</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -18780,12 +18812,12 @@
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
@@ -18805,15 +18837,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL127" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="n">
-        <v>7201250141</v>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -18827,12 +18857,12 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -18857,12 +18887,12 @@
       </c>
       <c r="J128" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
@@ -18872,16 +18902,16 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -18893,19 +18923,19 @@
       </c>
       <c r="R128" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S128" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T128" t="n">
-        <v>5054500</v>
+        <v>9750</v>
       </c>
       <c r="U128" t="n">
-        <v>5812675</v>
+        <v>631800</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -18934,12 +18964,12 @@
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
@@ -18959,15 +18989,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL128" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="n">
-        <v>7201250141</v>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -18981,12 +19009,12 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>02 Oct 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -19011,12 +19039,12 @@
       </c>
       <c r="J129" t="inlineStr">
         <is>
-          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -19026,16 +19054,16 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -19047,19 +19075,19 @@
       </c>
       <c r="R129" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S129" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T129" t="n">
-        <v>131650000</v>
+        <v>19500</v>
       </c>
       <c r="U129" t="n">
-        <v>151397500</v>
+        <v>1263600</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -19088,12 +19116,12 @@
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
@@ -19105,7 +19133,7 @@
       <c r="AI129" t="inlineStr"/>
       <c r="AJ129" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK129" t="inlineStr">
@@ -19113,15 +19141,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL129" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="n">
-        <v>7201250141</v>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -19135,12 +19161,12 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -19160,17 +19186,17 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -19180,20 +19206,20 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>489.8</v>
+        <v>36</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q130" t="n">
@@ -19201,19 +19227,19 @@
       </c>
       <c r="R130" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S130" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T130" t="n">
-        <v>25000</v>
+        <v>32500</v>
       </c>
       <c r="U130" t="n">
-        <v>12245000</v>
+        <v>1053000</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -19242,12 +19268,12 @@
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr"/>
@@ -19259,7 +19285,7 @@
       <c r="AI130" t="inlineStr"/>
       <c r="AJ130" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK130" t="inlineStr">
@@ -19267,11 +19293,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL130" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -19291,12 +19313,12 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -19316,17 +19338,17 @@
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -19336,16 +19358,16 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -19357,19 +19379,19 @@
       </c>
       <c r="R131" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S131" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T131" t="n">
-        <v>46750000</v>
+        <v>32500</v>
       </c>
       <c r="U131" t="n">
-        <v>53762499.99999999</v>
+        <v>1053000</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -19398,12 +19420,12 @@
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-02 09:38:18</t>
+          <t>2026-10-03 06:55:18</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>
@@ -19415,7 +19437,7 @@
       <c r="AI131" t="inlineStr"/>
       <c r="AJ131" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK131" t="inlineStr">
@@ -19423,11 +19445,311 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL131" t="inlineStr">
+      <c r="AL131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="O132" t="n">
+        <v>36</v>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q132" t="n">
+        <v>100</v>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>2026-10-03</t>
+        </is>
+      </c>
+      <c r="T132" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U132" t="n">
+        <v>1053000</v>
+      </c>
+      <c r="V132" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W132" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X132" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y132" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z132" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB132" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:55:18</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr"/>
+      <c r="AD132" t="inlineStr"/>
+      <c r="AE132" t="inlineStr"/>
+      <c r="AF132" t="inlineStr"/>
+      <c r="AG132" t="inlineStr"/>
+      <c r="AH132" t="inlineStr"/>
+      <c r="AI132" t="inlineStr"/>
+      <c r="AJ132" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK132" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
+      <c r="AL132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>10 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N133" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="O133" t="n">
+        <v>72</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>100</v>
+      </c>
+      <c r="R133" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="T133" t="n">
+        <v>15600</v>
+      </c>
+      <c r="U133" t="n">
+        <v>1010880</v>
+      </c>
+      <c r="V133" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W133" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X133" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y133" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>2026-10-03 06:55:18</t>
+        </is>
+      </c>
+      <c r="AC133" t="inlineStr"/>
+      <c r="AD133" t="inlineStr"/>
+      <c r="AE133" t="inlineStr"/>
+      <c r="AF133" t="inlineStr"/>
+      <c r="AG133" t="inlineStr"/>
+      <c r="AH133" t="inlineStr"/>
+      <c r="AI133" t="inlineStr"/>
+      <c r="AJ133" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK133" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5200,7 +5200,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5480,7 +5480,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5620,7 +5620,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5896,7 +5896,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6034,7 +6034,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6310,7 +6310,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6448,7 +6448,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6586,7 +6586,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6724,7 +6724,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -7000,7 +7000,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7276,7 +7276,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7414,7 +7414,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7552,7 +7552,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7690,7 +7690,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7966,7 +7966,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8104,7 +8104,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8522,7 +8522,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8664,7 +8664,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8806,7 +8806,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8948,7 +8948,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9090,7 +9090,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9232,7 +9232,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9374,7 +9374,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9516,7 +9516,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9658,7 +9658,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9800,7 +9800,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9942,7 +9942,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10084,7 +10084,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10368,7 +10368,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10510,7 +10510,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10954,7 +10954,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11104,7 +11104,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11404,7 +11404,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11554,7 +11554,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11704,7 +11704,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11854,7 +11854,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12154,7 +12154,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12304,7 +12304,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12454,7 +12454,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12604,7 +12604,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12908,7 +12908,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13058,7 +13058,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13208,7 +13208,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13358,7 +13358,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13508,7 +13508,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13658,7 +13658,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14108,7 +14108,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14408,7 +14408,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14562,7 +14562,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14712,7 +14712,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14862,7 +14862,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -15012,7 +15012,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15162,7 +15162,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15312,7 +15312,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15462,7 +15462,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15612,7 +15612,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15762,7 +15762,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15912,7 +15912,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -16062,7 +16062,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16212,7 +16212,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16362,7 +16362,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16514,7 +16514,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16668,7 +16668,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16822,7 +16822,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16976,7 +16976,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17131,7 +17131,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17285,7 +17285,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17439,7 +17439,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17593,7 +17593,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -17747,7 +17747,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -17901,7 +17901,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
@@ -18057,7 +18057,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
@@ -18209,7 +18209,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
@@ -18361,7 +18361,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
@@ -18513,7 +18513,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
@@ -18665,7 +18665,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
@@ -18817,7 +18817,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
@@ -18969,7 +18969,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
@@ -19121,7 +19121,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
@@ -19273,7 +19273,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr"/>
@@ -19425,7 +19425,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>
@@ -19531,12 +19531,12 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-10-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T132" t="n">
@@ -19577,7 +19577,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
@@ -19729,7 +19729,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-03 06:55:18</t>
+          <t>2026-10-03 09:44:40</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr"/>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL133"/>
+  <dimension ref="A1:AL145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1014,7 +1014,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1154,7 +1154,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1854,7 +1854,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2272,7 +2272,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2410,7 +2410,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2960,7 +2960,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3100,7 +3100,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3520,7 +3520,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3798,7 +3798,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4074,7 +4074,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>021/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E34" s="1" t="n">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen</t>
         </is>
       </c>
       <c r="K34" s="1" t="n">
@@ -5146,11 +5146,11 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q34" t="n">
@@ -5163,10 +5163,10 @@
         <v>46269</v>
       </c>
       <c r="T34" t="n">
-        <v>5054500</v>
+        <v>175000</v>
       </c>
       <c r="U34" t="n">
-        <v>5812675</v>
+        <v>517500</v>
       </c>
       <c r="V34" t="inlineStr">
         <is>
@@ -5195,12 +5195,12 @@
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5286,7 +5286,7 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P35" t="inlineStr">
         <is>
@@ -5303,10 +5303,10 @@
         <v>46269</v>
       </c>
       <c r="T35" t="n">
-        <v>175000</v>
+        <v>100000</v>
       </c>
       <c r="U35" t="n">
-        <v>517500</v>
+        <v>0</v>
       </c>
       <c r="V35" t="inlineStr">
         <is>
@@ -5335,12 +5335,12 @@
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 95 untuk Penyimpanan APD dan Dokument</t>
+          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5378,11 +5378,11 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>021/BSS-JOB/WS/IX/2026</t>
+          <t>004/BSS-JOB/WS/IV/2026</t>
         </is>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46269</v>
+        <v>46140</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -5400,15 +5400,15 @@
         </is>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>4500011236</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>(Provsum)  Penyediaan kontainer box untuk penyimpanan APD dan Dokumen</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="K36" s="1" t="n">
-        <v>46268</v>
+        <v>46071</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -5430,23 +5430,23 @@
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q36" t="n">
         <v>100</v>
       </c>
       <c r="R36" s="1" t="n">
-        <v>46269</v>
+        <v>46140</v>
       </c>
       <c r="S36" s="1" t="n">
-        <v>46269</v>
+        <v>46140</v>
       </c>
       <c r="T36" t="n">
-        <v>100000</v>
+        <v>773919900</v>
       </c>
       <c r="U36" t="n">
-        <v>0</v>
+        <v>890007885</v>
       </c>
       <c r="V36" t="inlineStr">
         <is>
@@ -5475,12 +5475,12 @@
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>Kontainer box ukuran 52 untuk Penyimpanan APD dan Dokument</t>
+          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5492,13 +5492,11 @@
       <c r="AI36" t="inlineStr"/>
       <c r="AJ36" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
-        </is>
-      </c>
-      <c r="AK36" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK36" t="n">
+        <v>1000025165</v>
       </c>
       <c r="AL36" t="inlineStr"/>
     </row>
@@ -5518,11 +5516,11 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/WS/IV/2026</t>
+          <t>003/BSS-JOB/WS/II/2026</t>
         </is>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -5540,15 +5538,15 @@
         </is>
       </c>
       <c r="I37" t="n">
-        <v>4500011236</v>
+        <v>4500011203</v>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="K37" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -5557,36 +5555,36 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
         </is>
       </c>
       <c r="O37" t="n">
-        <v>1</v>
+        <v>0.524</v>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q37" t="n">
         <v>100</v>
       </c>
       <c r="R37" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="S37" s="1" t="n">
-        <v>46140</v>
+        <v>46072</v>
       </c>
       <c r="T37" t="n">
-        <v>773919900</v>
+        <v>3125000</v>
       </c>
       <c r="U37" t="n">
-        <v>890007885</v>
+        <v>1637500</v>
       </c>
       <c r="V37" t="inlineStr">
         <is>
@@ -5615,12 +5613,12 @@
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>Pengiriman OCTG (Casing 9 5/8" dan Tubing 4 1/2") Celegon-Senoro</t>
+          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5632,11 +5630,11 @@
       <c r="AI37" t="inlineStr"/>
       <c r="AJ37" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK37" t="n">
-        <v>1000025165</v>
+        <v>1000025162</v>
       </c>
       <c r="AL37" t="inlineStr"/>
     </row>
@@ -5700,15 +5698,15 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O38" t="n">
-        <v>0.524</v>
+        <v>4</v>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q38" t="n">
@@ -5721,10 +5719,10 @@
         <v>46072</v>
       </c>
       <c r="T38" t="n">
-        <v>3125000</v>
+        <v>50000</v>
       </c>
       <c r="U38" t="n">
-        <v>1637500</v>
+        <v>200000</v>
       </c>
       <c r="V38" t="inlineStr">
         <is>
@@ -5753,12 +5751,12 @@
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>Kayu Kaso/lata, 5x5x400 Kayu kelas 2  Material pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5842,7 +5840,7 @@
         </is>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P39" t="inlineStr">
         <is>
@@ -5862,7 +5860,7 @@
         <v>50000</v>
       </c>
       <c r="U39" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="V39" t="inlineStr">
         <is>
@@ -5891,12 +5889,12 @@
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>Paku 10 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6029,12 +6027,12 @@
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>Paku 7 cm  pembuatan grouting annulus SNR-19.</t>
+          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6114,15 +6112,15 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="O41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q41" t="n">
@@ -6135,10 +6133,10 @@
         <v>46072</v>
       </c>
       <c r="T41" t="n">
-        <v>50000</v>
+        <v>55500</v>
       </c>
       <c r="U41" t="n">
-        <v>100000</v>
+        <v>55500</v>
       </c>
       <c r="V41" t="inlineStr">
         <is>
@@ -6167,12 +6165,12 @@
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>Paku 5 cm pembuatan grouting annulus SNR-19.</t>
+          <t>Pipa PVC AW 1/2" (4m)</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6252,7 +6250,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="O42" t="n">
@@ -6267,16 +6265,16 @@
         <v>100</v>
       </c>
       <c r="R42" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S42" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T42" t="n">
-        <v>55500</v>
+        <v>75000</v>
       </c>
       <c r="U42" t="n">
-        <v>55500</v>
+        <v>75000</v>
       </c>
       <c r="V42" t="inlineStr">
         <is>
@@ -6305,12 +6303,12 @@
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>Pipa PVC AW 1/2" (4m)</t>
+          <t>Lem pipa PVC</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6390,7 +6388,7 @@
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="O43" t="n">
@@ -6398,23 +6396,23 @@
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m3</t>
         </is>
       </c>
       <c r="Q43" t="n">
         <v>100</v>
       </c>
       <c r="R43" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="S43" s="1" t="n">
-        <v>46275</v>
+        <v>46072</v>
       </c>
       <c r="T43" t="n">
-        <v>75000</v>
+        <v>293750</v>
       </c>
       <c r="U43" t="n">
-        <v>75000</v>
+        <v>293750</v>
       </c>
       <c r="V43" t="inlineStr">
         <is>
@@ -6443,12 +6441,12 @@
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>Lem pipa PVC</t>
+          <t>Pasir</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6528,7 +6526,7 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Batu Agregate A</t>
         </is>
       </c>
       <c r="O44" t="n">
@@ -6549,10 +6547,10 @@
         <v>46072</v>
       </c>
       <c r="T44" t="n">
-        <v>293750</v>
+        <v>400000</v>
       </c>
       <c r="U44" t="n">
-        <v>293750</v>
+        <v>400000</v>
       </c>
       <c r="V44" t="inlineStr">
         <is>
@@ -6581,12 +6579,12 @@
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>Pasir</t>
+          <t>Batu Pecah 1-2</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6666,15 +6664,15 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>Batu Agregate A</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>m3</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q45" t="n">
@@ -6687,10 +6685,10 @@
         <v>46072</v>
       </c>
       <c r="T45" t="n">
-        <v>400000</v>
+        <v>120000</v>
       </c>
       <c r="U45" t="n">
-        <v>400000</v>
+        <v>1440000</v>
       </c>
       <c r="V45" t="inlineStr">
         <is>
@@ -6719,12 +6717,12 @@
       </c>
       <c r="AA45" t="inlineStr">
         <is>
-          <t>Batu Pecah 1-2</t>
+          <t>Semen PC 50 kg</t>
         </is>
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6804,11 +6802,11 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="O46" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="P46" t="inlineStr">
         <is>
@@ -6825,10 +6823,10 @@
         <v>46072</v>
       </c>
       <c r="T46" t="n">
-        <v>120000</v>
+        <v>93750</v>
       </c>
       <c r="U46" t="n">
-        <v>1440000</v>
+        <v>187500</v>
       </c>
       <c r="V46" t="inlineStr">
         <is>
@@ -6857,12 +6855,12 @@
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>Semen PC 50 kg</t>
+          <t>Skop</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -6942,7 +6940,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="O47" t="n">
@@ -6963,10 +6961,10 @@
         <v>46072</v>
       </c>
       <c r="T47" t="n">
-        <v>93750</v>
+        <v>37500</v>
       </c>
       <c r="U47" t="n">
-        <v>187500</v>
+        <v>75000</v>
       </c>
       <c r="V47" t="inlineStr">
         <is>
@@ -6995,12 +6993,12 @@
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>Skop</t>
+          <t>Sendok adukan</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7080,11 +7078,11 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="O48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P48" t="inlineStr">
         <is>
@@ -7104,7 +7102,7 @@
         <v>37500</v>
       </c>
       <c r="U48" t="n">
-        <v>75000</v>
+        <v>37500</v>
       </c>
       <c r="V48" t="inlineStr">
         <is>
@@ -7133,12 +7131,12 @@
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>Sendok adukan</t>
+          <t>Meteran @5m</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7218,15 +7216,15 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="O49" t="n">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>m</t>
         </is>
       </c>
       <c r="Q49" t="n">
@@ -7239,10 +7237,10 @@
         <v>46072</v>
       </c>
       <c r="T49" t="n">
-        <v>37500</v>
+        <v>31250</v>
       </c>
       <c r="U49" t="n">
-        <v>37500</v>
+        <v>1500000</v>
       </c>
       <c r="V49" t="inlineStr">
         <is>
@@ -7271,12 +7269,12 @@
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>Meteran @5m</t>
+          <t>Terpaulin A12</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7360,7 +7358,7 @@
         </is>
       </c>
       <c r="O50" t="n">
-        <v>48</v>
+        <v>20</v>
       </c>
       <c r="P50" t="inlineStr">
         <is>
@@ -7380,7 +7378,7 @@
         <v>31250</v>
       </c>
       <c r="U50" t="n">
-        <v>1500000</v>
+        <v>625000</v>
       </c>
       <c r="V50" t="inlineStr">
         <is>
@@ -7414,7 +7412,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7494,15 +7492,15 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="O51" t="n">
-        <v>20</v>
+        <v>0.2</v>
       </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>Roll</t>
         </is>
       </c>
       <c r="Q51" t="n">
@@ -7515,10 +7513,10 @@
         <v>46072</v>
       </c>
       <c r="T51" t="n">
-        <v>31250</v>
+        <v>712500</v>
       </c>
       <c r="U51" t="n">
-        <v>625000</v>
+        <v>142500</v>
       </c>
       <c r="V51" t="inlineStr">
         <is>
@@ -7547,12 +7545,12 @@
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>Terpaulin A12</t>
+          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7632,15 +7630,15 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Paku Zeng</t>
         </is>
       </c>
       <c r="O52" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Roll</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q52" t="n">
@@ -7653,10 +7651,10 @@
         <v>46072</v>
       </c>
       <c r="T52" t="n">
-        <v>712500</v>
+        <v>50000</v>
       </c>
       <c r="U52" t="n">
-        <v>142500</v>
+        <v>25000</v>
       </c>
       <c r="V52" t="inlineStr">
         <is>
@@ -7685,12 +7683,12 @@
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>Kabel 2x1.5mm NYA/NYM @50m</t>
+          <t>Paku 12 cm</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7785,10 +7783,10 @@
         <v>100</v>
       </c>
       <c r="R53" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="S53" s="1" t="n">
-        <v>46072</v>
+        <v>46275</v>
       </c>
       <c r="T53" t="n">
         <v>50000</v>
@@ -7823,12 +7821,12 @@
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>Paku 12 cm</t>
+          <t>Paku Beton 10 cm</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7864,11 +7862,11 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/WS/II/2026</t>
+          <t>006/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46072</v>
+        <v>46179</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -7882,19 +7880,19 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I54" t="n">
-        <v>4500011203</v>
+        <v>4500011579</v>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Material pembuatan grouting annulus SNR-19.</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46072</v>
+        <v>46177</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -7903,36 +7901,36 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>Paku Zeng</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O54" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q54" t="n">
         <v>100</v>
       </c>
       <c r="R54" s="1" t="n">
-        <v>46275</v>
+        <v>46179</v>
       </c>
       <c r="S54" s="1" t="n">
-        <v>46275</v>
+        <v>46179</v>
       </c>
       <c r="T54" t="n">
-        <v>50000</v>
+        <v>575000</v>
       </c>
       <c r="U54" t="n">
-        <v>25000</v>
+        <v>661250</v>
       </c>
       <c r="V54" t="inlineStr">
         <is>
@@ -7961,12 +7959,12 @@
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>Paku Beton 10 cm</t>
+          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -7982,7 +7980,7 @@
         </is>
       </c>
       <c r="AK54" t="n">
-        <v>1000025162</v>
+        <v>1000025742</v>
       </c>
       <c r="AL54" t="inlineStr"/>
     </row>
@@ -8002,7 +8000,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/WS/VI/2026</t>
+          <t>007/BSS-JOB/WS/VI/2026</t>
         </is>
       </c>
       <c r="E55" s="1" t="n">
@@ -8024,11 +8022,11 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>4500011579</v>
+        <v>4500011580</v>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="K55" s="1" t="n">
@@ -8041,12 +8039,12 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O55" t="n">
@@ -8054,7 +8052,7 @@
       </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q55" t="n">
@@ -8067,10 +8065,10 @@
         <v>46179</v>
       </c>
       <c r="T55" t="n">
-        <v>575000</v>
+        <v>1600000</v>
       </c>
       <c r="U55" t="n">
-        <v>661250</v>
+        <v>1600000</v>
       </c>
       <c r="V55" t="inlineStr">
         <is>
@@ -8099,12 +8097,12 @@
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>Pengadaan Ban Spare part Genset Field Maintenance</t>
+          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8116,35 +8114,35 @@
       <c r="AI55" t="inlineStr"/>
       <c r="AJ55" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK55" t="n">
-        <v>1000025742</v>
+        <v>1000025743</v>
       </c>
       <c r="AL55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>7201250141</v>
+        <v>7207250142</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>S25048TPD</t>
+          <t>S250551FLD-R1</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/WS/VI/2026</t>
+          <t>001/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -8158,19 +8156,19 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>24 Month</t>
         </is>
       </c>
       <c r="I56" t="n">
-        <v>4500011580</v>
+        <v>4599910747</v>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="K56" s="1" t="n">
-        <v>46177</v>
+        <v>46011</v>
       </c>
       <c r="L56" t="inlineStr">
         <is>
@@ -8179,12 +8177,12 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>JASA MOBILISASI</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
         </is>
       </c>
       <c r="O56" t="n">
@@ -8192,23 +8190,23 @@
       </c>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q56" t="n">
         <v>100</v>
       </c>
       <c r="R56" s="1" t="n">
-        <v>46179</v>
+        <v>46011</v>
       </c>
       <c r="S56" s="1" t="n">
-        <v>46179</v>
+        <v>46022</v>
       </c>
       <c r="T56" t="n">
-        <v>1600000</v>
+        <v>400000000</v>
       </c>
       <c r="U56" t="n">
-        <v>1600000</v>
+        <v>400000000</v>
       </c>
       <c r="V56" t="inlineStr">
         <is>
@@ -8237,12 +8235,12 @@
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>Transport Pengangkutan Material   Spare part Genset Field Maintenance</t>
+          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8258,9 +8256,13 @@
         </is>
       </c>
       <c r="AK56" t="n">
-        <v>1000025743</v>
-      </c>
-      <c r="AL56" t="inlineStr"/>
+        <v>1000024733</v>
+      </c>
+      <c r="AL56" t="inlineStr">
+        <is>
+          <t>7207250142-BSS-WO-2026-020</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8278,7 +8280,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>001/BSS-JOB/FLD/XII/2025</t>
+          <t>002/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E57" s="1" t="n">
@@ -8300,11 +8302,11 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>4599910747</v>
+        <v>4500010748</v>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Jasa Mobilisasi Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K57" s="1" t="n">
@@ -8317,20 +8319,20 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>JASA MOBILISASI</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis)</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="P57" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q57" t="n">
@@ -8343,10 +8345,10 @@
         <v>46022</v>
       </c>
       <c r="T57" t="n">
-        <v>400000000</v>
+        <v>75538000</v>
       </c>
       <c r="U57" t="n">
-        <v>400000000</v>
+        <v>29459820</v>
       </c>
       <c r="V57" t="inlineStr">
         <is>
@@ -8375,12 +8377,12 @@
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>Jasa Mob - Demob (Per Unit), Mobilisasi Semua Alat Berat Dari Luar Luwuk ke Luwuk (Monthly Basis) 5 unit Alat Berat Monthly Basis</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8392,15 +8394,15 @@
       <c r="AI57" t="inlineStr"/>
       <c r="AJ57" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK57" t="n">
-        <v>1000024733</v>
+        <v>1000024201</v>
       </c>
       <c r="AL57" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2026-020</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -8420,7 +8422,7 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>002/BSS-JOB/FLD/XII/2025</t>
+          <t>003/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E58" s="1" t="n">
@@ -8442,11 +8444,11 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>4500010748</v>
+        <v>4500010749</v>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K58" s="1" t="n">
@@ -8464,7 +8466,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O58" t="n">
@@ -8485,10 +8487,10 @@
         <v>46022</v>
       </c>
       <c r="T58" t="n">
-        <v>75538000</v>
+        <v>62818000</v>
       </c>
       <c r="U58" t="n">
-        <v>29459820</v>
+        <v>24499020</v>
       </c>
       <c r="V58" t="inlineStr">
         <is>
@@ -8517,12 +8519,12 @@
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8534,15 +8536,15 @@
       <c r="AI58" t="inlineStr"/>
       <c r="AJ58" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK58" t="n">
-        <v>1000024201</v>
+        <v>1000024205</v>
       </c>
       <c r="AL58" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -8562,7 +8564,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>003/BSS-JOB/FLD/XII/2025</t>
+          <t>004/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E59" s="1" t="n">
@@ -8584,11 +8586,11 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>4500010749</v>
+        <v>4500010750</v>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K59" s="1" t="n">
@@ -8606,7 +8608,7 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O59" t="n">
@@ -8627,10 +8629,10 @@
         <v>46022</v>
       </c>
       <c r="T59" t="n">
-        <v>62818000</v>
+        <v>78225000</v>
       </c>
       <c r="U59" t="n">
-        <v>24499020</v>
+        <v>30507750</v>
       </c>
       <c r="V59" t="inlineStr">
         <is>
@@ -8659,12 +8661,12 @@
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8680,11 +8682,11 @@
         </is>
       </c>
       <c r="AK59" t="n">
-        <v>1000024205</v>
+        <v>1000024200</v>
       </c>
       <c r="AL59" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -8704,7 +8706,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>004/BSS-JOB/FLD/XII/2025</t>
+          <t>005/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E60" s="1" t="n">
@@ -8726,11 +8728,11 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>4500010750</v>
+        <v>4500010746</v>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="K60" s="1" t="n">
@@ -8748,7 +8750,7 @@
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O60" t="n">
@@ -8769,10 +8771,10 @@
         <v>46022</v>
       </c>
       <c r="T60" t="n">
-        <v>78225000</v>
+        <v>189241000</v>
       </c>
       <c r="U60" t="n">
-        <v>30507750</v>
+        <v>73803990</v>
       </c>
       <c r="V60" t="inlineStr">
         <is>
@@ -8801,12 +8803,12 @@
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8822,11 +8824,11 @@
         </is>
       </c>
       <c r="AK60" t="n">
-        <v>1000024200</v>
+        <v>1000024199</v>
       </c>
       <c r="AL60" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8848,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/FLD/XII/2025</t>
+          <t>006/BSS-JOB/FLD/XII/2025</t>
         </is>
       </c>
       <c r="E61" s="1" t="n">
@@ -8868,11 +8870,11 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>4500010746</v>
+        <v>4500010745</v>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="K61" s="1" t="n">
@@ -8890,7 +8892,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -8911,10 +8913,10 @@
         <v>46022</v>
       </c>
       <c r="T61" t="n">
-        <v>189241000</v>
+        <v>131224000</v>
       </c>
       <c r="U61" t="n">
-        <v>73803990</v>
+        <v>51177360</v>
       </c>
       <c r="V61" t="inlineStr">
         <is>
@@ -8943,12 +8945,12 @@
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (20-31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -8964,11 +8966,11 @@
         </is>
       </c>
       <c r="AK61" t="n">
-        <v>1000024199</v>
+        <v>1000024198</v>
       </c>
       <c r="AL61" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
@@ -8988,7 +8990,7 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>006/BSS-JOB/FLD/XII/2025</t>
+          <t>007/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E62" s="1" t="n">
@@ -9014,7 +9016,7 @@
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="K62" s="1" t="n">
@@ -9036,7 +9038,7 @@
         </is>
       </c>
       <c r="O62" t="n">
-        <v>0.39</v>
+        <v>1</v>
       </c>
       <c r="P62" t="inlineStr">
         <is>
@@ -9047,16 +9049,16 @@
         <v>100</v>
       </c>
       <c r="R62" s="1" t="n">
-        <v>46011</v>
+        <v>46023</v>
       </c>
       <c r="S62" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="T62" t="n">
         <v>131224000</v>
       </c>
       <c r="U62" t="n">
-        <v>51177360</v>
+        <v>131224000</v>
       </c>
       <c r="V62" t="inlineStr">
         <is>
@@ -9085,12 +9087,12 @@
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (20 - 31 Desember 2025)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9106,7 +9108,7 @@
         </is>
       </c>
       <c r="AK62" t="n">
-        <v>1000024198</v>
+        <v>1000024508</v>
       </c>
       <c r="AL62" t="inlineStr">
         <is>
@@ -9130,11 +9132,11 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>007/BSS-JOB/FLD/I/2026</t>
+          <t>008/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -9152,11 +9154,11 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>4500010745</v>
+        <v>4500010749</v>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 s/d 31 Januari 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K63" s="1" t="n">
@@ -9174,7 +9176,7 @@
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O63" t="n">
@@ -9195,10 +9197,10 @@
         <v>46053</v>
       </c>
       <c r="T63" t="n">
-        <v>131224000</v>
+        <v>62818000</v>
       </c>
       <c r="U63" t="n">
-        <v>131224000</v>
+        <v>62818000</v>
       </c>
       <c r="V63" t="inlineStr">
         <is>
@@ -9227,12 +9229,12 @@
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 s/d 31 Januari 2026)</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9248,11 +9250,11 @@
         </is>
       </c>
       <c r="AK63" t="n">
-        <v>1000024508</v>
+        <v>1000024511</v>
       </c>
       <c r="AL63" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -9272,7 +9274,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/FLD/I/2026</t>
+          <t>009/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E64" s="1" t="n">
@@ -9294,11 +9296,11 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>4500010749</v>
+        <v>4500010746</v>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K64" s="1" t="n">
@@ -9316,7 +9318,7 @@
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O64" t="n">
@@ -9337,10 +9339,10 @@
         <v>46053</v>
       </c>
       <c r="T64" t="n">
-        <v>62818000</v>
+        <v>189241000</v>
       </c>
       <c r="U64" t="n">
-        <v>62818000</v>
+        <v>189241000</v>
       </c>
       <c r="V64" t="inlineStr">
         <is>
@@ -9369,12 +9371,12 @@
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9390,11 +9392,11 @@
         </is>
       </c>
       <c r="AK64" t="n">
-        <v>1000024511</v>
+        <v>1000024510</v>
       </c>
       <c r="AL64" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -9414,11 +9416,11 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>009/BSS-JOB/FLD/I/2026</t>
+          <t>010/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46053</v>
+        <v>46022</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -9436,11 +9438,11 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>4500010746</v>
+        <v>4500010748</v>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K65" s="1" t="n">
@@ -9458,7 +9460,7 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O65" t="n">
@@ -9479,10 +9481,10 @@
         <v>46053</v>
       </c>
       <c r="T65" t="n">
-        <v>189241000</v>
+        <v>75538000</v>
       </c>
       <c r="U65" t="n">
-        <v>189241000</v>
+        <v>75538000</v>
       </c>
       <c r="V65" t="inlineStr">
         <is>
@@ -9511,12 +9513,12 @@
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9532,11 +9534,11 @@
         </is>
       </c>
       <c r="AK65" t="n">
-        <v>1000024510</v>
+        <v>1000024516</v>
       </c>
       <c r="AL65" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -9556,11 +9558,11 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/FLD/I/2026</t>
+          <t>011/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46022</v>
+        <v>46053</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -9578,11 +9580,11 @@
         </is>
       </c>
       <c r="I66" t="n">
-        <v>4500010748</v>
+        <v>4500010750</v>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="K66" s="1" t="n">
@@ -9600,7 +9602,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O66" t="n">
@@ -9621,10 +9623,10 @@
         <v>46053</v>
       </c>
       <c r="T66" t="n">
-        <v>75538000</v>
+        <v>78225000</v>
       </c>
       <c r="U66" t="n">
-        <v>75538000</v>
+        <v>78225000</v>
       </c>
       <c r="V66" t="inlineStr">
         <is>
@@ -9653,12 +9655,12 @@
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
         </is>
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9674,11 +9676,11 @@
         </is>
       </c>
       <c r="AK66" t="n">
-        <v>1000024516</v>
+        <v>1000024509</v>
       </c>
       <c r="AL66" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -9698,11 +9700,11 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/FLD/I/2026</t>
+          <t>012/BSS-JOB/FLD/I/2026</t>
         </is>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46053</v>
+        <v>46063</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -9720,15 +9722,15 @@
         </is>
       </c>
       <c r="I67" t="n">
-        <v>4500010750</v>
+        <v>4500010980</v>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="K67" s="1" t="n">
-        <v>46011</v>
+        <v>46056</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -9737,36 +9739,36 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ON-CALL BASIS</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q67" t="n">
         <v>100</v>
       </c>
       <c r="R67" s="1" t="n">
-        <v>46023</v>
+        <v>46056</v>
       </c>
       <c r="S67" s="1" t="n">
-        <v>46053</v>
+        <v>46062</v>
       </c>
       <c r="T67" t="n">
-        <v>78225000</v>
+        <v>1936000</v>
       </c>
       <c r="U67" t="n">
-        <v>78225000</v>
+        <v>13552000</v>
       </c>
       <c r="V67" t="inlineStr">
         <is>
@@ -9795,12 +9797,12 @@
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 SD 31 JANUARI 2026)</t>
+          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
         </is>
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -9816,11 +9818,11 @@
         </is>
       </c>
       <c r="AK67" t="n">
-        <v>1000024509</v>
+        <v>1000024507</v>
       </c>
       <c r="AL67" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>7207250142-BSS-WO-2025-008</t>
         </is>
       </c>
     </row>
@@ -9840,11 +9842,11 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>012/BSS-JOB/FLD/I/2026</t>
+          <t>014/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46063</v>
+        <v>46081</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -9862,15 +9864,15 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>4500010980</v>
+        <v>4500010749</v>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K68" s="1" t="n">
-        <v>46056</v>
+        <v>46011</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -9879,36 +9881,36 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>ON-CALL BASIS</t>
+          <t>MONTHLY BASIS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat On Call Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Dump Truck 4 Ton min 120PS</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
         </is>
       </c>
       <c r="O68" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q68" t="n">
         <v>100</v>
       </c>
       <c r="R68" s="1" t="n">
-        <v>46056</v>
+        <v>46054</v>
       </c>
       <c r="S68" s="1" t="n">
-        <v>46062</v>
+        <v>46081</v>
       </c>
       <c r="T68" t="n">
-        <v>1936000</v>
+        <v>62818000</v>
       </c>
       <c r="U68" t="n">
-        <v>13552000</v>
+        <v>62818000</v>
       </c>
       <c r="V68" t="inlineStr">
         <is>
@@ -9937,12 +9939,12 @@
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Oncall Basis Dump Truck Untuk Pengangkutan Material Sirtu dari Area Red Zona ke Area Green Zona CPP Senoro</t>
+          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -9958,11 +9960,11 @@
         </is>
       </c>
       <c r="AK68" t="n">
-        <v>1000024507</v>
+        <v>1000024711</v>
       </c>
       <c r="AL68" t="inlineStr">
         <is>
-          <t>7207250142-BSS-WO-2025-008</t>
+          <t>S25051FLD-TOMORI-WO-003</t>
         </is>
       </c>
     </row>
@@ -9982,7 +9984,7 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>014/BSS-JOB/FLD/II/2026</t>
+          <t>013/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E69" s="1" t="n">
@@ -10004,11 +10006,11 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>4500010749</v>
+        <v>4500010748</v>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K69" s="1" t="n">
@@ -10026,7 +10028,7 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Man Lift Capacity 227 Kg</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
         </is>
       </c>
       <c r="O69" t="n">
@@ -10047,10 +10049,10 @@
         <v>46081</v>
       </c>
       <c r="T69" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="U69" t="n">
-        <v>62818000</v>
+        <v>75538000</v>
       </c>
       <c r="V69" t="inlineStr">
         <is>
@@ -10079,12 +10081,12 @@
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>Jasa Sewa Man Lift untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10100,11 +10102,11 @@
         </is>
       </c>
       <c r="AK69" t="n">
-        <v>1000024711</v>
+        <v>1000024712</v>
       </c>
       <c r="AL69" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-003</t>
+          <t>S25051FLD-TOMORI-WO-002</t>
         </is>
       </c>
     </row>
@@ -10124,7 +10126,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/FLD/II/2026</t>
+          <t>015/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E70" s="1" t="n">
@@ -10146,11 +10148,11 @@
         </is>
       </c>
       <c r="I70" t="n">
-        <v>4500010748</v>
+        <v>4500010750</v>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K70" s="1" t="n">
@@ -10168,7 +10170,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Backhoe Loader 70 - 100 HP</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
         </is>
       </c>
       <c r="O70" t="n">
@@ -10189,10 +10191,10 @@
         <v>46081</v>
       </c>
       <c r="T70" t="n">
-        <v>75538000</v>
+        <v>78225000</v>
       </c>
       <c r="U70" t="n">
-        <v>75538000</v>
+        <v>78225000</v>
       </c>
       <c r="V70" t="inlineStr">
         <is>
@@ -10221,12 +10223,12 @@
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>Jasa Sewa Backhoe Loader untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10242,11 +10244,11 @@
         </is>
       </c>
       <c r="AK70" t="n">
-        <v>1000024712</v>
+        <v>1000024709</v>
       </c>
       <c r="AL70" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-002</t>
+          <t>S25051FLD-TOMORI-WO-004</t>
         </is>
       </c>
     </row>
@@ -10266,7 +10268,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>015/BSS-JOB/FLD/II/2026</t>
+          <t>016/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E71" s="1" t="n">
@@ -10288,11 +10290,11 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>4500010750</v>
+        <v>4500010746</v>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K71" s="1" t="n">
@@ -10310,7 +10312,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Vacuum Truck 10.000 L</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
         </is>
       </c>
       <c r="O71" t="n">
@@ -10331,10 +10333,10 @@
         <v>46081</v>
       </c>
       <c r="T71" t="n">
-        <v>78225000</v>
+        <v>189241000</v>
       </c>
       <c r="U71" t="n">
-        <v>78225000</v>
+        <v>189241000</v>
       </c>
       <c r="V71" t="inlineStr">
         <is>
@@ -10363,12 +10365,12 @@
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>Jasa Sewa Vacuum Truck untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10384,11 +10386,11 @@
         </is>
       </c>
       <c r="AK71" t="n">
-        <v>1000024709</v>
+        <v>1000024708</v>
       </c>
       <c r="AL71" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-004</t>
+          <t>S25051FLD-TOMORI-WO-005</t>
         </is>
       </c>
     </row>
@@ -10408,7 +10410,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/FLD/II/2026</t>
+          <t>017/BSS-JOB/FLD/II/2026</t>
         </is>
       </c>
       <c r="E72" s="1" t="n">
@@ -10430,11 +10432,11 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>4500010746</v>
+        <v>4500010745</v>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="K72" s="1" t="n">
@@ -10452,7 +10454,7 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Mobile Crane Capacity 80 T</t>
+          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
         </is>
       </c>
       <c r="O72" t="n">
@@ -10473,10 +10475,10 @@
         <v>46081</v>
       </c>
       <c r="T72" t="n">
-        <v>189241000</v>
+        <v>131224000</v>
       </c>
       <c r="U72" t="n">
-        <v>189241000</v>
+        <v>131224000</v>
       </c>
       <c r="V72" t="inlineStr">
         <is>
@@ -10505,12 +10507,12 @@
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>Jasa sewa Crane Mobile Telescopic untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode (01 - 28 Februari 2026)</t>
+          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
         </is>
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10526,35 +10528,37 @@
         </is>
       </c>
       <c r="AK72" t="n">
-        <v>1000024708</v>
+        <v>1000024727</v>
       </c>
       <c r="AL72" t="inlineStr">
         <is>
-          <t>S25051FLD-TOMORI-WO-005</t>
+          <t>S25051FLD-TOMORI-WO-006</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>7207250142</v>
+        <v>7201250141</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Pendukung Operasional Senoro dan Tiaka</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>S250551FLD-R1</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>017/BSS-JOB/FLD/II/2026</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="n">
-        <v>46081</v>
+          <t>016/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -10568,19 +10572,23 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>24 Month</t>
-        </is>
-      </c>
-      <c r="I73" t="n">
-        <v>4500010745</v>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode 20 Desember 2025 - 31 Maret 2026 (01 - 28 Februari 2026)</t>
-        </is>
-      </c>
-      <c r="K73" s="1" t="n">
-        <v>46011</v>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -10589,36 +10597,40 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Alat Berat Monthly Basis (Include Operator, Rigger, Helper, BBM &amp; Sertifikasi), Truck Mounted Crane (TMC) Capacity 8 T</t>
+          <t>Food &amp; beverage, main course</t>
         </is>
       </c>
       <c r="O73" t="n">
-        <v>1</v>
+        <v>2578</v>
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q73" t="n">
         <v>100</v>
       </c>
-      <c r="R73" s="1" t="n">
-        <v>46054</v>
-      </c>
-      <c r="S73" s="1" t="n">
-        <v>46081</v>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="T73" t="n">
-        <v>131224000</v>
+        <v>65000</v>
       </c>
       <c r="U73" t="n">
-        <v>131224000</v>
+        <v>167570000</v>
       </c>
       <c r="V73" t="inlineStr">
         <is>
@@ -10647,12 +10659,12 @@
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>Jasa Sewa Boom Truck ( TMC ) untuk Support Kegiatan Operation dan Maintenance di Area Senoro dan Tiaka Periode  (01 - 28 Februari 2026)</t>
+          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
         </is>
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10667,14 +10679,12 @@
           <t>Pekerjaan Jasa</t>
         </is>
       </c>
-      <c r="AK73" t="n">
-        <v>1000024727</v>
-      </c>
-      <c r="AL73" t="inlineStr">
-        <is>
-          <t>S25051FLD-TOMORI-WO-006</t>
-        </is>
-      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10742,11 +10752,11 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, main course</t>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
         </is>
       </c>
       <c r="O74" t="n">
-        <v>2578</v>
+        <v>1157</v>
       </c>
       <c r="P74" t="inlineStr">
         <is>
@@ -10767,10 +10777,10 @@
         </is>
       </c>
       <c r="T74" t="n">
-        <v>65000</v>
+        <v>33000</v>
       </c>
       <c r="U74" t="n">
-        <v>167570000</v>
+        <v>38181000</v>
       </c>
       <c r="V74" t="inlineStr">
         <is>
@@ -10799,12 +10809,12 @@
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADDITIONAL CAMP SERVICES, Operational Consumption </t>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
         </is>
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -10842,7 +10852,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>016/BSS-JOB/WS/VIII/2026</t>
+          <t>023/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -10872,7 +10882,7 @@
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
@@ -10887,20 +10897,20 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
         </is>
       </c>
       <c r="O75" t="n">
-        <v>1157</v>
+        <v>22</v>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q75" t="n">
@@ -10917,10 +10927,10 @@
         </is>
       </c>
       <c r="T75" t="n">
-        <v>33000</v>
+        <v>750000</v>
       </c>
       <c r="U75" t="n">
-        <v>38181000</v>
+        <v>16500000</v>
       </c>
       <c r="V75" t="inlineStr">
         <is>
@@ -10949,12 +10959,12 @@
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
         </is>
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -10992,12 +11002,12 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>023/BSS-JOB/WS/VIII/2026</t>
+          <t>022/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -11022,7 +11032,7 @@
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
@@ -11046,11 +11056,11 @@
         </is>
       </c>
       <c r="O76" t="n">
-        <v>22</v>
+        <v>1</v>
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q76" t="n">
@@ -11058,19 +11068,19 @@
       </c>
       <c r="R76" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S76" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T76" t="n">
         <v>750000</v>
       </c>
       <c r="U76" t="n">
-        <v>16500000</v>
+        <v>750000</v>
       </c>
       <c r="V76" t="inlineStr">
         <is>
@@ -11099,12 +11109,12 @@
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>Personel GS - Koordinator Lapangan atas Nama Nur Afiata</t>
+          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
         </is>
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11187,12 +11197,12 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O77" t="n">
@@ -11217,10 +11227,10 @@
         </is>
       </c>
       <c r="T77" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="U77" t="n">
-        <v>750000</v>
+        <v>1600000</v>
       </c>
       <c r="V77" t="inlineStr">
         <is>
@@ -11249,12 +11259,12 @@
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>Tenaga Civil Engineer melakukan survey di Lokasi Sumur Senoro 16</t>
+          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
         </is>
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11292,12 +11302,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>022/BSS-JOB/WS/IX/2026</t>
+          <t>024/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -11322,7 +11332,7 @@
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Civil Enginner melakukan Survey untuk pengukuran dudukan X-Mas Tree di Sumur Senoro 16)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -11337,20 +11347,20 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Operator Crane</t>
         </is>
       </c>
       <c r="O78" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q78" t="n">
@@ -11358,19 +11368,19 @@
       </c>
       <c r="R78" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S78" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="T78" t="n">
-        <v>1600000</v>
+        <v>750000</v>
       </c>
       <c r="U78" t="n">
-        <v>1600000</v>
+        <v>9750000</v>
       </c>
       <c r="V78" t="inlineStr">
         <is>
@@ -11399,12 +11409,12 @@
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Double Cabin DN 8890 RG untuk transportasi Survey ke Lokasi</t>
+          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
         </is>
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11496,7 +11506,7 @@
         </is>
       </c>
       <c r="O79" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="P79" t="inlineStr">
         <is>
@@ -11508,19 +11518,19 @@
       </c>
       <c r="R79" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S79" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T79" t="n">
         <v>750000</v>
       </c>
       <c r="U79" t="n">
-        <v>9750000</v>
+        <v>6750000</v>
       </c>
       <c r="V79" t="inlineStr">
         <is>
@@ -11549,12 +11559,12 @@
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Rasid A Laugi</t>
+          <t>Operator Crane Shift Siang atas nama Wanhar</t>
         </is>
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11646,7 +11656,7 @@
         </is>
       </c>
       <c r="O80" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="P80" t="inlineStr">
         <is>
@@ -11658,7 +11668,7 @@
       </c>
       <c r="R80" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S80" t="inlineStr">
@@ -11670,7 +11680,7 @@
         <v>750000</v>
       </c>
       <c r="U80" t="n">
-        <v>6750000</v>
+        <v>12750000</v>
       </c>
       <c r="V80" t="inlineStr">
         <is>
@@ -11699,12 +11709,12 @@
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Siang atas nama Wanhar</t>
+          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
         </is>
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11792,11 +11802,11 @@
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>Operator Crane</t>
+          <t>Rigger</t>
         </is>
       </c>
       <c r="O81" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="P81" t="inlineStr">
         <is>
@@ -11817,10 +11827,10 @@
         </is>
       </c>
       <c r="T81" t="n">
-        <v>750000</v>
+        <v>650000</v>
       </c>
       <c r="U81" t="n">
-        <v>12750000</v>
+        <v>14300000</v>
       </c>
       <c r="V81" t="inlineStr">
         <is>
@@ -11849,12 +11859,12 @@
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>Operator Crane Shift Malam  atas nama Ilsan Adjedar</t>
+          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
         </is>
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -11946,7 +11956,7 @@
         </is>
       </c>
       <c r="O82" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="P82" t="inlineStr">
         <is>
@@ -11970,7 +11980,7 @@
         <v>650000</v>
       </c>
       <c r="U82" t="n">
-        <v>14300000</v>
+        <v>13650000</v>
       </c>
       <c r="V82" t="inlineStr">
         <is>
@@ -11999,12 +12009,12 @@
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Siang  atas nama Tison</t>
+          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
         </is>
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12092,11 +12102,11 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>Rigger</t>
+          <t>Mechanic/ Electrician</t>
         </is>
       </c>
       <c r="O83" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P83" t="inlineStr">
         <is>
@@ -12108,7 +12118,7 @@
       </c>
       <c r="R83" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S83" t="inlineStr">
@@ -12117,10 +12127,10 @@
         </is>
       </c>
       <c r="T83" t="n">
-        <v>650000</v>
+        <v>600000</v>
       </c>
       <c r="U83" t="n">
-        <v>13650000</v>
+        <v>13800000</v>
       </c>
       <c r="V83" t="inlineStr">
         <is>
@@ -12149,12 +12159,12 @@
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>Rigger  Crane Shift Malam  atas nama Agus Dg Mangata</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
         </is>
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12299,12 +12309,12 @@
       </c>
       <c r="AA84" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Sugeng</t>
+          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
         </is>
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12342,7 +12352,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>024/BSS-JOB/WS/VIII/2026</t>
+          <t>024A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -12392,15 +12402,15 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician</t>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="O85" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q85" t="n">
@@ -12417,10 +12427,10 @@
         </is>
       </c>
       <c r="T85" t="n">
-        <v>600000</v>
+        <v>500000</v>
       </c>
       <c r="U85" t="n">
-        <v>13800000</v>
+        <v>10500000</v>
       </c>
       <c r="V85" t="inlineStr">
         <is>
@@ -12449,12 +12459,12 @@
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>Mechanic/ Electrician operasikan Mesin Genset dan Lighting Tower atas nama Ahmad Dhani</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
         </is>
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12474,7 +12484,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL85" t="inlineStr"/>
+      <c r="AL85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12492,7 +12506,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>024A/BSS-JOB/WS/VIII/2026</t>
+          <t>026/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -12522,7 +12536,7 @@
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
@@ -12537,16 +12551,16 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O86" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="P86" t="inlineStr">
         <is>
@@ -12558,7 +12572,7 @@
       </c>
       <c r="R86" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S86" t="inlineStr">
@@ -12567,10 +12581,10 @@
         </is>
       </c>
       <c r="T86" t="n">
-        <v>500000</v>
+        <v>1600000</v>
       </c>
       <c r="U86" t="n">
-        <v>10500000</v>
+        <v>40000000</v>
       </c>
       <c r="V86" t="inlineStr">
         <is>
@@ -12599,12 +12613,12 @@
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, Operator Heavy Equipment (Vacuum Truck)</t>
+          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12624,11 +12638,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL86" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12700,7 +12710,7 @@
         </is>
       </c>
       <c r="O87" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="P87" t="inlineStr">
         <is>
@@ -12717,14 +12727,14 @@
       </c>
       <c r="S87" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="T87" t="n">
         <v>1600000</v>
       </c>
       <c r="U87" t="n">
-        <v>40000000</v>
+        <v>24000000</v>
       </c>
       <c r="V87" t="inlineStr">
         <is>
@@ -12753,12 +12763,12 @@
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1259 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -12850,7 +12860,7 @@
         </is>
       </c>
       <c r="O88" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="P88" t="inlineStr">
         <is>
@@ -12867,14 +12877,14 @@
       </c>
       <c r="S88" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T88" t="n">
         <v>1600000</v>
       </c>
       <c r="U88" t="n">
-        <v>24000000</v>
+        <v>40000000</v>
       </c>
       <c r="V88" t="inlineStr">
         <is>
@@ -12903,12 +12913,12 @@
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1258 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13000,7 +13010,7 @@
         </is>
       </c>
       <c r="O89" t="n">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="P89" t="inlineStr">
         <is>
@@ -13012,19 +13022,19 @@
       </c>
       <c r="R89" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="S89" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T89" t="n">
         <v>1600000</v>
       </c>
       <c r="U89" t="n">
-        <v>40000000</v>
+        <v>6400000</v>
       </c>
       <c r="V89" t="inlineStr">
         <is>
@@ -13053,12 +13063,12 @@
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Kendaraan Innova DN 1257 CL Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13146,11 +13156,11 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="P90" t="inlineStr">
         <is>
@@ -13162,19 +13172,19 @@
       </c>
       <c r="R90" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S90" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T90" t="n">
         <v>1600000</v>
       </c>
       <c r="U90" t="n">
-        <v>6400000</v>
+        <v>40000000</v>
       </c>
       <c r="V90" t="inlineStr">
         <is>
@@ -13203,12 +13213,12 @@
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>Kendaraan Pajero DN 1904 RA Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13300,7 +13310,7 @@
         </is>
       </c>
       <c r="O91" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="P91" t="inlineStr">
         <is>
@@ -13312,7 +13322,7 @@
       </c>
       <c r="R91" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S91" t="inlineStr">
@@ -13324,7 +13334,7 @@
         <v>1600000</v>
       </c>
       <c r="U91" t="n">
-        <v>40000000</v>
+        <v>35200000</v>
       </c>
       <c r="V91" t="inlineStr">
         <is>
@@ -13353,12 +13363,12 @@
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1916 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13396,7 +13406,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>026/BSS-JOB/WS/VIII/2026</t>
+          <t>027/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -13426,7 +13436,7 @@
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
@@ -13441,16 +13451,16 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="P92" t="inlineStr">
         <is>
@@ -13467,14 +13477,14 @@
       </c>
       <c r="S92" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="T92" t="n">
-        <v>1600000</v>
+        <v>8500000</v>
       </c>
       <c r="U92" t="n">
-        <v>35200000</v>
+        <v>59500000</v>
       </c>
       <c r="V92" t="inlineStr">
         <is>
@@ -13503,12 +13513,12 @@
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>Kendaraan Hilux DN 1917 CH Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13600,7 +13610,7 @@
         </is>
       </c>
       <c r="O93" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="P93" t="inlineStr">
         <is>
@@ -13612,19 +13622,19 @@
       </c>
       <c r="R93" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S93" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T93" t="n">
         <v>8500000</v>
       </c>
       <c r="U93" t="n">
-        <v>59500000</v>
+        <v>76500000</v>
       </c>
       <c r="V93" t="inlineStr">
         <is>
@@ -13653,12 +13663,12 @@
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Crane Tadano 70 ton Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13746,11 +13756,11 @@
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>crane min 70 ton, call out, (hanya unit)</t>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
         </is>
       </c>
       <c r="O94" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="P94" t="inlineStr">
         <is>
@@ -13762,7 +13772,7 @@
       </c>
       <c r="R94" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S94" t="inlineStr">
@@ -13771,10 +13781,10 @@
         </is>
       </c>
       <c r="T94" t="n">
-        <v>8500000</v>
+        <v>2750000</v>
       </c>
       <c r="U94" t="n">
-        <v>76500000</v>
+        <v>57750000</v>
       </c>
       <c r="V94" t="inlineStr">
         <is>
@@ -13803,12 +13813,12 @@
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Crane Sany 100 Ton untuk menggantikan Crane Tadano 70 Ton yang rusak</t>
+          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -13846,7 +13856,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>027/BSS-JOB/WS/VIII/2026</t>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -13871,17 +13881,17 @@
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>45000000test</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode Agustus 2026)</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
@@ -13891,20 +13901,20 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O95" t="n">
-        <v>21</v>
+        <v>1800</v>
       </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q95" t="n">
@@ -13912,7 +13922,7 @@
       </c>
       <c r="R95" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S95" t="inlineStr">
@@ -13921,10 +13931,10 @@
         </is>
       </c>
       <c r="T95" t="n">
-        <v>2750000</v>
+        <v>7500</v>
       </c>
       <c r="U95" t="n">
-        <v>57750000</v>
+        <v>12150000</v>
       </c>
       <c r="V95" t="inlineStr">
         <is>
@@ -13953,12 +13963,12 @@
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>Vacuum Truck  5000 L DN 8806 CH untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -13970,7 +13980,7 @@
       <c r="AI95" t="inlineStr"/>
       <c r="AJ95" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK95" t="inlineStr">
@@ -14046,11 +14056,11 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>Aqua 600 ml</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>1800</v>
+        <v>18</v>
       </c>
       <c r="P96" t="inlineStr">
         <is>
@@ -14062,7 +14072,7 @@
       </c>
       <c r="R96" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S96" t="inlineStr">
@@ -14071,10 +14081,10 @@
         </is>
       </c>
       <c r="T96" t="n">
-        <v>7500</v>
+        <v>53300</v>
       </c>
       <c r="U96" t="n">
-        <v>12150000</v>
+        <v>863460</v>
       </c>
       <c r="V96" t="inlineStr">
         <is>
@@ -14103,12 +14113,12 @@
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14146,7 +14156,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>028/BSS-JOB/WS/VIII/2026</t>
+          <t>031/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -14171,17 +14181,17 @@
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>45000000test</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
@@ -14191,20 +14201,20 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>Aqua Galon Segel</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="O97" t="n">
-        <v>18</v>
+        <v>316.8</v>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q97" t="n">
@@ -14212,7 +14222,7 @@
       </c>
       <c r="R97" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S97" t="inlineStr">
@@ -14221,10 +14231,10 @@
         </is>
       </c>
       <c r="T97" t="n">
-        <v>53300</v>
+        <v>25000</v>
       </c>
       <c r="U97" t="n">
-        <v>863460</v>
+        <v>7920000</v>
       </c>
       <c r="V97" t="inlineStr">
         <is>
@@ -14253,12 +14263,12 @@
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
         </is>
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14270,7 +14280,7 @@
       <c r="AI97" t="inlineStr"/>
       <c r="AJ97" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK97" t="inlineStr">
@@ -14278,7 +14288,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL97" t="inlineStr"/>
+      <c r="AL97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -14296,7 +14310,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>031/BSS-JOB/WS/VIII/2026</t>
+          <t>029/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -14321,17 +14335,17 @@
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, ADDITIONAL CAMP SERVICES Laundry services</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -14341,20 +14355,20 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PENGADAAN MATERIAL</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>316.8</v>
+        <v>250</v>
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q98" t="n">
@@ -14362,19 +14376,19 @@
       </c>
       <c r="R98" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S98" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T98" t="n">
         <v>25000</v>
       </c>
       <c r="U98" t="n">
-        <v>7920000</v>
+        <v>6250000</v>
       </c>
       <c r="V98" t="inlineStr">
         <is>
@@ -14403,12 +14417,12 @@
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES Laundry services , crew di Lokasi</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
         </is>
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14420,7 +14434,7 @@
       <c r="AI98" t="inlineStr"/>
       <c r="AJ98" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK98" t="inlineStr">
@@ -14428,11 +14442,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL98" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -14504,7 +14514,7 @@
         </is>
       </c>
       <c r="O99" t="n">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="P99" t="inlineStr">
         <is>
@@ -14516,19 +14526,19 @@
       </c>
       <c r="R99" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="S99" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="T99" t="n">
         <v>25000</v>
       </c>
       <c r="U99" t="n">
-        <v>6250000</v>
+        <v>5000000</v>
       </c>
       <c r="V99" t="inlineStr">
         <is>
@@ -14557,12 +14567,12 @@
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 70 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
         </is>
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14654,7 +14664,7 @@
         </is>
       </c>
       <c r="O100" t="n">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="P100" t="inlineStr">
         <is>
@@ -14666,19 +14676,19 @@
       </c>
       <c r="R100" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S100" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T100" t="n">
         <v>25000</v>
       </c>
       <c r="U100" t="n">
-        <v>5000000</v>
+        <v>1250000</v>
       </c>
       <c r="V100" t="inlineStr">
         <is>
@@ -14707,12 +14717,12 @@
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Crane 100 Ton</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
         </is>
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14862,7 +14872,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -14958,7 +14968,7 @@
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q102" t="n">
@@ -15007,12 +15017,12 @@
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Genset 80 KVa</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
         </is>
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15108,7 +15118,7 @@
       </c>
       <c r="P103" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ltr</t>
         </is>
       </c>
       <c r="Q103" t="n">
@@ -15157,12 +15167,12 @@
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 05</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
         </is>
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15254,7 +15264,7 @@
         </is>
       </c>
       <c r="O104" t="n">
-        <v>50</v>
+        <v>115</v>
       </c>
       <c r="P104" t="inlineStr">
         <is>
@@ -15271,14 +15281,14 @@
       </c>
       <c r="S104" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="T104" t="n">
         <v>25000</v>
       </c>
       <c r="U104" t="n">
-        <v>1250000</v>
+        <v>2875000</v>
       </c>
       <c r="V104" t="inlineStr">
         <is>
@@ -15307,12 +15317,12 @@
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Lighting Tower 06</t>
+          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15350,7 +15360,7 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>029/BSS-JOB/WS/VIII/2026</t>
+          <t>025/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -15375,17 +15385,17 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>07 Aug 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -15395,20 +15405,20 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>PENGADAAN MATERIAL</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel &amp; Lube Oil include Tranportir fee,</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
         </is>
       </c>
       <c r="O105" t="n">
-        <v>115</v>
+        <v>0.48</v>
       </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Ltr</t>
+          <t>Month</t>
         </is>
       </c>
       <c r="Q105" t="n">
@@ -15416,19 +15426,19 @@
       </c>
       <c r="R105" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="S105" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T105" t="n">
-        <v>25000</v>
+        <v>25000000</v>
       </c>
       <c r="U105" t="n">
-        <v>2875000</v>
+        <v>12000000</v>
       </c>
       <c r="V105" t="inlineStr">
         <is>
@@ -15457,12 +15467,12 @@
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Pengadaan Diesel Fuel include Tranportir fee, untuk Vacuum Truck 5000 L</t>
+          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15474,7 +15484,7 @@
       <c r="AI105" t="inlineStr"/>
       <c r="AJ105" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK105" t="inlineStr">
@@ -15550,7 +15560,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
         </is>
       </c>
       <c r="O106" t="n">
@@ -15575,10 +15585,10 @@
         </is>
       </c>
       <c r="T106" t="n">
-        <v>25000000</v>
+        <v>17500000</v>
       </c>
       <c r="U106" t="n">
-        <v>12000000</v>
+        <v>8400000</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15607,12 +15617,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>Portacamp - Office Camp,  ukuran 40 FT Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15695,16 +15705,16 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers)</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>0.48</v>
+        <v>0.74</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
@@ -15725,10 +15735,10 @@
         </is>
       </c>
       <c r="T107" t="n">
-        <v>17500000</v>
+        <v>60000000</v>
       </c>
       <c r="U107" t="n">
-        <v>8400000</v>
+        <v>44400000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15757,12 +15767,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>Portacamp - Living camp,ukuran 40FT (4 sleepers) Untuk Support Well Services di Lokasi Senoro</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15907,12 +15917,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Siang</t>
+          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -16000,7 +16010,7 @@
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -16025,10 +16035,10 @@
         </is>
       </c>
       <c r="T109" t="n">
-        <v>60000000</v>
+        <v>15000000</v>
       </c>
       <c r="U109" t="n">
-        <v>44400000</v>
+        <v>11100000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -16057,12 +16067,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Genset, cap min 80 KVA, silent type, include maintenance, Operasi Shift Malam</t>
+          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16212,7 +16222,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16250,12 +16260,12 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>025/BSS-JOB/WS/VIII/2026</t>
+          <t>033/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>08 Aug 2026</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -16280,7 +16290,9 @@
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Additional Camp Services, Heavy Transportation &amp; Equipment Rental Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
+Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
+Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -16300,15 +16312,15 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories</t>
+          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>0.74</v>
+        <v>1</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Month</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q111" t="n">
@@ -16316,19 +16328,19 @@
       </c>
       <c r="R111" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="S111" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="T111" t="n">
-        <v>15000000</v>
+        <v>12500000</v>
       </c>
       <c r="U111" t="n">
-        <v>11100000</v>
+        <v>12500000</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -16357,12 +16369,12 @@
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>Light Tower &amp; Lamp 1000 Watt, c/w cable,plug &amp; acessories Operasi Malam</t>
+          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16382,7 +16394,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL111" t="inlineStr"/>
+      <c r="AL111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -16400,12 +16416,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>033/BSS-JOB/WS/VIII/2026</t>
+          <t>023A/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>08 Aug 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -16430,9 +16446,7 @@
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL
-Mobilisasi/ Demobilisasicrane min 70 ton to/from Company
-Wellsite/ Contractor base</t>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
@@ -16447,20 +16461,20 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Mobilisasi/ Demobilisasi crane min 70 ton to/from Company Wellsite/ Contractor base</t>
+          <t>Welder (GTAW)</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q112" t="n">
@@ -16473,14 +16487,14 @@
       </c>
       <c r="S112" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T112" t="n">
-        <v>12500000</v>
+        <v>500000</v>
       </c>
       <c r="U112" t="n">
-        <v>12500000</v>
+        <v>12000000</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -16509,12 +16523,12 @@
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>Mobilisasi Crane Mobile Tadano Kapasitas 70 ton dari Workshop di Lamo ke Cluster B</t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
         </is>
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16663,12 +16677,12 @@
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel HSE Officer  ( Gusti Ngurah Dwipayana ) </t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
         </is>
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16817,12 +16831,12 @@
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Melita Bella ) </t>
+          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
         </is>
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -16864,12 +16878,12 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>023A/BSS-JOB/WS/VIII/2026</t>
+          <t>032/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>30 Aug 2026</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -16894,7 +16908,8 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan Agustus 2026)</t>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -16914,11 +16929,11 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Welder (GTAW)</t>
+          <t>Helper Local (non Skilled)</t>
         </is>
       </c>
       <c r="O115" t="n">
-        <v>24</v>
+        <v>48</v>
       </c>
       <c r="P115" t="inlineStr">
         <is>
@@ -16935,11 +16950,11 @@
       </c>
       <c r="S115" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="T115" t="n">
-        <v>500000</v>
+        <v>250000</v>
       </c>
       <c r="U115" t="n">
         <v>12000000</v>
@@ -16971,12 +16986,12 @@
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Supporting equipment kegiatan Wellservices 2026  Welder = Personel Paramedic  ( Widiya Satuwo ) </t>
+          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17018,12 +17033,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>032/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>30 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -17043,18 +17058,17 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
         <is>
-          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
-Helper Local (non Skilled)</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -17064,20 +17078,20 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Helper Local (non Skilled)</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O116" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="P116" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q116" t="n">
@@ -17085,19 +17099,19 @@
       </c>
       <c r="R116" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S116" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="T116" t="n">
-        <v>250000</v>
+        <v>5054500</v>
       </c>
       <c r="U116" t="n">
-        <v>12000000</v>
+        <v>5812675</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -17126,12 +17140,12 @@
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>Upah harian Flagman Periode 08 sd 30 Agustus 2026</t>
+          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17143,7 +17157,7 @@
       <c r="AI116" t="inlineStr"/>
       <c r="AJ116" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK116" t="inlineStr">
@@ -17173,12 +17187,12 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -17203,12 +17217,12 @@
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L117" t="inlineStr">
@@ -17239,19 +17253,19 @@
       </c>
       <c r="R117" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S117" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="T117" t="n">
-        <v>5054500</v>
+        <v>131650000</v>
       </c>
       <c r="U117" t="n">
-        <v>5812675</v>
+        <v>151397500</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -17280,12 +17294,12 @@
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 19/09/2026</t>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17297,7 +17311,7 @@
       <c r="AI117" t="inlineStr"/>
       <c r="AJ117" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK117" t="inlineStr">
@@ -17327,12 +17341,12 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -17352,17 +17366,17 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -17372,20 +17386,20 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="O118" t="n">
-        <v>1</v>
+        <v>489.8</v>
       </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q118" t="n">
@@ -17393,19 +17407,19 @@
       </c>
       <c r="R118" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S118" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="T118" t="n">
-        <v>5054500</v>
+        <v>25000</v>
       </c>
       <c r="U118" t="n">
-        <v>5812675</v>
+        <v>12245000</v>
       </c>
       <c r="V118" t="inlineStr">
         <is>
@@ -17434,12 +17448,12 @@
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17451,7 +17465,7 @@
       <c r="AI118" t="inlineStr"/>
       <c r="AJ118" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK118" t="inlineStr">
@@ -17481,12 +17495,12 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>02 Oct 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -17506,12 +17520,12 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
@@ -17552,14 +17566,14 @@
       </c>
       <c r="S119" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T119" t="n">
-        <v>131650000</v>
+        <v>46750000</v>
       </c>
       <c r="U119" t="n">
-        <v>151397500</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="V119" t="inlineStr">
         <is>
@@ -17588,12 +17602,12 @@
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -17635,12 +17649,12 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -17660,17 +17674,17 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
@@ -17680,20 +17694,20 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>489.8</v>
+        <v>8</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q120" t="n">
@@ -17701,19 +17715,19 @@
       </c>
       <c r="R120" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S120" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T120" t="n">
-        <v>25000</v>
+        <v>32500</v>
       </c>
       <c r="U120" t="n">
-        <v>12245000</v>
+        <v>234000</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -17742,12 +17756,12 @@
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -17759,7 +17773,7 @@
       <c r="AI120" t="inlineStr"/>
       <c r="AJ120" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK120" t="inlineStr">
@@ -17767,11 +17781,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL120" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -17789,12 +17799,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17814,17 +17824,17 @@
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -17834,20 +17844,20 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q121" t="n">
@@ -17855,19 +17865,19 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T121" t="n">
-        <v>46750000</v>
+        <v>84500</v>
       </c>
       <c r="U121" t="n">
-        <v>53762499.99999999</v>
+        <v>608400</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -17896,12 +17906,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
@@ -17913,7 +17923,7 @@
       <c r="AI121" t="inlineStr"/>
       <c r="AJ121" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK121" t="inlineStr">
@@ -17921,17 +17931,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL121" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL121" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A122" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B122" t="inlineStr">
         <is>
@@ -17995,11 +17999,11 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -18020,10 +18024,10 @@
         </is>
       </c>
       <c r="T122" t="n">
-        <v>32500</v>
+        <v>26000</v>
       </c>
       <c r="U122" t="n">
-        <v>234000</v>
+        <v>210600</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -18057,7 +18061,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
@@ -18080,10 +18084,8 @@
       <c r="AL122" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A123" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B123" t="inlineStr">
         <is>
@@ -18147,11 +18149,11 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>8</v>
+        <v>72</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -18172,10 +18174,10 @@
         </is>
       </c>
       <c r="T123" t="n">
-        <v>84500</v>
+        <v>9750</v>
       </c>
       <c r="U123" t="n">
-        <v>608400</v>
+        <v>631800</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -18209,7 +18211,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
@@ -18232,10 +18234,8 @@
       <c r="AL123" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A124" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B124" t="inlineStr">
         <is>
@@ -18299,11 +18299,11 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -18324,7 +18324,7 @@
         </is>
       </c>
       <c r="T124" t="n">
-        <v>26000</v>
+        <v>19500</v>
       </c>
       <c r="U124" t="n">
         <v>210600</v>
@@ -18361,7 +18361,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
@@ -18384,10 +18384,8 @@
       <c r="AL124" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A125" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B125" t="inlineStr">
         <is>
@@ -18451,7 +18449,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="O125" t="n">
@@ -18476,10 +18474,10 @@
         </is>
       </c>
       <c r="T125" t="n">
-        <v>9750</v>
+        <v>13000</v>
       </c>
       <c r="U125" t="n">
-        <v>631800</v>
+        <v>842400</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -18513,7 +18511,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
@@ -18536,10 +18534,8 @@
       <c r="AL125" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A126" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B126" t="inlineStr">
         <is>
@@ -18603,15 +18599,15 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q126" t="n">
@@ -18628,10 +18624,10 @@
         </is>
       </c>
       <c r="T126" t="n">
-        <v>19500</v>
+        <v>9750</v>
       </c>
       <c r="U126" t="n">
-        <v>210600</v>
+        <v>631800</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -18665,7 +18661,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
@@ -18688,10 +18684,8 @@
       <c r="AL126" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A127" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B127" t="inlineStr">
         <is>
@@ -18755,7 +18749,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -18763,7 +18757,7 @@
       </c>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q127" t="n">
@@ -18780,10 +18774,10 @@
         </is>
       </c>
       <c r="T127" t="n">
-        <v>13000</v>
+        <v>19500</v>
       </c>
       <c r="U127" t="n">
-        <v>842400</v>
+        <v>1263600</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -18817,7 +18811,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
@@ -18840,10 +18834,8 @@
       <c r="AL127" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A128" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B128" t="inlineStr">
         <is>
@@ -18907,11 +18899,11 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="O128" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="P128" t="inlineStr">
         <is>
@@ -18932,10 +18924,10 @@
         </is>
       </c>
       <c r="T128" t="n">
-        <v>9750</v>
+        <v>32500</v>
       </c>
       <c r="U128" t="n">
-        <v>631800</v>
+        <v>1053000</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -18969,7 +18961,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
@@ -18992,10 +18984,8 @@
       <c r="AL128" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A129" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B129" t="inlineStr">
         <is>
@@ -19059,11 +19049,11 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -19084,10 +19074,10 @@
         </is>
       </c>
       <c r="T129" t="n">
-        <v>19500</v>
+        <v>32500</v>
       </c>
       <c r="U129" t="n">
-        <v>1263600</v>
+        <v>1053000</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -19121,7 +19111,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
@@ -19144,10 +19134,8 @@
       <c r="AL129" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A130" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B130" t="inlineStr">
         <is>
@@ -19211,7 +19199,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="O130" t="n">
@@ -19273,7 +19261,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr"/>
@@ -19296,10 +19284,8 @@
       <c r="AL130" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A131" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B131" t="inlineStr">
         <is>
@@ -19363,11 +19349,11 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="O131" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="P131" t="inlineStr">
         <is>
@@ -19388,10 +19374,10 @@
         </is>
       </c>
       <c r="T131" t="n">
-        <v>32500</v>
+        <v>15600</v>
       </c>
       <c r="U131" t="n">
-        <v>1053000</v>
+        <v>1010880</v>
       </c>
       <c r="V131" t="inlineStr">
         <is>
@@ -19425,7 +19411,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>
@@ -19448,10 +19434,8 @@
       <c r="AL131" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A132" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B132" t="inlineStr">
         <is>
@@ -19465,12 +19449,12 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -19495,12 +19479,12 @@
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Sep 2026</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -19515,15 +19499,15 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="O132" t="n">
-        <v>36</v>
+        <v>5</v>
       </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q132" t="n">
@@ -19531,19 +19515,19 @@
       </c>
       <c r="R132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S132" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T132" t="n">
         <v>32500</v>
       </c>
       <c r="U132" t="n">
-        <v>1053000</v>
+        <v>146250</v>
       </c>
       <c r="V132" t="inlineStr">
         <is>
@@ -19572,12 +19556,12 @@
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
@@ -19600,10 +19584,8 @@
       <c r="AL132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A133" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B133" t="inlineStr">
         <is>
@@ -19617,12 +19599,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -19647,12 +19629,12 @@
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Sep 2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -19667,15 +19649,15 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>72</v>
+        <v>6</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q133" t="n">
@@ -19683,19 +19665,19 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T133" t="n">
-        <v>15600</v>
+        <v>84500</v>
       </c>
       <c r="U133" t="n">
-        <v>1010880</v>
+        <v>456300</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -19724,12 +19706,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-03 09:44:40</t>
+          <t>2026-10-03 12:18:01</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr"/>
@@ -19751,6 +19733,1818 @@
       </c>
       <c r="AL133" t="inlineStr"/>
     </row>
+    <row r="134">
+      <c r="A134" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="O134" t="n">
+        <v>5</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>100</v>
+      </c>
+      <c r="R134" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T134" t="n">
+        <v>26000</v>
+      </c>
+      <c r="U134" t="n">
+        <v>117000</v>
+      </c>
+      <c r="V134" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W134" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X134" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y134" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z134" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB134" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr"/>
+      <c r="AD134" t="inlineStr"/>
+      <c r="AE134" t="inlineStr"/>
+      <c r="AF134" t="inlineStr"/>
+      <c r="AG134" t="inlineStr"/>
+      <c r="AH134" t="inlineStr"/>
+      <c r="AI134" t="inlineStr"/>
+      <c r="AJ134" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK134" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N135" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="O135" t="n">
+        <v>72</v>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q135" t="n">
+        <v>100</v>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T135" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U135" t="n">
+        <v>631800</v>
+      </c>
+      <c r="V135" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W135" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X135" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y135" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr"/>
+      <c r="AD135" t="inlineStr"/>
+      <c r="AE135" t="inlineStr"/>
+      <c r="AF135" t="inlineStr"/>
+      <c r="AG135" t="inlineStr"/>
+      <c r="AH135" t="inlineStr"/>
+      <c r="AI135" t="inlineStr"/>
+      <c r="AJ135" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK135" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="O136" t="n">
+        <v>10</v>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q136" t="n">
+        <v>100</v>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T136" t="n">
+        <v>19500</v>
+      </c>
+      <c r="U136" t="n">
+        <v>175500</v>
+      </c>
+      <c r="V136" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W136" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X136" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y136" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z136" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB136" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr"/>
+      <c r="AD136" t="inlineStr"/>
+      <c r="AE136" t="inlineStr"/>
+      <c r="AF136" t="inlineStr"/>
+      <c r="AG136" t="inlineStr"/>
+      <c r="AH136" t="inlineStr"/>
+      <c r="AI136" t="inlineStr"/>
+      <c r="AJ136" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK136" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="O137" t="n">
+        <v>72</v>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q137" t="n">
+        <v>100</v>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T137" t="n">
+        <v>13000</v>
+      </c>
+      <c r="U137" t="n">
+        <v>842400</v>
+      </c>
+      <c r="V137" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W137" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X137" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y137" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr"/>
+      <c r="AD137" t="inlineStr"/>
+      <c r="AE137" t="inlineStr"/>
+      <c r="AF137" t="inlineStr"/>
+      <c r="AG137" t="inlineStr"/>
+      <c r="AH137" t="inlineStr"/>
+      <c r="AI137" t="inlineStr"/>
+      <c r="AJ137" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK137" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="O138" t="n">
+        <v>72</v>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q138" t="n">
+        <v>100</v>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T138" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U138" t="n">
+        <v>631800</v>
+      </c>
+      <c r="V138" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W138" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X138" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y138" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr"/>
+      <c r="AD138" t="inlineStr"/>
+      <c r="AE138" t="inlineStr"/>
+      <c r="AF138" t="inlineStr"/>
+      <c r="AG138" t="inlineStr"/>
+      <c r="AH138" t="inlineStr"/>
+      <c r="AI138" t="inlineStr"/>
+      <c r="AJ138" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK138" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="O139" t="n">
+        <v>72</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>100</v>
+      </c>
+      <c r="R139" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T139" t="n">
+        <v>19500</v>
+      </c>
+      <c r="U139" t="n">
+        <v>1263600</v>
+      </c>
+      <c r="V139" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W139" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X139" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y139" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z139" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA139" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB139" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr"/>
+      <c r="AD139" t="inlineStr"/>
+      <c r="AE139" t="inlineStr"/>
+      <c r="AF139" t="inlineStr"/>
+      <c r="AG139" t="inlineStr"/>
+      <c r="AH139" t="inlineStr"/>
+      <c r="AI139" t="inlineStr"/>
+      <c r="AJ139" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK139" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="O140" t="n">
+        <v>48</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>100</v>
+      </c>
+      <c r="R140" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T140" t="n">
+        <v>15600</v>
+      </c>
+      <c r="U140" t="n">
+        <v>673920</v>
+      </c>
+      <c r="V140" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W140" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X140" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y140" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA140" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC140" t="inlineStr"/>
+      <c r="AD140" t="inlineStr"/>
+      <c r="AE140" t="inlineStr"/>
+      <c r="AF140" t="inlineStr"/>
+      <c r="AG140" t="inlineStr"/>
+      <c r="AH140" t="inlineStr"/>
+      <c r="AI140" t="inlineStr"/>
+      <c r="AJ140" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK140" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="O141" t="n">
+        <v>10</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>100</v>
+      </c>
+      <c r="R141" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T141" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U141" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V141" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W141" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X141" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y141" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr"/>
+      <c r="AD141" t="inlineStr"/>
+      <c r="AE141" t="inlineStr"/>
+      <c r="AF141" t="inlineStr"/>
+      <c r="AG141" t="inlineStr"/>
+      <c r="AH141" t="inlineStr"/>
+      <c r="AI141" t="inlineStr"/>
+      <c r="AJ141" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK141" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="O142" t="n">
+        <v>10</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>100</v>
+      </c>
+      <c r="R142" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T142" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U142" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X142" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC142" t="inlineStr"/>
+      <c r="AD142" t="inlineStr"/>
+      <c r="AE142" t="inlineStr"/>
+      <c r="AF142" t="inlineStr"/>
+      <c r="AG142" t="inlineStr"/>
+      <c r="AH142" t="inlineStr"/>
+      <c r="AI142" t="inlineStr"/>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>020/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>04 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>03 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="O143" t="n">
+        <v>10</v>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>100</v>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="T143" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U143" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X143" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr"/>
+      <c r="AD143" t="inlineStr"/>
+      <c r="AE143" t="inlineStr"/>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="inlineStr"/>
+      <c r="AH143" t="inlineStr"/>
+      <c r="AI143" t="inlineStr"/>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="O144" t="n">
+        <v>5</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>100</v>
+      </c>
+      <c r="R144" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T144" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U144" t="n">
+        <v>146250</v>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X144" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik  di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC144" t="inlineStr"/>
+      <c r="AD144" t="inlineStr"/>
+      <c r="AE144" t="inlineStr"/>
+      <c r="AF144" t="inlineStr"/>
+      <c r="AG144" t="inlineStr"/>
+      <c r="AH144" t="inlineStr"/>
+      <c r="AI144" t="inlineStr"/>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL144" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="O145" t="n">
+        <v>6</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>100</v>
+      </c>
+      <c r="R145" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T145" t="n">
+        <v>84500</v>
+      </c>
+      <c r="U145" t="n">
+        <v>456300</v>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik  di Lokasi Senoro</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>2026-10-03 12:18:01</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr"/>
+      <c r="AD145" t="inlineStr"/>
+      <c r="AE145" t="inlineStr"/>
+      <c r="AF145" t="inlineStr"/>
+      <c r="AG145" t="inlineStr"/>
+      <c r="AH145" t="inlineStr"/>
+      <c r="AI145" t="inlineStr"/>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL145" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL145"/>
+  <dimension ref="A1:AL166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14522,7 +14522,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15633,12 +15633,12 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>037/BSS-JOB/WS/IX/2026</t>
+          <t>035/BSS-JOB/WS/X/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>02 Oct 2026</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -15663,12 +15663,12 @@
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>28 Sep 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -15699,19 +15699,19 @@
       </c>
       <c r="R106" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="S106" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="T106" t="n">
-        <v>5054500</v>
+        <v>131650000</v>
       </c>
       <c r="U106" t="n">
-        <v>5812675</v>
+        <v>151397500</v>
       </c>
       <c r="V106" t="inlineStr">
         <is>
@@ -15740,12 +15740,12 @@
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>(Provsum) Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
         </is>
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15757,7 +15757,7 @@
       <c r="AI106" t="inlineStr"/>
       <c r="AJ106" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK106" t="inlineStr">
@@ -15787,12 +15787,12 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>035/BSS-JOB/WS/X/2026</t>
+          <t>036/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>02 Oct 2026</t>
+          <t>10 Sep 2026</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -15812,12 +15812,12 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4500011739</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
         <is>
-          <t>(Provsum) Akomodasi Hotel untuk Personel JOB Tomori dan Serco  Support Well Services di Senoro</t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="K107" t="inlineStr">
@@ -15832,20 +15832,20 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ADDITIONAL CAMP SERVICES</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Laundry services</t>
         </is>
       </c>
       <c r="O107" t="n">
-        <v>1</v>
+        <v>489.8</v>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q107" t="n">
@@ -15862,10 +15862,10 @@
         </is>
       </c>
       <c r="T107" t="n">
-        <v>131650000</v>
+        <v>25000</v>
       </c>
       <c r="U107" t="n">
-        <v>151397500</v>
+        <v>12245000</v>
       </c>
       <c r="V107" t="inlineStr">
         <is>
@@ -15894,12 +15894,12 @@
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t xml:space="preserve">Akomodasi Personel JOB Tomori dan Serco di Hotel King Amear Periode 07 Agustus 2026 sd 10 September 2026, Sesuai rekap  dan Kwitansi terlampir </t>
+          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
         </is>
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -15941,12 +15941,12 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>036/BSS-JOB/WS/IX/2026</t>
+          <t>030/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>10 Sep 2026</t>
+          <t>31 Aug 2026</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -15966,12 +15966,12 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>4500011739</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
         </is>
       </c>
       <c r="K108" t="inlineStr">
@@ -15986,20 +15986,20 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>ADDITIONAL CAMP SERVICES</t>
+          <t>PROVISIONAL SUM</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>Laundry services</t>
+          <t>At Cost + Fee 15%</t>
         </is>
       </c>
       <c r="O108" t="n">
-        <v>489.8</v>
+        <v>1</v>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q108" t="n">
@@ -16012,14 +16012,14 @@
       </c>
       <c r="S108" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="T108" t="n">
-        <v>25000</v>
+        <v>46750000</v>
       </c>
       <c r="U108" t="n">
-        <v>12245000</v>
+        <v>53762499.99999999</v>
       </c>
       <c r="V108" t="inlineStr">
         <is>
@@ -16048,12 +16048,12 @@
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>Loundry Untuk Personel JOB dan Serco di Hotel King Amear Periode tanggal 07 Agustus sd 10 September 2026</t>
+          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
         </is>
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -16095,12 +16095,12 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>030/BSS-JOB/WS/VIII/2026</t>
+          <t>013/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>31 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -16120,17 +16120,17 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili</t>
+          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>10 Aug 2026</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -16140,20 +16140,20 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>PROVISIONAL SUM</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>At Cost + Fee 15%</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="O109" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q109" t="n">
@@ -16161,19 +16161,19 @@
       </c>
       <c r="R109" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="S109" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="T109" t="n">
-        <v>46750000</v>
+        <v>32500</v>
       </c>
       <c r="U109" t="n">
-        <v>53762499.99999999</v>
+        <v>234000</v>
       </c>
       <c r="V109" t="inlineStr">
         <is>
@@ -16202,12 +16202,12 @@
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>Provsum Akomodasi untuk crew well services di penginapan Yellow Toili Periode tanggal 07 Agustus sd 31 Agustus 2026</t>
+          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
         </is>
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16219,7 +16219,7 @@
       <c r="AI109" t="inlineStr"/>
       <c r="AJ109" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK109" t="inlineStr">
@@ -16227,11 +16227,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -16299,7 +16295,7 @@
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -16324,10 +16320,10 @@
         </is>
       </c>
       <c r="T110" t="n">
-        <v>32500</v>
+        <v>84500</v>
       </c>
       <c r="U110" t="n">
-        <v>234000</v>
+        <v>608400</v>
       </c>
       <c r="V110" t="inlineStr">
         <is>
@@ -16361,7 +16357,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16449,11 +16445,11 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P111" t="inlineStr">
         <is>
@@ -16474,10 +16470,10 @@
         </is>
       </c>
       <c r="T111" t="n">
-        <v>84500</v>
+        <v>26000</v>
       </c>
       <c r="U111" t="n">
-        <v>608400</v>
+        <v>210600</v>
       </c>
       <c r="V111" t="inlineStr">
         <is>
@@ -16511,7 +16507,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16599,11 +16595,11 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="P112" t="inlineStr">
         <is>
@@ -16624,10 +16620,10 @@
         </is>
       </c>
       <c r="T112" t="n">
-        <v>26000</v>
+        <v>9750</v>
       </c>
       <c r="U112" t="n">
-        <v>210600</v>
+        <v>631800</v>
       </c>
       <c r="V112" t="inlineStr">
         <is>
@@ -16661,7 +16657,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16749,11 +16745,11 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>72</v>
+        <v>12</v>
       </c>
       <c r="P113" t="inlineStr">
         <is>
@@ -16774,10 +16770,10 @@
         </is>
       </c>
       <c r="T113" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="U113" t="n">
-        <v>631800</v>
+        <v>210600</v>
       </c>
       <c r="V113" t="inlineStr">
         <is>
@@ -16811,7 +16807,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16899,11 +16895,11 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>12</v>
+        <v>72</v>
       </c>
       <c r="P114" t="inlineStr">
         <is>
@@ -16924,10 +16920,10 @@
         </is>
       </c>
       <c r="T114" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="U114" t="n">
-        <v>210600</v>
+        <v>842400</v>
       </c>
       <c r="V114" t="inlineStr">
         <is>
@@ -16961,7 +16957,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -17049,7 +17045,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="O115" t="n">
@@ -17057,7 +17053,7 @@
       </c>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="Q115" t="n">
@@ -17074,10 +17070,10 @@
         </is>
       </c>
       <c r="T115" t="n">
-        <v>13000</v>
+        <v>9750</v>
       </c>
       <c r="U115" t="n">
-        <v>842400</v>
+        <v>631800</v>
       </c>
       <c r="V115" t="inlineStr">
         <is>
@@ -17111,7 +17107,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17199,7 +17195,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="O116" t="n">
@@ -17224,10 +17220,10 @@
         </is>
       </c>
       <c r="T116" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="U116" t="n">
-        <v>631800</v>
+        <v>1263600</v>
       </c>
       <c r="V116" t="inlineStr">
         <is>
@@ -17261,7 +17257,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17349,11 +17345,11 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="O117" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="P117" t="inlineStr">
         <is>
@@ -17374,10 +17370,10 @@
         </is>
       </c>
       <c r="T117" t="n">
-        <v>19500</v>
+        <v>32500</v>
       </c>
       <c r="U117" t="n">
-        <v>1263600</v>
+        <v>1053000</v>
       </c>
       <c r="V117" t="inlineStr">
         <is>
@@ -17411,7 +17407,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17499,7 +17495,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="O118" t="n">
@@ -17561,7 +17557,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17649,7 +17645,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="O119" t="n">
@@ -17711,7 +17707,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -17799,11 +17795,11 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="O120" t="n">
-        <v>36</v>
+        <v>72</v>
       </c>
       <c r="P120" t="inlineStr">
         <is>
@@ -17824,10 +17820,10 @@
         </is>
       </c>
       <c r="T120" t="n">
-        <v>32500</v>
+        <v>15600</v>
       </c>
       <c r="U120" t="n">
-        <v>1053000</v>
+        <v>1010880</v>
       </c>
       <c r="V120" t="inlineStr">
         <is>
@@ -17861,7 +17857,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -17899,12 +17895,12 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>013/BSS-JOB/WS/VIII/2026</t>
+          <t>020/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>04 Sep 2026</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -17929,12 +17925,12 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>Kebutuhan Logistic Tambahan Kegiatan Well Services</t>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>10 Aug 2026</t>
+          <t>03 Sep 2026</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -17949,15 +17945,15 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="O121" t="n">
-        <v>72</v>
+        <v>5</v>
       </c>
       <c r="P121" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q121" t="n">
@@ -17965,19 +17961,19 @@
       </c>
       <c r="R121" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="S121" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="T121" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="U121" t="n">
-        <v>1010880</v>
+        <v>146250</v>
       </c>
       <c r="V121" t="inlineStr">
         <is>
@@ -18006,12 +18002,12 @@
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t xml:space="preserve">Kebutuhan Logistic di Lapangan </t>
+          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
         </is>
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
@@ -18099,11 +18095,11 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="O122" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P122" t="inlineStr">
         <is>
@@ -18124,10 +18120,10 @@
         </is>
       </c>
       <c r="T122" t="n">
-        <v>32500</v>
+        <v>84500</v>
       </c>
       <c r="U122" t="n">
-        <v>146250</v>
+        <v>456300</v>
       </c>
       <c r="V122" t="inlineStr">
         <is>
@@ -18161,7 +18157,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
@@ -18249,11 +18245,11 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="O123" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P123" t="inlineStr">
         <is>
@@ -18274,10 +18270,10 @@
         </is>
       </c>
       <c r="T123" t="n">
-        <v>84500</v>
+        <v>26000</v>
       </c>
       <c r="U123" t="n">
-        <v>456300</v>
+        <v>117000</v>
       </c>
       <c r="V123" t="inlineStr">
         <is>
@@ -18311,7 +18307,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
@@ -18399,11 +18395,11 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>Nescafe Classic renteng</t>
+          <t>Pop Mie</t>
         </is>
       </c>
       <c r="O124" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="P124" t="inlineStr">
         <is>
@@ -18424,10 +18420,10 @@
         </is>
       </c>
       <c r="T124" t="n">
-        <v>26000</v>
+        <v>9750</v>
       </c>
       <c r="U124" t="n">
-        <v>117000</v>
+        <v>631800</v>
       </c>
       <c r="V124" t="inlineStr">
         <is>
@@ -18461,7 +18457,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
@@ -18549,11 +18545,11 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>Pop Mie</t>
+          <t>Chitato 68 g</t>
         </is>
       </c>
       <c r="O125" t="n">
-        <v>72</v>
+        <v>10</v>
       </c>
       <c r="P125" t="inlineStr">
         <is>
@@ -18574,10 +18570,10 @@
         </is>
       </c>
       <c r="T125" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="U125" t="n">
-        <v>631800</v>
+        <v>175500</v>
       </c>
       <c r="V125" t="inlineStr">
         <is>
@@ -18611,7 +18607,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
@@ -18699,11 +18695,11 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>Chitato 68 g</t>
+          <t>Pocari Sweat</t>
         </is>
       </c>
       <c r="O126" t="n">
-        <v>10</v>
+        <v>72</v>
       </c>
       <c r="P126" t="inlineStr">
         <is>
@@ -18724,10 +18720,10 @@
         </is>
       </c>
       <c r="T126" t="n">
-        <v>19500</v>
+        <v>13000</v>
       </c>
       <c r="U126" t="n">
-        <v>175500</v>
+        <v>842400</v>
       </c>
       <c r="V126" t="inlineStr">
         <is>
@@ -18761,7 +18757,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
@@ -18849,7 +18845,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>Pocari Sweat</t>
+          <t>Teh Kotak</t>
         </is>
       </c>
       <c r="O127" t="n">
@@ -18874,10 +18870,10 @@
         </is>
       </c>
       <c r="T127" t="n">
-        <v>13000</v>
+        <v>9750</v>
       </c>
       <c r="U127" t="n">
-        <v>842400</v>
+        <v>631800</v>
       </c>
       <c r="V127" t="inlineStr">
         <is>
@@ -18911,7 +18907,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
@@ -18999,7 +18995,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>Teh Kotak</t>
+          <t>Susu Beruang</t>
         </is>
       </c>
       <c r="O128" t="n">
@@ -19024,10 +19020,10 @@
         </is>
       </c>
       <c r="T128" t="n">
-        <v>9750</v>
+        <v>19500</v>
       </c>
       <c r="U128" t="n">
-        <v>631800</v>
+        <v>1263600</v>
       </c>
       <c r="V128" t="inlineStr">
         <is>
@@ -19061,7 +19057,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
@@ -19149,11 +19145,11 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>Susu Beruang</t>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
         </is>
       </c>
       <c r="O129" t="n">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="P129" t="inlineStr">
         <is>
@@ -19174,10 +19170,10 @@
         </is>
       </c>
       <c r="T129" t="n">
-        <v>19500</v>
+        <v>15600</v>
       </c>
       <c r="U129" t="n">
-        <v>1263600</v>
+        <v>673920</v>
       </c>
       <c r="V129" t="inlineStr">
         <is>
@@ -19211,7 +19207,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
@@ -19299,11 +19295,11 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>Coffe Nescafe Kaleng 220 ml</t>
+          <t>Roti Sari Roti Coklat</t>
         </is>
       </c>
       <c r="O130" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="P130" t="inlineStr">
         <is>
@@ -19324,10 +19320,10 @@
         </is>
       </c>
       <c r="T130" t="n">
-        <v>15600</v>
+        <v>32500</v>
       </c>
       <c r="U130" t="n">
-        <v>673920</v>
+        <v>292500</v>
       </c>
       <c r="V130" t="inlineStr">
         <is>
@@ -19361,7 +19357,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr"/>
@@ -19449,7 +19445,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Coklat</t>
+          <t>Roti Sari Roti Keju</t>
         </is>
       </c>
       <c r="O131" t="n">
@@ -19511,7 +19507,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>
@@ -19599,7 +19595,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>Roti Sari Roti Keju</t>
+          <t>Roti Tawar Sari Roti</t>
         </is>
       </c>
       <c r="O132" t="n">
@@ -19661,7 +19657,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
@@ -19699,12 +19695,12 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>020/BSS-JOB/WS/IX/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>04 Sep 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -19719,22 +19715,22 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
         <is>
-          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 04/09/2026</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>03 Sep 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -19744,20 +19740,20 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>Roti Tawar Sari Roti</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O133" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q133" t="n">
@@ -19765,19 +19761,19 @@
       </c>
       <c r="R133" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="S133" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="T133" t="n">
-        <v>32500</v>
+        <v>200000</v>
       </c>
       <c r="U133" t="n">
-        <v>292500</v>
+        <v>3200000</v>
       </c>
       <c r="V133" t="inlineStr">
         <is>
@@ -19806,12 +19802,12 @@
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>Kebutuhan Additional Logistik di Lokasi Senoro</t>
+          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr"/>
@@ -19823,7 +19819,7 @@
       <c r="AI133" t="inlineStr"/>
       <c r="AJ133" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK133" t="inlineStr">
@@ -19849,12 +19845,12 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -19869,22 +19865,22 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -19894,20 +19890,20 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>Indocafe Coffemix Renteng</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O134" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q134" t="n">
@@ -19915,19 +19911,19 @@
       </c>
       <c r="R134" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="S134" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="T134" t="n">
-        <v>32500</v>
+        <v>250000</v>
       </c>
       <c r="U134" t="n">
-        <v>146250</v>
+        <v>250000</v>
       </c>
       <c r="V134" t="inlineStr">
         <is>
@@ -19956,12 +19952,12 @@
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>Etimated SUM Kebutuhan Additional Logistik  di Lokasi Senoro</t>
+          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
         </is>
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr"/>
@@ -19973,7 +19969,7 @@
       <c r="AI134" t="inlineStr"/>
       <c r="AJ134" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK134" t="inlineStr">
@@ -19981,11 +19977,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL134" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -20003,12 +19995,12 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>034/BSS-JOB/WS/IX/2026</t>
+          <t>005/BSS-JOB/WS/V/2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>20 May 2026</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -20023,22 +20015,22 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>14 Sep 2026</t>
+          <t>18 May 2026</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -20048,20 +20040,20 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>CAR &amp; TANSPORTATION</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>Kopi Kapal Api 380 g</t>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
         </is>
       </c>
       <c r="O135" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Ea</t>
+          <t>Day</t>
         </is>
       </c>
       <c r="Q135" t="n">
@@ -20069,19 +20061,19 @@
       </c>
       <c r="R135" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="S135" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="T135" t="n">
-        <v>84500</v>
+        <v>1600000</v>
       </c>
       <c r="U135" t="n">
-        <v>456300</v>
+        <v>1600000</v>
       </c>
       <c r="V135" t="inlineStr">
         <is>
@@ -20110,12 +20102,12 @@
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>Etimated SUM Kebutuhan Additional Logistik  di Lokasi Senoro</t>
+          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr"/>
@@ -20127,7 +20119,7 @@
       <c r="AI135" t="inlineStr"/>
       <c r="AJ135" t="inlineStr">
         <is>
-          <t>Pekerjaan Barang / Material</t>
+          <t>Pekerjaan Jasa</t>
         </is>
       </c>
       <c r="AK135" t="inlineStr">
@@ -20135,11 +20127,7 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL135" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="AL135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -20202,20 +20190,20 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O136" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q136" t="n">
@@ -20232,10 +20220,10 @@
         </is>
       </c>
       <c r="T136" t="n">
-        <v>200000</v>
+        <v>350000</v>
       </c>
       <c r="U136" t="n">
-        <v>3200000</v>
+        <v>700000</v>
       </c>
       <c r="V136" t="inlineStr">
         <is>
@@ -20264,12 +20252,12 @@
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>Pengiriman Sample air dari Lokasi Cluster B ke Jakarta</t>
+          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr"/>
@@ -20352,12 +20340,12 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O137" t="n">
@@ -20365,7 +20353,7 @@
       </c>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q137" t="n">
@@ -20373,19 +20361,19 @@
       </c>
       <c r="R137" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="S137" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="T137" t="n">
-        <v>250000</v>
+        <v>3250000</v>
       </c>
       <c r="U137" t="n">
-        <v>250000</v>
+        <v>2925000</v>
       </c>
       <c r="V137" t="inlineStr">
         <is>
@@ -20414,12 +20402,12 @@
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet Sample Air (packing Barang)</t>
+          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
         </is>
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
@@ -20457,12 +20445,12 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -20487,12 +20475,12 @@
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -20523,12 +20511,12 @@
       </c>
       <c r="R138" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S138" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="T138" t="n">
@@ -20564,12 +20552,12 @@
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>Pickup Material di Luwuk tgl 18 Mei 2026 dari Lokasi ke Bandara</t>
+          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
         </is>
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr"/>
@@ -20589,7 +20577,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL138" t="inlineStr"/>
+      <c r="AL138" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -20607,12 +20599,12 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -20637,12 +20629,12 @@
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -20652,20 +20644,20 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
         </is>
       </c>
       <c r="O139" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="P139" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Pallet</t>
         </is>
       </c>
       <c r="Q139" t="n">
@@ -20673,19 +20665,19 @@
       </c>
       <c r="R139" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S139" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="T139" t="n">
-        <v>350000</v>
+        <v>250000</v>
       </c>
       <c r="U139" t="n">
-        <v>700000</v>
+        <v>250000</v>
       </c>
       <c r="V139" t="inlineStr">
         <is>
@@ -20714,12 +20706,12 @@
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>Personel untuk pengurusan Barang di Luwuk dan Personel untuk pengurusan barang di Jakarta</t>
+          <t>Pembuatan Pallet untuk Pop Joint</t>
         </is>
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr"/>
@@ -20739,7 +20731,11 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL139" t="inlineStr"/>
+      <c r="AL139" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -20757,12 +20753,12 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>005/BSS-JOB/WS/V/2026</t>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>20 May 2026</t>
+          <t>04 Aug 2026</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -20787,12 +20783,12 @@
       </c>
       <c r="J140" t="inlineStr">
         <is>
-          <t>Pengiriman Sample Air dari Senoro Cluster B ke Jakarta</t>
+          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>18 May 2026</t>
+          <t>03 Aug 2026</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
@@ -20802,20 +20798,20 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>ESTIMATED SUM</t>
+          <t>PERSONEL ON CALL</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Helper Local (Skilled)</t>
         </is>
       </c>
       <c r="O140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>man-days</t>
         </is>
       </c>
       <c r="Q140" t="n">
@@ -20823,19 +20819,19 @@
       </c>
       <c r="R140" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="S140" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="T140" t="n">
-        <v>3250000</v>
+        <v>350000</v>
       </c>
       <c r="U140" t="n">
-        <v>2925000</v>
+        <v>700000</v>
       </c>
       <c r="V140" t="inlineStr">
         <is>
@@ -20864,12 +20860,12 @@
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>Land transportasi dari bandara Cengkareng ke alamat penerima sample air PT.Haliburton</t>
+          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
         </is>
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr"/>
@@ -20889,13 +20885,15 @@
           <t>-</t>
         </is>
       </c>
-      <c r="AL140" t="inlineStr"/>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>011/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A141" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B141" t="inlineStr">
         <is>
@@ -20954,20 +20952,20 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>MOVING AIR FREIGHT TRANSPORT</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
         </is>
       </c>
       <c r="O141" t="n">
-        <v>1</v>
+        <v>105</v>
       </c>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Kg</t>
         </is>
       </c>
       <c r="Q141" t="n">
@@ -20980,14 +20978,14 @@
       </c>
       <c r="S141" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="T141" t="n">
-        <v>1600000</v>
+        <v>200000</v>
       </c>
       <c r="U141" t="n">
-        <v>1600000</v>
+        <v>21000000</v>
       </c>
       <c r="V141" t="inlineStr">
         <is>
@@ -21016,12 +21014,12 @@
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>Pengambilan Material Pop Joint di Senoro 2 ke Luwuk</t>
+          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
         </is>
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr"/>
@@ -21048,10 +21046,8 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A142" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B142" t="inlineStr">
         <is>
@@ -21110,12 +21106,12 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
         <is>
-          <t>Jasa repacking for Airfreight, estimasi ukuran pallet 100x100x100 cm</t>
+          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
         </is>
       </c>
       <c r="O142" t="n">
@@ -21123,7 +21119,7 @@
       </c>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Pallet</t>
+          <t>Trip</t>
         </is>
       </c>
       <c r="Q142" t="n">
@@ -21131,19 +21127,19 @@
       </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="T142" t="n">
-        <v>250000</v>
+        <v>3250000</v>
       </c>
       <c r="U142" t="n">
-        <v>250000</v>
+        <v>2925000</v>
       </c>
       <c r="V142" t="inlineStr">
         <is>
@@ -21172,12 +21168,12 @@
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>Pembuatan Pallet untuk Pop Joint</t>
+          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
         </is>
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
@@ -21204,10 +21200,8 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A143" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B143" t="inlineStr">
         <is>
@@ -21221,12 +21215,12 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -21241,22 +21235,22 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -21266,20 +21260,20 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>PERSONEL ON CALL</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
         <is>
-          <t>Helper Local (Skilled)</t>
+          <t>Indocafe Coffemix Renteng</t>
         </is>
       </c>
       <c r="O143" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="P143" t="inlineStr">
         <is>
-          <t>man-days</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q143" t="n">
@@ -21287,19 +21281,19 @@
       </c>
       <c r="R143" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S143" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="T143" t="n">
-        <v>350000</v>
+        <v>32500</v>
       </c>
       <c r="U143" t="n">
-        <v>700000</v>
+        <v>146250</v>
       </c>
       <c r="V143" t="inlineStr">
         <is>
@@ -21328,12 +21322,12 @@
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>Personel Handling di Luwuk-Bandara 1 orang dan Jakarta-Bogor 1 orang</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr"/>
@@ -21345,7 +21339,7 @@
       <c r="AI143" t="inlineStr"/>
       <c r="AJ143" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK143" t="inlineStr">
@@ -21355,15 +21349,13 @@
       </c>
       <c r="AL143" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A144" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B144" t="inlineStr">
         <is>
@@ -21377,12 +21369,12 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -21397,22 +21389,22 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
@@ -21422,20 +21414,20 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>MOVING AIR FREIGHT TRANSPORT</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>Jabodetabek - Luwuk/ Senoro atau sebaliknya</t>
+          <t>Kopi Kapal Api 380 g</t>
         </is>
       </c>
       <c r="O144" t="n">
-        <v>105</v>
+        <v>6</v>
       </c>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Kg</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q144" t="n">
@@ -21443,19 +21435,19 @@
       </c>
       <c r="R144" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S144" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="T144" t="n">
-        <v>200000</v>
+        <v>84500</v>
       </c>
       <c r="U144" t="n">
-        <v>21000000</v>
+        <v>456300</v>
       </c>
       <c r="V144" t="inlineStr">
         <is>
@@ -21484,12 +21476,12 @@
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>Cargo Barang   Air Freight Material Pop Joint yang dikirim</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr"/>
@@ -21501,7 +21493,7 @@
       <c r="AI144" t="inlineStr"/>
       <c r="AJ144" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK144" t="inlineStr">
@@ -21511,15 +21503,13 @@
       </c>
       <c r="AL144" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>-</t>
         </is>
       </c>
     </row>
     <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A145" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B145" t="inlineStr">
         <is>
@@ -21533,12 +21523,12 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>037/BSS-JOB/WS/IX/2026</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>04 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -21553,22 +21543,22 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Pengiriman Material Pop Joint dari Senoro 2 ke Lamda Multi Dinamika yard</t>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>03 Aug 2026</t>
+          <t>28 Sep 2026</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
@@ -21583,15 +21573,15 @@
       </c>
       <c r="N145" t="inlineStr">
         <is>
-          <t>Jasa Transportasi dari dan ke Bandara Jasa transportasi menggunakan Pickup Air Port Cengkareng ke Jabodetabek dan sebaliknya</t>
+          <t>Nescafe Classic renteng</t>
         </is>
       </c>
       <c r="O145" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Trip</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q145" t="n">
@@ -21599,19 +21589,19 @@
       </c>
       <c r="R145" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="S145" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="T145" t="n">
-        <v>3250000</v>
+        <v>26000</v>
       </c>
       <c r="U145" t="n">
-        <v>2925000</v>
+        <v>117000</v>
       </c>
       <c r="V145" t="inlineStr">
         <is>
@@ -21640,12 +21630,12 @@
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>Pengiriman barang Pop Joint dari Bandara Cengkareng ke Bogor alamat  Lamda Multi Dinamika yard</t>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
         </is>
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-03 13:03:05</t>
+          <t>2026-10-05 09:43:58</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr"/>
@@ -21657,7 +21647,7 @@
       <c r="AI145" t="inlineStr"/>
       <c r="AJ145" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
+          <t>Pekerjaan Barang / Material</t>
         </is>
       </c>
       <c r="AK145" t="inlineStr">
@@ -21667,7 +21657,3265 @@
       </c>
       <c r="AL145" t="inlineStr">
         <is>
-          <t>011/BSS-JOB/WS/VIII/2026</t>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="O146" t="n">
+        <v>72</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>100</v>
+      </c>
+      <c r="R146" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T146" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U146" t="n">
+        <v>631800</v>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X146" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z146" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB146" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC146" t="inlineStr"/>
+      <c r="AD146" t="inlineStr"/>
+      <c r="AE146" t="inlineStr"/>
+      <c r="AF146" t="inlineStr"/>
+      <c r="AG146" t="inlineStr"/>
+      <c r="AH146" t="inlineStr"/>
+      <c r="AI146" t="inlineStr"/>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL146" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="O147" t="n">
+        <v>10</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>100</v>
+      </c>
+      <c r="R147" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T147" t="n">
+        <v>19500</v>
+      </c>
+      <c r="U147" t="n">
+        <v>175500</v>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X147" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z147" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB147" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr"/>
+      <c r="AD147" t="inlineStr"/>
+      <c r="AE147" t="inlineStr"/>
+      <c r="AF147" t="inlineStr"/>
+      <c r="AG147" t="inlineStr"/>
+      <c r="AH147" t="inlineStr"/>
+      <c r="AI147" t="inlineStr"/>
+      <c r="AJ147" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL147" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N148" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="O148" t="n">
+        <v>72</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>100</v>
+      </c>
+      <c r="R148" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T148" t="n">
+        <v>13000</v>
+      </c>
+      <c r="U148" t="n">
+        <v>842400</v>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X148" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z148" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB148" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC148" t="inlineStr"/>
+      <c r="AD148" t="inlineStr"/>
+      <c r="AE148" t="inlineStr"/>
+      <c r="AF148" t="inlineStr"/>
+      <c r="AG148" t="inlineStr"/>
+      <c r="AH148" t="inlineStr"/>
+      <c r="AI148" t="inlineStr"/>
+      <c r="AJ148" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL148" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N149" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="O149" t="n">
+        <v>72</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>100</v>
+      </c>
+      <c r="R149" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T149" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U149" t="n">
+        <v>631800</v>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr"/>
+      <c r="AD149" t="inlineStr"/>
+      <c r="AE149" t="inlineStr"/>
+      <c r="AF149" t="inlineStr"/>
+      <c r="AG149" t="inlineStr"/>
+      <c r="AH149" t="inlineStr"/>
+      <c r="AI149" t="inlineStr"/>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL149" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N150" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="O150" t="n">
+        <v>72</v>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q150" t="n">
+        <v>100</v>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T150" t="n">
+        <v>19500</v>
+      </c>
+      <c r="U150" t="n">
+        <v>1263600</v>
+      </c>
+      <c r="V150" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X150" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr"/>
+      <c r="AD150" t="inlineStr"/>
+      <c r="AE150" t="inlineStr"/>
+      <c r="AF150" t="inlineStr"/>
+      <c r="AG150" t="inlineStr"/>
+      <c r="AH150" t="inlineStr"/>
+      <c r="AI150" t="inlineStr"/>
+      <c r="AJ150" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL150" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N151" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="O151" t="n">
+        <v>48</v>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q151" t="n">
+        <v>100</v>
+      </c>
+      <c r="R151" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T151" t="n">
+        <v>15600</v>
+      </c>
+      <c r="U151" t="n">
+        <v>673920</v>
+      </c>
+      <c r="V151" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W151" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X151" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y151" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z151" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA151" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB151" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr"/>
+      <c r="AD151" t="inlineStr"/>
+      <c r="AE151" t="inlineStr"/>
+      <c r="AF151" t="inlineStr"/>
+      <c r="AG151" t="inlineStr"/>
+      <c r="AH151" t="inlineStr"/>
+      <c r="AI151" t="inlineStr"/>
+      <c r="AJ151" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL151" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="O152" t="n">
+        <v>10</v>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q152" t="n">
+        <v>100</v>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T152" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U152" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr"/>
+      <c r="AD152" t="inlineStr"/>
+      <c r="AE152" t="inlineStr"/>
+      <c r="AF152" t="inlineStr"/>
+      <c r="AG152" t="inlineStr"/>
+      <c r="AH152" t="inlineStr"/>
+      <c r="AI152" t="inlineStr"/>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL152" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="O153" t="n">
+        <v>10</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>100</v>
+      </c>
+      <c r="R153" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T153" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U153" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V153" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W153" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X153" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y153" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z153" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA153" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB153" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr"/>
+      <c r="AD153" t="inlineStr"/>
+      <c r="AE153" t="inlineStr"/>
+      <c r="AF153" t="inlineStr"/>
+      <c r="AG153" t="inlineStr"/>
+      <c r="AH153" t="inlineStr"/>
+      <c r="AI153" t="inlineStr"/>
+      <c r="AJ153" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL153" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>037/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Etimated SUM  Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>28 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="O154" t="n">
+        <v>10</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>100</v>
+      </c>
+      <c r="R154" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="T154" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U154" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V154" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W154" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X154" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y154" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z154" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA154" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 28/09/2026</t>
+        </is>
+      </c>
+      <c r="AB154" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC154" t="inlineStr"/>
+      <c r="AD154" t="inlineStr"/>
+      <c r="AE154" t="inlineStr"/>
+      <c r="AF154" t="inlineStr"/>
+      <c r="AG154" t="inlineStr"/>
+      <c r="AH154" t="inlineStr"/>
+      <c r="AI154" t="inlineStr"/>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL154" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>Indocafe Coffemix Renteng</t>
+        </is>
+      </c>
+      <c r="O155" t="n">
+        <v>5</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>100</v>
+      </c>
+      <c r="R155" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T155" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U155" t="n">
+        <v>146250</v>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr"/>
+      <c r="AD155" t="inlineStr"/>
+      <c r="AE155" t="inlineStr"/>
+      <c r="AF155" t="inlineStr"/>
+      <c r="AG155" t="inlineStr"/>
+      <c r="AH155" t="inlineStr"/>
+      <c r="AI155" t="inlineStr"/>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL155" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>Kopi Kapal Api 380 g</t>
+        </is>
+      </c>
+      <c r="O156" t="n">
+        <v>6</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>100</v>
+      </c>
+      <c r="R156" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T156" t="n">
+        <v>84500</v>
+      </c>
+      <c r="U156" t="n">
+        <v>456300</v>
+      </c>
+      <c r="V156" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W156" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X156" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y156" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z156" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA156" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB156" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr"/>
+      <c r="AD156" t="inlineStr"/>
+      <c r="AE156" t="inlineStr"/>
+      <c r="AF156" t="inlineStr"/>
+      <c r="AG156" t="inlineStr"/>
+      <c r="AH156" t="inlineStr"/>
+      <c r="AI156" t="inlineStr"/>
+      <c r="AJ156" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL156" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>Nescafe Classic renteng</t>
+        </is>
+      </c>
+      <c r="O157" t="n">
+        <v>5</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>100</v>
+      </c>
+      <c r="R157" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T157" t="n">
+        <v>26000</v>
+      </c>
+      <c r="U157" t="n">
+        <v>117000</v>
+      </c>
+      <c r="V157" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W157" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X157" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y157" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA157" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr"/>
+      <c r="AD157" t="inlineStr"/>
+      <c r="AE157" t="inlineStr"/>
+      <c r="AF157" t="inlineStr"/>
+      <c r="AG157" t="inlineStr"/>
+      <c r="AH157" t="inlineStr"/>
+      <c r="AI157" t="inlineStr"/>
+      <c r="AJ157" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL157" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>Pop Mie</t>
+        </is>
+      </c>
+      <c r="O158" t="n">
+        <v>72</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>100</v>
+      </c>
+      <c r="R158" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T158" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U158" t="n">
+        <v>631800</v>
+      </c>
+      <c r="V158" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W158" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X158" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y158" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z158" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB158" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr"/>
+      <c r="AD158" t="inlineStr"/>
+      <c r="AE158" t="inlineStr"/>
+      <c r="AF158" t="inlineStr"/>
+      <c r="AG158" t="inlineStr"/>
+      <c r="AH158" t="inlineStr"/>
+      <c r="AI158" t="inlineStr"/>
+      <c r="AJ158" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL158" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>Chitato 68 g</t>
+        </is>
+      </c>
+      <c r="O159" t="n">
+        <v>10</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>100</v>
+      </c>
+      <c r="R159" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T159" t="n">
+        <v>19500</v>
+      </c>
+      <c r="U159" t="n">
+        <v>175500</v>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr"/>
+      <c r="AD159" t="inlineStr"/>
+      <c r="AE159" t="inlineStr"/>
+      <c r="AF159" t="inlineStr"/>
+      <c r="AG159" t="inlineStr"/>
+      <c r="AH159" t="inlineStr"/>
+      <c r="AI159" t="inlineStr"/>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL159" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>Pocari Sweat</t>
+        </is>
+      </c>
+      <c r="O160" t="n">
+        <v>72</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>100</v>
+      </c>
+      <c r="R160" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T160" t="n">
+        <v>13000</v>
+      </c>
+      <c r="U160" t="n">
+        <v>842400</v>
+      </c>
+      <c r="V160" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W160" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X160" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y160" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z160" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA160" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB160" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr"/>
+      <c r="AD160" t="inlineStr"/>
+      <c r="AE160" t="inlineStr"/>
+      <c r="AF160" t="inlineStr"/>
+      <c r="AG160" t="inlineStr"/>
+      <c r="AH160" t="inlineStr"/>
+      <c r="AI160" t="inlineStr"/>
+      <c r="AJ160" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL160" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N161" t="inlineStr">
+        <is>
+          <t>Teh Kotak</t>
+        </is>
+      </c>
+      <c r="O161" t="n">
+        <v>72</v>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q161" t="n">
+        <v>100</v>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T161" t="n">
+        <v>9750</v>
+      </c>
+      <c r="U161" t="n">
+        <v>631800</v>
+      </c>
+      <c r="V161" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W161" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X161" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y161" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z161" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA161" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB161" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr"/>
+      <c r="AD161" t="inlineStr"/>
+      <c r="AE161" t="inlineStr"/>
+      <c r="AF161" t="inlineStr"/>
+      <c r="AG161" t="inlineStr"/>
+      <c r="AH161" t="inlineStr"/>
+      <c r="AI161" t="inlineStr"/>
+      <c r="AJ161" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL161" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>Susu Beruang</t>
+        </is>
+      </c>
+      <c r="O162" t="n">
+        <v>72</v>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q162" t="n">
+        <v>100</v>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T162" t="n">
+        <v>19500</v>
+      </c>
+      <c r="U162" t="n">
+        <v>1263600</v>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr"/>
+      <c r="AD162" t="inlineStr"/>
+      <c r="AE162" t="inlineStr"/>
+      <c r="AF162" t="inlineStr"/>
+      <c r="AG162" t="inlineStr"/>
+      <c r="AH162" t="inlineStr"/>
+      <c r="AI162" t="inlineStr"/>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL162" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N163" t="inlineStr">
+        <is>
+          <t>Coffe Nescafe Kaleng 220 ml</t>
+        </is>
+      </c>
+      <c r="O163" t="n">
+        <v>48</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>100</v>
+      </c>
+      <c r="R163" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T163" t="n">
+        <v>15600</v>
+      </c>
+      <c r="U163" t="n">
+        <v>673920</v>
+      </c>
+      <c r="V163" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W163" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X163" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y163" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA163" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr"/>
+      <c r="AD163" t="inlineStr"/>
+      <c r="AE163" t="inlineStr"/>
+      <c r="AF163" t="inlineStr"/>
+      <c r="AG163" t="inlineStr"/>
+      <c r="AH163" t="inlineStr"/>
+      <c r="AI163" t="inlineStr"/>
+      <c r="AJ163" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL163" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N164" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Coklat</t>
+        </is>
+      </c>
+      <c r="O164" t="n">
+        <v>10</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>100</v>
+      </c>
+      <c r="R164" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T164" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U164" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V164" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W164" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X164" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y164" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z164" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB164" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr"/>
+      <c r="AD164" t="inlineStr"/>
+      <c r="AE164" t="inlineStr"/>
+      <c r="AF164" t="inlineStr"/>
+      <c r="AG164" t="inlineStr"/>
+      <c r="AH164" t="inlineStr"/>
+      <c r="AI164" t="inlineStr"/>
+      <c r="AJ164" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL164" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr">
+        <is>
+          <t>Roti Sari Roti Keju</t>
+        </is>
+      </c>
+      <c r="O165" t="n">
+        <v>10</v>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q165" t="n">
+        <v>100</v>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T165" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U165" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V165" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W165" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X165" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y165" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA165" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC165" t="inlineStr"/>
+      <c r="AD165" t="inlineStr"/>
+      <c r="AE165" t="inlineStr"/>
+      <c r="AF165" t="inlineStr"/>
+      <c r="AG165" t="inlineStr"/>
+      <c r="AH165" t="inlineStr"/>
+      <c r="AI165" t="inlineStr"/>
+      <c r="AJ165" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>034/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>Etimated SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>14 Sep 2026</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>ESTIMATED SUM</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr">
+        <is>
+          <t>Roti Tawar Sari Roti</t>
+        </is>
+      </c>
+      <c r="O166" t="n">
+        <v>10</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>Ea</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>100</v>
+      </c>
+      <c r="R166" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="T166" t="n">
+        <v>32500</v>
+      </c>
+      <c r="U166" t="n">
+        <v>292500</v>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>Etimated  SUM Kebutuhan Additional Logistik Periode September 2026 tgl 14/09/2026</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>2026-10-05 09:43:58</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr"/>
+      <c r="AD166" t="inlineStr"/>
+      <c r="AE166" t="inlineStr"/>
+      <c r="AF166" t="inlineStr"/>
+      <c r="AG166" t="inlineStr"/>
+      <c r="AH166" t="inlineStr"/>
+      <c r="AI166" t="inlineStr"/>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL166" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
     </row>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL166"/>
+  <dimension ref="A1:AL187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -734,7 +734,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr"/>
@@ -1010,7 +1010,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr"/>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr"/>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr"/>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr"/>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr"/>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr"/>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr"/>
@@ -1980,7 +1980,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr"/>
@@ -2120,7 +2120,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr"/>
@@ -2534,7 +2534,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr"/>
@@ -2674,7 +2674,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr"/>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC17" t="inlineStr"/>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr"/>
@@ -3094,7 +3094,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr"/>
@@ -3234,7 +3234,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr"/>
@@ -3376,7 +3376,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC21" t="inlineStr"/>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr"/>
@@ -3660,7 +3660,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC23" t="inlineStr"/>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr"/>
@@ -3940,7 +3940,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC25" t="inlineStr"/>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr"/>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr"/>
@@ -4356,7 +4356,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr"/>
@@ -4494,7 +4494,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr"/>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr"/>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC31" t="inlineStr"/>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC32" t="inlineStr"/>
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr"/>
@@ -5184,7 +5184,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr"/>
@@ -5322,7 +5322,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr"/>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr"/>
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr"/>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr"/>
@@ -5874,7 +5874,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr"/>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr"/>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr"/>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr"/>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr"/>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr"/>
@@ -6702,7 +6702,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr"/>
@@ -6840,7 +6840,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr"/>
@@ -6982,7 +6982,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr"/>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr"/>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr"/>
@@ -7408,7 +7408,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr"/>
@@ -7550,7 +7550,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr"/>
@@ -7692,7 +7692,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr"/>
@@ -7834,7 +7834,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr"/>
@@ -7976,7 +7976,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr"/>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr"/>
@@ -8260,7 +8260,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr"/>
@@ -8402,7 +8402,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC57" t="inlineStr"/>
@@ -8544,7 +8544,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr"/>
@@ -8686,7 +8686,7 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr"/>
@@ -8828,7 +8828,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr"/>
@@ -8970,7 +8970,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC61" t="inlineStr"/>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr"/>
@@ -9264,7 +9264,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr"/>
@@ -9414,7 +9414,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC64" t="inlineStr"/>
@@ -9564,7 +9564,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr"/>
@@ -9714,7 +9714,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC66" t="inlineStr"/>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC67" t="inlineStr"/>
@@ -10014,7 +10014,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC68" t="inlineStr"/>
@@ -10164,7 +10164,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC69" t="inlineStr"/>
@@ -10314,7 +10314,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC70" t="inlineStr"/>
@@ -10464,7 +10464,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC71" t="inlineStr"/>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC72" t="inlineStr"/>
@@ -10764,7 +10764,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr"/>
@@ -10914,7 +10914,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC74" t="inlineStr"/>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC75" t="inlineStr"/>
@@ -11218,7 +11218,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC76" t="inlineStr"/>
@@ -11368,7 +11368,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC77" t="inlineStr"/>
@@ -11518,7 +11518,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC78" t="inlineStr"/>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC79" t="inlineStr"/>
@@ -11818,7 +11818,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC80" t="inlineStr"/>
@@ -11968,7 +11968,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC81" t="inlineStr"/>
@@ -12118,7 +12118,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC82" t="inlineStr"/>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr"/>
@@ -12418,7 +12418,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC84" t="inlineStr"/>
@@ -12568,7 +12568,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC85" t="inlineStr"/>
@@ -12718,7 +12718,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC86" t="inlineStr"/>
@@ -12868,7 +12868,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr"/>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC88" t="inlineStr"/>
@@ -13172,7 +13172,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr"/>
@@ -13322,7 +13322,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC90" t="inlineStr"/>
@@ -13472,7 +13472,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC91" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC92" t="inlineStr"/>
@@ -13772,7 +13772,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC93" t="inlineStr"/>
@@ -13922,7 +13922,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC94" t="inlineStr"/>
@@ -14072,7 +14072,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC95" t="inlineStr"/>
@@ -14222,7 +14222,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC96" t="inlineStr"/>
@@ -14372,7 +14372,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC97" t="inlineStr"/>
@@ -14522,7 +14522,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC98" t="inlineStr"/>
@@ -14672,7 +14672,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC100" t="inlineStr"/>
@@ -14974,7 +14974,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC101" t="inlineStr"/>
@@ -15128,7 +15128,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC102" t="inlineStr"/>
@@ -15282,7 +15282,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC103" t="inlineStr"/>
@@ -15436,7 +15436,7 @@
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC104" t="inlineStr"/>
@@ -15591,7 +15591,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC105" t="inlineStr"/>
@@ -15745,7 +15745,7 @@
       </c>
       <c r="AB106" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr"/>
@@ -15899,7 +15899,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC107" t="inlineStr"/>
@@ -16053,7 +16053,7 @@
       </c>
       <c r="AB108" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC108" t="inlineStr"/>
@@ -16207,7 +16207,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC109" t="inlineStr"/>
@@ -16357,7 +16357,7 @@
       </c>
       <c r="AB110" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC110" t="inlineStr"/>
@@ -16507,7 +16507,7 @@
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC111" t="inlineStr"/>
@@ -16657,7 +16657,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr"/>
@@ -16807,7 +16807,7 @@
       </c>
       <c r="AB113" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr"/>
@@ -16957,7 +16957,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr"/>
@@ -17107,7 +17107,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC115" t="inlineStr"/>
@@ -17257,7 +17257,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr"/>
@@ -17407,7 +17407,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr"/>
@@ -17557,7 +17557,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC118" t="inlineStr"/>
@@ -17707,7 +17707,7 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC119" t="inlineStr"/>
@@ -17857,7 +17857,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC120" t="inlineStr"/>
@@ -18007,7 +18007,7 @@
       </c>
       <c r="AB121" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC121" t="inlineStr"/>
@@ -18157,7 +18157,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC122" t="inlineStr"/>
@@ -18307,7 +18307,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC123" t="inlineStr"/>
@@ -18457,7 +18457,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC124" t="inlineStr"/>
@@ -18607,7 +18607,7 @@
       </c>
       <c r="AB125" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr"/>
@@ -18757,7 +18757,7 @@
       </c>
       <c r="AB126" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr"/>
@@ -18907,7 +18907,7 @@
       </c>
       <c r="AB127" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr"/>
@@ -19057,7 +19057,7 @@
       </c>
       <c r="AB128" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr"/>
@@ -19207,7 +19207,7 @@
       </c>
       <c r="AB129" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr"/>
@@ -19357,7 +19357,7 @@
       </c>
       <c r="AB130" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr"/>
@@ -19507,7 +19507,7 @@
       </c>
       <c r="AB131" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC131" t="inlineStr"/>
@@ -19657,7 +19657,7 @@
       </c>
       <c r="AB132" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC132" t="inlineStr"/>
@@ -19807,7 +19807,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC133" t="inlineStr"/>
@@ -19957,7 +19957,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC134" t="inlineStr"/>
@@ -20107,7 +20107,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC135" t="inlineStr"/>
@@ -20257,7 +20257,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr"/>
@@ -20407,7 +20407,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr"/>
@@ -20557,7 +20557,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC138" t="inlineStr"/>
@@ -20711,7 +20711,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr"/>
@@ -20865,7 +20865,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC140" t="inlineStr"/>
@@ -21019,7 +21019,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC141" t="inlineStr"/>
@@ -21173,7 +21173,7 @@
       </c>
       <c r="AB142" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC142" t="inlineStr"/>
@@ -21327,7 +21327,7 @@
       </c>
       <c r="AB143" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC143" t="inlineStr"/>
@@ -21481,7 +21481,7 @@
       </c>
       <c r="AB144" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC144" t="inlineStr"/>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="AB145" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr"/>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="AB146" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC146" t="inlineStr"/>
@@ -21943,7 +21943,7 @@
       </c>
       <c r="AB147" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr"/>
@@ -22097,7 +22097,7 @@
       </c>
       <c r="AB148" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr"/>
@@ -22251,7 +22251,7 @@
       </c>
       <c r="AB149" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr"/>
@@ -22405,7 +22405,7 @@
       </c>
       <c r="AB150" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC150" t="inlineStr"/>
@@ -22559,7 +22559,7 @@
       </c>
       <c r="AB151" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC151" t="inlineStr"/>
@@ -22713,7 +22713,7 @@
       </c>
       <c r="AB152" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC152" t="inlineStr"/>
@@ -22867,7 +22867,7 @@
       </c>
       <c r="AB153" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr"/>
@@ -23021,7 +23021,7 @@
       </c>
       <c r="AB154" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr"/>
@@ -23048,10 +23048,8 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A155" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B155" t="inlineStr">
         <is>
@@ -23177,7 +23175,7 @@
       </c>
       <c r="AB155" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr"/>
@@ -23204,10 +23202,8 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A156" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B156" t="inlineStr">
         <is>
@@ -23333,7 +23329,7 @@
       </c>
       <c r="AB156" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr"/>
@@ -23360,10 +23356,8 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A157" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B157" t="inlineStr">
         <is>
@@ -23489,7 +23483,7 @@
       </c>
       <c r="AB157" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC157" t="inlineStr"/>
@@ -23516,10 +23510,8 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A158" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B158" t="inlineStr">
         <is>
@@ -23645,7 +23637,7 @@
       </c>
       <c r="AB158" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC158" t="inlineStr"/>
@@ -23672,10 +23664,8 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A159" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B159" t="inlineStr">
         <is>
@@ -23801,7 +23791,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC159" t="inlineStr"/>
@@ -23828,10 +23818,8 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A160" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B160" t="inlineStr">
         <is>
@@ -23957,7 +23945,7 @@
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC160" t="inlineStr"/>
@@ -23984,10 +23972,8 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A161" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B161" t="inlineStr">
         <is>
@@ -24113,7 +24099,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC161" t="inlineStr"/>
@@ -24140,10 +24126,8 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A162" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B162" t="inlineStr">
         <is>
@@ -24269,7 +24253,7 @@
       </c>
       <c r="AB162" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC162" t="inlineStr"/>
@@ -24296,10 +24280,8 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A163" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B163" t="inlineStr">
         <is>
@@ -24425,7 +24407,7 @@
       </c>
       <c r="AB163" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC163" t="inlineStr"/>
@@ -24452,10 +24434,8 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A164" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B164" t="inlineStr">
         <is>
@@ -24581,7 +24561,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC164" t="inlineStr"/>
@@ -24608,10 +24588,8 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A165" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B165" t="inlineStr">
         <is>
@@ -24737,7 +24715,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC165" t="inlineStr"/>
@@ -24764,10 +24742,8 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>7201250141</t>
-        </is>
+      <c r="A166" t="n">
+        <v>7201250141</v>
       </c>
       <c r="B166" t="inlineStr">
         <is>
@@ -24893,7 +24869,7 @@
       </c>
       <c r="AB166" t="inlineStr">
         <is>
-          <t>2026-10-05 09:43:58</t>
+          <t>2026-10-06 13:23:28</t>
         </is>
       </c>
       <c r="AC166" t="inlineStr"/>
@@ -24919,6 +24895,3251 @@
         </is>
       </c>
     </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, main course</t>
+        </is>
+      </c>
+      <c r="O167" t="n">
+        <v>3195</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>100</v>
+      </c>
+      <c r="R167" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T167" t="n">
+        <v>65000</v>
+      </c>
+      <c r="U167" t="n">
+        <v>207675000</v>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X167" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">DDITIONAL CAMP SERVICES, Operational Consumption </t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC167" t="inlineStr"/>
+      <c r="AD167" t="inlineStr"/>
+      <c r="AE167" t="inlineStr"/>
+      <c r="AF167" t="inlineStr"/>
+      <c r="AG167" t="inlineStr"/>
+      <c r="AH167" t="inlineStr"/>
+      <c r="AI167" t="inlineStr"/>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL167" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>038/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 ADDITIONAL CAMP SERVICES, Operational Consumption dan Operational side consumption</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr">
+        <is>
+          <t>Food &amp; beverage, snack coffee/ tea &amp; desert</t>
+        </is>
+      </c>
+      <c r="O168" t="n">
+        <v>1486.5</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>100</v>
+      </c>
+      <c r="R168" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T168" t="n">
+        <v>33000</v>
+      </c>
+      <c r="U168" t="n">
+        <v>49054500</v>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X168" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>ADDITIONAL CAMP SERVICES, Operational side consumption</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC168" t="inlineStr"/>
+      <c r="AD168" t="inlineStr"/>
+      <c r="AE168" t="inlineStr"/>
+      <c r="AF168" t="inlineStr"/>
+      <c r="AG168" t="inlineStr"/>
+      <c r="AH168" t="inlineStr"/>
+      <c r="AI168" t="inlineStr"/>
+      <c r="AJ168" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL168" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>040/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr">
+        <is>
+          <t>Personnel GS in-charge di lokasi pemboran/ wellservices/ workover, personnel in charge</t>
+        </is>
+      </c>
+      <c r="O169" t="n">
+        <v>30</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>100</v>
+      </c>
+      <c r="R169" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T169" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U169" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>Personnel GS - Koordinator Lapangan atas nama Nur Afiata Periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr"/>
+      <c r="AD169" t="inlineStr"/>
+      <c r="AE169" t="inlineStr"/>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="inlineStr"/>
+      <c r="AH169" t="inlineStr"/>
+      <c r="AI169" t="inlineStr"/>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL169" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="O170" t="n">
+        <v>30</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>100</v>
+      </c>
+      <c r="R170" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T170" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U170" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X170" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = HSE Officer ( Gusti Ngurah Dwipayana) </t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC170" t="inlineStr"/>
+      <c r="AD170" t="inlineStr"/>
+      <c r="AE170" t="inlineStr"/>
+      <c r="AF170" t="inlineStr"/>
+      <c r="AG170" t="inlineStr"/>
+      <c r="AH170" t="inlineStr"/>
+      <c r="AI170" t="inlineStr"/>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="O171" t="n">
+        <v>30</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>100</v>
+      </c>
+      <c r="R171" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T171" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U171" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X171" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Meliita Bella)  </t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC171" t="inlineStr"/>
+      <c r="AD171" t="inlineStr"/>
+      <c r="AE171" t="inlineStr"/>
+      <c r="AF171" t="inlineStr"/>
+      <c r="AG171" t="inlineStr"/>
+      <c r="AH171" t="inlineStr"/>
+      <c r="AI171" t="inlineStr"/>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>041/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr">
+        <is>
+          <t>Welder (GTAW)</t>
+        </is>
+      </c>
+      <c r="O172" t="n">
+        <v>30</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>100</v>
+      </c>
+      <c r="R172" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T172" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U172" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Support Kegiatan Well Services di Senoro personel  Welder = Paramedic  ( Widiya Satuo)  </t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr"/>
+      <c r="AD172" t="inlineStr"/>
+      <c r="AE172" t="inlineStr"/>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="inlineStr"/>
+      <c r="AH172" t="inlineStr"/>
+      <c r="AI172" t="inlineStr"/>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="O173" t="n">
+        <v>30</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>100</v>
+      </c>
+      <c r="R173" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T173" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U173" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X173" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator Crane Shift Siang atas Nama Wanhar Renaldi </t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC173" t="inlineStr"/>
+      <c r="AD173" t="inlineStr"/>
+      <c r="AE173" t="inlineStr"/>
+      <c r="AF173" t="inlineStr"/>
+      <c r="AG173" t="inlineStr"/>
+      <c r="AH173" t="inlineStr"/>
+      <c r="AI173" t="inlineStr"/>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr">
+        <is>
+          <t>Operator Crane</t>
+        </is>
+      </c>
+      <c r="O174" t="n">
+        <v>30</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>100</v>
+      </c>
+      <c r="R174" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T174" t="n">
+        <v>750000</v>
+      </c>
+      <c r="U174" t="n">
+        <v>22500000</v>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X174" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z174" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Operator Crane Shift Malam atas Nama Ilsan Adjedar </t>
+        </is>
+      </c>
+      <c r="AB174" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr"/>
+      <c r="AD174" t="inlineStr"/>
+      <c r="AE174" t="inlineStr"/>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="inlineStr"/>
+      <c r="AH174" t="inlineStr"/>
+      <c r="AI174" t="inlineStr"/>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL174" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N175" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="O175" t="n">
+        <v>30</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>100</v>
+      </c>
+      <c r="R175" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T175" t="n">
+        <v>650000</v>
+      </c>
+      <c r="U175" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X175" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>RIgger Crane Shift Siang atas Nama Tison</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC175" t="inlineStr"/>
+      <c r="AD175" t="inlineStr"/>
+      <c r="AE175" t="inlineStr"/>
+      <c r="AF175" t="inlineStr"/>
+      <c r="AG175" t="inlineStr"/>
+      <c r="AH175" t="inlineStr"/>
+      <c r="AI175" t="inlineStr"/>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL175" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M176" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N176" t="inlineStr">
+        <is>
+          <t>Rigger</t>
+        </is>
+      </c>
+      <c r="O176" t="n">
+        <v>30</v>
+      </c>
+      <c r="P176" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q176" t="n">
+        <v>100</v>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T176" t="n">
+        <v>650000</v>
+      </c>
+      <c r="U176" t="n">
+        <v>19500000</v>
+      </c>
+      <c r="V176" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W176" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X176" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y176" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z176" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>Rigger Crane Shift Malam atas Nama Agus Dg Mangata</t>
+        </is>
+      </c>
+      <c r="AB176" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC176" t="inlineStr"/>
+      <c r="AD176" t="inlineStr"/>
+      <c r="AE176" t="inlineStr"/>
+      <c r="AF176" t="inlineStr"/>
+      <c r="AG176" t="inlineStr"/>
+      <c r="AH176" t="inlineStr"/>
+      <c r="AI176" t="inlineStr"/>
+      <c r="AJ176" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL176" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M177" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N177" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="O177" t="n">
+        <v>30</v>
+      </c>
+      <c r="P177" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q177" t="n">
+        <v>100</v>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T177" t="n">
+        <v>600000</v>
+      </c>
+      <c r="U177" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="V177" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W177" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X177" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y177" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z177" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Sugeng</t>
+        </is>
+      </c>
+      <c r="AB177" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC177" t="inlineStr"/>
+      <c r="AD177" t="inlineStr"/>
+      <c r="AE177" t="inlineStr"/>
+      <c r="AF177" t="inlineStr"/>
+      <c r="AG177" t="inlineStr"/>
+      <c r="AH177" t="inlineStr"/>
+      <c r="AI177" t="inlineStr"/>
+      <c r="AJ177" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL177" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>042/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M178" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N178" t="inlineStr">
+        <is>
+          <t>Mechanic/ Electrician</t>
+        </is>
+      </c>
+      <c r="O178" t="n">
+        <v>30</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>100</v>
+      </c>
+      <c r="R178" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T178" t="n">
+        <v>600000</v>
+      </c>
+      <c r="U178" t="n">
+        <v>18000000</v>
+      </c>
+      <c r="V178" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W178" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X178" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y178" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z178" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>Operator Mesin Genset dan Ligting Tower Shift Siang atas nama Ahmad Dhani</t>
+        </is>
+      </c>
+      <c r="AB178" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC178" t="inlineStr"/>
+      <c r="AD178" t="inlineStr"/>
+      <c r="AE178" t="inlineStr"/>
+      <c r="AF178" t="inlineStr"/>
+      <c r="AG178" t="inlineStr"/>
+      <c r="AH178" t="inlineStr"/>
+      <c r="AI178" t="inlineStr"/>
+      <c r="AJ178" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL178" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>043/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Personel Oncall Untuk Support Kegiatan Well Services di Senoro Periode Bulan September 2026)</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N179" t="inlineStr">
+        <is>
+          <t>Operator Heavy Equipment (Vacuum Truck)</t>
+        </is>
+      </c>
+      <c r="O179" t="n">
+        <v>30</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>100</v>
+      </c>
+      <c r="R179" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T179" t="n">
+        <v>500000</v>
+      </c>
+      <c r="U179" t="n">
+        <v>15000000</v>
+      </c>
+      <c r="V179" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W179" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X179" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y179" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z179" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>Driver Vacuum Truck atas nama Wijayanto Sucipto</t>
+        </is>
+      </c>
+      <c r="AB179" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC179" t="inlineStr"/>
+      <c r="AD179" t="inlineStr"/>
+      <c r="AE179" t="inlineStr"/>
+      <c r="AF179" t="inlineStr"/>
+      <c r="AG179" t="inlineStr"/>
+      <c r="AH179" t="inlineStr"/>
+      <c r="AI179" t="inlineStr"/>
+      <c r="AJ179" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL179" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>044/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>11 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026, PERSONNEL ON-CALL
+Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>PERSONEL ON CALL</t>
+        </is>
+      </c>
+      <c r="N180" t="inlineStr">
+        <is>
+          <t>Helper Local (non Skilled)</t>
+        </is>
+      </c>
+      <c r="O180" t="n">
+        <v>48</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>man-days</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>100</v>
+      </c>
+      <c r="R180" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="T180" t="n">
+        <v>250000</v>
+      </c>
+      <c r="U180" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="V180" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W180" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X180" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y180" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z180" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA180" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> PERSONNEL ON-CALL Helper Local (non Skilled) Tenaga Flagman Periode tgl 4 sd 11 September 2026</t>
+        </is>
+      </c>
+      <c r="AB180" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC180" t="inlineStr"/>
+      <c r="AD180" t="inlineStr"/>
+      <c r="AE180" t="inlineStr"/>
+      <c r="AF180" t="inlineStr"/>
+      <c r="AG180" t="inlineStr"/>
+      <c r="AH180" t="inlineStr"/>
+      <c r="AI180" t="inlineStr"/>
+      <c r="AJ180" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL180" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M181" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N181" t="inlineStr">
+        <is>
+          <t>crane min 70 ton, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="O181" t="n">
+        <v>30</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>100</v>
+      </c>
+      <c r="R181" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T181" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="U181" t="n">
+        <v>255000000</v>
+      </c>
+      <c r="V181" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W181" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X181" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y181" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z181" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>Crane Sany 100 ton menggantikan Crane Tadano 70 ton yang rusak Operasi periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC181" t="inlineStr"/>
+      <c r="AD181" t="inlineStr"/>
+      <c r="AE181" t="inlineStr"/>
+      <c r="AF181" t="inlineStr"/>
+      <c r="AG181" t="inlineStr"/>
+      <c r="AH181" t="inlineStr"/>
+      <c r="AI181" t="inlineStr"/>
+      <c r="AJ181" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL181" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="n">
+        <v>7201250141</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>045/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Heavy Transportation &amp; Equipment Rental  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>HEAVY TRANSPORTATION &amp; EQUIPMENT RENTAL</t>
+        </is>
+      </c>
+      <c r="N182" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr c/w vacuum pump &amp; acessories, call out, (hanya unit)</t>
+        </is>
+      </c>
+      <c r="O182" t="n">
+        <v>30</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>100</v>
+      </c>
+      <c r="R182" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T182" t="n">
+        <v>2750000</v>
+      </c>
+      <c r="U182" t="n">
+        <v>82500000</v>
+      </c>
+      <c r="V182" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W182" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X182" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y182" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z182" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>Vacuum Truck , Call out, Cap  5000 ltr  Operasi periode 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="AB182" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr"/>
+      <c r="AD182" t="inlineStr"/>
+      <c r="AE182" t="inlineStr"/>
+      <c r="AF182" t="inlineStr"/>
+      <c r="AG182" t="inlineStr"/>
+      <c r="AH182" t="inlineStr"/>
+      <c r="AI182" t="inlineStr"/>
+      <c r="AJ182" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL182" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M183" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N183" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O183" t="n">
+        <v>30</v>
+      </c>
+      <c r="P183" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q183" t="n">
+        <v>100</v>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T183" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U183" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="V183" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W183" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X183" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y183" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z183" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA183" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1259 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="AB183" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC183" t="inlineStr"/>
+      <c r="AD183" t="inlineStr"/>
+      <c r="AE183" t="inlineStr"/>
+      <c r="AF183" t="inlineStr"/>
+      <c r="AG183" t="inlineStr"/>
+      <c r="AH183" t="inlineStr"/>
+      <c r="AI183" t="inlineStr"/>
+      <c r="AJ183" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL183" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N184" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O184" t="n">
+        <v>30</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>100</v>
+      </c>
+      <c r="R184" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T184" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U184" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="V184" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W184" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X184" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y184" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z184" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA184" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1257 CL  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="AB184" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC184" t="inlineStr"/>
+      <c r="AD184" t="inlineStr"/>
+      <c r="AE184" t="inlineStr"/>
+      <c r="AF184" t="inlineStr"/>
+      <c r="AG184" t="inlineStr"/>
+      <c r="AH184" t="inlineStr"/>
+      <c r="AI184" t="inlineStr"/>
+      <c r="AJ184" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL184" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M185" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N185" t="inlineStr">
+        <is>
+          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O185" t="n">
+        <v>4</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>100</v>
+      </c>
+      <c r="R185" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T185" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U185" t="n">
+        <v>6400000</v>
+      </c>
+      <c r="V185" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W185" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X185" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y185" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z185" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA185" t="inlineStr">
+        <is>
+          <t>Kendaraan Inova DN 1258 CL  Support Well Services Periode tanggal 27 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="AB185" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC185" t="inlineStr"/>
+      <c r="AD185" t="inlineStr"/>
+      <c r="AE185" t="inlineStr"/>
+      <c r="AF185" t="inlineStr"/>
+      <c r="AG185" t="inlineStr"/>
+      <c r="AH185" t="inlineStr"/>
+      <c r="AI185" t="inlineStr"/>
+      <c r="AJ185" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL185" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M186" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N186" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O186" t="n">
+        <v>30</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>100</v>
+      </c>
+      <c r="R186" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T186" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U186" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="V186" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W186" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X186" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y186" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z186" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA186" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1916 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="AB186" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC186" t="inlineStr"/>
+      <c r="AD186" t="inlineStr"/>
+      <c r="AE186" t="inlineStr"/>
+      <c r="AF186" t="inlineStr"/>
+      <c r="AG186" t="inlineStr"/>
+      <c r="AH186" t="inlineStr"/>
+      <c r="AI186" t="inlineStr"/>
+      <c r="AJ186" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL186" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>7201250141</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>S25048TPD</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>046/BSS-JOB/WS/IX/2026</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>30 Sep 2026</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>JOB Pertamina - Medco E&amp;P Tomori Sulawesi</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Bidakara Office Tower I 4Th Floor, Jl. Gatot Subroto Kav. 71 - 73, Jakarta 12870, Indonesia</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>4500011739</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Supporting equipment kegiatan Wellservices 2026 (Penyediaan Car &amp; Tansportation  Periode September 2026)</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>03 Aug 2026</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>IDR</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr">
+        <is>
+          <t>CAR &amp; TANSPORTATION</t>
+        </is>
+      </c>
+      <c r="N187" t="inlineStr">
+        <is>
+          <t>Double cabin 4x4, diesel engine + driver + BBM,</t>
+        </is>
+      </c>
+      <c r="O187" t="n">
+        <v>30</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>Day</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>100</v>
+      </c>
+      <c r="R187" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="T187" t="n">
+        <v>1600000</v>
+      </c>
+      <c r="U187" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="V187" t="inlineStr">
+        <is>
+          <t>BANK RAKYAT INDONESIA (PERSERO) Tbk.</t>
+        </is>
+      </c>
+      <c r="W187" t="inlineStr">
+        <is>
+          <t>Cabang Luwuk</t>
+        </is>
+      </c>
+      <c r="X187" t="inlineStr">
+        <is>
+          <t>0167 0167 8888 303</t>
+        </is>
+      </c>
+      <c r="Y187" t="inlineStr">
+        <is>
+          <t>PT. BANGGAI SENTRAL SULAWESI</t>
+        </is>
+      </c>
+      <c r="Z187" t="inlineStr">
+        <is>
+          <t>Accounts Payable - Finance Department</t>
+        </is>
+      </c>
+      <c r="AA187" t="inlineStr">
+        <is>
+          <t>Kendaraan Double Cabin Hilux DN 1917 CH  Support Well Services Periode tanggal 01 sd 30 September 2026</t>
+        </is>
+      </c>
+      <c r="AB187" t="inlineStr">
+        <is>
+          <t>2026-10-06 13:23:28</t>
+        </is>
+      </c>
+      <c r="AC187" t="inlineStr"/>
+      <c r="AD187" t="inlineStr"/>
+      <c r="AE187" t="inlineStr"/>
+      <c r="AF187" t="inlineStr"/>
+      <c r="AG187" t="inlineStr"/>
+      <c r="AH187" t="inlineStr"/>
+      <c r="AI187" t="inlineStr"/>
+      <c r="AJ187" t="inlineStr">
+        <is>
+          <t>Pekerjaan Jasa</t>
+        </is>
+      </c>
+      <c r="AK187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AL187" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/database_penyimpanan_aman/database_transaksi_rincian.xlsx
+++ b/database_penyimpanan_aman/database_transaksi_rincian.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL187"/>
+  <dimension ref="A1:AL197"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -628,11 +628,13 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>008/BSS-JOB/WS/VII/2026</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="n">
-        <v>46212</v>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -646,22 +648,18 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2 tahun (17 Desember 2025 – 03 Desember 2027)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Support Team JOB Survey Lokasi di Senoro</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -671,36 +669,40 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>CAR &amp; TANSPORTATION</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Station wagon 7 seater diesel engine + driver + BBM,</t>
+          <t>Aqua 600 ml</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>1800</v>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Day</t>
+          <t>Ea</t>
         </is>
       </c>
       <c r="Q2" t="n">
         <v>100</v>
       </c>
-      <c r="R2" s="1" t="n">
-        <v>46209</v>
-      </c>
-      <c r="S2" s="1" t="n">
-        <v>46212</v>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="T2" t="n">
-        <v>1600000</v>
+        <v>7500</v>
       </c>
       <c r="U2" t="n">
-        <v>6400000</v>
+        <v>12150000</v>
       </c>
       <c r="V2" t="inlineStr">
         <is>
@@ -729,12 +731,12 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Kendaraan Operasional Inova DN 1257 CL Support Team JOB Survey Lokasi di Senoro tgl 6 sd 9 Juli 2026</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua 600 ml untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-10-06 13:23:28</t>
+          <t>2026-10-06 19:03:51</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -746,33 +748,39 @@
       <c r="AI2" t="inlineStr"/>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>Pekerjaan Jasa</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr"/>
+          <t>Pekerjaan Barang / Material</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
       <c r="AL2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>7203250036</v>
+        <v>7201250141</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Penyediaan Jasa Penyewaan Alat Berat Werehouse</t>
+          <t>Penyediaan General Services Untuk Mendukung Kegiaatan Pengemboran, Kerja Ulang Dan Perawatan Sumur di Blok Senoro - Toili, Sulawesi Tengah</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>S250009SCM</t>
+          <t>S25048TPD</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>010/BSS-JOB/WH/VII/2026</t>
-        </is>
-      </c>
-      <c r="E3" s="1" t="n">
-        <v>46234</v>
+          <t>028/BSS-JOB/WS/VIII/2026</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>31 Aug 2026</t>
+        </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -786,20 +794,18 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>03 Desember 2027</t>
-        </is>
-      </c>
-      <c r="I3" t="n">
-        <v>4500010848</v>
-      </c>
+          <t>2 tahun (17 Desember 2025 sd 03 Desember 2027)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Jasa Sewa 2 Unit Alat Berat Forklift 5 Ton</t>
+          <t>Penyediaan Estimated Sum Air Mineral Kemasan Untuk Support Pekerjaan Well Services di Senoro Periode Agustus 2026</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>2 Januari 2026</t>
+          <t>07 Aug 2026</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -809,16 +815,16 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>MONTHLY BASIS</t>
+          <t>ESTIMATED SUM</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>Daily Rate</t>
+          <t>Aqua Galon Segel</t>
         </is>
       </c>
       <c r="O3" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
@@ -828,17 +834,21 @@
       <c r="Q3" t="n">
         <v>100</v>
       </c>
-      <c r="R3" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="S3" s="1" t="n">
-        <v>46234</v>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
       </c>
       <c r="T3" t="n">
-        <v>1197000</v>
+        <v>53300</v>
       </c>
       <c r="U3" t="n">
-        <v>26334000</v>
+        <v>863460</v>
       </c>
       <c r="V3" t="inlineStr">
         <is>
@@ -867,12 +877,12 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>Untuk crew lokasi senoro</t>
+          <t>Penyediaan Estimated Sum Air Mineral Aqua Galon Segel untuk Support Pekerjaan Well Services di Senoro Periode Agustu